--- a/files/九龙-启德-The Henley I.xlsx
+++ b/files/九龙-启德-The Henley I.xlsx
@@ -2970,7 +2970,7 @@
       </c>
       <c r="G52" s="3" t="inlineStr">
         <is>
-          <t>2026-06-06</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="H52" s="5" t="n">
@@ -5040,7 +5040,7 @@
       </c>
       <c r="G97" s="3" t="inlineStr">
         <is>
-          <t>2026-06-06</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="H97" s="5" t="n">
@@ -5868,7 +5868,7 @@
       </c>
       <c r="G115" s="3" t="inlineStr">
         <is>
-          <t>2026-06-06</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="H115" s="5" t="n">
@@ -6604,7 +6604,7 @@
       </c>
       <c r="G131" s="3" t="inlineStr">
         <is>
-          <t>2026-01-18</t>
+          <t>2026-01-25</t>
         </is>
       </c>
       <c r="H131" s="5" t="n">
@@ -18371,7 +18371,7 @@
         </is>
       </c>
       <c r="E387" s="4" t="n">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="F387" s="3" t="inlineStr">
         <is>
@@ -18380,14 +18380,14 @@
       </c>
       <c r="G387" s="3" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="H387" s="5" t="n">
         <v>6227400</v>
       </c>
       <c r="I387" s="5" t="n">
-        <v>32100</v>
+        <v>31935</v>
       </c>
       <c r="J387" s="3" t="inlineStr">
         <is>
@@ -23269,7 +23269,7 @@
           <t>B | 550呎 (2房)
 $1,919万
 $34,896/呎
-(26年-06月)</t>
+(26年-07月)</t>
         </is>
       </c>
       <c r="D11" s="18" t="inlineStr">
@@ -23664,7 +23664,7 @@
           <t>B | 550呎 (2房)
 $1,892万
 $34,394/呎
-(26年-06月)</t>
+(26年-07月)</t>
         </is>
       </c>
       <c r="D16" s="18" t="inlineStr">
@@ -23822,7 +23822,7 @@
           <t>B | 550呎 (2房)
 $1,875万
 $34,094/呎
-(26年-06月)</t>
+(26年-07月)</t>
         </is>
       </c>
       <c r="D18" s="18" t="inlineStr">
@@ -26610,10 +26610,10 @@
       </c>
       <c r="I11" s="16" t="inlineStr">
         <is>
-          <t>H | 194呎 (开放式)
+          <t>H | 195呎 (开放式)
 $623万
-$32,100/呎
-(26年-06月)</t>
+$31,935/呎
+(26年-07月)</t>
         </is>
       </c>
     </row>

--- a/files/九龙-启德-The Henley I.xlsx
+++ b/files/九龙-启德-The Henley I.xlsx
@@ -8,11 +8,6 @@
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="销控汇总明细" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2座 销控表" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="低座A座 销控表" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="低座B座 销控表" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="低座C座 销控表" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="低座D座 销控表" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -24,7 +19,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="$#,##0"/>
   </numFmts>
-  <fonts count="14">
+  <fonts count="4">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -46,65 +41,8 @@
       <name val="Microsoft YaHei"/>
       <sz val="10"/>
     </font>
-    <font>
-      <name val="Microsoft YaHei"/>
-      <color rgb="007F7F7F"/>
-      <sz val="9"/>
-    </font>
-    <font>
-      <name val="Microsoft YaHei"/>
-      <b val="1"/>
-      <color rgb="007F7F7F"/>
-      <sz val="11"/>
-    </font>
-    <font>
-      <name val="Microsoft YaHei"/>
-      <b val="1"/>
-      <color rgb="00004D00"/>
-      <sz val="9"/>
-    </font>
-    <font>
-      <name val="Microsoft YaHei"/>
-      <b val="1"/>
-      <color rgb="00004D00"/>
-      <sz val="11"/>
-    </font>
-    <font>
-      <name val="Microsoft YaHei"/>
-      <color rgb="00002060"/>
-      <sz val="9"/>
-    </font>
-    <font>
-      <name val="Microsoft YaHei"/>
-      <b val="1"/>
-      <color rgb="00002060"/>
-      <sz val="11"/>
-    </font>
-    <font>
-      <name val="Microsoft YaHei"/>
-      <color rgb="00660000"/>
-      <sz val="9"/>
-    </font>
-    <font>
-      <name val="Microsoft YaHei"/>
-      <b val="1"/>
-      <color rgb="00660000"/>
-      <sz val="11"/>
-    </font>
-    <font>
-      <name val="Microsoft YaHei"/>
-      <b val="1"/>
-      <color rgb="00000000"/>
-      <sz val="9"/>
-    </font>
-    <font>
-      <name val="Microsoft YaHei"/>
-      <b val="1"/>
-      <color rgb="00000000"/>
-      <sz val="11"/>
-    </font>
   </fonts>
-  <fills count="9">
+  <fills count="3">
     <fill>
       <patternFill/>
     </fill>
@@ -115,42 +53,6 @@
       <patternFill patternType="solid">
         <fgColor rgb="00F2F2F2"/>
         <bgColor rgb="00F2F2F2"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00FFFFFF"/>
-        <bgColor rgb="00FFFFFF"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00A9F5A9"/>
-        <bgColor rgb="00A9F5A9"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00A9D0F5"/>
-        <bgColor rgb="00A9D0F5"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00F5A9A9"/>
-        <bgColor rgb="00F5A9A9"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00FFC000"/>
-        <bgColor rgb="00FFC000"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00E5E5E5"/>
-        <bgColor rgb="00E5E5E5"/>
       </patternFill>
     </fill>
   </fills>
@@ -180,7 +82,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="21">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -196,51 +98,6 @@
     </xf>
     <xf numFmtId="164" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -946,7 +803,7 @@
       </c>
       <c r="G8" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2021-06-01</t>
         </is>
       </c>
       <c r="H8" s="5" t="n">
@@ -1038,7 +895,7 @@
       </c>
       <c r="G10" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2021-07-13</t>
         </is>
       </c>
       <c r="H10" s="5" t="n">
@@ -1084,7 +941,7 @@
       </c>
       <c r="G11" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2021-06-01</t>
         </is>
       </c>
       <c r="H11" s="5" t="n">
@@ -1130,7 +987,7 @@
       </c>
       <c r="G12" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2021-06-02</t>
         </is>
       </c>
       <c r="H12" s="5" t="n">
@@ -1222,7 +1079,7 @@
       </c>
       <c r="G14" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2021-06-02</t>
         </is>
       </c>
       <c r="H14" s="5" t="n">
@@ -1452,7 +1309,7 @@
       </c>
       <c r="G19" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2021-07-28</t>
         </is>
       </c>
       <c r="H19" s="5" t="n">
@@ -1498,7 +1355,7 @@
       </c>
       <c r="G20" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2022-09-28</t>
         </is>
       </c>
       <c r="H20" s="5" t="n">
@@ -1636,7 +1493,7 @@
       </c>
       <c r="G23" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2021-06-01</t>
         </is>
       </c>
       <c r="H23" s="5" t="n">
@@ -1958,7 +1815,7 @@
       </c>
       <c r="G30" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2021-05-23</t>
         </is>
       </c>
       <c r="H30" s="5" t="n">
@@ -2050,7 +1907,7 @@
       </c>
       <c r="G32" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2021-06-07</t>
         </is>
       </c>
       <c r="H32" s="5" t="n">
@@ -2326,7 +2183,7 @@
       </c>
       <c r="G38" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2023-05-30</t>
         </is>
       </c>
       <c r="H38" s="5" t="n">
@@ -2372,7 +2229,7 @@
       </c>
       <c r="G39" s="3" t="inlineStr">
         <is>
-          <t>2025-09-21</t>
+          <t>2021-05-23</t>
         </is>
       </c>
       <c r="H39" s="5" t="n">
@@ -2464,7 +2321,7 @@
       </c>
       <c r="G41" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2021-06-15</t>
         </is>
       </c>
       <c r="H41" s="5" t="n">
@@ -2510,7 +2367,7 @@
       </c>
       <c r="G42" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2021-06-22</t>
         </is>
       </c>
       <c r="H42" s="5" t="n">
@@ -2786,7 +2643,7 @@
       </c>
       <c r="G48" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2021-05-27</t>
         </is>
       </c>
       <c r="H48" s="5" t="n">
@@ -2878,7 +2735,7 @@
       </c>
       <c r="G50" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2021-06-06</t>
         </is>
       </c>
       <c r="H50" s="5" t="n">
@@ -3016,7 +2873,7 @@
       </c>
       <c r="G53" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2021-06-07</t>
         </is>
       </c>
       <c r="H53" s="5" t="n">
@@ -3108,7 +2965,7 @@
       </c>
       <c r="G55" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2021-07-20</t>
         </is>
       </c>
       <c r="H55" s="5" t="n">
@@ -3154,7 +3011,7 @@
       </c>
       <c r="G56" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2023-04-19</t>
         </is>
       </c>
       <c r="H56" s="5" t="n">
@@ -3200,7 +3057,7 @@
       </c>
       <c r="G57" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2021-05-24</t>
         </is>
       </c>
       <c r="H57" s="5" t="n">
@@ -3292,7 +3149,7 @@
       </c>
       <c r="G59" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2021-06-15</t>
         </is>
       </c>
       <c r="H59" s="5" t="n">
@@ -3430,7 +3287,7 @@
       </c>
       <c r="G62" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2021-07-11</t>
         </is>
       </c>
       <c r="H62" s="5" t="n">
@@ -3522,7 +3379,7 @@
       </c>
       <c r="G64" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2021-07-08</t>
         </is>
       </c>
       <c r="H64" s="5" t="n">
@@ -3568,7 +3425,7 @@
       </c>
       <c r="G65" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2021-08-04</t>
         </is>
       </c>
       <c r="H65" s="5" t="n">
@@ -3614,7 +3471,7 @@
       </c>
       <c r="G66" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2021-05-30</t>
         </is>
       </c>
       <c r="H66" s="5" t="n">
@@ -3752,7 +3609,7 @@
       </c>
       <c r="G69" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2021-07-05</t>
         </is>
       </c>
       <c r="H69" s="5" t="n">
@@ -3936,7 +3793,7 @@
       </c>
       <c r="G73" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2021-07-05</t>
         </is>
       </c>
       <c r="H73" s="5" t="n">
@@ -4028,7 +3885,7 @@
       </c>
       <c r="G75" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2021-05-30</t>
         </is>
       </c>
       <c r="H75" s="5" t="n">
@@ -4120,7 +3977,7 @@
       </c>
       <c r="G77" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2021-07-29</t>
         </is>
       </c>
       <c r="H77" s="5" t="n">
@@ -4350,7 +4207,7 @@
       </c>
       <c r="G82" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2021-05-26</t>
         </is>
       </c>
       <c r="H82" s="5" t="n">
@@ -4396,7 +4253,7 @@
       </c>
       <c r="G83" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2021-06-09</t>
         </is>
       </c>
       <c r="H83" s="5" t="n">
@@ -4442,7 +4299,7 @@
       </c>
       <c r="G84" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2021-05-30</t>
         </is>
       </c>
       <c r="H84" s="5" t="n">
@@ -4580,7 +4437,7 @@
       </c>
       <c r="G87" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2021-06-06</t>
         </is>
       </c>
       <c r="H87" s="5" t="n">
@@ -4764,7 +4621,7 @@
       </c>
       <c r="G91" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2021-06-17</t>
         </is>
       </c>
       <c r="H91" s="5" t="n">
@@ -4810,7 +4667,7 @@
       </c>
       <c r="G92" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2021-06-09</t>
         </is>
       </c>
       <c r="H92" s="5" t="n">
@@ -4856,7 +4713,7 @@
       </c>
       <c r="G93" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2021-05-26</t>
         </is>
       </c>
       <c r="H93" s="5" t="n">
@@ -5178,7 +5035,7 @@
       </c>
       <c r="G100" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2021-06-15</t>
         </is>
       </c>
       <c r="H100" s="5" t="n">
@@ -5224,7 +5081,7 @@
       </c>
       <c r="G101" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2021-05-31</t>
         </is>
       </c>
       <c r="H101" s="5" t="n">
@@ -5500,7 +5357,7 @@
       </c>
       <c r="G107" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2021-05-27</t>
         </is>
       </c>
       <c r="H107" s="5" t="n">
@@ -5592,7 +5449,7 @@
       </c>
       <c r="G109" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2021-06-06</t>
         </is>
       </c>
       <c r="H109" s="5" t="n">
@@ -5638,7 +5495,7 @@
       </c>
       <c r="G110" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2021-05-30</t>
         </is>
       </c>
       <c r="H110" s="5" t="n">
@@ -5684,7 +5541,7 @@
       </c>
       <c r="G111" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2021-05-31</t>
         </is>
       </c>
       <c r="H111" s="5" t="n">
@@ -5914,7 +5771,7 @@
       </c>
       <c r="G116" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2021-07-11</t>
         </is>
       </c>
       <c r="H116" s="5" t="n">
@@ -6006,7 +5863,7 @@
       </c>
       <c r="G118" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2021-06-09</t>
         </is>
       </c>
       <c r="H118" s="5" t="n">
@@ -6052,7 +5909,7 @@
       </c>
       <c r="G119" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2021-05-23</t>
         </is>
       </c>
       <c r="H119" s="5" t="n">
@@ -6098,7 +5955,7 @@
       </c>
       <c r="G120" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2021-05-24</t>
         </is>
       </c>
       <c r="H120" s="5" t="n">
@@ -6236,7 +6093,7 @@
       </c>
       <c r="G123" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2021-06-09</t>
         </is>
       </c>
       <c r="H123" s="5" t="n">
@@ -6328,7 +6185,7 @@
       </c>
       <c r="G125" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2021-05-23</t>
         </is>
       </c>
       <c r="H125" s="5" t="n">
@@ -6420,7 +6277,7 @@
       </c>
       <c r="G127" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2021-05-26</t>
         </is>
       </c>
       <c r="H127" s="5" t="n">
@@ -6466,7 +6323,7 @@
       </c>
       <c r="G128" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2021-05-27</t>
         </is>
       </c>
       <c r="H128" s="5" t="n">
@@ -6512,7 +6369,7 @@
       </c>
       <c r="G129" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2021-05-30</t>
         </is>
       </c>
       <c r="H129" s="5" t="n">
@@ -6604,7 +6461,7 @@
       </c>
       <c r="G131" s="3" t="inlineStr">
         <is>
-          <t>2026-01-25</t>
+          <t>2021-05-30</t>
         </is>
       </c>
       <c r="H131" s="5" t="n">
@@ -6742,7 +6599,7 @@
       </c>
       <c r="G134" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2021-07-25</t>
         </is>
       </c>
       <c r="H134" s="5" t="n">
@@ -6834,7 +6691,7 @@
       </c>
       <c r="G136" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2021-05-30</t>
         </is>
       </c>
       <c r="H136" s="5" t="n">
@@ -6880,7 +6737,7 @@
       </c>
       <c r="G137" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2021-05-27</t>
         </is>
       </c>
       <c r="H137" s="5" t="n">
@@ -6926,7 +6783,7 @@
       </c>
       <c r="G138" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2021-05-30</t>
         </is>
       </c>
       <c r="H138" s="5" t="n">
@@ -7018,7 +6875,7 @@
       </c>
       <c r="G140" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2021-05-30</t>
         </is>
       </c>
       <c r="H140" s="5" t="n">
@@ -7156,7 +7013,7 @@
       </c>
       <c r="G143" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2021-05-30</t>
         </is>
       </c>
       <c r="H143" s="5" t="n">
@@ -7248,7 +7105,7 @@
       </c>
       <c r="G145" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2021-06-10</t>
         </is>
       </c>
       <c r="H145" s="5" t="n">
@@ -7294,7 +7151,7 @@
       </c>
       <c r="G146" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2021-05-23</t>
         </is>
       </c>
       <c r="H146" s="5" t="n">
@@ -7340,7 +7197,7 @@
       </c>
       <c r="G147" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2021-05-27</t>
         </is>
       </c>
       <c r="H147" s="5" t="n">
@@ -7386,7 +7243,7 @@
       </c>
       <c r="G148" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2021-05-30</t>
         </is>
       </c>
       <c r="H148" s="5" t="n">
@@ -7432,7 +7289,7 @@
       </c>
       <c r="G149" s="3" t="inlineStr">
         <is>
-          <t>2026-06-07</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="H149" s="5" t="n">
@@ -7570,7 +7427,7 @@
       </c>
       <c r="G152" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2021-10-05</t>
         </is>
       </c>
       <c r="H152" s="5" t="n">
@@ -7662,7 +7519,7 @@
       </c>
       <c r="G154" s="3" t="inlineStr">
         <is>
-          <t>2025-10-22</t>
+          <t>2021-05-30</t>
         </is>
       </c>
       <c r="H154" s="5" t="n">
@@ -7708,7 +7565,7 @@
       </c>
       <c r="G155" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2021-05-30</t>
         </is>
       </c>
       <c r="H155" s="5" t="n">
@@ -7754,7 +7611,7 @@
       </c>
       <c r="G156" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2021-05-30</t>
         </is>
       </c>
       <c r="H156" s="5" t="n">
@@ -7800,7 +7657,7 @@
       </c>
       <c r="G157" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2021-08-04</t>
         </is>
       </c>
       <c r="H157" s="5" t="n">
@@ -7846,7 +7703,7 @@
       </c>
       <c r="G158" s="3" t="inlineStr">
         <is>
-          <t>2025-10-30</t>
+          <t>2021-05-31</t>
         </is>
       </c>
       <c r="H158" s="5" t="n">
@@ -8076,7 +7933,7 @@
       </c>
       <c r="G163" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2021-05-31</t>
         </is>
       </c>
       <c r="H163" s="5" t="n">
@@ -8122,7 +7979,7 @@
       </c>
       <c r="G164" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2021-05-31</t>
         </is>
       </c>
       <c r="H164" s="5" t="n">
@@ -8214,7 +8071,7 @@
       </c>
       <c r="G166" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2021-05-26</t>
         </is>
       </c>
       <c r="H166" s="5" t="n">
@@ -8260,7 +8117,7 @@
       </c>
       <c r="G167" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2021-05-30</t>
         </is>
       </c>
       <c r="H167" s="5" t="n">
@@ -8444,7 +8301,7 @@
       </c>
       <c r="G171" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2023-02-28</t>
         </is>
       </c>
       <c r="H171" s="5" t="n">
@@ -8490,7 +8347,7 @@
       </c>
       <c r="G172" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2021-06-01</t>
         </is>
       </c>
       <c r="H172" s="5" t="n">
@@ -8536,7 +8393,7 @@
       </c>
       <c r="G173" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2021-06-01</t>
         </is>
       </c>
       <c r="H173" s="5" t="n">
@@ -8582,7 +8439,7 @@
       </c>
       <c r="G174" s="3" t="inlineStr">
         <is>
-          <t>2023-10-30</t>
+          <t>2021-06-01</t>
         </is>
       </c>
       <c r="H174" s="5" t="n">
@@ -8674,7 +8531,7 @@
       </c>
       <c r="G176" s="3" t="inlineStr">
         <is>
-          <t>2026-04-19</t>
+          <t>2021-05-25</t>
         </is>
       </c>
       <c r="H176" s="5" t="n">
@@ -8812,7 +8669,7 @@
       </c>
       <c r="G179" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2021-05-31</t>
         </is>
       </c>
       <c r="H179" s="5" t="n">
@@ -8904,7 +8761,7 @@
       </c>
       <c r="G181" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2021-06-01</t>
         </is>
       </c>
       <c r="H181" s="5" t="n">
@@ -8950,7 +8807,7 @@
       </c>
       <c r="G182" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2021-06-01</t>
         </is>
       </c>
       <c r="H182" s="5" t="n">
@@ -8996,7 +8853,7 @@
       </c>
       <c r="G183" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2021-06-01</t>
         </is>
       </c>
       <c r="H183" s="5" t="n">
@@ -9088,7 +8945,7 @@
       </c>
       <c r="G185" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2021-06-01</t>
         </is>
       </c>
       <c r="H185" s="5" t="n">
@@ -9226,7 +9083,7 @@
       </c>
       <c r="G188" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2021-05-25</t>
         </is>
       </c>
       <c r="H188" s="5" t="n">
@@ -9318,7 +9175,7 @@
       </c>
       <c r="G190" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2021-06-01</t>
         </is>
       </c>
       <c r="H190" s="5" t="n">
@@ -9364,7 +9221,7 @@
       </c>
       <c r="G191" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2021-06-01</t>
         </is>
       </c>
       <c r="H191" s="5" t="n">
@@ -9410,7 +9267,7 @@
       </c>
       <c r="G192" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2021-06-01</t>
         </is>
       </c>
       <c r="H192" s="5" t="n">
@@ -9456,7 +9313,7 @@
       </c>
       <c r="G193" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2021-06-01</t>
         </is>
       </c>
       <c r="H193" s="5" t="n">
@@ -9502,7 +9359,7 @@
       </c>
       <c r="G194" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2021-05-25</t>
         </is>
       </c>
       <c r="H194" s="5" t="n">
@@ -9732,7 +9589,7 @@
       </c>
       <c r="G199" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2021-06-01</t>
         </is>
       </c>
       <c r="H199" s="5" t="n">
@@ -9778,7 +9635,7 @@
       </c>
       <c r="G200" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2021-06-01</t>
         </is>
       </c>
       <c r="H200" s="5" t="n">
@@ -9824,7 +9681,7 @@
       </c>
       <c r="G201" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2021-06-01</t>
         </is>
       </c>
       <c r="H201" s="5" t="n">
@@ -9870,7 +9727,7 @@
       </c>
       <c r="G202" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2021-06-01</t>
         </is>
       </c>
       <c r="H202" s="5" t="n">
@@ -9916,7 +9773,7 @@
       </c>
       <c r="G203" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2021-06-01</t>
         </is>
       </c>
       <c r="H203" s="5" t="n">
@@ -10146,7 +10003,7 @@
       </c>
       <c r="G208" s="3" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2021-06-01</t>
         </is>
       </c>
       <c r="H208" s="5" t="n">
@@ -10192,7 +10049,7 @@
       </c>
       <c r="G209" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2021-06-01</t>
         </is>
       </c>
       <c r="H209" s="5" t="n">
@@ -10238,7 +10095,7 @@
       </c>
       <c r="G210" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2021-06-01</t>
         </is>
       </c>
       <c r="H210" s="5" t="n">
@@ -10284,7 +10141,7 @@
       </c>
       <c r="G211" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2021-06-01</t>
         </is>
       </c>
       <c r="H211" s="5" t="n">
@@ -10330,7 +10187,7 @@
       </c>
       <c r="G212" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2021-06-01</t>
         </is>
       </c>
       <c r="H212" s="5" t="n">
@@ -10560,7 +10417,7 @@
       </c>
       <c r="G217" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2021-06-16</t>
         </is>
       </c>
       <c r="H217" s="5" t="n">
@@ -10606,7 +10463,7 @@
       </c>
       <c r="G218" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2021-06-01</t>
         </is>
       </c>
       <c r="H218" s="5" t="n">
@@ -10652,7 +10509,7 @@
       </c>
       <c r="G219" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2021-06-01</t>
         </is>
       </c>
       <c r="H219" s="5" t="n">
@@ -10974,7 +10831,7 @@
       </c>
       <c r="G226" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2021-06-01</t>
         </is>
       </c>
       <c r="H226" s="5" t="n">
@@ -11020,7 +10877,7 @@
       </c>
       <c r="G227" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2021-06-01</t>
         </is>
       </c>
       <c r="H227" s="5" t="n">
@@ -11066,7 +10923,7 @@
       </c>
       <c r="G228" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2021-06-01</t>
         </is>
       </c>
       <c r="H228" s="5" t="n">
@@ -11158,7 +11015,7 @@
       </c>
       <c r="G230" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2021-06-01</t>
         </is>
       </c>
       <c r="H230" s="5" t="n">
@@ -11342,7 +11199,7 @@
       </c>
       <c r="G234" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2021-08-05</t>
         </is>
       </c>
       <c r="H234" s="5" t="n">
@@ -11388,7 +11245,7 @@
       </c>
       <c r="G235" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2021-06-01</t>
         </is>
       </c>
       <c r="H235" s="5" t="n">
@@ -11480,7 +11337,7 @@
       </c>
       <c r="G237" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2021-06-01</t>
         </is>
       </c>
       <c r="H237" s="5" t="n">
@@ -11572,7 +11429,7 @@
       </c>
       <c r="G239" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2021-06-01</t>
         </is>
       </c>
       <c r="H239" s="5" t="n">
@@ -11756,7 +11613,7 @@
       </c>
       <c r="G243" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2023-04-27</t>
         </is>
       </c>
       <c r="H243" s="5" t="n">
@@ -11802,7 +11659,7 @@
       </c>
       <c r="G244" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2021-06-01</t>
         </is>
       </c>
       <c r="H244" s="5" t="n">
@@ -11848,7 +11705,7 @@
       </c>
       <c r="G245" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2021-06-15</t>
         </is>
       </c>
       <c r="H245" s="5" t="n">
@@ -12216,7 +12073,7 @@
       </c>
       <c r="G253" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2021-06-02</t>
         </is>
       </c>
       <c r="H253" s="5" t="n">
@@ -12262,7 +12119,7 @@
       </c>
       <c r="G254" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2021-06-20</t>
         </is>
       </c>
       <c r="H254" s="5" t="n">
@@ -12308,7 +12165,7 @@
       </c>
       <c r="G255" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2021-06-01</t>
         </is>
       </c>
       <c r="H255" s="5" t="n">
@@ -12676,7 +12533,7 @@
       </c>
       <c r="G263" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2021-06-17</t>
         </is>
       </c>
       <c r="H263" s="5" t="n">
@@ -12722,7 +12579,7 @@
       </c>
       <c r="G264" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2021-06-02</t>
         </is>
       </c>
       <c r="H264" s="5" t="n">
@@ -13044,7 +12901,7 @@
       </c>
       <c r="G271" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2021-08-02</t>
         </is>
       </c>
       <c r="H271" s="5" t="n">
@@ -13090,7 +12947,7 @@
       </c>
       <c r="G272" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2021-07-04</t>
         </is>
       </c>
       <c r="H272" s="5" t="n">
@@ -13136,7 +12993,7 @@
       </c>
       <c r="G273" s="3" t="inlineStr">
         <is>
-          <t>2024-02-07</t>
+          <t>2021-06-15</t>
         </is>
       </c>
       <c r="H273" s="5" t="n">
@@ -13458,7 +13315,7 @@
       </c>
       <c r="G280" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2021-08-03</t>
         </is>
       </c>
       <c r="H280" s="5" t="n">
@@ -13504,7 +13361,7 @@
       </c>
       <c r="G281" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2021-07-13</t>
         </is>
       </c>
       <c r="H281" s="5" t="n">
@@ -13550,7 +13407,7 @@
       </c>
       <c r="G282" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2021-06-10</t>
         </is>
       </c>
       <c r="H282" s="5" t="n">
@@ -13872,7 +13729,7 @@
       </c>
       <c r="G289" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2021-08-30</t>
         </is>
       </c>
       <c r="H289" s="5" t="n">
@@ -13918,7 +13775,7 @@
       </c>
       <c r="G290" s="3" t="inlineStr">
         <is>
-          <t>2025-08-18</t>
+          <t>2021-07-18</t>
         </is>
       </c>
       <c r="H290" s="5" t="n">
@@ -13964,7 +13821,7 @@
       </c>
       <c r="G291" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2021-06-20</t>
         </is>
       </c>
       <c r="H291" s="5" t="n">
@@ -14286,7 +14143,7 @@
       </c>
       <c r="G298" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2022-09-07</t>
         </is>
       </c>
       <c r="H298" s="5" t="n">
@@ -14378,7 +14235,7 @@
       </c>
       <c r="G300" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2021-07-08</t>
         </is>
       </c>
       <c r="H300" s="5" t="n">
@@ -14470,7 +14327,7 @@
       </c>
       <c r="G302" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2021-09-02</t>
         </is>
       </c>
       <c r="H302" s="5" t="n">
@@ -14516,7 +14373,7 @@
       </c>
       <c r="G303" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2021-08-03</t>
         </is>
       </c>
       <c r="H303" s="5" t="n">
@@ -14562,7 +14419,7 @@
       </c>
       <c r="G304" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2021-07-14</t>
         </is>
       </c>
       <c r="H304" s="5" t="n">
@@ -14608,7 +14465,7 @@
       </c>
       <c r="G305" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2021-06-29</t>
         </is>
       </c>
       <c r="H305" s="5" t="n">
@@ -14654,7 +14511,7 @@
       </c>
       <c r="G306" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2021-06-29</t>
         </is>
       </c>
       <c r="H306" s="5" t="n">
@@ -14700,7 +14557,7 @@
       </c>
       <c r="G307" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2021-06-24</t>
         </is>
       </c>
       <c r="H307" s="5" t="n">
@@ -14792,7 +14649,7 @@
       </c>
       <c r="G309" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2021-06-14</t>
         </is>
       </c>
       <c r="H309" s="5" t="n">
@@ -14838,7 +14695,7 @@
       </c>
       <c r="G310" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2021-08-02</t>
         </is>
       </c>
       <c r="H310" s="5" t="n">
@@ -14884,7 +14741,7 @@
       </c>
       <c r="G311" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2021-06-09</t>
         </is>
       </c>
       <c r="H311" s="5" t="n">
@@ -14930,7 +14787,7 @@
       </c>
       <c r="G312" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2021-07-05</t>
         </is>
       </c>
       <c r="H312" s="5" t="n">
@@ -14976,7 +14833,7 @@
       </c>
       <c r="G313" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2021-06-09</t>
         </is>
       </c>
       <c r="H313" s="5" t="n">
@@ -15022,7 +14879,7 @@
       </c>
       <c r="G314" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2021-07-22</t>
         </is>
       </c>
       <c r="H314" s="5" t="n">
@@ -15114,7 +14971,7 @@
       </c>
       <c r="G316" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2021-06-06</t>
         </is>
       </c>
       <c r="H316" s="5" t="n">
@@ -15160,7 +15017,7 @@
       </c>
       <c r="G317" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2021-06-21</t>
         </is>
       </c>
       <c r="H317" s="5" t="n">
@@ -15206,7 +15063,7 @@
       </c>
       <c r="G318" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2021-06-08</t>
         </is>
       </c>
       <c r="H318" s="5" t="n">
@@ -15298,7 +15155,7 @@
       </c>
       <c r="G320" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2021-07-07</t>
         </is>
       </c>
       <c r="H320" s="5" t="n">
@@ -15344,7 +15201,7 @@
       </c>
       <c r="G321" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2021-06-10</t>
         </is>
       </c>
       <c r="H321" s="5" t="n">
@@ -15390,7 +15247,7 @@
       </c>
       <c r="G322" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2021-07-19</t>
         </is>
       </c>
       <c r="H322" s="5" t="n">
@@ -15482,7 +15339,7 @@
       </c>
       <c r="G324" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2021-06-08</t>
         </is>
       </c>
       <c r="H324" s="5" t="n">
@@ -15528,7 +15385,7 @@
       </c>
       <c r="G325" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2021-06-21</t>
         </is>
       </c>
       <c r="H325" s="5" t="n">
@@ -15574,7 +15431,7 @@
       </c>
       <c r="G326" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2021-08-19</t>
         </is>
       </c>
       <c r="H326" s="5" t="n">
@@ -15620,7 +15477,7 @@
       </c>
       <c r="G327" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2021-08-05</t>
         </is>
       </c>
       <c r="H327" s="5" t="n">
@@ -15666,7 +15523,7 @@
       </c>
       <c r="G328" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2021-07-15</t>
         </is>
       </c>
       <c r="H328" s="5" t="n">
@@ -15712,7 +15569,7 @@
       </c>
       <c r="G329" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2021-06-20</t>
         </is>
       </c>
       <c r="H329" s="5" t="n">
@@ -15758,7 +15615,7 @@
       </c>
       <c r="G330" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2021-07-20</t>
         </is>
       </c>
       <c r="H330" s="5" t="n">
@@ -15804,7 +15661,7 @@
       </c>
       <c r="G331" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2021-06-09</t>
         </is>
       </c>
       <c r="H331" s="5" t="n">
@@ -15850,7 +15707,7 @@
       </c>
       <c r="G332" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2021-06-06</t>
         </is>
       </c>
       <c r="H332" s="5" t="n">
@@ -15896,7 +15753,7 @@
       </c>
       <c r="G333" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2021-06-29</t>
         </is>
       </c>
       <c r="H333" s="5" t="n">
@@ -15942,7 +15799,7 @@
       </c>
       <c r="G334" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2021-09-01</t>
         </is>
       </c>
       <c r="H334" s="5" t="n">
@@ -15988,7 +15845,7 @@
       </c>
       <c r="G335" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2021-09-08</t>
         </is>
       </c>
       <c r="H335" s="5" t="n">
@@ -16034,7 +15891,7 @@
       </c>
       <c r="G336" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2021-07-15</t>
         </is>
       </c>
       <c r="H336" s="5" t="n">
@@ -16080,7 +15937,7 @@
       </c>
       <c r="G337" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2021-06-24</t>
         </is>
       </c>
       <c r="H337" s="5" t="n">
@@ -16172,7 +16029,7 @@
       </c>
       <c r="G339" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2021-06-22</t>
         </is>
       </c>
       <c r="H339" s="5" t="n">
@@ -16264,7 +16121,7 @@
       </c>
       <c r="G341" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2021-06-24</t>
         </is>
       </c>
       <c r="H341" s="5" t="n">
@@ -16356,7 +16213,7 @@
       </c>
       <c r="G343" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2021-06-24</t>
         </is>
       </c>
       <c r="H343" s="5" t="n">
@@ -16402,7 +16259,7 @@
       </c>
       <c r="G344" s="3" t="inlineStr">
         <is>
-          <t>2025-08-18</t>
+          <t>2021-07-04</t>
         </is>
       </c>
       <c r="H344" s="5" t="n">
@@ -16448,7 +16305,7 @@
       </c>
       <c r="G345" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2021-06-07</t>
         </is>
       </c>
       <c r="H345" s="5" t="n">
@@ -16494,7 +16351,7 @@
       </c>
       <c r="G346" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2021-07-15</t>
         </is>
       </c>
       <c r="H346" s="5" t="n">
@@ -16540,7 +16397,7 @@
       </c>
       <c r="G347" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2021-07-05</t>
         </is>
       </c>
       <c r="H347" s="5" t="n">
@@ -16586,7 +16443,7 @@
       </c>
       <c r="G348" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2021-06-15</t>
         </is>
       </c>
       <c r="H348" s="5" t="n">
@@ -16632,7 +16489,7 @@
       </c>
       <c r="G349" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2021-06-22</t>
         </is>
       </c>
       <c r="H349" s="5" t="n">
@@ -16678,7 +16535,7 @@
       </c>
       <c r="G350" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2021-07-18</t>
         </is>
       </c>
       <c r="H350" s="5" t="n">
@@ -16770,7 +16627,7 @@
       </c>
       <c r="G352" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2021-07-19</t>
         </is>
       </c>
       <c r="H352" s="5" t="n">
@@ -16816,7 +16673,7 @@
       </c>
       <c r="G353" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2021-06-09</t>
         </is>
       </c>
       <c r="H353" s="5" t="n">
@@ -16862,7 +16719,7 @@
       </c>
       <c r="G354" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2021-06-15</t>
         </is>
       </c>
       <c r="H354" s="5" t="n">
@@ -16908,7 +16765,7 @@
       </c>
       <c r="G355" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2021-06-09</t>
         </is>
       </c>
       <c r="H355" s="5" t="n">
@@ -16954,7 +16811,7 @@
       </c>
       <c r="G356" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2021-06-15</t>
         </is>
       </c>
       <c r="H356" s="5" t="n">
@@ -17000,7 +16857,7 @@
       </c>
       <c r="G357" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2021-06-17</t>
         </is>
       </c>
       <c r="H357" s="5" t="n">
@@ -17046,7 +16903,7 @@
       </c>
       <c r="G358" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2021-07-07</t>
         </is>
       </c>
       <c r="H358" s="5" t="n">
@@ -17138,7 +16995,7 @@
       </c>
       <c r="G360" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2021-07-19</t>
         </is>
       </c>
       <c r="H360" s="5" t="n">
@@ -17184,7 +17041,7 @@
       </c>
       <c r="G361" s="3" t="inlineStr">
         <is>
-          <t>2025-09-28</t>
+          <t>2021-06-09</t>
         </is>
       </c>
       <c r="H361" s="5" t="n">
@@ -17230,7 +17087,7 @@
       </c>
       <c r="G362" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2021-06-09</t>
         </is>
       </c>
       <c r="H362" s="5" t="n">
@@ -17276,7 +17133,7 @@
       </c>
       <c r="G363" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2021-06-16</t>
         </is>
       </c>
       <c r="H363" s="5" t="n">
@@ -17322,7 +17179,7 @@
       </c>
       <c r="G364" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2021-06-09</t>
         </is>
       </c>
       <c r="H364" s="5" t="n">
@@ -17368,7 +17225,7 @@
       </c>
       <c r="G365" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2021-06-21</t>
         </is>
       </c>
       <c r="H365" s="5" t="n">
@@ -17414,7 +17271,7 @@
       </c>
       <c r="G366" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2021-07-06</t>
         </is>
       </c>
       <c r="H366" s="5" t="n">
@@ -17506,7 +17363,7 @@
       </c>
       <c r="G368" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2021-07-06</t>
         </is>
       </c>
       <c r="H368" s="5" t="n">
@@ -17598,7 +17455,7 @@
       </c>
       <c r="G370" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2021-06-17</t>
         </is>
       </c>
       <c r="H370" s="5" t="n">
@@ -17644,7 +17501,7 @@
       </c>
       <c r="G371" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2021-06-09</t>
         </is>
       </c>
       <c r="H371" s="5" t="n">
@@ -17690,7 +17547,7 @@
       </c>
       <c r="G372" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2021-06-09</t>
         </is>
       </c>
       <c r="H372" s="5" t="n">
@@ -17736,7 +17593,7 @@
       </c>
       <c r="G373" s="3" t="inlineStr">
         <is>
-          <t>2024-10-14</t>
+          <t>2021-07-22</t>
         </is>
       </c>
       <c r="H373" s="5" t="n">
@@ -17782,7 +17639,7 @@
       </c>
       <c r="G374" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2021-07-14</t>
         </is>
       </c>
       <c r="H374" s="5" t="n">
@@ -17874,7 +17731,7 @@
       </c>
       <c r="G376" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2021-07-06</t>
         </is>
       </c>
       <c r="H376" s="5" t="n">
@@ -17920,7 +17777,7 @@
       </c>
       <c r="G377" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2021-06-16</t>
         </is>
       </c>
       <c r="H377" s="5" t="n">
@@ -17966,7 +17823,7 @@
       </c>
       <c r="G378" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2021-06-17</t>
         </is>
       </c>
       <c r="H378" s="5" t="n">
@@ -18012,7 +17869,7 @@
       </c>
       <c r="G379" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2021-09-07</t>
         </is>
       </c>
       <c r="H379" s="5" t="n">
@@ -18058,7 +17915,7 @@
       </c>
       <c r="G380" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2021-06-22</t>
         </is>
       </c>
       <c r="H380" s="5" t="n">
@@ -18104,7 +17961,7 @@
       </c>
       <c r="G381" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2021-07-15</t>
         </is>
       </c>
       <c r="H381" s="5" t="n">
@@ -18150,7 +18007,7 @@
       </c>
       <c r="G382" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2021-07-18</t>
         </is>
       </c>
       <c r="H382" s="5" t="n">
@@ -18196,7 +18053,7 @@
       </c>
       <c r="G383" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2021-07-28</t>
         </is>
       </c>
       <c r="H383" s="5" t="n">
@@ -18242,7 +18099,7 @@
       </c>
       <c r="G384" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2021-07-20</t>
         </is>
       </c>
       <c r="H384" s="5" t="n">
@@ -18288,7 +18145,7 @@
       </c>
       <c r="G385" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2021-07-04</t>
         </is>
       </c>
       <c r="H385" s="5" t="n">
@@ -18334,7 +18191,7 @@
       </c>
       <c r="G386" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2021-07-04</t>
         </is>
       </c>
       <c r="H386" s="5" t="n">
@@ -18564,7 +18421,7 @@
       </c>
       <c r="G391" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2021-08-25</t>
         </is>
       </c>
       <c r="H391" s="5" t="n">
@@ -18656,7 +18513,7 @@
       </c>
       <c r="G393" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2021-07-28</t>
         </is>
       </c>
       <c r="H393" s="5" t="n">
@@ -18702,7 +18559,7 @@
       </c>
       <c r="G394" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2021-06-01</t>
         </is>
       </c>
       <c r="H394" s="5" t="n">
@@ -18748,7 +18605,7 @@
       </c>
       <c r="G395" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2021-06-01</t>
         </is>
       </c>
       <c r="H395" s="5" t="n">
@@ -18794,7 +18651,7 @@
       </c>
       <c r="G396" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2021-07-18</t>
         </is>
       </c>
       <c r="H396" s="5" t="n">
@@ -18840,7 +18697,7 @@
       </c>
       <c r="G397" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2021-06-01</t>
         </is>
       </c>
       <c r="H397" s="5" t="n">
@@ -18886,7 +18743,7 @@
       </c>
       <c r="G398" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2021-06-01</t>
         </is>
       </c>
       <c r="H398" s="5" t="n">
@@ -18932,7 +18789,7 @@
       </c>
       <c r="G399" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2021-06-01</t>
         </is>
       </c>
       <c r="H399" s="5" t="n">
@@ -18978,7 +18835,7 @@
       </c>
       <c r="G400" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2021-07-22</t>
         </is>
       </c>
       <c r="H400" s="5" t="n">
@@ -19024,7 +18881,7 @@
       </c>
       <c r="G401" s="3" t="inlineStr">
         <is>
-          <t>2025-06-23</t>
+          <t>2021-07-12</t>
         </is>
       </c>
       <c r="H401" s="5" t="n">
@@ -19070,7 +18927,7 @@
       </c>
       <c r="G402" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2021-06-01</t>
         </is>
       </c>
       <c r="H402" s="5" t="n">
@@ -19116,7 +18973,7 @@
       </c>
       <c r="G403" s="3" t="inlineStr">
         <is>
-          <t>2026-05-26</t>
+          <t>2021-06-01</t>
         </is>
       </c>
       <c r="H403" s="5" t="n">
@@ -19208,7 +19065,7 @@
       </c>
       <c r="G405" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2021-06-01</t>
         </is>
       </c>
       <c r="H405" s="5" t="n">
@@ -19254,7 +19111,7 @@
       </c>
       <c r="G406" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2021-06-01</t>
         </is>
       </c>
       <c r="H406" s="5" t="n">
@@ -19300,7 +19157,7 @@
       </c>
       <c r="G407" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2021-06-01</t>
         </is>
       </c>
       <c r="H407" s="5" t="n">
@@ -19346,7 +19203,7 @@
       </c>
       <c r="G408" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2021-07-20</t>
         </is>
       </c>
       <c r="H408" s="5" t="n">
@@ -19392,7 +19249,7 @@
       </c>
       <c r="G409" s="3" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2021-07-18</t>
         </is>
       </c>
       <c r="H409" s="5" t="n">
@@ -19438,7 +19295,7 @@
       </c>
       <c r="G410" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2021-05-30</t>
         </is>
       </c>
       <c r="H410" s="5" t="n">
@@ -19484,7 +19341,7 @@
       </c>
       <c r="G411" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2021-05-30</t>
         </is>
       </c>
       <c r="H411" s="5" t="n">
@@ -19530,7 +19387,7 @@
       </c>
       <c r="G412" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2021-07-19</t>
         </is>
       </c>
       <c r="H412" s="5" t="n">
@@ -19576,7 +19433,7 @@
       </c>
       <c r="G413" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2021-05-23</t>
         </is>
       </c>
       <c r="H413" s="5" t="n">
@@ -19622,7 +19479,7 @@
       </c>
       <c r="G414" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2021-05-24</t>
         </is>
       </c>
       <c r="H414" s="5" t="n">
@@ -19668,7 +19525,7 @@
       </c>
       <c r="G415" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2021-05-19</t>
         </is>
       </c>
       <c r="H415" s="5" t="n">
@@ -19760,7 +19617,7 @@
       </c>
       <c r="G417" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2021-07-18</t>
         </is>
       </c>
       <c r="H417" s="5" t="n">
@@ -19806,7 +19663,7 @@
       </c>
       <c r="G418" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2021-07-05</t>
         </is>
       </c>
       <c r="H418" s="5" t="n">
@@ -19852,7 +19709,7 @@
       </c>
       <c r="G419" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2021-07-08</t>
         </is>
       </c>
       <c r="H419" s="5" t="n">
@@ -19898,7 +19755,7 @@
       </c>
       <c r="G420" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2021-07-18</t>
         </is>
       </c>
       <c r="H420" s="5" t="n">
@@ -19944,7 +19801,7 @@
       </c>
       <c r="G421" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2021-05-24</t>
         </is>
       </c>
       <c r="H421" s="5" t="n">
@@ -19990,7 +19847,7 @@
       </c>
       <c r="G422" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2021-05-26</t>
         </is>
       </c>
       <c r="H422" s="5" t="n">
@@ -20036,7 +19893,7 @@
       </c>
       <c r="G423" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2021-05-30</t>
         </is>
       </c>
       <c r="H423" s="5" t="n">
@@ -20082,7 +19939,7 @@
       </c>
       <c r="G424" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2021-08-11</t>
         </is>
       </c>
       <c r="H424" s="5" t="n">
@@ -20128,7 +19985,7 @@
       </c>
       <c r="G425" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2021-08-04</t>
         </is>
       </c>
       <c r="H425" s="5" t="n">
@@ -20174,7 +20031,7 @@
       </c>
       <c r="G426" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2021-05-30</t>
         </is>
       </c>
       <c r="H426" s="5" t="n">
@@ -20220,7 +20077,7 @@
       </c>
       <c r="G427" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2021-07-15</t>
         </is>
       </c>
       <c r="H427" s="5" t="n">
@@ -20312,7 +20169,7 @@
       </c>
       <c r="G429" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2021-05-31</t>
         </is>
       </c>
       <c r="H429" s="5" t="n">
@@ -20358,7 +20215,7 @@
       </c>
       <c r="G430" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2021-05-30</t>
         </is>
       </c>
       <c r="H430" s="5" t="n">
@@ -20404,7 +20261,7 @@
       </c>
       <c r="G431" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2021-05-31</t>
         </is>
       </c>
       <c r="H431" s="5" t="n">
@@ -20450,7 +20307,7 @@
       </c>
       <c r="G432" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2021-08-10</t>
         </is>
       </c>
       <c r="H432" s="5" t="n">
@@ -20496,7 +20353,7 @@
       </c>
       <c r="G433" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2021-07-18</t>
         </is>
       </c>
       <c r="H433" s="5" t="n">
@@ -20634,7 +20491,7 @@
       </c>
       <c r="G436" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2023-05-09</t>
         </is>
       </c>
       <c r="H436" s="5" t="n">
@@ -20680,7 +20537,7 @@
       </c>
       <c r="G437" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2021-05-26</t>
         </is>
       </c>
       <c r="H437" s="5" t="n">
@@ -20726,7 +20583,7 @@
       </c>
       <c r="G438" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2021-07-26</t>
         </is>
       </c>
       <c r="H438" s="5" t="n">
@@ -20818,7 +20675,7 @@
       </c>
       <c r="G440" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2021-05-26</t>
         </is>
       </c>
       <c r="H440" s="5" t="n">
@@ -20864,7 +20721,7 @@
       </c>
       <c r="G441" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2021-05-27</t>
         </is>
       </c>
       <c r="H441" s="5" t="n">
@@ -20910,7 +20767,7 @@
       </c>
       <c r="G442" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2021-05-27</t>
         </is>
       </c>
       <c r="H442" s="5" t="n">
@@ -20956,7 +20813,7 @@
       </c>
       <c r="G443" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2021-05-26</t>
         </is>
       </c>
       <c r="H443" s="5" t="n">
@@ -21002,7 +20859,7 @@
       </c>
       <c r="G444" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2021-05-26</t>
         </is>
       </c>
       <c r="H444" s="5" t="n">
@@ -21048,7 +20905,7 @@
       </c>
       <c r="G445" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2021-05-30</t>
         </is>
       </c>
       <c r="H445" s="5" t="n">
@@ -21094,7 +20951,7 @@
       </c>
       <c r="G446" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2021-07-20</t>
         </is>
       </c>
       <c r="H446" s="5" t="n">
@@ -21140,7 +20997,7 @@
       </c>
       <c r="G447" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2021-05-27</t>
         </is>
       </c>
       <c r="H447" s="5" t="n">
@@ -21186,7 +21043,7 @@
       </c>
       <c r="G448" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2021-05-27</t>
         </is>
       </c>
       <c r="H448" s="5" t="n">
@@ -21232,7 +21089,7 @@
       </c>
       <c r="G449" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2021-05-26</t>
         </is>
       </c>
       <c r="H449" s="5" t="n">
@@ -21278,7 +21135,7 @@
       </c>
       <c r="G450" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2021-05-30</t>
         </is>
       </c>
       <c r="H450" s="5" t="n">
@@ -21324,7 +21181,7 @@
       </c>
       <c r="G451" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2021-05-26</t>
         </is>
       </c>
       <c r="H451" s="5" t="n">
@@ -21416,7 +21273,7 @@
       </c>
       <c r="G453" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2021-05-24</t>
         </is>
       </c>
       <c r="H453" s="5" t="n">
@@ -21462,7 +21319,7 @@
       </c>
       <c r="G454" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2021-07-22</t>
         </is>
       </c>
       <c r="H454" s="5" t="n">
@@ -21508,7 +21365,7 @@
       </c>
       <c r="G455" s="3" t="inlineStr">
         <is>
-          <t>2024-01-16</t>
+          <t>2021-05-24</t>
         </is>
       </c>
       <c r="H455" s="5" t="n">
@@ -21646,7 +21503,7 @@
       </c>
       <c r="G458" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2021-05-23</t>
         </is>
       </c>
       <c r="H458" s="5" t="n">
@@ -21692,7 +21549,7 @@
       </c>
       <c r="G459" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2021-05-23</t>
         </is>
       </c>
       <c r="H459" s="5" t="n">
@@ -21922,7 +21779,7 @@
       </c>
       <c r="G464" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2021-05-23</t>
         </is>
       </c>
       <c r="H464" s="5" t="n">
@@ -21968,7 +21825,7 @@
       </c>
       <c r="G465" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2021-05-24</t>
         </is>
       </c>
       <c r="H465" s="5" t="n">
@@ -22014,7 +21871,7 @@
       </c>
       <c r="G466" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2021-05-25</t>
         </is>
       </c>
       <c r="H466" s="5" t="n">
@@ -22060,7 +21917,7 @@
       </c>
       <c r="G467" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2021-05-23</t>
         </is>
       </c>
       <c r="H467" s="5" t="n">
@@ -22106,7 +21963,7 @@
       </c>
       <c r="G468" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2021-07-11</t>
         </is>
       </c>
       <c r="H468" s="5" t="n">
@@ -22152,7 +22009,7 @@
       </c>
       <c r="G469" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2021-07-19</t>
         </is>
       </c>
       <c r="H469" s="5" t="n">
@@ -22198,7 +22055,7 @@
       </c>
       <c r="G470" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2021-09-05</t>
         </is>
       </c>
       <c r="H470" s="5" t="n">
@@ -22290,7 +22147,7 @@
       </c>
       <c r="G472" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2021-06-02</t>
         </is>
       </c>
       <c r="H472" s="5" t="n">
@@ -22336,7 +22193,7 @@
       </c>
       <c r="G473" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2021-07-18</t>
         </is>
       </c>
       <c r="H473" s="5" t="n">
@@ -22382,7 +22239,7 @@
       </c>
       <c r="G474" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2021-07-28</t>
         </is>
       </c>
       <c r="H474" s="5" t="n">
@@ -22428,7 +22285,7 @@
       </c>
       <c r="G475" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2021-06-02</t>
         </is>
       </c>
       <c r="H475" s="5" t="n">
@@ -22474,7 +22331,7 @@
       </c>
       <c r="G476" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2021-07-18</t>
         </is>
       </c>
       <c r="H476" s="5" t="n">
@@ -22730,5002 +22587,4 @@
   <pageMargins left="0.25" right="0.25" top="0.25" bottom="0.25" header="0.1" footer="0.1"/>
   <pageSetup orientation="portrait" paperSize="9" fitToHeight="0" fitToWidth="1"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr fitToPage="1"/>
-  </sheetPr>
-  <dimension ref="A1:J39"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="12" customWidth="1" min="1" max="1"/>
-    <col width="18" customWidth="1" min="2" max="2"/>
-    <col width="18" customWidth="1" min="3" max="3"/>
-    <col width="18" customWidth="1" min="4" max="4"/>
-    <col width="18" customWidth="1" min="5" max="5"/>
-    <col width="18" customWidth="1" min="6" max="6"/>
-    <col width="18" customWidth="1" min="7" max="7"/>
-    <col width="18" customWidth="1" min="8" max="8"/>
-    <col width="18" customWidth="1" min="9" max="9"/>
-    <col width="18" customWidth="1" min="10" max="10"/>
-  </cols>
-  <sheetData>
-    <row r="1" ht="40" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>The Henley I - 2座 销控网格图</t>
-        </is>
-      </c>
-    </row>
-    <row r="2" ht="20" customHeight="1">
-      <c r="A2" s="6" t="inlineStr">
-        <is>
-          <t>总套数</t>
-        </is>
-      </c>
-      <c r="B2" s="7" t="inlineStr">
-        <is>
-          <t>在售 (Sale)</t>
-        </is>
-      </c>
-      <c r="C2" s="8" t="inlineStr">
-        <is>
-          <t>已定价未售</t>
-        </is>
-      </c>
-      <c r="D2" s="9" t="inlineStr">
-        <is>
-          <t>已售 (Sold)</t>
-        </is>
-      </c>
-      <c r="E2" s="10" t="inlineStr">
-        <is>
-          <t>暂停销售</t>
-        </is>
-      </c>
-      <c r="F2" s="6" t="inlineStr">
-        <is>
-          <t>待售 (Pending)</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="25" customHeight="1">
-      <c r="A3" s="11" t="inlineStr">
-        <is>
-          <t>299 套</t>
-        </is>
-      </c>
-      <c r="B3" s="12" t="inlineStr">
-        <is>
-          <t>26 套</t>
-        </is>
-      </c>
-      <c r="C3" s="13" t="inlineStr">
-        <is>
-          <t>32 套</t>
-        </is>
-      </c>
-      <c r="D3" s="14" t="inlineStr">
-        <is>
-          <t>221 套</t>
-        </is>
-      </c>
-      <c r="E3" s="15" t="inlineStr">
-        <is>
-          <t>20 套</t>
-        </is>
-      </c>
-      <c r="F3" s="11" t="inlineStr">
-        <is>
-          <t>0 套</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="25" customHeight="1">
-      <c r="A5" s="2" t="inlineStr">
-        <is>
-          <t>楼层\房号</t>
-        </is>
-      </c>
-      <c r="B5" s="2" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>D</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>E</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>F</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>G</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>H</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>J</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="65" customHeight="1">
-      <c r="A6" s="2" t="inlineStr">
-        <is>
-          <t>40/F</t>
-        </is>
-      </c>
-      <c r="B6" s="16" t="inlineStr">
-        <is>
-          <t>A | 1350呎 (3房)
-$8,355万
-$61,888/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="C6" s="17" t="inlineStr"/>
-      <c r="D6" s="17" t="inlineStr"/>
-      <c r="E6" s="17" t="inlineStr"/>
-      <c r="F6" s="18" t="inlineStr">
-        <is>
-          <t>E | 696呎 (3房)
-招标单位
--
-(在售)</t>
-        </is>
-      </c>
-      <c r="G6" s="16" t="inlineStr">
-        <is>
-          <t>F | 505呎 (2房)
-$1,370万
-$27,129/呎
-(25年-12月)</t>
-        </is>
-      </c>
-      <c r="H6" s="16" t="inlineStr">
-        <is>
-          <t>G | 380呎 (1房)
-$827万
-$21,753/呎
-(25年-07月)</t>
-        </is>
-      </c>
-      <c r="I6" s="16" t="inlineStr">
-        <is>
-          <t>H | 379呎 (1房)
-$820万
-$21,630/呎
-(25年-06月)</t>
-        </is>
-      </c>
-      <c r="J6" s="18" t="inlineStr">
-        <is>
-          <t>J | 418呎 (1房)
-$1,443万
-$34,531/呎
-(在售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="65" customHeight="1">
-      <c r="A7" s="2" t="inlineStr">
-        <is>
-          <t>39/F</t>
-        </is>
-      </c>
-      <c r="B7" s="16" t="inlineStr">
-        <is>
-          <t>A | 890呎 (3房)
-$2,996万
-$33,662/呎
-(26年-01月)</t>
-        </is>
-      </c>
-      <c r="C7" s="18" t="inlineStr">
-        <is>
-          <t>B | 550呎 (2房)
-$2,035万
-$36,993/呎
-(在售)</t>
-        </is>
-      </c>
-      <c r="D7" s="18" t="inlineStr">
-        <is>
-          <t>C | 550呎 (2房)
-$2,015万
-$36,633/呎
-(在售)</t>
-        </is>
-      </c>
-      <c r="E7" s="16" t="inlineStr">
-        <is>
-          <t>D | 546呎 (2房)
-$1,950万
-$35,721/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="F7" s="16" t="inlineStr">
-        <is>
-          <t>E | 695呎 (3房)
-$1,557万
-$22,404/呎
-(25年-07月)</t>
-        </is>
-      </c>
-      <c r="G7" s="16" t="inlineStr">
-        <is>
-          <t>F | 505呎 (2房)
-$1,437万
-$28,453/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="H7" s="16" t="inlineStr">
-        <is>
-          <t>G | 380呎 (1房)
-$1,055万
-$27,765/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="I7" s="16" t="inlineStr">
-        <is>
-          <t>H | 379呎 (1房)
-$1,058万
-$27,903/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="J7" s="18" t="inlineStr">
-        <is>
-          <t>J | 418呎 (1房)
-$1,139万
-$27,242/呎
-(在售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="8" ht="65" customHeight="1">
-      <c r="A8" s="2" t="inlineStr">
-        <is>
-          <t>38/F</t>
-        </is>
-      </c>
-      <c r="B8" s="16" t="inlineStr">
-        <is>
-          <t>A | 890呎 (3房)
-$2,960万
-$33,263/呎
-(26年-02月)</t>
-        </is>
-      </c>
-      <c r="C8" s="18" t="inlineStr">
-        <is>
-          <t>B | 550呎 (2房)
-$2,012万
-$36,578/呎
-(在售)</t>
-        </is>
-      </c>
-      <c r="D8" s="18" t="inlineStr">
-        <is>
-          <t>C | 550呎 (2房)
-$1,992万
-$36,222/呎
-(在售)</t>
-        </is>
-      </c>
-      <c r="E8" s="16" t="inlineStr">
-        <is>
-          <t>D | 546呎 (2房)
-$1,880万
-$34,428/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="F8" s="16" t="inlineStr">
-        <is>
-          <t>E | 695呎 (3房)
-$1,540万
-$22,152/呎
-(25年-07月)</t>
-        </is>
-      </c>
-      <c r="G8" s="16" t="inlineStr">
-        <is>
-          <t>F | 505呎 (2房)
-$1,392万
-$27,556/呎
-(21年-05月)</t>
-        </is>
-      </c>
-      <c r="H8" s="16" t="inlineStr">
-        <is>
-          <t>G | 380呎 (1房)
-$1,043万
-$27,447/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="I8" s="16" t="inlineStr">
-        <is>
-          <t>H | 379呎 (1房)
-$1,046万
-$27,592/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="J8" s="18" t="inlineStr">
-        <is>
-          <t>J | 418呎 (1房)
-$1,126万
-$26,933/呎
-(在售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="9" ht="65" customHeight="1">
-      <c r="A9" s="2" t="inlineStr">
-        <is>
-          <t>37/F</t>
-        </is>
-      </c>
-      <c r="B9" s="16" t="inlineStr">
-        <is>
-          <t>A | 890呎 (3房)
-$2,943万
-$33,063/呎
-(26年-02月)</t>
-        </is>
-      </c>
-      <c r="C9" s="19" t="inlineStr">
-        <is>
-          <t>B | 550呎 (2房)
-$2,000万
-$36,371/呎
-(已定价未售)</t>
-        </is>
-      </c>
-      <c r="D9" s="18" t="inlineStr">
-        <is>
-          <t>C | 550呎 (2房)
-$1,981万
-$36,016/呎
-(在售)</t>
-        </is>
-      </c>
-      <c r="E9" s="16" t="inlineStr">
-        <is>
-          <t>D | 546呎 (2房)
-$1,887万
-$34,551/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="F9" s="16" t="inlineStr">
-        <is>
-          <t>E | 695呎 (3房)
-$1,528万
-$21,979/呎
-(25年-06月)</t>
-        </is>
-      </c>
-      <c r="G9" s="16" t="inlineStr">
-        <is>
-          <t>F | 505呎 (2房)
-$1,425万
-$28,226/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="H9" s="16" t="inlineStr">
-        <is>
-          <t>G | 380呎 (1房)
-$812万
-$21,364/呎
-(25年-06月)</t>
-        </is>
-      </c>
-      <c r="I9" s="16" t="inlineStr">
-        <is>
-          <t>H | 379呎 (1房)
-$806万
-$21,256/呎
-(25年-07月)</t>
-        </is>
-      </c>
-      <c r="J9" s="18" t="inlineStr">
-        <is>
-          <t>J | 417呎 (1房)
-$1,117万
-$26,779/呎
-(在售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="10" ht="65" customHeight="1">
-      <c r="A10" s="2" t="inlineStr">
-        <is>
-          <t>36/F</t>
-        </is>
-      </c>
-      <c r="B10" s="16" t="inlineStr">
-        <is>
-          <t>A | 890呎 (3房)
-$2,934万
-$32,963/呎
-(26年-02月)</t>
-        </is>
-      </c>
-      <c r="C10" s="18" t="inlineStr">
-        <is>
-          <t>B | 550呎 (2房)
-$1,995万
-$36,265/呎
-(在售)</t>
-        </is>
-      </c>
-      <c r="D10" s="16" t="inlineStr">
-        <is>
-          <t>C | 550呎 (2房)
-$1,965万
-$35,733/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="E10" s="16" t="inlineStr">
-        <is>
-          <t>D | 546呎 (2房)
-$1,881万
-$34,451/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="F10" s="16" t="inlineStr">
-        <is>
-          <t>E | 695呎 (3房)
-$1,523万
-$21,918/呎
-(25年-06月)</t>
-        </is>
-      </c>
-      <c r="G10" s="16" t="inlineStr">
-        <is>
-          <t>F | 505呎 (2房)
-$1,436万
-$28,433/呎
-(25年-09月)</t>
-        </is>
-      </c>
-      <c r="H10" s="16" t="inlineStr">
-        <is>
-          <t>G | 380呎 (1房)
-$1,034万
-$27,210/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="I10" s="16" t="inlineStr">
-        <is>
-          <t>H | 379呎 (1房)
-$803万
-$21,196/呎
-(25年-06月)</t>
-        </is>
-      </c>
-      <c r="J10" s="16" t="inlineStr">
-        <is>
-          <t>J | 418呎 (1房)
-$1,013万
-$24,241/呎
-(26年-06月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="11" ht="65" customHeight="1">
-      <c r="A11" s="2" t="inlineStr">
-        <is>
-          <t>35/F</t>
-        </is>
-      </c>
-      <c r="B11" s="16" t="inlineStr">
-        <is>
-          <t>A | 889呎 (3房)
-$3,131万
-$35,222/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="C11" s="16" t="inlineStr">
-        <is>
-          <t>B | 550呎 (2房)
-$1,919万
-$34,896/呎
-(26年-07月)</t>
-        </is>
-      </c>
-      <c r="D11" s="18" t="inlineStr">
-        <is>
-          <t>C | 550呎 (2房)
-$1,970万
-$35,809/呎
-(在售)</t>
-        </is>
-      </c>
-      <c r="E11" s="16" t="inlineStr">
-        <is>
-          <t>D | 546呎 (2房)
-$1,876万
-$34,351/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="F11" s="16" t="inlineStr">
-        <is>
-          <t>E | 695呎 (3房)
-$1,519万
-$21,855/呎
-(25年-06月)</t>
-        </is>
-      </c>
-      <c r="G11" s="16" t="inlineStr">
-        <is>
-          <t>F | 505呎 (2房)
-$1,388万
-$27,492/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="H11" s="16" t="inlineStr">
-        <is>
-          <t>G | 380呎 (1房)
-$807万
-$21,239/呎
-(25年-06月)</t>
-        </is>
-      </c>
-      <c r="I11" s="16" t="inlineStr">
-        <is>
-          <t>H | 379呎 (1房)
-$953万
-$25,149/呎
-(25年-05月)</t>
-        </is>
-      </c>
-      <c r="J11" s="16" t="inlineStr">
-        <is>
-          <t>J | 418呎 (1房)
-$1,010万
-$24,172/呎
-(26年-06月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="12" ht="65" customHeight="1">
-      <c r="A12" s="2" t="inlineStr">
-        <is>
-          <t>33/F</t>
-        </is>
-      </c>
-      <c r="B12" s="16" t="inlineStr">
-        <is>
-          <t>A | 889呎 (3房)
-$3,122万
-$35,122/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="C12" s="18" t="inlineStr">
-        <is>
-          <t>B | 550呎 (2房)
-$1,983万
-$36,060/呎
-(在售)</t>
-        </is>
-      </c>
-      <c r="D12" s="18" t="inlineStr">
-        <is>
-          <t>C | 550呎 (2房)
-$1,964万
-$35,707/呎
-(在售)</t>
-        </is>
-      </c>
-      <c r="E12" s="16" t="inlineStr">
-        <is>
-          <t>D | 546呎 (2房)
-$1,870万
-$34,250/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="F12" s="16" t="inlineStr">
-        <is>
-          <t>E | 695呎 (3房)
-$1,515万
-$21,792/呎
-(25年-06月)</t>
-        </is>
-      </c>
-      <c r="G12" s="16" t="inlineStr">
-        <is>
-          <t>F | 505呎 (2房)
-$1,370万
-$27,129/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="H12" s="16" t="inlineStr">
-        <is>
-          <t>G | 380呎 (1房)
-$1,071万
-$28,189/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="I12" s="16" t="inlineStr">
-        <is>
-          <t>H | 379呎 (1房)
-$1,020万
-$26,921/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="J12" s="18" t="inlineStr">
-        <is>
-          <t>J | 417呎 (1房)
-$1,107万
-$26,547/呎
-(在售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="13" ht="65" customHeight="1">
-      <c r="A13" s="2" t="inlineStr">
-        <is>
-          <t>32/F</t>
-        </is>
-      </c>
-      <c r="B13" s="16" t="inlineStr">
-        <is>
-          <t>A | 890呎 (3房)
-$2,907万
-$32,663/呎
-(25年-09月)</t>
-        </is>
-      </c>
-      <c r="C13" s="19" t="inlineStr">
-        <is>
-          <t>B | 550呎 (2房)
-$1,978万
-$35,955/呎
-(已定价未售)</t>
-        </is>
-      </c>
-      <c r="D13" s="16" t="inlineStr">
-        <is>
-          <t>C | 550呎 (2房)
-$1,860万
-$33,823/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="E13" s="16" t="inlineStr">
-        <is>
-          <t>D | 546呎 (2房)
-$1,865万
-$34,151/呎
-(26年-04月)</t>
-        </is>
-      </c>
-      <c r="F13" s="16" t="inlineStr">
-        <is>
-          <t>E | 695呎 (3房)
-$1,466万
-$21,091/呎
-(25年-06月)</t>
-        </is>
-      </c>
-      <c r="G13" s="16" t="inlineStr">
-        <is>
-          <t>F | 505呎 (2房)
-$1,380万
-$27,336/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="H13" s="16" t="inlineStr">
-        <is>
-          <t>G | 380呎 (1房)
-$1,025万
-$26,970/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="I13" s="16" t="inlineStr">
-        <is>
-          <t>H | 379呎 (1房)
-$1,028万
-$27,123/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="J13" s="16" t="inlineStr">
-        <is>
-          <t>J | 418呎 (1房)
-$1,004万
-$24,030/呎
-(26年-07月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="14" ht="65" customHeight="1">
-      <c r="A14" s="2" t="inlineStr">
-        <is>
-          <t>31/F</t>
-        </is>
-      </c>
-      <c r="B14" s="16" t="inlineStr">
-        <is>
-          <t>A | 890呎 (3房)
-$2,898万
-$32,564/呎
-(25年-12月)</t>
-        </is>
-      </c>
-      <c r="C14" s="19" t="inlineStr">
-        <is>
-          <t>B | 550呎 (2房)
-$1,972万
-$35,851/呎
-(已定价未售)</t>
-        </is>
-      </c>
-      <c r="D14" s="18" t="inlineStr">
-        <is>
-          <t>C | 550呎 (2房)
-$1,952万
-$35,500/呎
-(在售)</t>
-        </is>
-      </c>
-      <c r="E14" s="16" t="inlineStr">
-        <is>
-          <t>D | 546呎 (2房)
-$1,859万
-$34,052/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="F14" s="16" t="inlineStr">
-        <is>
-          <t>E | 695呎 (3房)
-$1,462万
-$21,030/呎
-(25年-06月)</t>
-        </is>
-      </c>
-      <c r="G14" s="16" t="inlineStr">
-        <is>
-          <t>F | 505呎 (2房)
-$1,355万
-$26,839/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="H14" s="16" t="inlineStr">
-        <is>
-          <t>G | 380呎 (1房)
-$1,038万
-$27,327/呎
-(21年-05月)</t>
-        </is>
-      </c>
-      <c r="I14" s="16" t="inlineStr">
-        <is>
-          <t>H | 379呎 (1房)
-$989万
-$26,101/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="J14" s="16" t="inlineStr">
-        <is>
-          <t>J | 418呎 (1房)
-$901万
-$21,559/呎
-(25年-12月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="15" ht="65" customHeight="1">
-      <c r="A15" s="2" t="inlineStr">
-        <is>
-          <t>30/F</t>
-        </is>
-      </c>
-      <c r="B15" s="16" t="inlineStr">
-        <is>
-          <t>A | 890呎 (3房)
-$2,916万
-$32,763/呎
-(24年-07月)</t>
-        </is>
-      </c>
-      <c r="C15" s="18" t="inlineStr">
-        <is>
-          <t>B | 550呎 (2房)
-$1,966万
-$35,747/呎
-(在售)</t>
-        </is>
-      </c>
-      <c r="D15" s="16" t="inlineStr">
-        <is>
-          <t>C | 550呎 (2房)
-$1,850万
-$33,628/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="E15" s="16" t="inlineStr">
-        <is>
-          <t>D | 546呎 (2房)
-$1,854万
-$33,951/呎
-(26年-02月)</t>
-        </is>
-      </c>
-      <c r="F15" s="16" t="inlineStr">
-        <is>
-          <t>E | 695呎 (3房)
-$1,457万
-$20,968/呎
-(25年-06月)</t>
-        </is>
-      </c>
-      <c r="G15" s="16" t="inlineStr">
-        <is>
-          <t>F | 505呎 (2房)
-$1,366万
-$27,043/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="H15" s="16" t="inlineStr">
-        <is>
-          <t>G | 380呎 (1房)
-$994万
-$26,145/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="I15" s="16" t="inlineStr">
-        <is>
-          <t>H | 379呎 (1房)
-$997万
-$26,300/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="J15" s="16" t="inlineStr">
-        <is>
-          <t>J | 418呎 (1房)
-$899万
-$21,496/呎
-(25年-12月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="16" ht="65" customHeight="1">
-      <c r="A16" s="2" t="inlineStr">
-        <is>
-          <t>29/F</t>
-        </is>
-      </c>
-      <c r="B16" s="16" t="inlineStr">
-        <is>
-          <t>A | 890呎 (3房)
-$2,916万
-$32,763/呎
-(26年-04月)</t>
-        </is>
-      </c>
-      <c r="C16" s="16" t="inlineStr">
-        <is>
-          <t>B | 550呎 (2房)
-$1,892万
-$34,394/呎
-(26年-07月)</t>
-        </is>
-      </c>
-      <c r="D16" s="18" t="inlineStr">
-        <is>
-          <t>C | 550呎 (2房)
-$1,941万
-$35,295/呎
-(在售)</t>
-        </is>
-      </c>
-      <c r="E16" s="16" t="inlineStr">
-        <is>
-          <t>D | 546呎 (2房)
-$1,848万
-$33,852/呎
-(25年-10月)</t>
-        </is>
-      </c>
-      <c r="F16" s="16" t="inlineStr">
-        <is>
-          <t>E | 695呎 (3房)
-$1,453万
-$20,908/呎
-(25年-06月)</t>
-        </is>
-      </c>
-      <c r="G16" s="16" t="inlineStr">
-        <is>
-          <t>F | 505呎 (2房)
-$1,348万
-$26,685/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="H16" s="16" t="inlineStr">
-        <is>
-          <t>G | 380呎 (1房)
-$1,001万
-$26,342/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="I16" s="16" t="inlineStr">
-        <is>
-          <t>H | 379呎 (1房)
-$984万
-$25,951/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="J16" s="16" t="inlineStr">
-        <is>
-          <t>J | 418呎 (1房)
-$896万
-$21,433/呎
-(25年-12月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="17" ht="65" customHeight="1">
-      <c r="A17" s="2" t="inlineStr">
-        <is>
-          <t>28/F</t>
-        </is>
-      </c>
-      <c r="B17" s="16" t="inlineStr">
-        <is>
-          <t>A | 889呎 (3房)
-$3,036万
-$34,145/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="C17" s="18" t="inlineStr">
-        <is>
-          <t>B | 550呎 (2房)
-$1,955万
-$35,538/呎
-(在售)</t>
-        </is>
-      </c>
-      <c r="D17" s="18" t="inlineStr">
-        <is>
-          <t>C | 550呎 (2房)
-$1,936万
-$35,193/呎
-(在售)</t>
-        </is>
-      </c>
-      <c r="E17" s="16" t="inlineStr">
-        <is>
-          <t>D | 546呎 (2房)
-$1,843万
-$33,751/呎
-(26年-05月)</t>
-        </is>
-      </c>
-      <c r="F17" s="16" t="inlineStr">
-        <is>
-          <t>E | 695呎 (3房)
-$1,449万
-$20,848/呎
-(25年-06月)</t>
-        </is>
-      </c>
-      <c r="G17" s="16" t="inlineStr">
-        <is>
-          <t>F | 505呎 (2房)
-$1,372万
-$27,168/呎
-(21年-05月)</t>
-        </is>
-      </c>
-      <c r="H17" s="16" t="inlineStr">
-        <is>
-          <t>G | 380呎 (1房)
-$998万
-$26,263/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="I17" s="16" t="inlineStr">
-        <is>
-          <t>H | 379呎 (1房)
-$1,001万
-$26,420/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="J17" s="16" t="inlineStr">
-        <is>
-          <t>J | 418呎 (1房)
-$893万
-$21,370/呎
-(25年-12月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="18" ht="65" customHeight="1">
-      <c r="A18" s="2" t="inlineStr">
-        <is>
-          <t>27/F</t>
-        </is>
-      </c>
-      <c r="B18" s="16" t="inlineStr">
-        <is>
-          <t>A | 890呎 (3房)
-$2,996万
-$33,665/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="C18" s="16" t="inlineStr">
-        <is>
-          <t>B | 550呎 (2房)
-$1,875万
-$34,094/呎
-(26年-07月)</t>
-        </is>
-      </c>
-      <c r="D18" s="18" t="inlineStr">
-        <is>
-          <t>C | 550呎 (2房)
-$1,924万
-$34,985/呎
-(在售)</t>
-        </is>
-      </c>
-      <c r="E18" s="16" t="inlineStr">
-        <is>
-          <t>D | 546呎 (2房)
-$1,832万
-$33,553/呎
-(26年-06月)</t>
-        </is>
-      </c>
-      <c r="F18" s="16" t="inlineStr">
-        <is>
-          <t>E | 695呎 (3房)
-$1,440万
-$20,725/呎
-(25年-06月)</t>
-        </is>
-      </c>
-      <c r="G18" s="16" t="inlineStr">
-        <is>
-          <t>F | 505呎 (2房)
-$1,336万
-$26,453/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="H18" s="16" t="inlineStr">
-        <is>
-          <t>G | 380呎 (1房)
-$992万
-$26,107/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="I18" s="16" t="inlineStr">
-        <is>
-          <t>H | 379呎 (1房)
-$985万
-$25,996/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="J18" s="16" t="inlineStr">
-        <is>
-          <t>J | 418呎 (1房)
-$888万
-$21,243/呎
-(25年-12月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="19" ht="65" customHeight="1">
-      <c r="A19" s="2" t="inlineStr">
-        <is>
-          <t>26/F</t>
-        </is>
-      </c>
-      <c r="B19" s="16" t="inlineStr">
-        <is>
-          <t>A | 889呎 (3房)
-$2,788万
-$31,363/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="C19" s="19" t="inlineStr">
-        <is>
-          <t>B | 550呎 (2房)
-$1,938万
-$35,227/呎
-(已定价未售)</t>
-        </is>
-      </c>
-      <c r="D19" s="16" t="inlineStr">
-        <is>
-          <t>C | 550呎 (2房)
-$1,823万
-$33,139/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="E19" s="16" t="inlineStr">
-        <is>
-          <t>D | 546呎 (2房)
-$1,826万
-$33,452/呎
-(26年-04月)</t>
-        </is>
-      </c>
-      <c r="F19" s="16" t="inlineStr">
-        <is>
-          <t>E | 695呎 (3房)
-$1,415万
-$20,358/呎
-(25年-06月)</t>
-        </is>
-      </c>
-      <c r="G19" s="16" t="inlineStr">
-        <is>
-          <t>F | 505呎 (2房)
-$1,346万
-$26,654/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="H19" s="16" t="inlineStr">
-        <is>
-          <t>G | 380呎 (1房)
-$989万
-$26,028/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="I19" s="16" t="inlineStr">
-        <is>
-          <t>H | 379呎 (1房)
-$993万
-$26,190/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="J19" s="16" t="inlineStr">
-        <is>
-          <t>J | 418呎 (1房)
-$885万
-$21,180/呎
-(25年-11月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="20" ht="65" customHeight="1">
-      <c r="A20" s="2" t="inlineStr">
-        <is>
-          <t>25/F</t>
-        </is>
-      </c>
-      <c r="B20" s="16" t="inlineStr">
-        <is>
-          <t>A | 889呎 (3房)
-$3,010万
-$33,857/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="C20" s="19" t="inlineStr">
-        <is>
-          <t>B | 550呎 (2房)
-$1,932万
-$35,124/呎
-(已定价未售)</t>
-        </is>
-      </c>
-      <c r="D20" s="18" t="inlineStr">
-        <is>
-          <t>C | 550呎 (2房)
-$1,913万
-$34,780/呎
-(在售)</t>
-        </is>
-      </c>
-      <c r="E20" s="16" t="inlineStr">
-        <is>
-          <t>D | 546呎 (2房)
-$1,841万
-$33,723/呎
-(26年-01月)</t>
-        </is>
-      </c>
-      <c r="F20" s="16" t="inlineStr">
-        <is>
-          <t>E | 695呎 (3房)
-$1,710万
-$24,604/呎
-(24年-12月)</t>
-        </is>
-      </c>
-      <c r="G20" s="16" t="inlineStr">
-        <is>
-          <t>F | 505呎 (2房)
-$1,328万
-$26,299/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="H20" s="16" t="inlineStr">
-        <is>
-          <t>G | 380呎 (1房)
-$976万
-$25,680/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="I20" s="16" t="inlineStr">
-        <is>
-          <t>H | 379呎 (1房)
-$1,000万
-$26,382/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="J20" s="16" t="inlineStr">
-        <is>
-          <t>J | 418呎 (1房)
-$883万
-$21,119/呎
-(25年-07月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="21" ht="65" customHeight="1">
-      <c r="A21" s="2" t="inlineStr">
-        <is>
-          <t>23/F</t>
-        </is>
-      </c>
-      <c r="B21" s="16" t="inlineStr">
-        <is>
-          <t>A | 889呎 (3房)
-$2,772万
-$31,178/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="C21" s="19" t="inlineStr">
-        <is>
-          <t>B | 550呎 (2房)
-$1,926万
-$35,018/呎
-(已定价未售)</t>
-        </is>
-      </c>
-      <c r="D21" s="18" t="inlineStr">
-        <is>
-          <t>C | 550呎 (2房)
-$1,907万
-$34,676/呎
-(在售)</t>
-        </is>
-      </c>
-      <c r="E21" s="16" t="inlineStr">
-        <is>
-          <t>D | 546呎 (2房)
-$1,836万
-$33,624/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="F21" s="16" t="inlineStr">
-        <is>
-          <t>E | 695呎 (3房)
-$1,929万
-$27,756/呎
-(24年-01月)</t>
-        </is>
-      </c>
-      <c r="G21" s="16" t="inlineStr">
-        <is>
-          <t>F | 505呎 (2房)
-$1,352万
-$26,774/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="H21" s="16" t="inlineStr">
-        <is>
-          <t>G | 380呎 (1房)
-$973万
-$25,605/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="I21" s="16" t="inlineStr">
-        <is>
-          <t>H | 379呎 (1房)
-$997万
-$26,305/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="J21" s="16" t="inlineStr">
-        <is>
-          <t>J | 418呎 (1房)
-$880万
-$21,054/呎
-(25年-12月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="22" ht="65" customHeight="1">
-      <c r="A22" s="2" t="inlineStr">
-        <is>
-          <t>22/F</t>
-        </is>
-      </c>
-      <c r="B22" s="16" t="inlineStr">
-        <is>
-          <t>A | 890呎 (3房)
-$2,936万
-$32,985/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="C22" s="19" t="inlineStr">
-        <is>
-          <t>B | 550呎 (2房)
-$1,920万
-$34,915/呎
-(已定价未售)</t>
-        </is>
-      </c>
-      <c r="D22" s="18" t="inlineStr">
-        <is>
-          <t>C | 550呎 (2房)
-$1,902万
-$34,575/呎
-(在售)</t>
-        </is>
-      </c>
-      <c r="E22" s="16" t="inlineStr">
-        <is>
-          <t>D | 546呎 (2房)
-$1,839万
-$33,676/呎
-(26年-06月)</t>
-        </is>
-      </c>
-      <c r="F22" s="16" t="inlineStr">
-        <is>
-          <t>E | 695呎 (3房)
-$1,865万
-$26,836/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="G22" s="16" t="inlineStr">
-        <is>
-          <t>F | 505呎 (2房)
-$1,320万
-$26,145/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="H22" s="16" t="inlineStr">
-        <is>
-          <t>G | 380呎 (1房)
-$970万
-$25,527/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="I22" s="16" t="inlineStr">
-        <is>
-          <t>H | 379呎 (1房)
-$974万
-$25,694/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="J22" s="16" t="inlineStr">
-        <is>
-          <t>J | 418呎 (1房)
-$877万
-$20,992/呎
-(25年-12月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="23" ht="65" customHeight="1">
-      <c r="A23" s="2" t="inlineStr">
-        <is>
-          <t>21/F</t>
-        </is>
-      </c>
-      <c r="B23" s="16" t="inlineStr">
-        <is>
-          <t>A | 890呎 (3房)
-$2,896万
-$32,544/呎
-(26年-02月)</t>
-        </is>
-      </c>
-      <c r="C23" s="19" t="inlineStr">
-        <is>
-          <t>B | 550呎 (2房)
-$1,915万
-$34,811/呎
-(已定价未售)</t>
-        </is>
-      </c>
-      <c r="D23" s="16" t="inlineStr">
-        <is>
-          <t>C | 550呎 (2房)
-$1,801万
-$32,747/呎
-(26年-06月)</t>
-        </is>
-      </c>
-      <c r="E23" s="16" t="inlineStr">
-        <is>
-          <t>D | 546呎 (2房)
-$1,853万
-$33,932/呎
-(25年-10月)</t>
-        </is>
-      </c>
-      <c r="F23" s="16" t="inlineStr">
-        <is>
-          <t>E | 696呎 (3房)
-$1,879万
-$26,996/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="G23" s="16" t="inlineStr">
-        <is>
-          <t>F | 505呎 (2房)
-$1,344万
-$26,616/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="H23" s="16" t="inlineStr">
-        <is>
-          <t>G | 380呎 (1房)
-$998万
-$26,254/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="I23" s="16" t="inlineStr">
-        <is>
-          <t>H | 379呎 (1房)
-$991万
-$26,152/呎
-(25年-10月)</t>
-        </is>
-      </c>
-      <c r="J23" s="16" t="inlineStr">
-        <is>
-          <t>J | 418呎 (1房)
-$885万
-$21,168/呎
-(25年-08月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="24" ht="65" customHeight="1">
-      <c r="A24" s="2" t="inlineStr">
-        <is>
-          <t>20/F</t>
-        </is>
-      </c>
-      <c r="B24" s="16" t="inlineStr">
-        <is>
-          <t>A | 890呎 (3房)
-$2,888万
-$32,446/呎
-(26年-04月)</t>
-        </is>
-      </c>
-      <c r="C24" s="19" t="inlineStr">
-        <is>
-          <t>B | 550呎 (2房)
-$1,909万
-$34,705/呎
-(已定价未售)</t>
-        </is>
-      </c>
-      <c r="D24" s="20" t="inlineStr">
-        <is>
-          <t>C | 550呎 (2房)
-$1,890万
-$34,369/呎
-(暂停销售)</t>
-        </is>
-      </c>
-      <c r="E24" s="16" t="inlineStr">
-        <is>
-          <t>D | 546呎 (2房)
-$1,791万
-$32,805/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="F24" s="16" t="inlineStr">
-        <is>
-          <t>E | 695呎 (3房)
-$1,893万
-$27,231/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="G24" s="16" t="inlineStr">
-        <is>
-          <t>F | 505呎 (2房)
-$1,333万
-$26,395/呎
-(21年-05月)</t>
-        </is>
-      </c>
-      <c r="H24" s="16" t="inlineStr">
-        <is>
-          <t>G | 380呎 (1房)
-$974万
-$25,639/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="I24" s="16" t="inlineStr">
-        <is>
-          <t>H | 379呎 (1房)
-$968万
-$25,542/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="J24" s="16" t="inlineStr">
-        <is>
-          <t>J | 418呎 (1房)
-$872万
-$20,866/呎
-(25年-07月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="25" ht="65" customHeight="1">
-      <c r="A25" s="2" t="inlineStr">
-        <is>
-          <t>19/F</t>
-        </is>
-      </c>
-      <c r="B25" s="16" t="inlineStr">
-        <is>
-          <t>A | 889呎 (3房)
-$2,795万
-$31,437/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="C25" s="19" t="inlineStr">
-        <is>
-          <t>B | 550呎 (2房)
-$1,903万
-$34,604/呎
-(已定价未售)</t>
-        </is>
-      </c>
-      <c r="D25" s="20" t="inlineStr">
-        <is>
-          <t>C | 550呎 (2房)
-$1,885万
-$34,265/呎
-(暂停销售)</t>
-        </is>
-      </c>
-      <c r="E25" s="16" t="inlineStr">
-        <is>
-          <t>D | 546呎 (2房)
-$1,767万
-$32,364/呎
-(26年-04月)</t>
-        </is>
-      </c>
-      <c r="F25" s="16" t="inlineStr">
-        <is>
-          <t>E | 696呎 (3房)
-$1,906万
-$27,389/呎
-(21年-05月)</t>
-        </is>
-      </c>
-      <c r="G25" s="16" t="inlineStr">
-        <is>
-          <t>F | 505呎 (2房)
-$1,315万
-$26,043/呎
-(23年-10月)</t>
-        </is>
-      </c>
-      <c r="H25" s="16" t="inlineStr">
-        <is>
-          <t>G | 380呎 (1房)
-$992万
-$26,094/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="I25" s="16" t="inlineStr">
-        <is>
-          <t>H | 379呎 (1房)
-$955万
-$25,201/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="J25" s="16" t="inlineStr">
-        <is>
-          <t>J | 418呎 (1房)
-$1,111万
-$26,570/呎
-(已售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="26" ht="65" customHeight="1">
-      <c r="A26" s="2" t="inlineStr">
-        <is>
-          <t>18/F</t>
-        </is>
-      </c>
-      <c r="B26" s="16" t="inlineStr">
-        <is>
-          <t>A | 889呎 (3房)
-$2,854万
-$32,098/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="C26" s="19" t="inlineStr">
-        <is>
-          <t>B | 550呎 (2房)
-$1,903万
-$34,604/呎
-(已定价未售)</t>
-        </is>
-      </c>
-      <c r="D26" s="20" t="inlineStr">
-        <is>
-          <t>C | 550呎 (2房)
-$1,885万
-$34,265/呎
-(暂停销售)</t>
-        </is>
-      </c>
-      <c r="E26" s="16" t="inlineStr">
-        <is>
-          <t>D | 546呎 (2房)
-$1,786万
-$32,705/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="F26" s="16" t="inlineStr">
-        <is>
-          <t>E | 695呎 (3房)
-$1,685万
-$24,242/呎
-(25年-04月)</t>
-        </is>
-      </c>
-      <c r="G26" s="16" t="inlineStr">
-        <is>
-          <t>F | 505呎 (2房)
-$1,329万
-$26,317/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="H26" s="16" t="inlineStr">
-        <is>
-          <t>G | 380呎 (1房)
-$971万
-$25,561/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="I26" s="16" t="inlineStr">
-        <is>
-          <t>H | 379呎 (1房)
-$985万
-$25,997/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="J26" s="16" t="inlineStr">
-        <is>
-          <t>J | 418呎 (1房)
-$869万
-$20,801/呎
-(25年-06月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="27" ht="65" customHeight="1">
-      <c r="A27" s="2" t="inlineStr">
-        <is>
-          <t>17/F</t>
-        </is>
-      </c>
-      <c r="B27" s="16" t="inlineStr">
-        <is>
-          <t>A | 890呎 (3房)
-$2,842万
-$31,933/呎
-(26年-04月)</t>
-        </is>
-      </c>
-      <c r="C27" s="19" t="inlineStr">
-        <is>
-          <t>B | 550呎 (2房)
-$1,898万
-$34,500/呎
-(已定价未售)</t>
-        </is>
-      </c>
-      <c r="D27" s="20" t="inlineStr">
-        <is>
-          <t>C | 550呎 (2房)
-$1,879万
-$34,162/呎
-(暂停销售)</t>
-        </is>
-      </c>
-      <c r="E27" s="16" t="inlineStr">
-        <is>
-          <t>D | 546呎 (2房)
-$1,762万
-$32,267/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="F27" s="16" t="inlineStr">
-        <is>
-          <t>E | 696呎 (3房)
-$1,862万
-$26,754/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="G27" s="16" t="inlineStr">
-        <is>
-          <t>F | 505呎 (2房)
-$1,325万
-$26,237/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="H27" s="16" t="inlineStr">
-        <is>
-          <t>G | 380呎 (1房)
-$989万
-$26,014/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="I27" s="16" t="inlineStr">
-        <is>
-          <t>H | 379呎 (1房)
-$962万
-$25,391/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="J27" s="16" t="inlineStr">
-        <is>
-          <t>J | 418呎 (1房)
-$867万
-$20,740/呎
-(25年-07月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="28" ht="65" customHeight="1">
-      <c r="A28" s="2" t="inlineStr">
-        <is>
-          <t>16/F</t>
-        </is>
-      </c>
-      <c r="B28" s="16" t="inlineStr">
-        <is>
-          <t>A | 890呎 (3房)
-$2,833万
-$31,837/呎
-(26年-05月)</t>
-        </is>
-      </c>
-      <c r="C28" s="19" t="inlineStr">
-        <is>
-          <t>B | 550呎 (2房)
-$1,892万
-$34,395/呎
-(已定价未售)</t>
-        </is>
-      </c>
-      <c r="D28" s="20" t="inlineStr">
-        <is>
-          <t>C | 550呎 (2房)
-$1,873万
-$34,060/呎
-(暂停销售)</t>
-        </is>
-      </c>
-      <c r="E28" s="16" t="inlineStr">
-        <is>
-          <t>D | 546呎 (2房)
-$1,775万
-$32,506/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="F28" s="16" t="inlineStr">
-        <is>
-          <t>E | 695呎 (3房)
-$1,809万
-$26,030/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="G28" s="16" t="inlineStr">
-        <is>
-          <t>F | 505呎 (2房)
-$1,275万
-$25,244/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="H28" s="16" t="inlineStr">
-        <is>
-          <t>G | 380呎 (1房)
-$975万
-$25,669/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="I28" s="16" t="inlineStr">
-        <is>
-          <t>H | 379呎 (1房)
-$959万
-$25,315/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="J28" s="16" t="inlineStr">
-        <is>
-          <t>J | 418呎 (1房)
-$899万
-$21,502/呎
-(25年-06月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="29" ht="65" customHeight="1">
-      <c r="A29" s="2" t="inlineStr">
-        <is>
-          <t>15/F</t>
-        </is>
-      </c>
-      <c r="B29" s="16" t="inlineStr">
-        <is>
-          <t>A | 890呎 (3房)
-$2,825万
-$31,741/呎
-(26年-06月)</t>
-        </is>
-      </c>
-      <c r="C29" s="19" t="inlineStr">
-        <is>
-          <t>B | 550呎 (2房)
-$1,886万
-$34,291/呎
-(已定价未售)</t>
-        </is>
-      </c>
-      <c r="D29" s="20" t="inlineStr">
-        <is>
-          <t>C | 550呎 (2房)
-$1,868万
-$33,956/呎
-(暂停销售)</t>
-        </is>
-      </c>
-      <c r="E29" s="16" t="inlineStr">
-        <is>
-          <t>D | 546呎 (2房)
-$1,788万
-$32,745/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="F29" s="16" t="inlineStr">
-        <is>
-          <t>E | 696呎 (3房)
-$1,823万
-$26,188/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="G29" s="16" t="inlineStr">
-        <is>
-          <t>F | 505呎 (2房)
-$1,284万
-$25,433/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="H29" s="16" t="inlineStr">
-        <is>
-          <t>G | 380呎 (1房)
-$962万
-$25,326/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="I29" s="16" t="inlineStr">
-        <is>
-          <t>H | 379呎 (1房)
-$966万
-$25,501/呎
-(26年-06月)</t>
-        </is>
-      </c>
-      <c r="J29" s="16" t="inlineStr">
-        <is>
-          <t>J | 418呎 (1房)
-$871万
-$20,848/呎
-(25年-06月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="30" ht="65" customHeight="1">
-      <c r="A30" s="2" t="inlineStr">
-        <is>
-          <t>12/F</t>
-        </is>
-      </c>
-      <c r="B30" s="16" t="inlineStr">
-        <is>
-          <t>A | 890呎 (3房)
-$2,905万
-$32,636/呎
-(26年-07月)</t>
-        </is>
-      </c>
-      <c r="C30" s="19" t="inlineStr">
-        <is>
-          <t>B | 550呎 (2房)
-$1,880万
-$34,187/呎
-(已定价未售)</t>
-        </is>
-      </c>
-      <c r="D30" s="20" t="inlineStr">
-        <is>
-          <t>C | 550呎 (2房)
-$1,862万
-$33,853/呎
-(暂停销售)</t>
-        </is>
-      </c>
-      <c r="E30" s="20" t="inlineStr">
-        <is>
-          <t>D | 546呎 (2房)
-$1,865万
-$34,159/呎
-(暂停销售)</t>
-        </is>
-      </c>
-      <c r="F30" s="16" t="inlineStr">
-        <is>
-          <t>E | 695呎 (3房)
-$1,684万
-$24,225/呎
-(24年-05月)</t>
-        </is>
-      </c>
-      <c r="G30" s="16" t="inlineStr">
-        <is>
-          <t>F | 505呎 (2房)
-$1,294万
-$25,619/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="H30" s="16" t="inlineStr">
-        <is>
-          <t>G | 380呎 (1房)
-$949万
-$24,985/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="I30" s="16" t="inlineStr">
-        <is>
-          <t>H | 379呎 (1房)
-$954万
-$25,163/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="J30" s="16" t="inlineStr">
-        <is>
-          <t>J | 418呎 (1房)
-$859万
-$20,552/呎
-(25年-07月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="31" ht="65" customHeight="1">
-      <c r="A31" s="2" t="inlineStr">
-        <is>
-          <t>10/F</t>
-        </is>
-      </c>
-      <c r="B31" s="18" t="inlineStr">
-        <is>
-          <t>A | 889呎 (3房)
-$2,934万
-$33,001/呎
-(在售)</t>
-        </is>
-      </c>
-      <c r="C31" s="19" t="inlineStr">
-        <is>
-          <t>B | 550呎 (2房)
-$1,852万
-$33,667/呎
-(已定价未售)</t>
-        </is>
-      </c>
-      <c r="D31" s="20" t="inlineStr">
-        <is>
-          <t>C | 550呎 (2房)
-$1,834万
-$33,338/呎
-(暂停销售)</t>
-        </is>
-      </c>
-      <c r="E31" s="16" t="inlineStr">
-        <is>
-          <t>D | 546呎 (2房)
-$1,693万
-$31,004/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="F31" s="16" t="inlineStr">
-        <is>
-          <t>E | 695呎 (3房)
-$1,866万
-$26,854/呎
-(24年-01月)</t>
-        </is>
-      </c>
-      <c r="G31" s="16" t="inlineStr">
-        <is>
-          <t>F | 505呎 (2房)
-$1,260万
-$24,941/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="H31" s="16" t="inlineStr">
-        <is>
-          <t>G | 380呎 (1房)
-$944万
-$24,830/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="I31" s="16" t="inlineStr">
-        <is>
-          <t>H | 379呎 (1房)
-$968万
-$25,532/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="J31" s="18" t="inlineStr">
-        <is>
-          <t>J | 417呎 (1房)
-$1,043万
-$25,002/呎
-(在售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="32" ht="65" customHeight="1">
-      <c r="A32" s="2" t="inlineStr">
-        <is>
-          <t>9/F</t>
-        </is>
-      </c>
-      <c r="B32" s="20" t="inlineStr">
-        <is>
-          <t>A | 889呎 (3房)
-$2,866万
-$32,241/呎
-(暂停销售)</t>
-        </is>
-      </c>
-      <c r="C32" s="19" t="inlineStr">
-        <is>
-          <t>B | 550呎 (2房)
-$1,846万
-$33,564/呎
-(已定价未售)</t>
-        </is>
-      </c>
-      <c r="D32" s="20" t="inlineStr">
-        <is>
-          <t>C | 550呎 (2房)
-$1,828万
-$33,236/呎
-(暂停销售)</t>
-        </is>
-      </c>
-      <c r="E32" s="16" t="inlineStr">
-        <is>
-          <t>D | 546呎 (2房)
-$1,723万
-$31,559/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="F32" s="16" t="inlineStr">
-        <is>
-          <t>E | 695呎 (3房)
-$1,644万
-$23,661/呎
-(24年-07月)</t>
-        </is>
-      </c>
-      <c r="G32" s="16" t="inlineStr">
-        <is>
-          <t>F | 505呎 (2房)
-$1,256万
-$24,866/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="H32" s="16" t="inlineStr">
-        <is>
-          <t>G | 380呎 (1房)
-$970万
-$25,534/呎
-(21年-05月)</t>
-        </is>
-      </c>
-      <c r="I32" s="16" t="inlineStr">
-        <is>
-          <t>H | 379呎 (1房)
-$965万
-$25,454/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="J32" s="16" t="inlineStr">
-        <is>
-          <t>J | 417呎 (1房)
-$1,077万
-$25,828/呎
-(已售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="33" ht="65" customHeight="1">
-      <c r="A33" s="2" t="inlineStr">
-        <is>
-          <t>8/F</t>
-        </is>
-      </c>
-      <c r="B33" s="20" t="inlineStr">
-        <is>
-          <t>A | 889呎 (3房)
-$2,866万
-$32,237/呎
-(暂停销售)</t>
-        </is>
-      </c>
-      <c r="C33" s="19" t="inlineStr">
-        <is>
-          <t>B | 550呎 (2房)
-$1,846万
-$33,564/呎
-(已定价未售)</t>
-        </is>
-      </c>
-      <c r="D33" s="20" t="inlineStr">
-        <is>
-          <t>C | 550呎 (2房)
-$1,828万
-$33,236/呎
-(暂停销售)</t>
-        </is>
-      </c>
-      <c r="E33" s="20" t="inlineStr">
-        <is>
-          <t>D | 546呎 (2房)
-$1,831万
-$33,529/呎
-(暂停销售)</t>
-        </is>
-      </c>
-      <c r="F33" s="16" t="inlineStr">
-        <is>
-          <t>E | 695呎 (3房)
-$1,357万
-$19,521/呎
-(25年-06月)</t>
-        </is>
-      </c>
-      <c r="G33" s="16" t="inlineStr">
-        <is>
-          <t>F | 505呎 (2房)
-$1,295万
-$25,651/呎
-(21年-05月)</t>
-        </is>
-      </c>
-      <c r="H33" s="16" t="inlineStr">
-        <is>
-          <t>G | 380呎 (1房)
-$950万
-$25,013/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="I33" s="16" t="inlineStr">
-        <is>
-          <t>H | 379呎 (1房)
-$965万
-$25,454/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="J33" s="16" t="inlineStr">
-        <is>
-          <t>J | 418呎 (1房)
-$1,088万
-$26,034/呎
-(已售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="34" ht="65" customHeight="1">
-      <c r="A34" s="2" t="inlineStr">
-        <is>
-          <t>7/F</t>
-        </is>
-      </c>
-      <c r="B34" s="19" t="inlineStr">
-        <is>
-          <t>A | 889呎 (3房)
-$2,859万
-$32,156/呎
-(已定价未售)</t>
-        </is>
-      </c>
-      <c r="C34" s="19" t="inlineStr">
-        <is>
-          <t>B | 550呎 (2房)
-$1,840万
-$33,458/呎
-(已定价未售)</t>
-        </is>
-      </c>
-      <c r="D34" s="20" t="inlineStr">
-        <is>
-          <t>C | 550呎 (2房)
-$1,822万
-$33,133/呎
-(暂停销售)</t>
-        </is>
-      </c>
-      <c r="E34" s="20" t="inlineStr">
-        <is>
-          <t>D | 546呎 (2房)
-$1,825万
-$33,423/呎
-(暂停销售)</t>
-        </is>
-      </c>
-      <c r="F34" s="16" t="inlineStr">
-        <is>
-          <t>E | 695呎 (3房)
-$1,639万
-$23,588/呎
-(24年-05月)</t>
-        </is>
-      </c>
-      <c r="G34" s="16" t="inlineStr">
-        <is>
-          <t>F | 505呎 (2房)
-$1,252万
-$24,788/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="H34" s="16" t="inlineStr">
-        <is>
-          <t>G | 380呎 (1房)
-$967万
-$25,454/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="I34" s="16" t="inlineStr">
-        <is>
-          <t>H | 379呎 (1房)
-$972万
-$25,635/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="J34" s="16" t="inlineStr">
-        <is>
-          <t>J | 418呎 (1房)
-$832万
-$19,899/呎
-(25年-07月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="35" ht="65" customHeight="1">
-      <c r="A35" s="2" t="inlineStr">
-        <is>
-          <t>6/F</t>
-        </is>
-      </c>
-      <c r="B35" s="19" t="inlineStr">
-        <is>
-          <t>A | 889呎 (3房)
-$2,850万
-$32,057/呎
-(已定价未售)</t>
-        </is>
-      </c>
-      <c r="C35" s="19" t="inlineStr">
-        <is>
-          <t>B | 550呎 (2房)
-$1,834万
-$33,355/呎
-(已定价未售)</t>
-        </is>
-      </c>
-      <c r="D35" s="19" t="inlineStr">
-        <is>
-          <t>C | 550呎 (2房)
-$1,817万
-$33,029/呎
-(已定价未售)</t>
-        </is>
-      </c>
-      <c r="E35" s="20" t="inlineStr">
-        <is>
-          <t>D | 546呎 (2房)
-$1,783万
-$32,661/呎
-(暂停销售)</t>
-        </is>
-      </c>
-      <c r="F35" s="16" t="inlineStr">
-        <is>
-          <t>E | 695呎 (3房)
-$1,849万
-$26,610/呎
-(24年-04月)</t>
-        </is>
-      </c>
-      <c r="G35" s="16" t="inlineStr">
-        <is>
-          <t>F | 505呎 (2房)
-$1,240万
-$24,563/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="H35" s="16" t="inlineStr">
-        <is>
-          <t>G | 380呎 (1房)
-$929万
-$24,442/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="I35" s="16" t="inlineStr">
-        <is>
-          <t>H | 379呎 (1房)
-$953万
-$25,151/呎
-(21年-05月)</t>
-        </is>
-      </c>
-      <c r="J35" s="16" t="inlineStr">
-        <is>
-          <t>J | 418呎 (1房)
-$824万
-$19,711/呎
-(25年-08月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="36" ht="65" customHeight="1">
-      <c r="A36" s="2" t="inlineStr">
-        <is>
-          <t>5/F</t>
-        </is>
-      </c>
-      <c r="B36" s="19" t="inlineStr">
-        <is>
-          <t>A | 889呎 (3房)
-$2,841万
-$31,956/呎
-(已定价未售)</t>
-        </is>
-      </c>
-      <c r="C36" s="19" t="inlineStr">
-        <is>
-          <t>B | 550呎 (2房)
-$1,829万
-$33,251/呎
-(已定价未售)</t>
-        </is>
-      </c>
-      <c r="D36" s="19" t="inlineStr">
-        <is>
-          <t>C | 550呎 (2房)
-$1,811万
-$32,927/呎
-(已定价未售)</t>
-        </is>
-      </c>
-      <c r="E36" s="20" t="inlineStr">
-        <is>
-          <t>D | 546呎 (2房)
-$1,778万
-$32,557/呎
-(暂停销售)</t>
-        </is>
-      </c>
-      <c r="F36" s="16" t="inlineStr">
-        <is>
-          <t>E | 695呎 (3房)
-$1,364万
-$19,633/呎
-(25年-06月)</t>
-        </is>
-      </c>
-      <c r="G36" s="16" t="inlineStr">
-        <is>
-          <t>F | 505呎 (2房)
-$1,279万
-$25,328/呎
-(24年-02月)</t>
-        </is>
-      </c>
-      <c r="H36" s="16" t="inlineStr">
-        <is>
-          <t>G | 380呎 (1房)
-$988万
-$25,996/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="I36" s="16" t="inlineStr">
-        <is>
-          <t>H | 379呎 (1房)
-$973万
-$25,665/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="J36" s="16" t="inlineStr">
-        <is>
-          <t>J | 418呎 (1房)
-$840万
-$20,089/呎
-(25年-06月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="37" ht="65" customHeight="1">
-      <c r="A37" s="2" t="inlineStr">
-        <is>
-          <t>3/F</t>
-        </is>
-      </c>
-      <c r="B37" s="19" t="inlineStr">
-        <is>
-          <t>A | 889呎 (3房)
-$2,823万
-$31,757/呎
-(已定价未售)</t>
-        </is>
-      </c>
-      <c r="C37" s="19" t="inlineStr">
-        <is>
-          <t>B | 550呎 (2房)
-$1,817万
-$33,044/呎
-(已定价未售)</t>
-        </is>
-      </c>
-      <c r="D37" s="19" t="inlineStr">
-        <is>
-          <t>C | 550呎 (2房)
-$1,800万
-$32,720/呎
-(已定价未售)</t>
-        </is>
-      </c>
-      <c r="E37" s="20" t="inlineStr">
-        <is>
-          <t>D | 546呎 (2房)
-$1,766万
-$32,352/呎
-(暂停销售)</t>
-        </is>
-      </c>
-      <c r="F37" s="16" t="inlineStr">
-        <is>
-          <t>E | 695呎 (3房)
-$1,387万
-$19,958/呎
-(25年-06月)</t>
-        </is>
-      </c>
-      <c r="G37" s="16" t="inlineStr">
-        <is>
-          <t>F | 505呎 (2房)
-$1,315万
-$26,047/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="H37" s="16" t="inlineStr">
-        <is>
-          <t>G | 380呎 (1房)
-$965万
-$25,384/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="I37" s="16" t="inlineStr">
-        <is>
-          <t>H | 379呎 (1房)
-$960万
-$25,322/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="J37" s="16" t="inlineStr">
-        <is>
-          <t>J | 418呎 (1房)
-$814万
-$19,468/呎
-(25年-08月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="38" ht="65" customHeight="1">
-      <c r="A38" s="2" t="inlineStr">
-        <is>
-          <t>2/F</t>
-        </is>
-      </c>
-      <c r="B38" s="19" t="inlineStr">
-        <is>
-          <t>A | 889呎 (3房)
-$2,796万
-$31,457/呎
-(已定价未售)</t>
-        </is>
-      </c>
-      <c r="C38" s="19" t="inlineStr">
-        <is>
-          <t>B | 550呎 (2房)
-$1,800万
-$32,731/呎
-(已定价未售)</t>
-        </is>
-      </c>
-      <c r="D38" s="19" t="inlineStr">
-        <is>
-          <t>C | 550呎 (2房)
-$1,783万
-$32,413/呎
-(已定价未售)</t>
-        </is>
-      </c>
-      <c r="E38" s="20" t="inlineStr">
-        <is>
-          <t>D | 546呎 (2房)
-$1,750万
-$32,042/呎
-(暂停销售)</t>
-        </is>
-      </c>
-      <c r="F38" s="16" t="inlineStr">
-        <is>
-          <t>E | 695呎 (3房)
-$1,371万
-$19,722/呎
-(25年-06月)</t>
-        </is>
-      </c>
-      <c r="G38" s="16" t="inlineStr">
-        <is>
-          <t>F | 505呎 (2房)
-$1,280万
-$25,355/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="H38" s="16" t="inlineStr">
-        <is>
-          <t>G | 380呎 (1房)
-$948万
-$24,957/呎
-(25年-08月)</t>
-        </is>
-      </c>
-      <c r="I38" s="16" t="inlineStr">
-        <is>
-          <t>H | 379呎 (1房)
-$984万
-$25,951/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="J38" s="16" t="inlineStr">
-        <is>
-          <t>J | 418呎 (1房)
-$809万
-$19,344/呎
-(25年-08月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="39" ht="65" customHeight="1">
-      <c r="A39" s="2" t="inlineStr">
-        <is>
-          <t>1/F</t>
-        </is>
-      </c>
-      <c r="B39" s="17" t="inlineStr"/>
-      <c r="C39" s="17" t="inlineStr"/>
-      <c r="D39" s="17" t="inlineStr"/>
-      <c r="E39" s="17" t="inlineStr"/>
-      <c r="F39" s="16" t="inlineStr">
-        <is>
-          <t>E | 705呎 (3房)
-$1,357万
-$19,241/呎
-(25年-06月)</t>
-        </is>
-      </c>
-      <c r="G39" s="16" t="inlineStr">
-        <is>
-          <t>F | 505呎 (2房)
-$1,312万
-$25,985/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="H39" s="16" t="inlineStr">
-        <is>
-          <t>G | 380呎 (1房)
-$952万
-$25,058/呎
-(23年-12月)</t>
-        </is>
-      </c>
-      <c r="I39" s="16" t="inlineStr">
-        <is>
-          <t>H | 379呎 (1房)
-$938万
-$24,747/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="J39" s="16" t="inlineStr">
-        <is>
-          <t>J | 418呎 (1房)
-$817万
-$19,552/呎
-(25年-07月)</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="A1:J1"/>
-  </mergeCells>
-  <pageMargins left="0.25" right="0.25" top="0.25" bottom="0.25" header="0.1" footer="0.1"/>
-  <pageSetup orientation="landscape" paperSize="9" fitToHeight="1" fitToWidth="1"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr fitToPage="1"/>
-  </sheetPr>
-  <dimension ref="A1:I11"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="12" customWidth="1" min="1" max="1"/>
-    <col width="18" customWidth="1" min="2" max="2"/>
-    <col width="18" customWidth="1" min="3" max="3"/>
-    <col width="18" customWidth="1" min="4" max="4"/>
-    <col width="18" customWidth="1" min="5" max="5"/>
-    <col width="18" customWidth="1" min="6" max="6"/>
-    <col width="18" customWidth="1" min="7" max="7"/>
-    <col width="18" customWidth="1" min="8" max="8"/>
-    <col width="18" customWidth="1" min="9" max="9"/>
-  </cols>
-  <sheetData>
-    <row r="1" ht="40" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>The Henley I - 低座A座 销控网格图</t>
-        </is>
-      </c>
-    </row>
-    <row r="2" ht="20" customHeight="1">
-      <c r="A2" s="6" t="inlineStr">
-        <is>
-          <t>总套数</t>
-        </is>
-      </c>
-      <c r="B2" s="7" t="inlineStr">
-        <is>
-          <t>在售 (Sale)</t>
-        </is>
-      </c>
-      <c r="C2" s="8" t="inlineStr">
-        <is>
-          <t>已定价未售</t>
-        </is>
-      </c>
-      <c r="D2" s="9" t="inlineStr">
-        <is>
-          <t>已售 (Sold)</t>
-        </is>
-      </c>
-      <c r="E2" s="10" t="inlineStr">
-        <is>
-          <t>暂停销售</t>
-        </is>
-      </c>
-      <c r="F2" s="6" t="inlineStr">
-        <is>
-          <t>待售 (Pending)</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="25" customHeight="1">
-      <c r="A3" s="11" t="inlineStr">
-        <is>
-          <t>45 套</t>
-        </is>
-      </c>
-      <c r="B3" s="12" t="inlineStr">
-        <is>
-          <t>0 套</t>
-        </is>
-      </c>
-      <c r="C3" s="13" t="inlineStr">
-        <is>
-          <t>0 套</t>
-        </is>
-      </c>
-      <c r="D3" s="14" t="inlineStr">
-        <is>
-          <t>45 套</t>
-        </is>
-      </c>
-      <c r="E3" s="15" t="inlineStr">
-        <is>
-          <t>0 套</t>
-        </is>
-      </c>
-      <c r="F3" s="11" t="inlineStr">
-        <is>
-          <t>0 套</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="25" customHeight="1">
-      <c r="A5" s="2" t="inlineStr">
-        <is>
-          <t>楼层\房号</t>
-        </is>
-      </c>
-      <c r="B5" s="2" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>D</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>E</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>F</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>G</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>H</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="65" customHeight="1">
-      <c r="A6" s="2" t="inlineStr">
-        <is>
-          <t>6/F</t>
-        </is>
-      </c>
-      <c r="B6" s="16" t="inlineStr">
-        <is>
-          <t>A | 320呎 (1房)
-$876万
-$27,366/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="C6" s="16" t="inlineStr">
-        <is>
-          <t>B | 296呎 (1房)
-$819万
-$27,653/呎
-(21年-05月)</t>
-        </is>
-      </c>
-      <c r="D6" s="16" t="inlineStr">
-        <is>
-          <t>C | 321呎 (1房)
-$870万
-$27,098/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="E6" s="16" t="inlineStr">
-        <is>
-          <t>D | 331呎 (1房)
-$878万
-$26,537/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="F6" s="16" t="inlineStr">
-        <is>
-          <t>E | 301呎 (1房)
-$810万
-$26,915/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="G6" s="16" t="inlineStr">
-        <is>
-          <t>F | 301呎 (1房)
-$835万
-$27,749/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="H6" s="16" t="inlineStr">
-        <is>
-          <t>G | 208呎 (开放式)
-$595万
-$28,614/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="I6" s="16" t="inlineStr">
-        <is>
-          <t>H | 216呎 (开放式)
-$627万
-$29,040/呎
-(已售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="65" customHeight="1">
-      <c r="A7" s="2" t="inlineStr">
-        <is>
-          <t>5/F</t>
-        </is>
-      </c>
-      <c r="B7" s="16" t="inlineStr">
-        <is>
-          <t>A | 320呎 (1房)
-$856万
-$26,757/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="C7" s="16" t="inlineStr">
-        <is>
-          <t>B | 296呎 (1房)
-$776万
-$26,228/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="D7" s="16" t="inlineStr">
-        <is>
-          <t>C | 321呎 (1房)
-$860万
-$26,780/呎
-(21年-05月)</t>
-        </is>
-      </c>
-      <c r="E7" s="16" t="inlineStr">
-        <is>
-          <t>D | 330呎 (1房)
-$886万
-$26,851/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="F7" s="16" t="inlineStr">
-        <is>
-          <t>E | 301呎 (1房)
-$817万
-$27,147/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="G7" s="16" t="inlineStr">
-        <is>
-          <t>F | 302呎 (1房)
-$817万
-$27,047/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="H7" s="16" t="inlineStr">
-        <is>
-          <t>G | 208呎 (开放式)
-$607万
-$29,183/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="I7" s="16" t="inlineStr">
-        <is>
-          <t>H | 216呎 (开放式)
-$620万
-$28,702/呎
-(已售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="8" ht="65" customHeight="1">
-      <c r="A8" s="2" t="inlineStr">
-        <is>
-          <t>3/F</t>
-        </is>
-      </c>
-      <c r="B8" s="16" t="inlineStr">
-        <is>
-          <t>A | 320呎 (1房)
-$857万
-$26,793/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="C8" s="16" t="inlineStr">
-        <is>
-          <t>B | 296呎 (1房)
-$769万
-$25,993/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="D8" s="16" t="inlineStr">
-        <is>
-          <t>C | 321呎 (1房)
-$835万
-$25,998/呎
-(21年-05月)</t>
-        </is>
-      </c>
-      <c r="E8" s="16" t="inlineStr">
-        <is>
-          <t>D | 330呎 (1房)
-$869万
-$26,336/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="F8" s="16" t="inlineStr">
-        <is>
-          <t>E | 302呎 (1房)
-$810万
-$26,814/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="G8" s="16" t="inlineStr">
-        <is>
-          <t>F | 302呎 (1房)
-$818万
-$27,083/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="H8" s="16" t="inlineStr">
-        <is>
-          <t>G | 208呎 (开放式)
-$600万
-$28,826/呎
-(21年-06月)</t>
-        </is>
-      </c>
-      <c r="I8" s="16" t="inlineStr">
-        <is>
-          <t>H | 216呎 (开放式)
-$627万
-$29,041/呎
-(已售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="9" ht="65" customHeight="1">
-      <c r="A9" s="2" t="inlineStr">
-        <is>
-          <t>2/F</t>
-        </is>
-      </c>
-      <c r="B9" s="16" t="inlineStr">
-        <is>
-          <t>A | 320呎 (1房)
-$841万
-$26,270/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="C9" s="16" t="inlineStr">
-        <is>
-          <t>B | 296呎 (1房)
-$771万
-$26,033/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="D9" s="16" t="inlineStr">
-        <is>
-          <t>C | 321呎 (1房)
-$844万
-$26,301/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="E9" s="16" t="inlineStr">
-        <is>
-          <t>D | 331呎 (1房)
-$861万
-$26,018/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="F9" s="16" t="inlineStr">
-        <is>
-          <t>E | 301呎 (1房)
-$802万
-$26,655/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="G9" s="16" t="inlineStr">
-        <is>
-          <t>F | 301呎 (1房)
-$794万
-$26,373/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="H9" s="16" t="inlineStr">
-        <is>
-          <t>G | 208呎 (开放式)
-$578万
-$27,797/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="I9" s="16" t="inlineStr">
-        <is>
-          <t>H | 216呎 (开放式)
-$615万
-$28,489/呎
-(已售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="10" ht="65" customHeight="1">
-      <c r="A10" s="2" t="inlineStr">
-        <is>
-          <t>1/F</t>
-        </is>
-      </c>
-      <c r="B10" s="16" t="inlineStr">
-        <is>
-          <t>A | 299呎 (1房)
-$862万
-$28,823/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="C10" s="16" t="inlineStr">
-        <is>
-          <t>B | 272呎 (1房)
-$967万
-$35,561/呎
-(21年-05月)</t>
-        </is>
-      </c>
-      <c r="D10" s="16" t="inlineStr">
-        <is>
-          <t>C | 299呎 (1房)
-$823万
-$27,535/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="E10" s="16" t="inlineStr">
-        <is>
-          <t>D | 330呎 (1房)
-$844万
-$25,587/呎
-(21年-07月)</t>
-        </is>
-      </c>
-      <c r="F10" s="16" t="inlineStr">
-        <is>
-          <t>E | 302呎 (1房)
-$779万
-$25,786/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="G10" s="16" t="inlineStr">
-        <is>
-          <t>F | 302呎 (1房)
-$803万
-$26,586/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="H10" s="16" t="inlineStr">
-        <is>
-          <t>G | 208呎 (开放式)
-$573万
-$27,554/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="I10" s="16" t="inlineStr">
-        <is>
-          <t>H | 216呎 (开放式)
-$597万
-$27,651/呎
-(已售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="11" ht="65" customHeight="1">
-      <c r="A11" s="2" t="inlineStr">
-        <is>
-          <t>G/F</t>
-        </is>
-      </c>
-      <c r="B11" s="17" t="inlineStr"/>
-      <c r="C11" s="17" t="inlineStr"/>
-      <c r="D11" s="17" t="inlineStr"/>
-      <c r="E11" s="16" t="inlineStr">
-        <is>
-          <t>D | 309呎 (1房)
-$995万
-$32,200/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="F11" s="16" t="inlineStr">
-        <is>
-          <t>E | 280呎 (1房)
-$920万
-$32,858/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="G11" s="16" t="inlineStr">
-        <is>
-          <t>F | 280呎 (1房)
-$910万
-$32,510/呎
-(25年-08月)</t>
-        </is>
-      </c>
-      <c r="H11" s="16" t="inlineStr">
-        <is>
-          <t>G | 186呎 (开放式)
-$682万
-$36,655/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="I11" s="16" t="inlineStr">
-        <is>
-          <t>H | 195呎 (开放式)
-$567万
-$29,100/呎
-(26年-02月)</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="A1:I1"/>
-  </mergeCells>
-  <pageMargins left="0.25" right="0.25" top="0.25" bottom="0.25" header="0.1" footer="0.1"/>
-  <pageSetup orientation="landscape" paperSize="9" fitToHeight="1" fitToWidth="1"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr fitToPage="1"/>
-  </sheetPr>
-  <dimension ref="A1:I11"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="12" customWidth="1" min="1" max="1"/>
-    <col width="18" customWidth="1" min="2" max="2"/>
-    <col width="18" customWidth="1" min="3" max="3"/>
-    <col width="18" customWidth="1" min="4" max="4"/>
-    <col width="18" customWidth="1" min="5" max="5"/>
-    <col width="18" customWidth="1" min="6" max="6"/>
-    <col width="18" customWidth="1" min="7" max="7"/>
-    <col width="18" customWidth="1" min="8" max="8"/>
-    <col width="18" customWidth="1" min="9" max="9"/>
-  </cols>
-  <sheetData>
-    <row r="1" ht="40" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>The Henley I - 低座B座 销控网格图</t>
-        </is>
-      </c>
-    </row>
-    <row r="2" ht="20" customHeight="1">
-      <c r="A2" s="6" t="inlineStr">
-        <is>
-          <t>总套数</t>
-        </is>
-      </c>
-      <c r="B2" s="7" t="inlineStr">
-        <is>
-          <t>在售 (Sale)</t>
-        </is>
-      </c>
-      <c r="C2" s="8" t="inlineStr">
-        <is>
-          <t>已定价未售</t>
-        </is>
-      </c>
-      <c r="D2" s="9" t="inlineStr">
-        <is>
-          <t>已售 (Sold)</t>
-        </is>
-      </c>
-      <c r="E2" s="10" t="inlineStr">
-        <is>
-          <t>暂停销售</t>
-        </is>
-      </c>
-      <c r="F2" s="6" t="inlineStr">
-        <is>
-          <t>待售 (Pending)</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="25" customHeight="1">
-      <c r="A3" s="11" t="inlineStr">
-        <is>
-          <t>45 套</t>
-        </is>
-      </c>
-      <c r="B3" s="12" t="inlineStr">
-        <is>
-          <t>0 套</t>
-        </is>
-      </c>
-      <c r="C3" s="13" t="inlineStr">
-        <is>
-          <t>0 套</t>
-        </is>
-      </c>
-      <c r="D3" s="14" t="inlineStr">
-        <is>
-          <t>45 套</t>
-        </is>
-      </c>
-      <c r="E3" s="15" t="inlineStr">
-        <is>
-          <t>0 套</t>
-        </is>
-      </c>
-      <c r="F3" s="11" t="inlineStr">
-        <is>
-          <t>0 套</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="25" customHeight="1">
-      <c r="A5" s="2" t="inlineStr">
-        <is>
-          <t>楼层\房号</t>
-        </is>
-      </c>
-      <c r="B5" s="2" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>D</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>E</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>F</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>G</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>H</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="65" customHeight="1">
-      <c r="A6" s="2" t="inlineStr">
-        <is>
-          <t>6/F</t>
-        </is>
-      </c>
-      <c r="B6" s="16" t="inlineStr">
-        <is>
-          <t>A | 320呎 (1房)
-$899万
-$28,107/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="C6" s="16" t="inlineStr">
-        <is>
-          <t>B | 296呎 (1房)
-$815万
-$27,545/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="D6" s="16" t="inlineStr">
-        <is>
-          <t>C | 321呎 (1房)
-$873万
-$27,204/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="E6" s="16" t="inlineStr">
-        <is>
-          <t>D | 330呎 (1房)
-$701万
-$21,238/呎
-(25年-07月)</t>
-        </is>
-      </c>
-      <c r="F6" s="16" t="inlineStr">
-        <is>
-          <t>E | 301呎 (1房)
-$825万
-$27,414/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="G6" s="16" t="inlineStr">
-        <is>
-          <t>F | 301呎 (1房)
-$834万
-$27,703/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="H6" s="16" t="inlineStr">
-        <is>
-          <t>G | 208呎 (开放式)
-$613万
-$29,473/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="I6" s="16" t="inlineStr">
-        <is>
-          <t>H | 216呎 (开放式)
-$645万
-$29,867/呎
-(已售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="65" customHeight="1">
-      <c r="A7" s="2" t="inlineStr">
-        <is>
-          <t>5/F</t>
-        </is>
-      </c>
-      <c r="B7" s="16" t="inlineStr">
-        <is>
-          <t>A | 320呎 (1房)
-$879万
-$27,482/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="C7" s="16" t="inlineStr">
-        <is>
-          <t>B | 296呎 (1房)
-$806万
-$27,224/呎
-(25年-09月)</t>
-        </is>
-      </c>
-      <c r="D7" s="16" t="inlineStr">
-        <is>
-          <t>C | 321呎 (1房)
-$890万
-$27,733/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="E7" s="16" t="inlineStr">
-        <is>
-          <t>D | 330呎 (1房)
-$692万
-$20,984/呎
-(25年-07月)</t>
-        </is>
-      </c>
-      <c r="F7" s="16" t="inlineStr">
-        <is>
-          <t>E | 302呎 (1房)
-$824万
-$27,283/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="G7" s="16" t="inlineStr">
-        <is>
-          <t>F | 301呎 (1房)
-$841万
-$27,945/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="H7" s="16" t="inlineStr">
-        <is>
-          <t>G | 208呎 (开放式)
-$593万
-$28,518/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="I7" s="16" t="inlineStr">
-        <is>
-          <t>H | 216呎 (开放式)
-$644万
-$29,824/呎
-(已售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="8" ht="65" customHeight="1">
-      <c r="A8" s="2" t="inlineStr">
-        <is>
-          <t>3/F</t>
-        </is>
-      </c>
-      <c r="B8" s="16" t="inlineStr">
-        <is>
-          <t>A | 320呎 (1房)
-$872万
-$27,235/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="C8" s="16" t="inlineStr">
-        <is>
-          <t>B | 296呎 (1房)
-$799万
-$26,984/呎
-(21年-05月)</t>
-        </is>
-      </c>
-      <c r="D8" s="16" t="inlineStr">
-        <is>
-          <t>C | 321呎 (1房)
-$882万
-$27,489/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="E8" s="16" t="inlineStr">
-        <is>
-          <t>D | 330呎 (1房)
-$698万
-$21,152/呎
-(25年-06月)</t>
-        </is>
-      </c>
-      <c r="F8" s="16" t="inlineStr">
-        <is>
-          <t>E | 302呎 (1房)
-$808万
-$26,757/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="G8" s="16" t="inlineStr">
-        <is>
-          <t>F | 301呎 (1房)
-$817万
-$27,129/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="H8" s="16" t="inlineStr">
-        <is>
-          <t>G | 208呎 (开放式)
-$588万
-$28,258/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="I8" s="16" t="inlineStr">
-        <is>
-          <t>H | 216呎 (开放式)
-$632万
-$29,268/呎
-(已售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="9" ht="65" customHeight="1">
-      <c r="A9" s="2" t="inlineStr">
-        <is>
-          <t>2/F</t>
-        </is>
-      </c>
-      <c r="B9" s="16" t="inlineStr">
-        <is>
-          <t>A | 320呎 (1房)
-$891万
-$27,838/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="C9" s="16" t="inlineStr">
-        <is>
-          <t>B | 296呎 (1房)
-$808万
-$27,301/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="D9" s="16" t="inlineStr">
-        <is>
-          <t>C | 321呎 (1房)
-$848万
-$26,407/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="E9" s="16" t="inlineStr">
-        <is>
-          <t>D | 330呎 (1房)
-$680万
-$20,608/呎
-(25年-06月)</t>
-        </is>
-      </c>
-      <c r="F9" s="16" t="inlineStr">
-        <is>
-          <t>E | 302呎 (1房)
-$826万
-$27,349/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="G9" s="16" t="inlineStr">
-        <is>
-          <t>F | 301呎 (1房)
-$809万
-$26,880/呎
-(24年-10月)</t>
-        </is>
-      </c>
-      <c r="H9" s="16" t="inlineStr">
-        <is>
-          <t>G | 208呎 (开放式)
-$601万
-$28,886/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="I9" s="16" t="inlineStr">
-        <is>
-          <t>H | 216呎 (开放式)
-$627万
-$29,010/呎
-(已售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="10" ht="65" customHeight="1">
-      <c r="A10" s="2" t="inlineStr">
-        <is>
-          <t>1/F</t>
-        </is>
-      </c>
-      <c r="B10" s="16" t="inlineStr">
-        <is>
-          <t>A | 299呎 (1房)
-$876万
-$29,307/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="C10" s="16" t="inlineStr">
-        <is>
-          <t>B | 272呎 (1房)
-$789万
-$29,008/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="D10" s="16" t="inlineStr">
-        <is>
-          <t>C | 299呎 (1房)
-$853万
-$28,527/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="E10" s="16" t="inlineStr">
-        <is>
-          <t>D | 331呎 (1房)
-$870万
-$26,277/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="F10" s="16" t="inlineStr">
-        <is>
-          <t>E | 302呎 (1房)
-$818万
-$27,099/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="G10" s="16" t="inlineStr">
-        <is>
-          <t>F | 302呎 (1房)
-$793万
-$26,270/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="H10" s="16" t="inlineStr">
-        <is>
-          <t>G | 208呎 (开放式)
-$583万
-$28,034/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="I10" s="16" t="inlineStr">
-        <is>
-          <t>H | 216呎 (开放式)
-$608万
-$28,164/呎
-(已售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="11" ht="65" customHeight="1">
-      <c r="A11" s="2" t="inlineStr">
-        <is>
-          <t>G/F</t>
-        </is>
-      </c>
-      <c r="B11" s="17" t="inlineStr"/>
-      <c r="C11" s="17" t="inlineStr"/>
-      <c r="D11" s="17" t="inlineStr"/>
-      <c r="E11" s="16" t="inlineStr">
-        <is>
-          <t>D | 309呎 (1房)
-$1,022万
-$33,087/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="F11" s="16" t="inlineStr">
-        <is>
-          <t>E | 280呎 (1房)
-$806万
-$28,800/呎
-(26年-04月)</t>
-        </is>
-      </c>
-      <c r="G11" s="16" t="inlineStr">
-        <is>
-          <t>F | 280呎 (1房)
-$740万
-$26,421/呎
-(26年-01月)</t>
-        </is>
-      </c>
-      <c r="H11" s="16" t="inlineStr">
-        <is>
-          <t>G | 186呎 (开放式)
-$513万
-$27,581/呎
-(25年-07月)</t>
-        </is>
-      </c>
-      <c r="I11" s="16" t="inlineStr">
-        <is>
-          <t>H | 195呎 (开放式)
-$623万
-$31,935/呎
-(26年-07月)</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="A1:I1"/>
-  </mergeCells>
-  <pageMargins left="0.25" right="0.25" top="0.25" bottom="0.25" header="0.1" footer="0.1"/>
-  <pageSetup orientation="landscape" paperSize="9" fitToHeight="1" fitToWidth="1"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr fitToPage="1"/>
-  </sheetPr>
-  <dimension ref="A1:I11"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="12" customWidth="1" min="1" max="1"/>
-    <col width="18" customWidth="1" min="2" max="2"/>
-    <col width="18" customWidth="1" min="3" max="3"/>
-    <col width="18" customWidth="1" min="4" max="4"/>
-    <col width="18" customWidth="1" min="5" max="5"/>
-    <col width="18" customWidth="1" min="6" max="6"/>
-    <col width="18" customWidth="1" min="7" max="7"/>
-    <col width="18" customWidth="1" min="8" max="8"/>
-    <col width="18" customWidth="1" min="9" max="9"/>
-  </cols>
-  <sheetData>
-    <row r="1" ht="40" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>The Henley I - 低座C座 销控网格图</t>
-        </is>
-      </c>
-    </row>
-    <row r="2" ht="20" customHeight="1">
-      <c r="A2" s="6" t="inlineStr">
-        <is>
-          <t>总套数</t>
-        </is>
-      </c>
-      <c r="B2" s="7" t="inlineStr">
-        <is>
-          <t>在售 (Sale)</t>
-        </is>
-      </c>
-      <c r="C2" s="8" t="inlineStr">
-        <is>
-          <t>已定价未售</t>
-        </is>
-      </c>
-      <c r="D2" s="9" t="inlineStr">
-        <is>
-          <t>已售 (Sold)</t>
-        </is>
-      </c>
-      <c r="E2" s="10" t="inlineStr">
-        <is>
-          <t>暂停销售</t>
-        </is>
-      </c>
-      <c r="F2" s="6" t="inlineStr">
-        <is>
-          <t>待售 (Pending)</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="25" customHeight="1">
-      <c r="A3" s="11" t="inlineStr">
-        <is>
-          <t>45 套</t>
-        </is>
-      </c>
-      <c r="B3" s="12" t="inlineStr">
-        <is>
-          <t>0 套</t>
-        </is>
-      </c>
-      <c r="C3" s="13" t="inlineStr">
-        <is>
-          <t>0 套</t>
-        </is>
-      </c>
-      <c r="D3" s="14" t="inlineStr">
-        <is>
-          <t>45 套</t>
-        </is>
-      </c>
-      <c r="E3" s="15" t="inlineStr">
-        <is>
-          <t>0 套</t>
-        </is>
-      </c>
-      <c r="F3" s="11" t="inlineStr">
-        <is>
-          <t>0 套</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="25" customHeight="1">
-      <c r="A5" s="2" t="inlineStr">
-        <is>
-          <t>楼层\房号</t>
-        </is>
-      </c>
-      <c r="B5" s="2" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>D</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>E</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>F</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>G</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>H</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="65" customHeight="1">
-      <c r="A6" s="2" t="inlineStr">
-        <is>
-          <t>6/F</t>
-        </is>
-      </c>
-      <c r="B6" s="16" t="inlineStr">
-        <is>
-          <t>A | 320呎 (1房)
-$898万
-$28,074/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="C6" s="16" t="inlineStr">
-        <is>
-          <t>B | 296呎 (1房)
-$806万
-$27,229/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="D6" s="16" t="inlineStr">
-        <is>
-          <t>C | 321呎 (1房)
-$856万
-$26,679/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="E6" s="16" t="inlineStr">
-        <is>
-          <t>D | 331呎 (1房)
-$898万
-$27,129/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="F6" s="16" t="inlineStr">
-        <is>
-          <t>E | 302呎 (1房)
-$828万
-$27,411/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="G6" s="16" t="inlineStr">
-        <is>
-          <t>F | 302呎 (1房)
-$836万
-$27,690/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="H6" s="16" t="inlineStr">
-        <is>
-          <t>G | 208呎 (开放式)
-$614万
-$29,518/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="I6" s="16" t="inlineStr">
-        <is>
-          <t>H | 216呎 (开放式)
-$634万
-$29,342/呎
-(21年-06月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="65" customHeight="1">
-      <c r="A7" s="2" t="inlineStr">
-        <is>
-          <t>5/F</t>
-        </is>
-      </c>
-      <c r="B7" s="16" t="inlineStr">
-        <is>
-          <t>A | 320呎 (1房)
-$870万
-$27,174/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="C7" s="16" t="inlineStr">
-        <is>
-          <t>B | 296呎 (1房)
-$788万
-$26,636/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="D7" s="16" t="inlineStr">
-        <is>
-          <t>C | 321呎 (1房)
-$846万
-$26,365/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="E7" s="16" t="inlineStr">
-        <is>
-          <t>D | 330呎 (1房)
-$878万
-$26,613/呎
-(21年-07月)</t>
-        </is>
-      </c>
-      <c r="F7" s="16" t="inlineStr">
-        <is>
-          <t>E | 301呎 (1房)
-$810万
-$26,896/呎
-(26年-05月)</t>
-        </is>
-      </c>
-      <c r="G7" s="16" t="inlineStr">
-        <is>
-          <t>F | 301呎 (1房)
-$801万
-$26,618/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="H7" s="16" t="inlineStr">
-        <is>
-          <t>G | 208呎 (开放式)
-$588万
-$28,290/呎
-(25年-06月)</t>
-        </is>
-      </c>
-      <c r="I7" s="16" t="inlineStr">
-        <is>
-          <t>H | 216呎 (开放式)
-$633万
-$29,300/呎
-(已售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="8" ht="65" customHeight="1">
-      <c r="A8" s="2" t="inlineStr">
-        <is>
-          <t>3/F</t>
-        </is>
-      </c>
-      <c r="B8" s="16" t="inlineStr">
-        <is>
-          <t>A | 320呎 (1房)
-$880万
-$27,489/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="C8" s="16" t="inlineStr">
-        <is>
-          <t>B | 296呎 (1房)
-$806万
-$27,225/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="D8" s="16" t="inlineStr">
-        <is>
-          <t>C | 321呎 (1房)
-$856万
-$26,674/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="E8" s="16" t="inlineStr">
-        <is>
-          <t>D | 330呎 (1房)
-$879万
-$26,644/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="F8" s="16" t="inlineStr">
-        <is>
-          <t>E | 302呎 (1房)
-$794万
-$26,292/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="G8" s="16" t="inlineStr">
-        <is>
-          <t>F | 302呎 (1房)
-$811万
-$26,839/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="H8" s="16" t="inlineStr">
-        <is>
-          <t>G | 208呎 (开放式)
-$608万
-$29,224/呎
-(26年-06月)</t>
-        </is>
-      </c>
-      <c r="I8" s="16" t="inlineStr">
-        <is>
-          <t>H | 216呎 (开放式)
-$608万
-$28,152/呎
-(已售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="9" ht="65" customHeight="1">
-      <c r="A9" s="2" t="inlineStr">
-        <is>
-          <t>2/F</t>
-        </is>
-      </c>
-      <c r="B9" s="16" t="inlineStr">
-        <is>
-          <t>A | 320呎 (1房)
-$863万
-$26,960/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="C9" s="16" t="inlineStr">
-        <is>
-          <t>B | 296呎 (1房)
-$766万
-$25,891/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="D9" s="16" t="inlineStr">
-        <is>
-          <t>C | 321呎 (1房)
-$840万
-$26,163/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="E9" s="16" t="inlineStr">
-        <is>
-          <t>D | 331呎 (1房)
-$844万
-$25,512/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="F9" s="16" t="inlineStr">
-        <is>
-          <t>E | 302呎 (1房)
-$795万
-$26,322/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="G9" s="16" t="inlineStr">
-        <is>
-          <t>F | 302呎 (1房)
-$787万
-$26,050/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="H9" s="16" t="inlineStr">
-        <is>
-          <t>G | 208呎 (开放式)
-$596万
-$28,674/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="I9" s="16" t="inlineStr">
-        <is>
-          <t>H | 216呎 (开放式)
-$609万
-$28,195/呎
-(21年-07月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="10" ht="65" customHeight="1">
-      <c r="A10" s="2" t="inlineStr">
-        <is>
-          <t>1/F</t>
-        </is>
-      </c>
-      <c r="B10" s="16" t="inlineStr">
-        <is>
-          <t>A | 299呎 (1房)
-$840万
-$28,084/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="C10" s="16" t="inlineStr">
-        <is>
-          <t>B | 274呎 (1房)
-$790万
-$28,842/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="D10" s="16" t="inlineStr">
-        <is>
-          <t>C | 299呎 (1房)
-$836万
-$27,961/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="E10" s="16" t="inlineStr">
-        <is>
-          <t>D | 330呎 (1房)
-$655万
-$19,852/呎
-(25年-06月)</t>
-        </is>
-      </c>
-      <c r="F10" s="16" t="inlineStr">
-        <is>
-          <t>E | 301呎 (1房)
-$771万
-$25,625/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="G10" s="16" t="inlineStr">
-        <is>
-          <t>F | 302呎 (1房)
-$796万
-$26,346/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="H10" s="16" t="inlineStr">
-        <is>
-          <t>G | 208呎 (开放式)
-$573万
-$27,554/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="I10" s="16" t="inlineStr">
-        <is>
-          <t>H | 216呎 (开放式)
-$597万
-$27,651/呎
-(已售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="11" ht="65" customHeight="1">
-      <c r="A11" s="2" t="inlineStr">
-        <is>
-          <t>G/F</t>
-        </is>
-      </c>
-      <c r="B11" s="17" t="inlineStr"/>
-      <c r="C11" s="17" t="inlineStr"/>
-      <c r="D11" s="17" t="inlineStr"/>
-      <c r="E11" s="16" t="inlineStr">
-        <is>
-          <t>D | 309呎 (1房)
-$980万
-$31,722/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="F11" s="16" t="inlineStr">
-        <is>
-          <t>E | 280呎 (1房)
-$806万
-$28,800/呎
-(26年-03月)</t>
-        </is>
-      </c>
-      <c r="G11" s="16" t="inlineStr">
-        <is>
-          <t>F | 280呎 (1房)
-$806万
-$28,800/呎
-(26年-04月)</t>
-        </is>
-      </c>
-      <c r="H11" s="16" t="inlineStr">
-        <is>
-          <t>G | 186呎 (开放式)
-$683万
-$36,718/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="I11" s="16" t="inlineStr">
-        <is>
-          <t>H | 194呎 (开放式)
-$708万
-$36,472/呎
-(已售)</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="A1:I1"/>
-  </mergeCells>
-  <pageMargins left="0.25" right="0.25" top="0.25" bottom="0.25" header="0.1" footer="0.1"/>
-  <pageSetup orientation="landscape" paperSize="9" fitToHeight="1" fitToWidth="1"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr fitToPage="1"/>
-  </sheetPr>
-  <dimension ref="A1:I11"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="12" customWidth="1" min="1" max="1"/>
-    <col width="18" customWidth="1" min="2" max="2"/>
-    <col width="18" customWidth="1" min="3" max="3"/>
-    <col width="18" customWidth="1" min="4" max="4"/>
-    <col width="18" customWidth="1" min="5" max="5"/>
-    <col width="18" customWidth="1" min="6" max="6"/>
-    <col width="18" customWidth="1" min="7" max="7"/>
-    <col width="18" customWidth="1" min="8" max="8"/>
-    <col width="18" customWidth="1" min="9" max="9"/>
-  </cols>
-  <sheetData>
-    <row r="1" ht="40" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>The Henley I - 低座D座 销控网格图</t>
-        </is>
-      </c>
-    </row>
-    <row r="2" ht="20" customHeight="1">
-      <c r="A2" s="6" t="inlineStr">
-        <is>
-          <t>总套数</t>
-        </is>
-      </c>
-      <c r="B2" s="7" t="inlineStr">
-        <is>
-          <t>在售 (Sale)</t>
-        </is>
-      </c>
-      <c r="C2" s="8" t="inlineStr">
-        <is>
-          <t>已定价未售</t>
-        </is>
-      </c>
-      <c r="D2" s="9" t="inlineStr">
-        <is>
-          <t>已售 (Sold)</t>
-        </is>
-      </c>
-      <c r="E2" s="10" t="inlineStr">
-        <is>
-          <t>暂停销售</t>
-        </is>
-      </c>
-      <c r="F2" s="6" t="inlineStr">
-        <is>
-          <t>待售 (Pending)</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="25" customHeight="1">
-      <c r="A3" s="11" t="inlineStr">
-        <is>
-          <t>45 套</t>
-        </is>
-      </c>
-      <c r="B3" s="12" t="inlineStr">
-        <is>
-          <t>1 套</t>
-        </is>
-      </c>
-      <c r="C3" s="13" t="inlineStr">
-        <is>
-          <t>0 套</t>
-        </is>
-      </c>
-      <c r="D3" s="14" t="inlineStr">
-        <is>
-          <t>44 套</t>
-        </is>
-      </c>
-      <c r="E3" s="15" t="inlineStr">
-        <is>
-          <t>0 套</t>
-        </is>
-      </c>
-      <c r="F3" s="11" t="inlineStr">
-        <is>
-          <t>0 套</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="25" customHeight="1">
-      <c r="A5" s="2" t="inlineStr">
-        <is>
-          <t>楼层\房号</t>
-        </is>
-      </c>
-      <c r="B5" s="2" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>D</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>E</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>F</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>G</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>H</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="65" customHeight="1">
-      <c r="A6" s="2" t="inlineStr">
-        <is>
-          <t>6/F</t>
-        </is>
-      </c>
-      <c r="B6" s="16" t="inlineStr">
-        <is>
-          <t>A | 320呎 (1房)
-$868万
-$27,114/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="C6" s="16" t="inlineStr">
-        <is>
-          <t>B | 296呎 (1房)
-$823万
-$27,788/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="D6" s="16" t="inlineStr">
-        <is>
-          <t>C | 321呎 (1房)
-$871万
-$27,122/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="E6" s="16" t="inlineStr">
-        <is>
-          <t>D | 331呎 (1房)
-$853万
-$25,773/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="F6" s="16" t="inlineStr">
-        <is>
-          <t>E | 301呎 (1房)
-$786万
-$26,127/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="G6" s="16" t="inlineStr">
-        <is>
-          <t>F | 299呎 (1房)
-$778万
-$26,025/呎
-(21年-05月)</t>
-        </is>
-      </c>
-      <c r="H6" s="16" t="inlineStr">
-        <is>
-          <t>G | 207呎 (开放式)
-$605万
-$29,211/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="I6" s="16" t="inlineStr">
-        <is>
-          <t>H | 321呎 (1房)
-$883万
-$27,510/呎
-(已售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="65" customHeight="1">
-      <c r="A7" s="2" t="inlineStr">
-        <is>
-          <t>5/F</t>
-        </is>
-      </c>
-      <c r="B7" s="16" t="inlineStr">
-        <is>
-          <t>A | 320呎 (1房)
-$857万
-$26,790/呎
-(21年-05月)</t>
-        </is>
-      </c>
-      <c r="C7" s="16" t="inlineStr">
-        <is>
-          <t>B | 296呎 (1房)
-$821万
-$27,740/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="D7" s="16" t="inlineStr">
-        <is>
-          <t>C | 321呎 (1房)
-$852万
-$26,534/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="E7" s="16" t="inlineStr">
-        <is>
-          <t>D | 330呎 (1房)
-$870万
-$26,350/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="F7" s="16" t="inlineStr">
-        <is>
-          <t>E | 301呎 (1房)
-$793万
-$26,357/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="G7" s="16" t="inlineStr">
-        <is>
-          <t>F | 299呎 (1房)
-$777万
-$25,994/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="H7" s="16" t="inlineStr">
-        <is>
-          <t>G | 207呎 (开放式)
-$597万
-$28,862/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="I7" s="16" t="inlineStr">
-        <is>
-          <t>H | 321呎 (1房)
-$855万
-$26,629/呎
-(已售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="8" ht="65" customHeight="1">
-      <c r="A8" s="2" t="inlineStr">
-        <is>
-          <t>3/F</t>
-        </is>
-      </c>
-      <c r="B8" s="16" t="inlineStr">
-        <is>
-          <t>A | 320呎 (1房)
-$841万
-$26,273/呎
-(21年-05月)</t>
-        </is>
-      </c>
-      <c r="C8" s="16" t="inlineStr">
-        <is>
-          <t>B | 296呎 (1房)
-$781万
-$26,382/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="D8" s="16" t="inlineStr">
-        <is>
-          <t>C | 321呎 (1房)
-$853万
-$26,570/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="E8" s="16" t="inlineStr">
-        <is>
-          <t>D | 331呎 (1房)
-$835万
-$25,234/呎
-(21年-05月)</t>
-        </is>
-      </c>
-      <c r="F8" s="16" t="inlineStr">
-        <is>
-          <t>E | 301呎 (1房)
-$770万
-$25,580/呎
-(21年-05月)</t>
-        </is>
-      </c>
-      <c r="G8" s="16" t="inlineStr">
-        <is>
-          <t>F | 299呎 (1房)
-$794万
-$26,571/呎
-(24年-01月)</t>
-        </is>
-      </c>
-      <c r="H8" s="16" t="inlineStr">
-        <is>
-          <t>G | 207呎 (开放式)
-$598万
-$28,906/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="I8" s="16" t="inlineStr">
-        <is>
-          <t>H | 321呎 (1房)
-$873万
-$27,211/呎
-(已售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="9" ht="65" customHeight="1">
-      <c r="A9" s="2" t="inlineStr">
-        <is>
-          <t>2/F</t>
-        </is>
-      </c>
-      <c r="B9" s="16" t="inlineStr">
-        <is>
-          <t>A | 320呎 (1房)
-$841万
-$26,294/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="C9" s="16" t="inlineStr">
-        <is>
-          <t>B | 296呎 (1房)
-$798万
-$26,967/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="D9" s="16" t="inlineStr">
-        <is>
-          <t>C | 321呎 (1房)
-$819万
-$25,529/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="E9" s="16" t="inlineStr">
-        <is>
-          <t>D | 330呎 (1房)
-$836万
-$25,344/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="F9" s="16" t="inlineStr">
-        <is>
-          <t>E | 302呎 (1房)
-$787万
-$26,061/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="G9" s="16" t="inlineStr">
-        <is>
-          <t>F | 299呎 (1房)
-$763万
-$25,534/呎
-(21年-05月)</t>
-        </is>
-      </c>
-      <c r="H9" s="16" t="inlineStr">
-        <is>
-          <t>G | 207呎 (开放式)
-$605万
-$29,239/呎
-(21年-07月)</t>
-        </is>
-      </c>
-      <c r="I9" s="16" t="inlineStr">
-        <is>
-          <t>H | 321呎 (1房)
-$857万
-$26,692/呎
-(21年-05月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="10" ht="65" customHeight="1">
-      <c r="A10" s="2" t="inlineStr">
-        <is>
-          <t>1/F</t>
-        </is>
-      </c>
-      <c r="B10" s="16" t="inlineStr">
-        <is>
-          <t>A | 298呎 (1房)
-$838万
-$28,108/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="C10" s="16" t="inlineStr">
-        <is>
-          <t>B | 272呎 (1房)
-$795万
-$29,231/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="D10" s="16" t="inlineStr">
-        <is>
-          <t>C | 299呎 (1房)
-$824万
-$27,563/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="E10" s="16" t="inlineStr">
-        <is>
-          <t>D | 330呎 (1房)
-$828万
-$25,094/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="F10" s="16" t="inlineStr">
-        <is>
-          <t>E | 301呎 (1房)
-$764万
-$25,378/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="G10" s="16" t="inlineStr">
-        <is>
-          <t>F | 299呎 (1房)
-$780万
-$26,101/呎
-(21年-05月)</t>
-        </is>
-      </c>
-      <c r="H10" s="16" t="inlineStr">
-        <is>
-          <t>G | 207呎 (开放式)
-$587万
-$28,378/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="I10" s="16" t="inlineStr">
-        <is>
-          <t>H | 321呎 (1房)
-$857万
-$26,710/呎
-(已售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="11" ht="65" customHeight="1">
-      <c r="A11" s="2" t="inlineStr">
-        <is>
-          <t>G/F</t>
-        </is>
-      </c>
-      <c r="B11" s="17" t="inlineStr"/>
-      <c r="C11" s="17" t="inlineStr"/>
-      <c r="D11" s="17" t="inlineStr"/>
-      <c r="E11" s="16" t="inlineStr">
-        <is>
-          <t>D | 309呎 (1房)
-$908万
-$29,385/呎
-(26年-06月)</t>
-        </is>
-      </c>
-      <c r="F11" s="16" t="inlineStr">
-        <is>
-          <t>E | 280呎 (1房)
-$848万
-$30,286/呎
-(26年-06月)</t>
-        </is>
-      </c>
-      <c r="G11" s="16" t="inlineStr">
-        <is>
-          <t>F | 277呎 (1房)
-$803万
-$29,000/呎
-(26年-06月)</t>
-        </is>
-      </c>
-      <c r="H11" s="18" t="inlineStr">
-        <is>
-          <t>G | 186呎 (开放式)
-招标单位
--
-(在售)</t>
-        </is>
-      </c>
-      <c r="I11" s="16" t="inlineStr">
-        <is>
-          <t>H | 300呎 (1房)
-$918万
-$30,600/呎
-(26年-05月)</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="A1:I1"/>
-  </mergeCells>
-  <pageMargins left="0.25" right="0.25" top="0.25" bottom="0.25" header="0.1" footer="0.1"/>
-  <pageSetup orientation="landscape" paperSize="9" fitToHeight="1" fitToWidth="1"/>
-</worksheet>
 </file>
--- a/files/九龙-启德-The Henley I.xlsx
+++ b/files/九龙-启德-The Henley I.xlsx
@@ -8,6 +8,11 @@
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="销控汇总明细" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2座" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="低座A座" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="低座B座" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="低座C座" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="低座D座" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -19,7 +24,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="$#,##0"/>
   </numFmts>
-  <fonts count="4">
+  <fonts count="21">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -41,8 +46,102 @@
       <name val="Microsoft YaHei"/>
       <sz val="10"/>
     </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <sz val="13"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <color rgb="00000000"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <color rgb="00000000"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <color rgb="00004D00"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <color rgb="00004D00"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <color rgb="00002060"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <color rgb="00002060"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <color rgb="00660000"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <color rgb="00660000"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <color rgb="00000000"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <color rgb="007F7F7F"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <color rgb="007F7F7F"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <color rgb="00660000"/>
+      <sz val="8"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <color rgb="00004D00"/>
+      <sz val="8"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <color rgb="00002060"/>
+      <sz val="8"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <color rgb="00000000"/>
+      <sz val="8"/>
+    </font>
   </fonts>
-  <fills count="3">
+  <fills count="9">
     <fill>
       <patternFill/>
     </fill>
@@ -53,6 +152,42 @@
       <patternFill patternType="solid">
         <fgColor rgb="00F2F2F2"/>
         <bgColor rgb="00F2F2F2"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFFFFF"/>
+        <bgColor rgb="00FFFFFF"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00A9F5A9"/>
+        <bgColor rgb="00A9F5A9"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00A9D0F5"/>
+        <bgColor rgb="00A9D0F5"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00F5A9A9"/>
+        <bgColor rgb="00F5A9A9"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFC000"/>
+        <bgColor rgb="00FFC000"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00E8E8E8"/>
+        <bgColor rgb="00E8E8E8"/>
       </patternFill>
     </fill>
   </fills>
@@ -82,7 +217,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="25">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -98,6 +233,63 @@
     </xf>
     <xf numFmtId="164" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -474,7 +666,7 @@
     <col width="13" customWidth="1" min="5" max="5"/>
     <col width="12" customWidth="1" min="6" max="6"/>
     <col width="13" customWidth="1" min="7" max="7"/>
-    <col width="13" customWidth="1" min="8" max="8"/>
+    <col width="12" customWidth="1" min="8" max="8"/>
     <col width="14" customWidth="1" min="9" max="9"/>
     <col width="12" customWidth="1" min="10" max="10"/>
   </cols>
@@ -22587,4 +22779,5002 @@
   <pageMargins left="0.25" right="0.25" top="0.25" bottom="0.25" header="0.1" footer="0.1"/>
   <pageSetup orientation="portrait" paperSize="9" fitToHeight="0" fitToWidth="1"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:J38"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="8" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
+    <col width="14" customWidth="1" min="9" max="9"/>
+    <col width="14" customWidth="1" min="10" max="10"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="28" customHeight="1">
+      <c r="A1" s="6" t="inlineStr">
+        <is>
+          <t>2座 销控网格图</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="20" customHeight="1">
+      <c r="A2" s="7" t="inlineStr">
+        <is>
+          <t>总套数</t>
+        </is>
+      </c>
+      <c r="B2" s="8" t="inlineStr">
+        <is>
+          <t>在售 (Sale)</t>
+        </is>
+      </c>
+      <c r="C2" s="9" t="inlineStr">
+        <is>
+          <t>已定价未售</t>
+        </is>
+      </c>
+      <c r="D2" s="10" t="inlineStr">
+        <is>
+          <t>已售 (Sold)</t>
+        </is>
+      </c>
+      <c r="E2" s="11" t="inlineStr">
+        <is>
+          <t>暂停销售</t>
+        </is>
+      </c>
+      <c r="F2" s="12" t="inlineStr">
+        <is>
+          <t>待售 (Pending)</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="20" customHeight="1">
+      <c r="A3" s="13" t="inlineStr">
+        <is>
+          <t>299</t>
+        </is>
+      </c>
+      <c r="B3" s="14" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="C3" s="15" t="inlineStr">
+        <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="D3" s="16" t="inlineStr">
+        <is>
+          <t>221</t>
+        </is>
+      </c>
+      <c r="E3" s="17" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="F3" s="18" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="18" customHeight="1">
+      <c r="A4" s="19" t="inlineStr">
+        <is>
+          <t>楼层</t>
+        </is>
+      </c>
+      <c r="B4" s="19" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="C4" s="19" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="D4" s="19" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="E4" s="19" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="F4" s="19" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+      <c r="G4" s="19" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="H4" s="19" t="inlineStr">
+        <is>
+          <t>G</t>
+        </is>
+      </c>
+      <c r="I4" s="19" t="inlineStr">
+        <is>
+          <t>H</t>
+        </is>
+      </c>
+      <c r="J4" s="19" t="inlineStr">
+        <is>
+          <t>J</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="58" customHeight="1">
+      <c r="A5" s="19" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="B5" s="20" t="inlineStr">
+        <is>
+          <t>A | 1350呎 (3房)
+$8355万
+$61,888/呎
+(21年-06月)</t>
+        </is>
+      </c>
+      <c r="C5" s="21" t="inlineStr"/>
+      <c r="D5" s="21" t="inlineStr"/>
+      <c r="E5" s="21" t="inlineStr"/>
+      <c r="F5" s="22" t="inlineStr">
+        <is>
+          <t>E | 696呎 (3房)
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+      <c r="G5" s="20" t="inlineStr">
+        <is>
+          <t>F | 505呎 (2房)
+$1370万
+$27,129/呎
+(25年-12月)</t>
+        </is>
+      </c>
+      <c r="H5" s="20" t="inlineStr">
+        <is>
+          <t>G | 380呎 (1房)
+$827万
+$21,753/呎
+(25年-07月)</t>
+        </is>
+      </c>
+      <c r="I5" s="20" t="inlineStr">
+        <is>
+          <t>H | 379呎 (1房)
+$820万
+$21,630/呎
+(25年-06月)</t>
+        </is>
+      </c>
+      <c r="J5" s="22" t="inlineStr">
+        <is>
+          <t>J | 418呎 (1房)
+$1443万
+$34,531/呎
+(在售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="58" customHeight="1">
+      <c r="A6" s="19" t="inlineStr">
+        <is>
+          <t>39</t>
+        </is>
+      </c>
+      <c r="B6" s="20" t="inlineStr">
+        <is>
+          <t>A | 890呎 (3房)
+$2996万
+$33,662/呎
+(26年-01月)</t>
+        </is>
+      </c>
+      <c r="C6" s="22" t="inlineStr">
+        <is>
+          <t>B | 550呎 (2房)
+$2035万
+$36,993/呎
+(在售)</t>
+        </is>
+      </c>
+      <c r="D6" s="22" t="inlineStr">
+        <is>
+          <t>C | 550呎 (2房)
+$2015万
+$36,633/呎
+(在售)</t>
+        </is>
+      </c>
+      <c r="E6" s="20" t="inlineStr">
+        <is>
+          <t>D | 546呎 (2房)
+$1950万
+$35,721/呎
+(21年-06月)</t>
+        </is>
+      </c>
+      <c r="F6" s="20" t="inlineStr">
+        <is>
+          <t>E | 695呎 (3房)
+$1557万
+$22,404/呎
+(25年-07月)</t>
+        </is>
+      </c>
+      <c r="G6" s="20" t="inlineStr">
+        <is>
+          <t>F | 505呎 (2房)
+$1437万
+$28,453/呎
+(21年-06月)</t>
+        </is>
+      </c>
+      <c r="H6" s="20" t="inlineStr">
+        <is>
+          <t>G | 380呎 (1房)
+$1055万
+$27,765/呎
+(21年-06月)</t>
+        </is>
+      </c>
+      <c r="I6" s="20" t="inlineStr">
+        <is>
+          <t>H | 379呎 (1房)
+$1058万
+$27,903/呎
+(21年-07月)</t>
+        </is>
+      </c>
+      <c r="J6" s="22" t="inlineStr">
+        <is>
+          <t>J | 418呎 (1房)
+$1139万
+$27,242/呎
+(在售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="58" customHeight="1">
+      <c r="A7" s="19" t="inlineStr">
+        <is>
+          <t>38</t>
+        </is>
+      </c>
+      <c r="B7" s="20" t="inlineStr">
+        <is>
+          <t>A | 890呎 (3房)
+$2960万
+$33,263/呎
+(26年-02月)</t>
+        </is>
+      </c>
+      <c r="C7" s="22" t="inlineStr">
+        <is>
+          <t>B | 550呎 (2房)
+$2012万
+$36,578/呎
+(在售)</t>
+        </is>
+      </c>
+      <c r="D7" s="22" t="inlineStr">
+        <is>
+          <t>C | 550呎 (2房)
+$1992万
+$36,222/呎
+(在售)</t>
+        </is>
+      </c>
+      <c r="E7" s="20" t="inlineStr">
+        <is>
+          <t>D | 546呎 (2房)
+$1880万
+$34,428/呎
+(21年-06月)</t>
+        </is>
+      </c>
+      <c r="F7" s="20" t="inlineStr">
+        <is>
+          <t>E | 695呎 (3房)
+$1540万
+$22,152/呎
+(25年-07月)</t>
+        </is>
+      </c>
+      <c r="G7" s="20" t="inlineStr">
+        <is>
+          <t>F | 505呎 (2房)
+$1392万
+$27,556/呎
+(21年-05月)</t>
+        </is>
+      </c>
+      <c r="H7" s="20" t="inlineStr">
+        <is>
+          <t>G | 380呎 (1房)
+$1043万
+$27,447/呎
+(22年-09月)</t>
+        </is>
+      </c>
+      <c r="I7" s="20" t="inlineStr">
+        <is>
+          <t>H | 379呎 (1房)
+$1046万
+$27,592/呎
+(21年-07月)</t>
+        </is>
+      </c>
+      <c r="J7" s="22" t="inlineStr">
+        <is>
+          <t>J | 418呎 (1房)
+$1126万
+$26,933/呎
+(在售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="58" customHeight="1">
+      <c r="A8" s="19" t="inlineStr">
+        <is>
+          <t>37</t>
+        </is>
+      </c>
+      <c r="B8" s="20" t="inlineStr">
+        <is>
+          <t>A | 890呎 (3房)
+$2943万
+$33,063/呎
+(26年-02月)</t>
+        </is>
+      </c>
+      <c r="C8" s="23" t="inlineStr">
+        <is>
+          <t>B | 550呎 (2房)
+$2000万
+$36,371/呎
+(已定价未售)</t>
+        </is>
+      </c>
+      <c r="D8" s="22" t="inlineStr">
+        <is>
+          <t>C | 550呎 (2房)
+$1981万
+$36,016/呎
+(在售)</t>
+        </is>
+      </c>
+      <c r="E8" s="20" t="inlineStr">
+        <is>
+          <t>D | 546呎 (2房)
+$1887万
+$34,551/呎
+(21年-06月)</t>
+        </is>
+      </c>
+      <c r="F8" s="20" t="inlineStr">
+        <is>
+          <t>E | 695呎 (3房)
+$1528万
+$21,979/呎
+(25年-06月)</t>
+        </is>
+      </c>
+      <c r="G8" s="20" t="inlineStr">
+        <is>
+          <t>F | 505呎 (2房)
+$1425万
+$28,226/呎
+(21年-05月)</t>
+        </is>
+      </c>
+      <c r="H8" s="20" t="inlineStr">
+        <is>
+          <t>G | 380呎 (1房)
+$812万
+$21,364/呎
+(25年-06月)</t>
+        </is>
+      </c>
+      <c r="I8" s="20" t="inlineStr">
+        <is>
+          <t>H | 379呎 (1房)
+$806万
+$21,256/呎
+(25年-07月)</t>
+        </is>
+      </c>
+      <c r="J8" s="22" t="inlineStr">
+        <is>
+          <t>J | 417呎 (1房)
+$1117万
+$26,779/呎
+(在售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="58" customHeight="1">
+      <c r="A9" s="19" t="inlineStr">
+        <is>
+          <t>36</t>
+        </is>
+      </c>
+      <c r="B9" s="20" t="inlineStr">
+        <is>
+          <t>A | 890呎 (3房)
+$2934万
+$32,963/呎
+(26年-02月)</t>
+        </is>
+      </c>
+      <c r="C9" s="22" t="inlineStr">
+        <is>
+          <t>B | 550呎 (2房)
+$1995万
+$36,265/呎
+(在售)</t>
+        </is>
+      </c>
+      <c r="D9" s="20" t="inlineStr">
+        <is>
+          <t>C | 550呎 (2房)
+$1965万
+$35,733/呎
+(21年-06月)</t>
+        </is>
+      </c>
+      <c r="E9" s="20" t="inlineStr">
+        <is>
+          <t>D | 546呎 (2房)
+$1881万
+$34,451/呎
+(21年-06月)</t>
+        </is>
+      </c>
+      <c r="F9" s="20" t="inlineStr">
+        <is>
+          <t>E | 695呎 (3房)
+$1523万
+$21,918/呎
+(25年-06月)</t>
+        </is>
+      </c>
+      <c r="G9" s="20" t="inlineStr">
+        <is>
+          <t>F | 505呎 (2房)
+$1436万
+$28,433/呎
+(21年-05月)</t>
+        </is>
+      </c>
+      <c r="H9" s="20" t="inlineStr">
+        <is>
+          <t>G | 380呎 (1房)
+$1034万
+$27,210/呎
+(23年-05月)</t>
+        </is>
+      </c>
+      <c r="I9" s="20" t="inlineStr">
+        <is>
+          <t>H | 379呎 (1房)
+$803万
+$21,196/呎
+(25年-06月)</t>
+        </is>
+      </c>
+      <c r="J9" s="20" t="inlineStr">
+        <is>
+          <t>J | 418呎 (1房)
+$1013万
+$24,241/呎
+(26年-06月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="58" customHeight="1">
+      <c r="A10" s="19" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="B10" s="20" t="inlineStr">
+        <is>
+          <t>A | 889呎 (3房)
+$3131万
+$35,222/呎
+(21年-06月)</t>
+        </is>
+      </c>
+      <c r="C10" s="20" t="inlineStr">
+        <is>
+          <t>B | 550呎 (2房)
+$1919万
+$34,896/呎
+(26年-07月)</t>
+        </is>
+      </c>
+      <c r="D10" s="22" t="inlineStr">
+        <is>
+          <t>C | 550呎 (2房)
+$1970万
+$35,809/呎
+(在售)</t>
+        </is>
+      </c>
+      <c r="E10" s="20" t="inlineStr">
+        <is>
+          <t>D | 546呎 (2房)
+$1876万
+$34,351/呎
+(21年-06月)</t>
+        </is>
+      </c>
+      <c r="F10" s="20" t="inlineStr">
+        <is>
+          <t>E | 695呎 (3房)
+$1519万
+$21,855/呎
+(25年-06月)</t>
+        </is>
+      </c>
+      <c r="G10" s="20" t="inlineStr">
+        <is>
+          <t>F | 505呎 (2房)
+$1388万
+$27,492/呎
+(21年-05月)</t>
+        </is>
+      </c>
+      <c r="H10" s="20" t="inlineStr">
+        <is>
+          <t>G | 380呎 (1房)
+$807万
+$21,239/呎
+(25年-06月)</t>
+        </is>
+      </c>
+      <c r="I10" s="20" t="inlineStr">
+        <is>
+          <t>H | 379呎 (1房)
+$953万
+$25,149/呎
+(25年-05月)</t>
+        </is>
+      </c>
+      <c r="J10" s="20" t="inlineStr">
+        <is>
+          <t>J | 418呎 (1房)
+$1010万
+$24,172/呎
+(26年-06月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="58" customHeight="1">
+      <c r="A11" s="19" t="inlineStr">
+        <is>
+          <t>33</t>
+        </is>
+      </c>
+      <c r="B11" s="20" t="inlineStr">
+        <is>
+          <t>A | 889呎 (3房)
+$3122万
+$35,122/呎
+(21年-07月)</t>
+        </is>
+      </c>
+      <c r="C11" s="22" t="inlineStr">
+        <is>
+          <t>B | 550呎 (2房)
+$1983万
+$36,060/呎
+(在售)</t>
+        </is>
+      </c>
+      <c r="D11" s="22" t="inlineStr">
+        <is>
+          <t>C | 550呎 (2房)
+$1964万
+$35,707/呎
+(在售)</t>
+        </is>
+      </c>
+      <c r="E11" s="20" t="inlineStr">
+        <is>
+          <t>D | 546呎 (2房)
+$1870万
+$34,250/呎
+(21年-06月)</t>
+        </is>
+      </c>
+      <c r="F11" s="20" t="inlineStr">
+        <is>
+          <t>E | 695呎 (3房)
+$1515万
+$21,792/呎
+(25年-06月)</t>
+        </is>
+      </c>
+      <c r="G11" s="20" t="inlineStr">
+        <is>
+          <t>F | 505呎 (2房)
+$1370万
+$27,129/呎
+(21年-05月)</t>
+        </is>
+      </c>
+      <c r="H11" s="20" t="inlineStr">
+        <is>
+          <t>G | 380呎 (1房)
+$1071万
+$28,189/呎
+(23年-04月)</t>
+        </is>
+      </c>
+      <c r="I11" s="20" t="inlineStr">
+        <is>
+          <t>H | 379呎 (1房)
+$1020万
+$26,921/呎
+(21年-07月)</t>
+        </is>
+      </c>
+      <c r="J11" s="22" t="inlineStr">
+        <is>
+          <t>J | 417呎 (1房)
+$1107万
+$26,547/呎
+(在售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="58" customHeight="1">
+      <c r="A12" s="19" t="inlineStr">
+        <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="B12" s="20" t="inlineStr">
+        <is>
+          <t>A | 890呎 (3房)
+$2907万
+$32,663/呎
+(25年-09月)</t>
+        </is>
+      </c>
+      <c r="C12" s="23" t="inlineStr">
+        <is>
+          <t>B | 550呎 (2房)
+$1978万
+$35,955/呎
+(已定价未售)</t>
+        </is>
+      </c>
+      <c r="D12" s="20" t="inlineStr">
+        <is>
+          <t>C | 550呎 (2房)
+$1860万
+$33,823/呎
+(21年-07月)</t>
+        </is>
+      </c>
+      <c r="E12" s="20" t="inlineStr">
+        <is>
+          <t>D | 546呎 (2房)
+$1865万
+$34,151/呎
+(26年-04月)</t>
+        </is>
+      </c>
+      <c r="F12" s="20" t="inlineStr">
+        <is>
+          <t>E | 695呎 (3房)
+$1466万
+$21,091/呎
+(25年-06月)</t>
+        </is>
+      </c>
+      <c r="G12" s="20" t="inlineStr">
+        <is>
+          <t>F | 505呎 (2房)
+$1380万
+$27,336/呎
+(21年-05月)</t>
+        </is>
+      </c>
+      <c r="H12" s="20" t="inlineStr">
+        <is>
+          <t>G | 380呎 (1房)
+$1025万
+$26,970/呎
+(21年-08月)</t>
+        </is>
+      </c>
+      <c r="I12" s="20" t="inlineStr">
+        <is>
+          <t>H | 379呎 (1房)
+$1028万
+$27,123/呎
+(21年-07月)</t>
+        </is>
+      </c>
+      <c r="J12" s="20" t="inlineStr">
+        <is>
+          <t>J | 418呎 (1房)
+$1004万
+$24,030/呎
+(26年-07月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="58" customHeight="1">
+      <c r="A13" s="19" t="inlineStr">
+        <is>
+          <t>31</t>
+        </is>
+      </c>
+      <c r="B13" s="20" t="inlineStr">
+        <is>
+          <t>A | 890呎 (3房)
+$2898万
+$32,564/呎
+(25年-12月)</t>
+        </is>
+      </c>
+      <c r="C13" s="23" t="inlineStr">
+        <is>
+          <t>B | 550呎 (2房)
+$1972万
+$35,851/呎
+(已定价未售)</t>
+        </is>
+      </c>
+      <c r="D13" s="22" t="inlineStr">
+        <is>
+          <t>C | 550呎 (2房)
+$1952万
+$35,500/呎
+(在售)</t>
+        </is>
+      </c>
+      <c r="E13" s="20" t="inlineStr">
+        <is>
+          <t>D | 546呎 (2房)
+$1859万
+$34,052/呎
+(21年-07月)</t>
+        </is>
+      </c>
+      <c r="F13" s="20" t="inlineStr">
+        <is>
+          <t>E | 695呎 (3房)
+$1462万
+$21,030/呎
+(25年-06月)</t>
+        </is>
+      </c>
+      <c r="G13" s="20" t="inlineStr">
+        <is>
+          <t>F | 505呎 (2房)
+$1355万
+$26,839/呎
+(21年-05月)</t>
+        </is>
+      </c>
+      <c r="H13" s="20" t="inlineStr">
+        <is>
+          <t>G | 380呎 (1房)
+$1038万
+$27,327/呎
+(21年-05月)</t>
+        </is>
+      </c>
+      <c r="I13" s="20" t="inlineStr">
+        <is>
+          <t>H | 379呎 (1房)
+$989万
+$26,101/呎
+(21年-07月)</t>
+        </is>
+      </c>
+      <c r="J13" s="20" t="inlineStr">
+        <is>
+          <t>J | 418呎 (1房)
+$901万
+$21,559/呎
+(25年-12月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="58" customHeight="1">
+      <c r="A14" s="19" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="B14" s="20" t="inlineStr">
+        <is>
+          <t>A | 890呎 (3房)
+$2916万
+$32,763/呎
+(24年-07月)</t>
+        </is>
+      </c>
+      <c r="C14" s="22" t="inlineStr">
+        <is>
+          <t>B | 550呎 (2房)
+$1966万
+$35,747/呎
+(在售)</t>
+        </is>
+      </c>
+      <c r="D14" s="20" t="inlineStr">
+        <is>
+          <t>C | 550呎 (2房)
+$1850万
+$33,628/呎
+(21年-06月)</t>
+        </is>
+      </c>
+      <c r="E14" s="20" t="inlineStr">
+        <is>
+          <t>D | 546呎 (2房)
+$1854万
+$33,951/呎
+(26年-02月)</t>
+        </is>
+      </c>
+      <c r="F14" s="20" t="inlineStr">
+        <is>
+          <t>E | 695呎 (3房)
+$1457万
+$20,968/呎
+(25年-06月)</t>
+        </is>
+      </c>
+      <c r="G14" s="20" t="inlineStr">
+        <is>
+          <t>F | 505呎 (2房)
+$1366万
+$27,043/呎
+(21年-05月)</t>
+        </is>
+      </c>
+      <c r="H14" s="20" t="inlineStr">
+        <is>
+          <t>G | 380呎 (1房)
+$994万
+$26,145/呎
+(21年-06月)</t>
+        </is>
+      </c>
+      <c r="I14" s="20" t="inlineStr">
+        <is>
+          <t>H | 379呎 (1房)
+$997万
+$26,300/呎
+(21年-05月)</t>
+        </is>
+      </c>
+      <c r="J14" s="20" t="inlineStr">
+        <is>
+          <t>J | 418呎 (1房)
+$899万
+$21,496/呎
+(25年-12月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="58" customHeight="1">
+      <c r="A15" s="19" t="inlineStr">
+        <is>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="B15" s="20" t="inlineStr">
+        <is>
+          <t>A | 890呎 (3房)
+$2916万
+$32,763/呎
+(26年-04月)</t>
+        </is>
+      </c>
+      <c r="C15" s="20" t="inlineStr">
+        <is>
+          <t>B | 550呎 (2房)
+$1892万
+$34,394/呎
+(26年-07月)</t>
+        </is>
+      </c>
+      <c r="D15" s="22" t="inlineStr">
+        <is>
+          <t>C | 550呎 (2房)
+$1941万
+$35,295/呎
+(在售)</t>
+        </is>
+      </c>
+      <c r="E15" s="20" t="inlineStr">
+        <is>
+          <t>D | 546呎 (2房)
+$1848万
+$33,852/呎
+(25年-10月)</t>
+        </is>
+      </c>
+      <c r="F15" s="20" t="inlineStr">
+        <is>
+          <t>E | 695呎 (3房)
+$1453万
+$20,908/呎
+(25年-06月)</t>
+        </is>
+      </c>
+      <c r="G15" s="20" t="inlineStr">
+        <is>
+          <t>F | 505呎 (2房)
+$1348万
+$26,685/呎
+(21年-05月)</t>
+        </is>
+      </c>
+      <c r="H15" s="20" t="inlineStr">
+        <is>
+          <t>G | 380呎 (1房)
+$1001万
+$26,342/呎
+(21年-06月)</t>
+        </is>
+      </c>
+      <c r="I15" s="20" t="inlineStr">
+        <is>
+          <t>H | 379呎 (1房)
+$984万
+$25,951/呎
+(21年-06月)</t>
+        </is>
+      </c>
+      <c r="J15" s="20" t="inlineStr">
+        <is>
+          <t>J | 418呎 (1房)
+$896万
+$21,433/呎
+(25年-12月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="58" customHeight="1">
+      <c r="A16" s="19" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="B16" s="20" t="inlineStr">
+        <is>
+          <t>A | 889呎 (3房)
+$3036万
+$34,145/呎
+(21年-05月)</t>
+        </is>
+      </c>
+      <c r="C16" s="22" t="inlineStr">
+        <is>
+          <t>B | 550呎 (2房)
+$1955万
+$35,538/呎
+(在售)</t>
+        </is>
+      </c>
+      <c r="D16" s="22" t="inlineStr">
+        <is>
+          <t>C | 550呎 (2房)
+$1936万
+$35,193/呎
+(在售)</t>
+        </is>
+      </c>
+      <c r="E16" s="20" t="inlineStr">
+        <is>
+          <t>D | 546呎 (2房)
+$1843万
+$33,751/呎
+(26年-05月)</t>
+        </is>
+      </c>
+      <c r="F16" s="20" t="inlineStr">
+        <is>
+          <t>E | 695呎 (3房)
+$1449万
+$20,848/呎
+(25年-06月)</t>
+        </is>
+      </c>
+      <c r="G16" s="20" t="inlineStr">
+        <is>
+          <t>F | 505呎 (2房)
+$1372万
+$27,168/呎
+(21年-05月)</t>
+        </is>
+      </c>
+      <c r="H16" s="20" t="inlineStr">
+        <is>
+          <t>G | 380呎 (1房)
+$998万
+$26,263/呎
+(21年-05月)</t>
+        </is>
+      </c>
+      <c r="I16" s="20" t="inlineStr">
+        <is>
+          <t>H | 379呎 (1房)
+$1001万
+$26,420/呎
+(21年-06月)</t>
+        </is>
+      </c>
+      <c r="J16" s="20" t="inlineStr">
+        <is>
+          <t>J | 418呎 (1房)
+$893万
+$21,370/呎
+(25年-12月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="58" customHeight="1">
+      <c r="A17" s="19" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="B17" s="20" t="inlineStr">
+        <is>
+          <t>A | 890呎 (3房)
+$2996万
+$33,665/呎
+(21年-07月)</t>
+        </is>
+      </c>
+      <c r="C17" s="20" t="inlineStr">
+        <is>
+          <t>B | 550呎 (2房)
+$1875万
+$34,094/呎
+(26年-07月)</t>
+        </is>
+      </c>
+      <c r="D17" s="22" t="inlineStr">
+        <is>
+          <t>C | 550呎 (2房)
+$1924万
+$34,985/呎
+(在售)</t>
+        </is>
+      </c>
+      <c r="E17" s="20" t="inlineStr">
+        <is>
+          <t>D | 546呎 (2房)
+$1832万
+$33,553/呎
+(26年-06月)</t>
+        </is>
+      </c>
+      <c r="F17" s="20" t="inlineStr">
+        <is>
+          <t>E | 695呎 (3房)
+$1440万
+$20,725/呎
+(25年-06月)</t>
+        </is>
+      </c>
+      <c r="G17" s="20" t="inlineStr">
+        <is>
+          <t>F | 505呎 (2房)
+$1336万
+$26,453/呎
+(21年-05月)</t>
+        </is>
+      </c>
+      <c r="H17" s="20" t="inlineStr">
+        <is>
+          <t>G | 380呎 (1房)
+$992万
+$26,107/呎
+(21年-05月)</t>
+        </is>
+      </c>
+      <c r="I17" s="20" t="inlineStr">
+        <is>
+          <t>H | 379呎 (1房)
+$985万
+$25,996/呎
+(21年-06月)</t>
+        </is>
+      </c>
+      <c r="J17" s="20" t="inlineStr">
+        <is>
+          <t>J | 418呎 (1房)
+$888万
+$21,243/呎
+(25年-12月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="58" customHeight="1">
+      <c r="A18" s="19" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="B18" s="20" t="inlineStr">
+        <is>
+          <t>A | 889呎 (3房)
+$2788万
+$31,363/呎
+(21年-05月)</t>
+        </is>
+      </c>
+      <c r="C18" s="23" t="inlineStr">
+        <is>
+          <t>B | 550呎 (2房)
+$1938万
+$35,227/呎
+(已定价未售)</t>
+        </is>
+      </c>
+      <c r="D18" s="20" t="inlineStr">
+        <is>
+          <t>C | 550呎 (2房)
+$1823万
+$33,139/呎
+(21年-06月)</t>
+        </is>
+      </c>
+      <c r="E18" s="20" t="inlineStr">
+        <is>
+          <t>D | 546呎 (2房)
+$1826万
+$33,452/呎
+(26年-04月)</t>
+        </is>
+      </c>
+      <c r="F18" s="20" t="inlineStr">
+        <is>
+          <t>E | 695呎 (3房)
+$1415万
+$20,358/呎
+(25年-06月)</t>
+        </is>
+      </c>
+      <c r="G18" s="20" t="inlineStr">
+        <is>
+          <t>F | 505呎 (2房)
+$1346万
+$26,654/呎
+(21年-05月)</t>
+        </is>
+      </c>
+      <c r="H18" s="20" t="inlineStr">
+        <is>
+          <t>G | 380呎 (1房)
+$989万
+$26,028/呎
+(21年-05月)</t>
+        </is>
+      </c>
+      <c r="I18" s="20" t="inlineStr">
+        <is>
+          <t>H | 379呎 (1房)
+$993万
+$26,190/呎
+(21年-06月)</t>
+        </is>
+      </c>
+      <c r="J18" s="20" t="inlineStr">
+        <is>
+          <t>J | 418呎 (1房)
+$885万
+$21,180/呎
+(25年-11月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="58" customHeight="1">
+      <c r="A19" s="19" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="B19" s="20" t="inlineStr">
+        <is>
+          <t>A | 889呎 (3房)
+$3010万
+$33,857/呎
+(21年-07月)</t>
+        </is>
+      </c>
+      <c r="C19" s="23" t="inlineStr">
+        <is>
+          <t>B | 550呎 (2房)
+$1932万
+$35,124/呎
+(已定价未售)</t>
+        </is>
+      </c>
+      <c r="D19" s="22" t="inlineStr">
+        <is>
+          <t>C | 550呎 (2房)
+$1913万
+$34,780/呎
+(在售)</t>
+        </is>
+      </c>
+      <c r="E19" s="20" t="inlineStr">
+        <is>
+          <t>D | 546呎 (2房)
+$1841万
+$33,723/呎
+(21年-05月)</t>
+        </is>
+      </c>
+      <c r="F19" s="20" t="inlineStr">
+        <is>
+          <t>E | 695呎 (3房)
+$1710万
+$24,604/呎
+(24年-12月)</t>
+        </is>
+      </c>
+      <c r="G19" s="20" t="inlineStr">
+        <is>
+          <t>F | 505呎 (2房)
+$1328万
+$26,299/呎
+(21年-05月)</t>
+        </is>
+      </c>
+      <c r="H19" s="20" t="inlineStr">
+        <is>
+          <t>G | 380呎 (1房)
+$976万
+$25,680/呎
+(21年-05月)</t>
+        </is>
+      </c>
+      <c r="I19" s="20" t="inlineStr">
+        <is>
+          <t>H | 379呎 (1房)
+$1000万
+$26,382/呎
+(21年-05月)</t>
+        </is>
+      </c>
+      <c r="J19" s="20" t="inlineStr">
+        <is>
+          <t>J | 418呎 (1房)
+$883万
+$21,119/呎
+(25年-07月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="58" customHeight="1">
+      <c r="A20" s="19" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="B20" s="20" t="inlineStr">
+        <is>
+          <t>A | 889呎 (3房)
+$2772万
+$31,178/呎
+(21年-05月)</t>
+        </is>
+      </c>
+      <c r="C20" s="23" t="inlineStr">
+        <is>
+          <t>B | 550呎 (2房)
+$1926万
+$35,018/呎
+(已定价未售)</t>
+        </is>
+      </c>
+      <c r="D20" s="22" t="inlineStr">
+        <is>
+          <t>C | 550呎 (2房)
+$1907万
+$34,676/呎
+(在售)</t>
+        </is>
+      </c>
+      <c r="E20" s="20" t="inlineStr">
+        <is>
+          <t>D | 546呎 (2房)
+$1836万
+$33,624/呎
+(21年-05月)</t>
+        </is>
+      </c>
+      <c r="F20" s="20" t="inlineStr">
+        <is>
+          <t>E | 695呎 (3房)
+$1929万
+$27,756/呎
+(24年-01月)</t>
+        </is>
+      </c>
+      <c r="G20" s="20" t="inlineStr">
+        <is>
+          <t>F | 505呎 (2房)
+$1352万
+$26,774/呎
+(21年-05月)</t>
+        </is>
+      </c>
+      <c r="H20" s="20" t="inlineStr">
+        <is>
+          <t>G | 380呎 (1房)
+$973万
+$25,605/呎
+(21年-05月)</t>
+        </is>
+      </c>
+      <c r="I20" s="20" t="inlineStr">
+        <is>
+          <t>H | 379呎 (1房)
+$997万
+$26,305/呎
+(21年-05月)</t>
+        </is>
+      </c>
+      <c r="J20" s="20" t="inlineStr">
+        <is>
+          <t>J | 418呎 (1房)
+$880万
+$21,054/呎
+(25年-12月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="58" customHeight="1">
+      <c r="A21" s="19" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="B21" s="20" t="inlineStr">
+        <is>
+          <t>A | 890呎 (3房)
+$2936万
+$32,985/呎
+(21年-10月)</t>
+        </is>
+      </c>
+      <c r="C21" s="23" t="inlineStr">
+        <is>
+          <t>B | 550呎 (2房)
+$1920万
+$34,915/呎
+(已定价未售)</t>
+        </is>
+      </c>
+      <c r="D21" s="22" t="inlineStr">
+        <is>
+          <t>C | 550呎 (2房)
+$1902万
+$34,575/呎
+(在售)</t>
+        </is>
+      </c>
+      <c r="E21" s="20" t="inlineStr">
+        <is>
+          <t>D | 546呎 (2房)
+$1839万
+$33,676/呎
+(26年-07月)</t>
+        </is>
+      </c>
+      <c r="F21" s="20" t="inlineStr">
+        <is>
+          <t>E | 695呎 (3房)
+$1865万
+$26,836/呎
+(21年-05月)</t>
+        </is>
+      </c>
+      <c r="G21" s="20" t="inlineStr">
+        <is>
+          <t>F | 505呎 (2房)
+$1320万
+$26,145/呎
+(21年-05月)</t>
+        </is>
+      </c>
+      <c r="H21" s="20" t="inlineStr">
+        <is>
+          <t>G | 380呎 (1房)
+$970万
+$25,527/呎
+(21年-05月)</t>
+        </is>
+      </c>
+      <c r="I21" s="20" t="inlineStr">
+        <is>
+          <t>H | 379呎 (1房)
+$974万
+$25,694/呎
+(21年-06月)</t>
+        </is>
+      </c>
+      <c r="J21" s="20" t="inlineStr">
+        <is>
+          <t>J | 418呎 (1房)
+$877万
+$20,992/呎
+(25年-12月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="58" customHeight="1">
+      <c r="A22" s="19" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="B22" s="20" t="inlineStr">
+        <is>
+          <t>A | 890呎 (3房)
+$2896万
+$32,544/呎
+(26年-02月)</t>
+        </is>
+      </c>
+      <c r="C22" s="23" t="inlineStr">
+        <is>
+          <t>B | 550呎 (2房)
+$1915万
+$34,811/呎
+(已定价未售)</t>
+        </is>
+      </c>
+      <c r="D22" s="20" t="inlineStr">
+        <is>
+          <t>C | 550呎 (2房)
+$1801万
+$32,747/呎
+(26年-06月)</t>
+        </is>
+      </c>
+      <c r="E22" s="20" t="inlineStr">
+        <is>
+          <t>D | 546呎 (2房)
+$1853万
+$33,932/呎
+(21年-05月)</t>
+        </is>
+      </c>
+      <c r="F22" s="20" t="inlineStr">
+        <is>
+          <t>E | 696呎 (3房)
+$1879万
+$26,996/呎
+(21年-08月)</t>
+        </is>
+      </c>
+      <c r="G22" s="20" t="inlineStr">
+        <is>
+          <t>F | 505呎 (2房)
+$1344万
+$26,616/呎
+(21年-05月)</t>
+        </is>
+      </c>
+      <c r="H22" s="20" t="inlineStr">
+        <is>
+          <t>G | 380呎 (1房)
+$998万
+$26,254/呎
+(21年-05月)</t>
+        </is>
+      </c>
+      <c r="I22" s="20" t="inlineStr">
+        <is>
+          <t>H | 379呎 (1房)
+$991万
+$26,152/呎
+(21年-05月)</t>
+        </is>
+      </c>
+      <c r="J22" s="20" t="inlineStr">
+        <is>
+          <t>J | 418呎 (1房)
+$885万
+$21,168/呎
+(25年-08月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="58" customHeight="1">
+      <c r="A23" s="19" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="B23" s="20" t="inlineStr">
+        <is>
+          <t>A | 890呎 (3房)
+$2888万
+$32,446/呎
+(26年-04月)</t>
+        </is>
+      </c>
+      <c r="C23" s="23" t="inlineStr">
+        <is>
+          <t>B | 550呎 (2房)
+$1909万
+$34,705/呎
+(已定价未售)</t>
+        </is>
+      </c>
+      <c r="D23" s="24" t="inlineStr">
+        <is>
+          <t>C | 550呎 (2房)
+$1890万
+$34,369/呎
+(暂停销售)</t>
+        </is>
+      </c>
+      <c r="E23" s="20" t="inlineStr">
+        <is>
+          <t>D | 546呎 (2房)
+$1791万
+$32,805/呎
+(21年-05月)</t>
+        </is>
+      </c>
+      <c r="F23" s="20" t="inlineStr">
+        <is>
+          <t>E | 695呎 (3房)
+$1893万
+$27,231/呎
+(21年-05月)</t>
+        </is>
+      </c>
+      <c r="G23" s="20" t="inlineStr">
+        <is>
+          <t>F | 505呎 (2房)
+$1333万
+$26,395/呎
+(21年-05月)</t>
+        </is>
+      </c>
+      <c r="H23" s="20" t="inlineStr">
+        <is>
+          <t>G | 380呎 (1房)
+$974万
+$25,639/呎
+(21年-05月)</t>
+        </is>
+      </c>
+      <c r="I23" s="20" t="inlineStr">
+        <is>
+          <t>H | 379呎 (1房)
+$968万
+$25,542/呎
+(21年-05月)</t>
+        </is>
+      </c>
+      <c r="J23" s="20" t="inlineStr">
+        <is>
+          <t>J | 418呎 (1房)
+$872万
+$20,866/呎
+(25年-07月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="58" customHeight="1">
+      <c r="A24" s="19" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="B24" s="20" t="inlineStr">
+        <is>
+          <t>A | 889呎 (3房)
+$2795万
+$31,437/呎
+(21年-05月)</t>
+        </is>
+      </c>
+      <c r="C24" s="23" t="inlineStr">
+        <is>
+          <t>B | 550呎 (2房)
+$1903万
+$34,604/呎
+(已定价未售)</t>
+        </is>
+      </c>
+      <c r="D24" s="24" t="inlineStr">
+        <is>
+          <t>C | 550呎 (2房)
+$1885万
+$34,265/呎
+(暂停销售)</t>
+        </is>
+      </c>
+      <c r="E24" s="20" t="inlineStr">
+        <is>
+          <t>D | 546呎 (2房)
+$1767万
+$32,364/呎
+(21年-05月)</t>
+        </is>
+      </c>
+      <c r="F24" s="20" t="inlineStr">
+        <is>
+          <t>E | 696呎 (3房)
+$1906万
+$27,389/呎
+(21年-05月)</t>
+        </is>
+      </c>
+      <c r="G24" s="20" t="inlineStr">
+        <is>
+          <t>F | 505呎 (2房)
+$1315万
+$26,043/呎
+(21年-06月)</t>
+        </is>
+      </c>
+      <c r="H24" s="20" t="inlineStr">
+        <is>
+          <t>G | 380呎 (1房)
+$992万
+$26,094/呎
+(21年-06月)</t>
+        </is>
+      </c>
+      <c r="I24" s="20" t="inlineStr">
+        <is>
+          <t>H | 379呎 (1房)
+$955万
+$25,201/呎
+(21年-06月)</t>
+        </is>
+      </c>
+      <c r="J24" s="20" t="inlineStr">
+        <is>
+          <t>J | 418呎 (1房)
+$1111万
+$26,570/呎
+(23年-02月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="58" customHeight="1">
+      <c r="A25" s="19" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="B25" s="20" t="inlineStr">
+        <is>
+          <t>A | 889呎 (3房)
+$2854万
+$32,098/呎
+(21年-05月)</t>
+        </is>
+      </c>
+      <c r="C25" s="23" t="inlineStr">
+        <is>
+          <t>B | 550呎 (2房)
+$1903万
+$34,604/呎
+(已定价未售)</t>
+        </is>
+      </c>
+      <c r="D25" s="24" t="inlineStr">
+        <is>
+          <t>C | 550呎 (2房)
+$1885万
+$34,265/呎
+(暂停销售)</t>
+        </is>
+      </c>
+      <c r="E25" s="20" t="inlineStr">
+        <is>
+          <t>D | 546呎 (2房)
+$1786万
+$32,705/呎
+(21年-06月)</t>
+        </is>
+      </c>
+      <c r="F25" s="20" t="inlineStr">
+        <is>
+          <t>E | 695呎 (3房)
+$1685万
+$24,242/呎
+(25年-04月)</t>
+        </is>
+      </c>
+      <c r="G25" s="20" t="inlineStr">
+        <is>
+          <t>F | 505呎 (2房)
+$1329万
+$26,317/呎
+(21年-06月)</t>
+        </is>
+      </c>
+      <c r="H25" s="20" t="inlineStr">
+        <is>
+          <t>G | 380呎 (1房)
+$971万
+$25,561/呎
+(21年-06月)</t>
+        </is>
+      </c>
+      <c r="I25" s="20" t="inlineStr">
+        <is>
+          <t>H | 379呎 (1房)
+$985万
+$25,997/呎
+(21年-06月)</t>
+        </is>
+      </c>
+      <c r="J25" s="20" t="inlineStr">
+        <is>
+          <t>J | 418呎 (1房)
+$869万
+$20,801/呎
+(25年-06月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="58" customHeight="1">
+      <c r="A26" s="19" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="B26" s="20" t="inlineStr">
+        <is>
+          <t>A | 890呎 (3房)
+$2842万
+$31,933/呎
+(26年-04月)</t>
+        </is>
+      </c>
+      <c r="C26" s="23" t="inlineStr">
+        <is>
+          <t>B | 550呎 (2房)
+$1898万
+$34,500/呎
+(已定价未售)</t>
+        </is>
+      </c>
+      <c r="D26" s="24" t="inlineStr">
+        <is>
+          <t>C | 550呎 (2房)
+$1879万
+$34,162/呎
+(暂停销售)</t>
+        </is>
+      </c>
+      <c r="E26" s="20" t="inlineStr">
+        <is>
+          <t>D | 546呎 (2房)
+$1762万
+$32,267/呎
+(21年-05月)</t>
+        </is>
+      </c>
+      <c r="F26" s="20" t="inlineStr">
+        <is>
+          <t>E | 696呎 (3房)
+$1862万
+$26,754/呎
+(21年-06月)</t>
+        </is>
+      </c>
+      <c r="G26" s="20" t="inlineStr">
+        <is>
+          <t>F | 505呎 (2房)
+$1325万
+$26,237/呎
+(21年-06月)</t>
+        </is>
+      </c>
+      <c r="H26" s="20" t="inlineStr">
+        <is>
+          <t>G | 380呎 (1房)
+$989万
+$26,014/呎
+(21年-06月)</t>
+        </is>
+      </c>
+      <c r="I26" s="20" t="inlineStr">
+        <is>
+          <t>H | 379呎 (1房)
+$962万
+$25,391/呎
+(21年-06月)</t>
+        </is>
+      </c>
+      <c r="J26" s="20" t="inlineStr">
+        <is>
+          <t>J | 418呎 (1房)
+$867万
+$20,740/呎
+(25年-07月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="58" customHeight="1">
+      <c r="A27" s="19" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="B27" s="20" t="inlineStr">
+        <is>
+          <t>A | 890呎 (3房)
+$2833万
+$31,837/呎
+(26年-05月)</t>
+        </is>
+      </c>
+      <c r="C27" s="23" t="inlineStr">
+        <is>
+          <t>B | 550呎 (2房)
+$1892万
+$34,395/呎
+(已定价未售)</t>
+        </is>
+      </c>
+      <c r="D27" s="24" t="inlineStr">
+        <is>
+          <t>C | 550呎 (2房)
+$1873万
+$34,060/呎
+(暂停销售)</t>
+        </is>
+      </c>
+      <c r="E27" s="20" t="inlineStr">
+        <is>
+          <t>D | 546呎 (2房)
+$1775万
+$32,506/呎
+(21年-06月)</t>
+        </is>
+      </c>
+      <c r="F27" s="20" t="inlineStr">
+        <is>
+          <t>E | 695呎 (3房)
+$1809万
+$26,030/呎
+(21年-06月)</t>
+        </is>
+      </c>
+      <c r="G27" s="20" t="inlineStr">
+        <is>
+          <t>F | 505呎 (2房)
+$1275万
+$25,244/呎
+(21年-06月)</t>
+        </is>
+      </c>
+      <c r="H27" s="20" t="inlineStr">
+        <is>
+          <t>G | 380呎 (1房)
+$975万
+$25,669/呎
+(21年-06月)</t>
+        </is>
+      </c>
+      <c r="I27" s="20" t="inlineStr">
+        <is>
+          <t>H | 379呎 (1房)
+$959万
+$25,315/呎
+(21年-06月)</t>
+        </is>
+      </c>
+      <c r="J27" s="20" t="inlineStr">
+        <is>
+          <t>J | 418呎 (1房)
+$899万
+$21,502/呎
+(25年-06月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="58" customHeight="1">
+      <c r="A28" s="19" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="B28" s="20" t="inlineStr">
+        <is>
+          <t>A | 890呎 (3房)
+$2825万
+$31,741/呎
+(26年-06月)</t>
+        </is>
+      </c>
+      <c r="C28" s="23" t="inlineStr">
+        <is>
+          <t>B | 550呎 (2房)
+$1886万
+$34,291/呎
+(已定价未售)</t>
+        </is>
+      </c>
+      <c r="D28" s="24" t="inlineStr">
+        <is>
+          <t>C | 550呎 (2房)
+$1868万
+$33,956/呎
+(暂停销售)</t>
+        </is>
+      </c>
+      <c r="E28" s="20" t="inlineStr">
+        <is>
+          <t>D | 546呎 (2房)
+$1788万
+$32,745/呎
+(21年-06月)</t>
+        </is>
+      </c>
+      <c r="F28" s="20" t="inlineStr">
+        <is>
+          <t>E | 696呎 (3房)
+$1823万
+$26,188/呎
+(21年-06月)</t>
+        </is>
+      </c>
+      <c r="G28" s="20" t="inlineStr">
+        <is>
+          <t>F | 505呎 (2房)
+$1284万
+$25,433/呎
+(21年-06月)</t>
+        </is>
+      </c>
+      <c r="H28" s="20" t="inlineStr">
+        <is>
+          <t>G | 380呎 (1房)
+$962万
+$25,326/呎
+(21年-06月)</t>
+        </is>
+      </c>
+      <c r="I28" s="20" t="inlineStr">
+        <is>
+          <t>H | 379呎 (1房)
+$966万
+$25,501/呎
+(21年-06月)</t>
+        </is>
+      </c>
+      <c r="J28" s="20" t="inlineStr">
+        <is>
+          <t>J | 418呎 (1房)
+$871万
+$20,848/呎
+(25年-06月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" ht="58" customHeight="1">
+      <c r="A29" s="19" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="B29" s="20" t="inlineStr">
+        <is>
+          <t>A | 890呎 (3房)
+$2905万
+$32,636/呎
+(26年-07月)</t>
+        </is>
+      </c>
+      <c r="C29" s="23" t="inlineStr">
+        <is>
+          <t>B | 550呎 (2房)
+$1880万
+$34,187/呎
+(已定价未售)</t>
+        </is>
+      </c>
+      <c r="D29" s="24" t="inlineStr">
+        <is>
+          <t>C | 550呎 (2房)
+$1862万
+$33,853/呎
+(暂停销售)</t>
+        </is>
+      </c>
+      <c r="E29" s="24" t="inlineStr">
+        <is>
+          <t>D | 546呎 (2房)
+$1865万
+$34,159/呎
+(暂停销售)</t>
+        </is>
+      </c>
+      <c r="F29" s="20" t="inlineStr">
+        <is>
+          <t>E | 695呎 (3房)
+$1684万
+$24,225/呎
+(24年-05月)</t>
+        </is>
+      </c>
+      <c r="G29" s="20" t="inlineStr">
+        <is>
+          <t>F | 505呎 (2房)
+$1294万
+$25,619/呎
+(21年-06月)</t>
+        </is>
+      </c>
+      <c r="H29" s="20" t="inlineStr">
+        <is>
+          <t>G | 380呎 (1房)
+$949万
+$24,985/呎
+(21年-06月)</t>
+        </is>
+      </c>
+      <c r="I29" s="20" t="inlineStr">
+        <is>
+          <t>H | 379呎 (1房)
+$954万
+$25,163/呎
+(21年-06月)</t>
+        </is>
+      </c>
+      <c r="J29" s="20" t="inlineStr">
+        <is>
+          <t>J | 418呎 (1房)
+$859万
+$20,552/呎
+(25年-07月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="30" ht="58" customHeight="1">
+      <c r="A30" s="19" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="B30" s="22" t="inlineStr">
+        <is>
+          <t>A | 889呎 (3房)
+$2934万
+$33,001/呎
+(在售)</t>
+        </is>
+      </c>
+      <c r="C30" s="23" t="inlineStr">
+        <is>
+          <t>B | 550呎 (2房)
+$1852万
+$33,667/呎
+(已定价未售)</t>
+        </is>
+      </c>
+      <c r="D30" s="24" t="inlineStr">
+        <is>
+          <t>C | 550呎 (2房)
+$1834万
+$33,338/呎
+(暂停销售)</t>
+        </is>
+      </c>
+      <c r="E30" s="20" t="inlineStr">
+        <is>
+          <t>D | 546呎 (2房)
+$1693万
+$31,004/呎
+(21年-06月)</t>
+        </is>
+      </c>
+      <c r="F30" s="20" t="inlineStr">
+        <is>
+          <t>E | 695呎 (3房)
+$1866万
+$26,854/呎
+(24年-01月)</t>
+        </is>
+      </c>
+      <c r="G30" s="20" t="inlineStr">
+        <is>
+          <t>F | 505呎 (2房)
+$1260万
+$24,941/呎
+(21年-06月)</t>
+        </is>
+      </c>
+      <c r="H30" s="20" t="inlineStr">
+        <is>
+          <t>G | 380呎 (1房)
+$944万
+$24,830/呎
+(21年-06月)</t>
+        </is>
+      </c>
+      <c r="I30" s="20" t="inlineStr">
+        <is>
+          <t>H | 379呎 (1房)
+$968万
+$25,532/呎
+(21年-06月)</t>
+        </is>
+      </c>
+      <c r="J30" s="22" t="inlineStr">
+        <is>
+          <t>J | 417呎 (1房)
+$1043万
+$25,002/呎
+(在售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="31" ht="58" customHeight="1">
+      <c r="A31" s="19" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="B31" s="24" t="inlineStr">
+        <is>
+          <t>A | 889呎 (3房)
+$2866万
+$32,241/呎
+(暂停销售)</t>
+        </is>
+      </c>
+      <c r="C31" s="23" t="inlineStr">
+        <is>
+          <t>B | 550呎 (2房)
+$1846万
+$33,564/呎
+(已定价未售)</t>
+        </is>
+      </c>
+      <c r="D31" s="24" t="inlineStr">
+        <is>
+          <t>C | 550呎 (2房)
+$1828万
+$33,236/呎
+(暂停销售)</t>
+        </is>
+      </c>
+      <c r="E31" s="20" t="inlineStr">
+        <is>
+          <t>D | 546呎 (2房)
+$1723万
+$31,559/呎
+(21年-06月)</t>
+        </is>
+      </c>
+      <c r="F31" s="20" t="inlineStr">
+        <is>
+          <t>E | 695呎 (3房)
+$1644万
+$23,661/呎
+(24年-07月)</t>
+        </is>
+      </c>
+      <c r="G31" s="20" t="inlineStr">
+        <is>
+          <t>F | 505呎 (2房)
+$1256万
+$24,866/呎
+(21年-06月)</t>
+        </is>
+      </c>
+      <c r="H31" s="20" t="inlineStr">
+        <is>
+          <t>G | 380呎 (1房)
+$970万
+$25,534/呎
+(21年-05月)</t>
+        </is>
+      </c>
+      <c r="I31" s="20" t="inlineStr">
+        <is>
+          <t>H | 379呎 (1房)
+$965万
+$25,454/呎
+(21年-06月)</t>
+        </is>
+      </c>
+      <c r="J31" s="20" t="inlineStr">
+        <is>
+          <t>J | 417呎 (1房)
+$1077万
+$25,828/呎
+(21年-08月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="32" ht="58" customHeight="1">
+      <c r="A32" s="19" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="B32" s="24" t="inlineStr">
+        <is>
+          <t>A | 889呎 (3房)
+$2866万
+$32,237/呎
+(暂停销售)</t>
+        </is>
+      </c>
+      <c r="C32" s="23" t="inlineStr">
+        <is>
+          <t>B | 550呎 (2房)
+$1846万
+$33,564/呎
+(已定价未售)</t>
+        </is>
+      </c>
+      <c r="D32" s="24" t="inlineStr">
+        <is>
+          <t>C | 550呎 (2房)
+$1828万
+$33,236/呎
+(暂停销售)</t>
+        </is>
+      </c>
+      <c r="E32" s="24" t="inlineStr">
+        <is>
+          <t>D | 546呎 (2房)
+$1831万
+$33,529/呎
+(暂停销售)</t>
+        </is>
+      </c>
+      <c r="F32" s="20" t="inlineStr">
+        <is>
+          <t>E | 695呎 (3房)
+$1357万
+$19,521/呎
+(25年-06月)</t>
+        </is>
+      </c>
+      <c r="G32" s="20" t="inlineStr">
+        <is>
+          <t>F | 505呎 (2房)
+$1295万
+$25,651/呎
+(21年-05月)</t>
+        </is>
+      </c>
+      <c r="H32" s="20" t="inlineStr">
+        <is>
+          <t>G | 380呎 (1房)
+$950万
+$25,013/呎
+(21年-06月)</t>
+        </is>
+      </c>
+      <c r="I32" s="20" t="inlineStr">
+        <is>
+          <t>H | 379呎 (1房)
+$965万
+$25,454/呎
+(21年-06月)</t>
+        </is>
+      </c>
+      <c r="J32" s="20" t="inlineStr">
+        <is>
+          <t>J | 418呎 (1房)
+$1088万
+$26,034/呎
+(23年-04月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="33" ht="58" customHeight="1">
+      <c r="A33" s="19" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="B33" s="23" t="inlineStr">
+        <is>
+          <t>A | 889呎 (3房)
+$2859万
+$32,156/呎
+(已定价未售)</t>
+        </is>
+      </c>
+      <c r="C33" s="23" t="inlineStr">
+        <is>
+          <t>B | 550呎 (2房)
+$1840万
+$33,458/呎
+(已定价未售)</t>
+        </is>
+      </c>
+      <c r="D33" s="24" t="inlineStr">
+        <is>
+          <t>C | 550呎 (2房)
+$1822万
+$33,133/呎
+(暂停销售)</t>
+        </is>
+      </c>
+      <c r="E33" s="24" t="inlineStr">
+        <is>
+          <t>D | 546呎 (2房)
+$1825万
+$33,423/呎
+(暂停销售)</t>
+        </is>
+      </c>
+      <c r="F33" s="20" t="inlineStr">
+        <is>
+          <t>E | 695呎 (3房)
+$1639万
+$23,588/呎
+(24年-05月)</t>
+        </is>
+      </c>
+      <c r="G33" s="20" t="inlineStr">
+        <is>
+          <t>F | 505呎 (2房)
+$1252万
+$24,788/呎
+(21年-06月)</t>
+        </is>
+      </c>
+      <c r="H33" s="20" t="inlineStr">
+        <is>
+          <t>G | 380呎 (1房)
+$967万
+$25,454/呎
+(21年-06月)</t>
+        </is>
+      </c>
+      <c r="I33" s="20" t="inlineStr">
+        <is>
+          <t>H | 379呎 (1房)
+$972万
+$25,635/呎
+(21年-06月)</t>
+        </is>
+      </c>
+      <c r="J33" s="20" t="inlineStr">
+        <is>
+          <t>J | 418呎 (1房)
+$832万
+$19,899/呎
+(25年-07月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="34" ht="58" customHeight="1">
+      <c r="A34" s="19" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="B34" s="23" t="inlineStr">
+        <is>
+          <t>A | 889呎 (3房)
+$2850万
+$32,057/呎
+(已定价未售)</t>
+        </is>
+      </c>
+      <c r="C34" s="23" t="inlineStr">
+        <is>
+          <t>B | 550呎 (2房)
+$1834万
+$33,355/呎
+(已定价未售)</t>
+        </is>
+      </c>
+      <c r="D34" s="23" t="inlineStr">
+        <is>
+          <t>C | 550呎 (2房)
+$1817万
+$33,029/呎
+(已定价未售)</t>
+        </is>
+      </c>
+      <c r="E34" s="24" t="inlineStr">
+        <is>
+          <t>D | 546呎 (2房)
+$1783万
+$32,661/呎
+(暂停销售)</t>
+        </is>
+      </c>
+      <c r="F34" s="20" t="inlineStr">
+        <is>
+          <t>E | 695呎 (3房)
+$1849万
+$26,610/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="G34" s="20" t="inlineStr">
+        <is>
+          <t>F | 505呎 (2房)
+$1240万
+$24,563/呎
+(21年-06月)</t>
+        </is>
+      </c>
+      <c r="H34" s="20" t="inlineStr">
+        <is>
+          <t>G | 380呎 (1房)
+$929万
+$24,442/呎
+(21年-06月)</t>
+        </is>
+      </c>
+      <c r="I34" s="20" t="inlineStr">
+        <is>
+          <t>H | 379呎 (1房)
+$953万
+$25,151/呎
+(21年-05月)</t>
+        </is>
+      </c>
+      <c r="J34" s="20" t="inlineStr">
+        <is>
+          <t>J | 418呎 (1房)
+$824万
+$19,711/呎
+(25年-08月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="35" ht="58" customHeight="1">
+      <c r="A35" s="19" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="B35" s="23" t="inlineStr">
+        <is>
+          <t>A | 889呎 (3房)
+$2841万
+$31,956/呎
+(已定价未售)</t>
+        </is>
+      </c>
+      <c r="C35" s="23" t="inlineStr">
+        <is>
+          <t>B | 550呎 (2房)
+$1829万
+$33,251/呎
+(已定价未售)</t>
+        </is>
+      </c>
+      <c r="D35" s="23" t="inlineStr">
+        <is>
+          <t>C | 550呎 (2房)
+$1811万
+$32,927/呎
+(已定价未售)</t>
+        </is>
+      </c>
+      <c r="E35" s="24" t="inlineStr">
+        <is>
+          <t>D | 546呎 (2房)
+$1778万
+$32,557/呎
+(暂停销售)</t>
+        </is>
+      </c>
+      <c r="F35" s="20" t="inlineStr">
+        <is>
+          <t>E | 695呎 (3房)
+$1364万
+$19,633/呎
+(25年-06月)</t>
+        </is>
+      </c>
+      <c r="G35" s="20" t="inlineStr">
+        <is>
+          <t>F | 505呎 (2房)
+$1279万
+$25,328/呎
+(21年-06月)</t>
+        </is>
+      </c>
+      <c r="H35" s="20" t="inlineStr">
+        <is>
+          <t>G | 380呎 (1房)
+$988万
+$25,996/呎
+(21年-07月)</t>
+        </is>
+      </c>
+      <c r="I35" s="20" t="inlineStr">
+        <is>
+          <t>H | 379呎 (1房)
+$973万
+$25,665/呎
+(21年-08月)</t>
+        </is>
+      </c>
+      <c r="J35" s="20" t="inlineStr">
+        <is>
+          <t>J | 418呎 (1房)
+$840万
+$20,089/呎
+(25年-06月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="36" ht="58" customHeight="1">
+      <c r="A36" s="19" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="B36" s="23" t="inlineStr">
+        <is>
+          <t>A | 889呎 (3房)
+$2823万
+$31,757/呎
+(已定价未售)</t>
+        </is>
+      </c>
+      <c r="C36" s="23" t="inlineStr">
+        <is>
+          <t>B | 550呎 (2房)
+$1817万
+$33,044/呎
+(已定价未售)</t>
+        </is>
+      </c>
+      <c r="D36" s="23" t="inlineStr">
+        <is>
+          <t>C | 550呎 (2房)
+$1800万
+$32,720/呎
+(已定价未售)</t>
+        </is>
+      </c>
+      <c r="E36" s="24" t="inlineStr">
+        <is>
+          <t>D | 546呎 (2房)
+$1766万
+$32,352/呎
+(暂停销售)</t>
+        </is>
+      </c>
+      <c r="F36" s="20" t="inlineStr">
+        <is>
+          <t>E | 695呎 (3房)
+$1387万
+$19,958/呎
+(25年-06月)</t>
+        </is>
+      </c>
+      <c r="G36" s="20" t="inlineStr">
+        <is>
+          <t>F | 505呎 (2房)
+$1315万
+$26,047/呎
+(21年-06月)</t>
+        </is>
+      </c>
+      <c r="H36" s="20" t="inlineStr">
+        <is>
+          <t>G | 380呎 (1房)
+$965万
+$25,384/呎
+(21年-07月)</t>
+        </is>
+      </c>
+      <c r="I36" s="20" t="inlineStr">
+        <is>
+          <t>H | 379呎 (1房)
+$960万
+$25,322/呎
+(21年-08月)</t>
+        </is>
+      </c>
+      <c r="J36" s="20" t="inlineStr">
+        <is>
+          <t>J | 418呎 (1房)
+$814万
+$19,468/呎
+(25年-08月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="37" ht="58" customHeight="1">
+      <c r="A37" s="19" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="B37" s="23" t="inlineStr">
+        <is>
+          <t>A | 889呎 (3房)
+$2796万
+$31,457/呎
+(已定价未售)</t>
+        </is>
+      </c>
+      <c r="C37" s="23" t="inlineStr">
+        <is>
+          <t>B | 550呎 (2房)
+$1800万
+$32,731/呎
+(已定价未售)</t>
+        </is>
+      </c>
+      <c r="D37" s="23" t="inlineStr">
+        <is>
+          <t>C | 550呎 (2房)
+$1783万
+$32,413/呎
+(已定价未售)</t>
+        </is>
+      </c>
+      <c r="E37" s="24" t="inlineStr">
+        <is>
+          <t>D | 546呎 (2房)
+$1750万
+$32,042/呎
+(暂停销售)</t>
+        </is>
+      </c>
+      <c r="F37" s="20" t="inlineStr">
+        <is>
+          <t>E | 695呎 (3房)
+$1371万
+$19,722/呎
+(25年-06月)</t>
+        </is>
+      </c>
+      <c r="G37" s="20" t="inlineStr">
+        <is>
+          <t>F | 505呎 (2房)
+$1280万
+$25,355/呎
+(21年-06月)</t>
+        </is>
+      </c>
+      <c r="H37" s="20" t="inlineStr">
+        <is>
+          <t>G | 380呎 (1房)
+$948万
+$24,957/呎
+(21年-07月)</t>
+        </is>
+      </c>
+      <c r="I37" s="20" t="inlineStr">
+        <is>
+          <t>H | 379呎 (1房)
+$984万
+$25,951/呎
+(21年-08月)</t>
+        </is>
+      </c>
+      <c r="J37" s="20" t="inlineStr">
+        <is>
+          <t>J | 418呎 (1房)
+$809万
+$19,344/呎
+(25年-08月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="38" ht="58" customHeight="1">
+      <c r="A38" s="19" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="B38" s="21" t="inlineStr"/>
+      <c r="C38" s="21" t="inlineStr"/>
+      <c r="D38" s="21" t="inlineStr"/>
+      <c r="E38" s="21" t="inlineStr"/>
+      <c r="F38" s="20" t="inlineStr">
+        <is>
+          <t>E | 705呎 (3房)
+$1357万
+$19,241/呎
+(25年-06月)</t>
+        </is>
+      </c>
+      <c r="G38" s="20" t="inlineStr">
+        <is>
+          <t>F | 505呎 (2房)
+$1312万
+$25,985/呎
+(21年-07月)</t>
+        </is>
+      </c>
+      <c r="H38" s="20" t="inlineStr">
+        <is>
+          <t>G | 380呎 (1房)
+$952万
+$25,058/呎
+(23年-12月)</t>
+        </is>
+      </c>
+      <c r="I38" s="20" t="inlineStr">
+        <is>
+          <t>H | 379呎 (1房)
+$938万
+$24,747/呎
+(22年-09月)</t>
+        </is>
+      </c>
+      <c r="J38" s="20" t="inlineStr">
+        <is>
+          <t>J | 418呎 (1房)
+$817万
+$19,552/呎
+(25年-07月)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:F1"/>
+  </mergeCells>
+  <pageMargins left="0.25" right="0.25" top="0.25" bottom="0.25" header="0.1" footer="0.1"/>
+  <pageSetup orientation="landscape" paperSize="9" fitToHeight="1" fitToWidth="1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:I10"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="8" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
+    <col width="14" customWidth="1" min="9" max="9"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="28" customHeight="1">
+      <c r="A1" s="6" t="inlineStr">
+        <is>
+          <t>低座A座 销控网格图</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="20" customHeight="1">
+      <c r="A2" s="7" t="inlineStr">
+        <is>
+          <t>总套数</t>
+        </is>
+      </c>
+      <c r="B2" s="8" t="inlineStr">
+        <is>
+          <t>在售 (Sale)</t>
+        </is>
+      </c>
+      <c r="C2" s="9" t="inlineStr">
+        <is>
+          <t>已定价未售</t>
+        </is>
+      </c>
+      <c r="D2" s="10" t="inlineStr">
+        <is>
+          <t>已售 (Sold)</t>
+        </is>
+      </c>
+      <c r="E2" s="11" t="inlineStr">
+        <is>
+          <t>暂停销售</t>
+        </is>
+      </c>
+      <c r="F2" s="12" t="inlineStr">
+        <is>
+          <t>待售 (Pending)</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="20" customHeight="1">
+      <c r="A3" s="13" t="inlineStr">
+        <is>
+          <t>45</t>
+        </is>
+      </c>
+      <c r="B3" s="14" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="C3" s="15" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D3" s="16" t="inlineStr">
+        <is>
+          <t>45</t>
+        </is>
+      </c>
+      <c r="E3" s="17" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F3" s="18" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="18" customHeight="1">
+      <c r="A4" s="19" t="inlineStr">
+        <is>
+          <t>楼层</t>
+        </is>
+      </c>
+      <c r="B4" s="19" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="C4" s="19" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="D4" s="19" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="E4" s="19" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="F4" s="19" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+      <c r="G4" s="19" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="H4" s="19" t="inlineStr">
+        <is>
+          <t>G</t>
+        </is>
+      </c>
+      <c r="I4" s="19" t="inlineStr">
+        <is>
+          <t>H</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="58" customHeight="1">
+      <c r="A5" s="19" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="B5" s="20" t="inlineStr">
+        <is>
+          <t>A | 320呎 (1房)
+$876万
+$27,366/呎
+(21年-06月)</t>
+        </is>
+      </c>
+      <c r="C5" s="20" t="inlineStr">
+        <is>
+          <t>B | 296呎 (1房)
+$819万
+$27,653/呎
+(21年-05月)</t>
+        </is>
+      </c>
+      <c r="D5" s="20" t="inlineStr">
+        <is>
+          <t>C | 321呎 (1房)
+$870万
+$27,098/呎
+(21年-06月)</t>
+        </is>
+      </c>
+      <c r="E5" s="20" t="inlineStr">
+        <is>
+          <t>D | 331呎 (1房)
+$878万
+$26,537/呎
+(21年-06月)</t>
+        </is>
+      </c>
+      <c r="F5" s="20" t="inlineStr">
+        <is>
+          <t>E | 301呎 (1房)
+$810万
+$26,915/呎
+(21年-06月)</t>
+        </is>
+      </c>
+      <c r="G5" s="20" t="inlineStr">
+        <is>
+          <t>F | 301呎 (1房)
+$835万
+$27,749/呎
+(21年-07月)</t>
+        </is>
+      </c>
+      <c r="H5" s="20" t="inlineStr">
+        <is>
+          <t>G | 208呎 (开放式)
+$595万
+$28,614/呎
+(21年-08月)</t>
+        </is>
+      </c>
+      <c r="I5" s="20" t="inlineStr">
+        <is>
+          <t>H | 216呎 (开放式)
+$627万
+$29,040/呎
+(21年-09月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="58" customHeight="1">
+      <c r="A6" s="19" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="B6" s="20" t="inlineStr">
+        <is>
+          <t>A | 320呎 (1房)
+$856万
+$26,757/呎
+(21年-06月)</t>
+        </is>
+      </c>
+      <c r="C6" s="20" t="inlineStr">
+        <is>
+          <t>B | 296呎 (1房)
+$776万
+$26,228/呎
+(21年-06月)</t>
+        </is>
+      </c>
+      <c r="D6" s="20" t="inlineStr">
+        <is>
+          <t>C | 321呎 (1房)
+$860万
+$26,780/呎
+(21年-05月)</t>
+        </is>
+      </c>
+      <c r="E6" s="20" t="inlineStr">
+        <is>
+          <t>D | 330呎 (1房)
+$886万
+$26,851/呎
+(21年-07月)</t>
+        </is>
+      </c>
+      <c r="F6" s="20" t="inlineStr">
+        <is>
+          <t>E | 301呎 (1房)
+$817万
+$27,147/呎
+(21年-06月)</t>
+        </is>
+      </c>
+      <c r="G6" s="20" t="inlineStr">
+        <is>
+          <t>F | 302呎 (1房)
+$817万
+$27,047/呎
+(21年-07月)</t>
+        </is>
+      </c>
+      <c r="H6" s="20" t="inlineStr">
+        <is>
+          <t>G | 208呎 (开放式)
+$607万
+$29,183/呎
+(21年-06月)</t>
+        </is>
+      </c>
+      <c r="I6" s="20" t="inlineStr">
+        <is>
+          <t>H | 216呎 (开放式)
+$620万
+$28,702/呎
+(21年-08月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="58" customHeight="1">
+      <c r="A7" s="19" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="B7" s="20" t="inlineStr">
+        <is>
+          <t>A | 320呎 (1房)
+$857万
+$26,793/呎
+(21年-06月)</t>
+        </is>
+      </c>
+      <c r="C7" s="20" t="inlineStr">
+        <is>
+          <t>B | 296呎 (1房)
+$769万
+$25,993/呎
+(21年-06月)</t>
+        </is>
+      </c>
+      <c r="D7" s="20" t="inlineStr">
+        <is>
+          <t>C | 321呎 (1房)
+$835万
+$25,998/呎
+(21年-05月)</t>
+        </is>
+      </c>
+      <c r="E7" s="20" t="inlineStr">
+        <is>
+          <t>D | 330呎 (1房)
+$869万
+$26,336/呎
+(21年-07月)</t>
+        </is>
+      </c>
+      <c r="F7" s="20" t="inlineStr">
+        <is>
+          <t>E | 302呎 (1房)
+$810万
+$26,814/呎
+(21年-06月)</t>
+        </is>
+      </c>
+      <c r="G7" s="20" t="inlineStr">
+        <is>
+          <t>F | 302呎 (1房)
+$818万
+$27,083/呎
+(21年-07月)</t>
+        </is>
+      </c>
+      <c r="H7" s="20" t="inlineStr">
+        <is>
+          <t>G | 208呎 (开放式)
+$600万
+$28,826/呎
+(21年-06月)</t>
+        </is>
+      </c>
+      <c r="I7" s="20" t="inlineStr">
+        <is>
+          <t>H | 216呎 (开放式)
+$627万
+$29,041/呎
+(21年-06月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="58" customHeight="1">
+      <c r="A8" s="19" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="B8" s="20" t="inlineStr">
+        <is>
+          <t>A | 320呎 (1房)
+$841万
+$26,270/呎
+(21年-06月)</t>
+        </is>
+      </c>
+      <c r="C8" s="20" t="inlineStr">
+        <is>
+          <t>B | 296呎 (1房)
+$771万
+$26,033/呎
+(21年-06月)</t>
+        </is>
+      </c>
+      <c r="D8" s="20" t="inlineStr">
+        <is>
+          <t>C | 321呎 (1房)
+$844万
+$26,301/呎
+(21年-06月)</t>
+        </is>
+      </c>
+      <c r="E8" s="20" t="inlineStr">
+        <is>
+          <t>D | 331呎 (1房)
+$861万
+$26,018/呎
+(21年-07月)</t>
+        </is>
+      </c>
+      <c r="F8" s="20" t="inlineStr">
+        <is>
+          <t>E | 301呎 (1房)
+$802万
+$26,655/呎
+(21年-06月)</t>
+        </is>
+      </c>
+      <c r="G8" s="20" t="inlineStr">
+        <is>
+          <t>F | 301呎 (1房)
+$794万
+$26,373/呎
+(21年-07月)</t>
+        </is>
+      </c>
+      <c r="H8" s="20" t="inlineStr">
+        <is>
+          <t>G | 208呎 (开放式)
+$578万
+$27,797/呎
+(21年-08月)</t>
+        </is>
+      </c>
+      <c r="I8" s="20" t="inlineStr">
+        <is>
+          <t>H | 216呎 (开放式)
+$615万
+$28,489/呎
+(21年-08月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="58" customHeight="1">
+      <c r="A9" s="19" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="B9" s="20" t="inlineStr">
+        <is>
+          <t>A | 299呎 (1房)
+$862万
+$28,823/呎
+(21年-06月)</t>
+        </is>
+      </c>
+      <c r="C9" s="20" t="inlineStr">
+        <is>
+          <t>B | 272呎 (1房)
+$967万
+$35,561/呎
+(21年-05月)</t>
+        </is>
+      </c>
+      <c r="D9" s="20" t="inlineStr">
+        <is>
+          <t>C | 299呎 (1房)
+$823万
+$27,535/呎
+(21年-06月)</t>
+        </is>
+      </c>
+      <c r="E9" s="20" t="inlineStr">
+        <is>
+          <t>D | 330呎 (1房)
+$844万
+$25,587/呎
+(21年-07月)</t>
+        </is>
+      </c>
+      <c r="F9" s="20" t="inlineStr">
+        <is>
+          <t>E | 302呎 (1房)
+$779万
+$25,786/呎
+(21年-06月)</t>
+        </is>
+      </c>
+      <c r="G9" s="20" t="inlineStr">
+        <is>
+          <t>F | 302呎 (1房)
+$803万
+$26,586/呎
+(21年-07月)</t>
+        </is>
+      </c>
+      <c r="H9" s="20" t="inlineStr">
+        <is>
+          <t>G | 208呎 (开放式)
+$573万
+$27,554/呎
+(21年-09月)</t>
+        </is>
+      </c>
+      <c r="I9" s="20" t="inlineStr">
+        <is>
+          <t>H | 216呎 (开放式)
+$597万
+$27,651/呎
+(21年-09月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="58" customHeight="1">
+      <c r="A10" s="19" t="inlineStr">
+        <is>
+          <t>G</t>
+        </is>
+      </c>
+      <c r="B10" s="21" t="inlineStr"/>
+      <c r="C10" s="21" t="inlineStr"/>
+      <c r="D10" s="21" t="inlineStr"/>
+      <c r="E10" s="20" t="inlineStr">
+        <is>
+          <t>D | 309呎 (1房)
+$995万
+$32,200/呎
+(21年-07月)</t>
+        </is>
+      </c>
+      <c r="F10" s="20" t="inlineStr">
+        <is>
+          <t>E | 280呎 (1房)
+$920万
+$32,858/呎
+(21年-06月)</t>
+        </is>
+      </c>
+      <c r="G10" s="20" t="inlineStr">
+        <is>
+          <t>F | 280呎 (1房)
+$910万
+$32,510/呎
+(21年-07月)</t>
+        </is>
+      </c>
+      <c r="H10" s="20" t="inlineStr">
+        <is>
+          <t>G | 186呎 (开放式)
+$682万
+$36,655/呎
+(21年-06月)</t>
+        </is>
+      </c>
+      <c r="I10" s="20" t="inlineStr">
+        <is>
+          <t>H | 195呎 (开放式)
+$567万
+$29,100/呎
+(26年-02月)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:F1"/>
+  </mergeCells>
+  <pageMargins left="0.25" right="0.25" top="0.25" bottom="0.25" header="0.1" footer="0.1"/>
+  <pageSetup orientation="landscape" paperSize="9" fitToHeight="1" fitToWidth="1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:I10"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="8" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
+    <col width="14" customWidth="1" min="9" max="9"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="28" customHeight="1">
+      <c r="A1" s="6" t="inlineStr">
+        <is>
+          <t>低座B座 销控网格图</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="20" customHeight="1">
+      <c r="A2" s="7" t="inlineStr">
+        <is>
+          <t>总套数</t>
+        </is>
+      </c>
+      <c r="B2" s="8" t="inlineStr">
+        <is>
+          <t>在售 (Sale)</t>
+        </is>
+      </c>
+      <c r="C2" s="9" t="inlineStr">
+        <is>
+          <t>已定价未售</t>
+        </is>
+      </c>
+      <c r="D2" s="10" t="inlineStr">
+        <is>
+          <t>已售 (Sold)</t>
+        </is>
+      </c>
+      <c r="E2" s="11" t="inlineStr">
+        <is>
+          <t>暂停销售</t>
+        </is>
+      </c>
+      <c r="F2" s="12" t="inlineStr">
+        <is>
+          <t>待售 (Pending)</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="20" customHeight="1">
+      <c r="A3" s="13" t="inlineStr">
+        <is>
+          <t>45</t>
+        </is>
+      </c>
+      <c r="B3" s="14" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="C3" s="15" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D3" s="16" t="inlineStr">
+        <is>
+          <t>45</t>
+        </is>
+      </c>
+      <c r="E3" s="17" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F3" s="18" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="18" customHeight="1">
+      <c r="A4" s="19" t="inlineStr">
+        <is>
+          <t>楼层</t>
+        </is>
+      </c>
+      <c r="B4" s="19" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="C4" s="19" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="D4" s="19" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="E4" s="19" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="F4" s="19" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+      <c r="G4" s="19" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="H4" s="19" t="inlineStr">
+        <is>
+          <t>G</t>
+        </is>
+      </c>
+      <c r="I4" s="19" t="inlineStr">
+        <is>
+          <t>H</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="58" customHeight="1">
+      <c r="A5" s="19" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="B5" s="20" t="inlineStr">
+        <is>
+          <t>A | 320呎 (1房)
+$899万
+$28,107/呎
+(21年-06月)</t>
+        </is>
+      </c>
+      <c r="C5" s="20" t="inlineStr">
+        <is>
+          <t>B | 296呎 (1房)
+$815万
+$27,545/呎
+(21年-06月)</t>
+        </is>
+      </c>
+      <c r="D5" s="20" t="inlineStr">
+        <is>
+          <t>C | 321呎 (1房)
+$873万
+$27,204/呎
+(21年-07月)</t>
+        </is>
+      </c>
+      <c r="E5" s="20" t="inlineStr">
+        <is>
+          <t>D | 330呎 (1房)
+$701万
+$21,238/呎
+(25年-07月)</t>
+        </is>
+      </c>
+      <c r="F5" s="20" t="inlineStr">
+        <is>
+          <t>E | 301呎 (1房)
+$825万
+$27,414/呎
+(21年-07月)</t>
+        </is>
+      </c>
+      <c r="G5" s="20" t="inlineStr">
+        <is>
+          <t>F | 301呎 (1房)
+$834万
+$27,703/呎
+(21年-06月)</t>
+        </is>
+      </c>
+      <c r="H5" s="20" t="inlineStr">
+        <is>
+          <t>G | 208呎 (开放式)
+$613万
+$29,473/呎
+(21年-06月)</t>
+        </is>
+      </c>
+      <c r="I5" s="20" t="inlineStr">
+        <is>
+          <t>H | 216呎 (开放式)
+$645万
+$29,867/呎
+(21年-07月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="58" customHeight="1">
+      <c r="A6" s="19" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="B6" s="20" t="inlineStr">
+        <is>
+          <t>A | 320呎 (1房)
+$879万
+$27,482/呎
+(21年-06月)</t>
+        </is>
+      </c>
+      <c r="C6" s="20" t="inlineStr">
+        <is>
+          <t>B | 296呎 (1房)
+$806万
+$27,224/呎
+(21年-06月)</t>
+        </is>
+      </c>
+      <c r="D6" s="20" t="inlineStr">
+        <is>
+          <t>C | 321呎 (1房)
+$890万
+$27,733/呎
+(21年-07月)</t>
+        </is>
+      </c>
+      <c r="E6" s="20" t="inlineStr">
+        <is>
+          <t>D | 330呎 (1房)
+$692万
+$20,984/呎
+(25年-07月)</t>
+        </is>
+      </c>
+      <c r="F6" s="20" t="inlineStr">
+        <is>
+          <t>E | 302呎 (1房)
+$824万
+$27,283/呎
+(21年-07月)</t>
+        </is>
+      </c>
+      <c r="G6" s="20" t="inlineStr">
+        <is>
+          <t>F | 301呎 (1房)
+$841万
+$27,945/呎
+(21年-06月)</t>
+        </is>
+      </c>
+      <c r="H6" s="20" t="inlineStr">
+        <is>
+          <t>G | 208呎 (开放式)
+$593万
+$28,518/呎
+(21年-06月)</t>
+        </is>
+      </c>
+      <c r="I6" s="20" t="inlineStr">
+        <is>
+          <t>H | 216呎 (开放式)
+$644万
+$29,824/呎
+(21年-06月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="58" customHeight="1">
+      <c r="A7" s="19" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="B7" s="20" t="inlineStr">
+        <is>
+          <t>A | 320呎 (1房)
+$872万
+$27,235/呎
+(21年-06月)</t>
+        </is>
+      </c>
+      <c r="C7" s="20" t="inlineStr">
+        <is>
+          <t>B | 296呎 (1房)
+$799万
+$26,984/呎
+(21年-05月)</t>
+        </is>
+      </c>
+      <c r="D7" s="20" t="inlineStr">
+        <is>
+          <t>C | 321呎 (1房)
+$882万
+$27,489/呎
+(21年-07月)</t>
+        </is>
+      </c>
+      <c r="E7" s="20" t="inlineStr">
+        <is>
+          <t>D | 330呎 (1房)
+$698万
+$21,152/呎
+(25年-06月)</t>
+        </is>
+      </c>
+      <c r="F7" s="20" t="inlineStr">
+        <is>
+          <t>E | 302呎 (1房)
+$808万
+$26,757/呎
+(21年-07月)</t>
+        </is>
+      </c>
+      <c r="G7" s="20" t="inlineStr">
+        <is>
+          <t>F | 301呎 (1房)
+$817万
+$27,129/呎
+(21年-06月)</t>
+        </is>
+      </c>
+      <c r="H7" s="20" t="inlineStr">
+        <is>
+          <t>G | 208呎 (开放式)
+$588万
+$28,258/呎
+(21年-06月)</t>
+        </is>
+      </c>
+      <c r="I7" s="20" t="inlineStr">
+        <is>
+          <t>H | 216呎 (开放式)
+$632万
+$29,268/呎
+(21年-06月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="58" customHeight="1">
+      <c r="A8" s="19" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="B8" s="20" t="inlineStr">
+        <is>
+          <t>A | 320呎 (1房)
+$891万
+$27,838/呎
+(21年-06月)</t>
+        </is>
+      </c>
+      <c r="C8" s="20" t="inlineStr">
+        <is>
+          <t>B | 296呎 (1房)
+$808万
+$27,301/呎
+(21年-06月)</t>
+        </is>
+      </c>
+      <c r="D8" s="20" t="inlineStr">
+        <is>
+          <t>C | 321呎 (1房)
+$848万
+$26,407/呎
+(21年-07月)</t>
+        </is>
+      </c>
+      <c r="E8" s="20" t="inlineStr">
+        <is>
+          <t>D | 330呎 (1房)
+$680万
+$20,608/呎
+(25年-06月)</t>
+        </is>
+      </c>
+      <c r="F8" s="20" t="inlineStr">
+        <is>
+          <t>E | 302呎 (1房)
+$826万
+$27,349/呎
+(21年-07月)</t>
+        </is>
+      </c>
+      <c r="G8" s="20" t="inlineStr">
+        <is>
+          <t>F | 301呎 (1房)
+$809万
+$26,880/呎
+(21年-07月)</t>
+        </is>
+      </c>
+      <c r="H8" s="20" t="inlineStr">
+        <is>
+          <t>G | 208呎 (开放式)
+$601万
+$28,886/呎
+(21年-06月)</t>
+        </is>
+      </c>
+      <c r="I8" s="20" t="inlineStr">
+        <is>
+          <t>H | 216呎 (开放式)
+$627万
+$29,010/呎
+(21年-06月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="58" customHeight="1">
+      <c r="A9" s="19" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="B9" s="20" t="inlineStr">
+        <is>
+          <t>A | 299呎 (1房)
+$876万
+$29,307/呎
+(21年-07月)</t>
+        </is>
+      </c>
+      <c r="C9" s="20" t="inlineStr">
+        <is>
+          <t>B | 272呎 (1房)
+$789万
+$29,008/呎
+(21年-07月)</t>
+        </is>
+      </c>
+      <c r="D9" s="20" t="inlineStr">
+        <is>
+          <t>C | 299呎 (1房)
+$853万
+$28,527/呎
+(21年-07月)</t>
+        </is>
+      </c>
+      <c r="E9" s="20" t="inlineStr">
+        <is>
+          <t>D | 331呎 (1房)
+$870万
+$26,277/呎
+(21年-07月)</t>
+        </is>
+      </c>
+      <c r="F9" s="20" t="inlineStr">
+        <is>
+          <t>E | 302呎 (1房)
+$818万
+$27,099/呎
+(21年-07月)</t>
+        </is>
+      </c>
+      <c r="G9" s="20" t="inlineStr">
+        <is>
+          <t>F | 302呎 (1房)
+$793万
+$26,270/呎
+(21年-07月)</t>
+        </is>
+      </c>
+      <c r="H9" s="20" t="inlineStr">
+        <is>
+          <t>G | 208呎 (开放式)
+$583万
+$28,034/呎
+(21年-06月)</t>
+        </is>
+      </c>
+      <c r="I9" s="20" t="inlineStr">
+        <is>
+          <t>H | 216呎 (开放式)
+$608万
+$28,164/呎
+(21年-09月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="58" customHeight="1">
+      <c r="A10" s="19" t="inlineStr">
+        <is>
+          <t>G</t>
+        </is>
+      </c>
+      <c r="B10" s="21" t="inlineStr"/>
+      <c r="C10" s="21" t="inlineStr"/>
+      <c r="D10" s="21" t="inlineStr"/>
+      <c r="E10" s="20" t="inlineStr">
+        <is>
+          <t>D | 309呎 (1房)
+$1022万
+$33,087/呎
+(21年-08月)</t>
+        </is>
+      </c>
+      <c r="F10" s="20" t="inlineStr">
+        <is>
+          <t>E | 280呎 (1房)
+$806万
+$28,800/呎
+(26年-04月)</t>
+        </is>
+      </c>
+      <c r="G10" s="20" t="inlineStr">
+        <is>
+          <t>F | 280呎 (1房)
+$740万
+$26,421/呎
+(26年-01月)</t>
+        </is>
+      </c>
+      <c r="H10" s="20" t="inlineStr">
+        <is>
+          <t>G | 186呎 (开放式)
+$513万
+$27,581/呎
+(25年-07月)</t>
+        </is>
+      </c>
+      <c r="I10" s="20" t="inlineStr">
+        <is>
+          <t>H | 195呎 (开放式)
+$623万
+$31,935/呎
+(26年-07月)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:F1"/>
+  </mergeCells>
+  <pageMargins left="0.25" right="0.25" top="0.25" bottom="0.25" header="0.1" footer="0.1"/>
+  <pageSetup orientation="landscape" paperSize="9" fitToHeight="1" fitToWidth="1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:I10"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="8" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
+    <col width="14" customWidth="1" min="9" max="9"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="28" customHeight="1">
+      <c r="A1" s="6" t="inlineStr">
+        <is>
+          <t>低座C座 销控网格图</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="20" customHeight="1">
+      <c r="A2" s="7" t="inlineStr">
+        <is>
+          <t>总套数</t>
+        </is>
+      </c>
+      <c r="B2" s="8" t="inlineStr">
+        <is>
+          <t>在售 (Sale)</t>
+        </is>
+      </c>
+      <c r="C2" s="9" t="inlineStr">
+        <is>
+          <t>已定价未售</t>
+        </is>
+      </c>
+      <c r="D2" s="10" t="inlineStr">
+        <is>
+          <t>已售 (Sold)</t>
+        </is>
+      </c>
+      <c r="E2" s="11" t="inlineStr">
+        <is>
+          <t>暂停销售</t>
+        </is>
+      </c>
+      <c r="F2" s="12" t="inlineStr">
+        <is>
+          <t>待售 (Pending)</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="20" customHeight="1">
+      <c r="A3" s="13" t="inlineStr">
+        <is>
+          <t>45</t>
+        </is>
+      </c>
+      <c r="B3" s="14" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="C3" s="15" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D3" s="16" t="inlineStr">
+        <is>
+          <t>45</t>
+        </is>
+      </c>
+      <c r="E3" s="17" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F3" s="18" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="18" customHeight="1">
+      <c r="A4" s="19" t="inlineStr">
+        <is>
+          <t>楼层</t>
+        </is>
+      </c>
+      <c r="B4" s="19" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="C4" s="19" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="D4" s="19" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="E4" s="19" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="F4" s="19" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+      <c r="G4" s="19" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="H4" s="19" t="inlineStr">
+        <is>
+          <t>G</t>
+        </is>
+      </c>
+      <c r="I4" s="19" t="inlineStr">
+        <is>
+          <t>H</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="58" customHeight="1">
+      <c r="A5" s="19" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="B5" s="20" t="inlineStr">
+        <is>
+          <t>A | 320呎 (1房)
+$898万
+$28,074/呎
+(21年-06月)</t>
+        </is>
+      </c>
+      <c r="C5" s="20" t="inlineStr">
+        <is>
+          <t>B | 296呎 (1房)
+$806万
+$27,229/呎
+(21年-06月)</t>
+        </is>
+      </c>
+      <c r="D5" s="20" t="inlineStr">
+        <is>
+          <t>C | 321呎 (1房)
+$856万
+$26,679/呎
+(21年-06月)</t>
+        </is>
+      </c>
+      <c r="E5" s="20" t="inlineStr">
+        <is>
+          <t>D | 331呎 (1房)
+$898万
+$27,129/呎
+(21年-07月)</t>
+        </is>
+      </c>
+      <c r="F5" s="20" t="inlineStr">
+        <is>
+          <t>E | 302呎 (1房)
+$828万
+$27,411/呎
+(21年-06月)</t>
+        </is>
+      </c>
+      <c r="G5" s="20" t="inlineStr">
+        <is>
+          <t>F | 302呎 (1房)
+$836万
+$27,690/呎
+(21年-06月)</t>
+        </is>
+      </c>
+      <c r="H5" s="20" t="inlineStr">
+        <is>
+          <t>G | 208呎 (开放式)
+$614万
+$29,518/呎
+(21年-07月)</t>
+        </is>
+      </c>
+      <c r="I5" s="20" t="inlineStr">
+        <is>
+          <t>H | 216呎 (开放式)
+$634万
+$29,342/呎
+(21年-06月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="58" customHeight="1">
+      <c r="A6" s="19" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="B6" s="20" t="inlineStr">
+        <is>
+          <t>A | 320呎 (1房)
+$870万
+$27,174/呎
+(21年-06月)</t>
+        </is>
+      </c>
+      <c r="C6" s="20" t="inlineStr">
+        <is>
+          <t>B | 296呎 (1房)
+$788万
+$26,636/呎
+(21年-06月)</t>
+        </is>
+      </c>
+      <c r="D6" s="20" t="inlineStr">
+        <is>
+          <t>C | 321呎 (1房)
+$846万
+$26,365/呎
+(21年-06月)</t>
+        </is>
+      </c>
+      <c r="E6" s="20" t="inlineStr">
+        <is>
+          <t>D | 330呎 (1房)
+$878万
+$26,613/呎
+(21年-07月)</t>
+        </is>
+      </c>
+      <c r="F6" s="20" t="inlineStr">
+        <is>
+          <t>E | 301呎 (1房)
+$810万
+$26,896/呎
+(21年-06月)</t>
+        </is>
+      </c>
+      <c r="G6" s="20" t="inlineStr">
+        <is>
+          <t>F | 301呎 (1房)
+$801万
+$26,618/呎
+(21年-06月)</t>
+        </is>
+      </c>
+      <c r="H6" s="20" t="inlineStr">
+        <is>
+          <t>G | 208呎 (开放式)
+$588万
+$28,290/呎
+(21年-07月)</t>
+        </is>
+      </c>
+      <c r="I6" s="20" t="inlineStr">
+        <is>
+          <t>H | 216呎 (开放式)
+$633万
+$29,300/呎
+(21年-07月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="58" customHeight="1">
+      <c r="A7" s="19" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="B7" s="20" t="inlineStr">
+        <is>
+          <t>A | 320呎 (1房)
+$880万
+$27,489/呎
+(21年-05月)</t>
+        </is>
+      </c>
+      <c r="C7" s="20" t="inlineStr">
+        <is>
+          <t>B | 296呎 (1房)
+$806万
+$27,225/呎
+(21年-05月)</t>
+        </is>
+      </c>
+      <c r="D7" s="20" t="inlineStr">
+        <is>
+          <t>C | 321呎 (1房)
+$856万
+$26,674/呎
+(21年-05月)</t>
+        </is>
+      </c>
+      <c r="E7" s="20" t="inlineStr">
+        <is>
+          <t>D | 330呎 (1房)
+$879万
+$26,644/呎
+(21年-07月)</t>
+        </is>
+      </c>
+      <c r="F7" s="20" t="inlineStr">
+        <is>
+          <t>E | 302呎 (1房)
+$794万
+$26,292/呎
+(21年-05月)</t>
+        </is>
+      </c>
+      <c r="G7" s="20" t="inlineStr">
+        <is>
+          <t>F | 302呎 (1房)
+$811万
+$26,839/呎
+(21年-05月)</t>
+        </is>
+      </c>
+      <c r="H7" s="20" t="inlineStr">
+        <is>
+          <t>G | 208呎 (开放式)
+$608万
+$29,224/呎
+(21年-07月)</t>
+        </is>
+      </c>
+      <c r="I7" s="20" t="inlineStr">
+        <is>
+          <t>H | 216呎 (开放式)
+$608万
+$28,152/呎
+(21年-07月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="58" customHeight="1">
+      <c r="A8" s="19" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="B8" s="20" t="inlineStr">
+        <is>
+          <t>A | 320呎 (1房)
+$863万
+$26,960/呎
+(21年-05月)</t>
+        </is>
+      </c>
+      <c r="C8" s="20" t="inlineStr">
+        <is>
+          <t>B | 296呎 (1房)
+$766万
+$25,891/呎
+(21年-05月)</t>
+        </is>
+      </c>
+      <c r="D8" s="20" t="inlineStr">
+        <is>
+          <t>C | 321呎 (1房)
+$840万
+$26,163/呎
+(21年-05月)</t>
+        </is>
+      </c>
+      <c r="E8" s="20" t="inlineStr">
+        <is>
+          <t>D | 331呎 (1房)
+$844万
+$25,512/呎
+(21年-07月)</t>
+        </is>
+      </c>
+      <c r="F8" s="20" t="inlineStr">
+        <is>
+          <t>E | 302呎 (1房)
+$795万
+$26,322/呎
+(21年-07月)</t>
+        </is>
+      </c>
+      <c r="G8" s="20" t="inlineStr">
+        <is>
+          <t>F | 302呎 (1房)
+$787万
+$26,050/呎
+(21年-07月)</t>
+        </is>
+      </c>
+      <c r="H8" s="20" t="inlineStr">
+        <is>
+          <t>G | 208呎 (开放式)
+$596万
+$28,674/呎
+(21年-07月)</t>
+        </is>
+      </c>
+      <c r="I8" s="20" t="inlineStr">
+        <is>
+          <t>H | 216呎 (开放式)
+$609万
+$28,195/呎
+(21年-07月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="58" customHeight="1">
+      <c r="A9" s="19" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="B9" s="20" t="inlineStr">
+        <is>
+          <t>A | 299呎 (1房)
+$840万
+$28,084/呎
+(21年-05月)</t>
+        </is>
+      </c>
+      <c r="C9" s="20" t="inlineStr">
+        <is>
+          <t>B | 274呎 (1房)
+$790万
+$28,842/呎
+(21年-05月)</t>
+        </is>
+      </c>
+      <c r="D9" s="20" t="inlineStr">
+        <is>
+          <t>C | 299呎 (1房)
+$836万
+$27,961/呎
+(21年-05月)</t>
+        </is>
+      </c>
+      <c r="E9" s="20" t="inlineStr">
+        <is>
+          <t>D | 330呎 (1房)
+$655万
+$19,852/呎
+(25年-06月)</t>
+        </is>
+      </c>
+      <c r="F9" s="20" t="inlineStr">
+        <is>
+          <t>E | 301呎 (1房)
+$771万
+$25,625/呎
+(21年-07月)</t>
+        </is>
+      </c>
+      <c r="G9" s="20" t="inlineStr">
+        <is>
+          <t>F | 302呎 (1房)
+$796万
+$26,346/呎
+(21年-05月)</t>
+        </is>
+      </c>
+      <c r="H9" s="20" t="inlineStr">
+        <is>
+          <t>G | 208呎 (开放式)
+$573万
+$27,554/呎
+(21年-08月)</t>
+        </is>
+      </c>
+      <c r="I9" s="20" t="inlineStr">
+        <is>
+          <t>H | 216呎 (开放式)
+$597万
+$27,651/呎
+(21年-08月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="58" customHeight="1">
+      <c r="A10" s="19" t="inlineStr">
+        <is>
+          <t>G</t>
+        </is>
+      </c>
+      <c r="B10" s="21" t="inlineStr"/>
+      <c r="C10" s="21" t="inlineStr"/>
+      <c r="D10" s="21" t="inlineStr"/>
+      <c r="E10" s="20" t="inlineStr">
+        <is>
+          <t>D | 309呎 (1房)
+$980万
+$31,722/呎
+(23年-05月)</t>
+        </is>
+      </c>
+      <c r="F10" s="20" t="inlineStr">
+        <is>
+          <t>E | 280呎 (1房)
+$806万
+$28,800/呎
+(26年-03月)</t>
+        </is>
+      </c>
+      <c r="G10" s="20" t="inlineStr">
+        <is>
+          <t>F | 280呎 (1房)
+$806万
+$28,800/呎
+(26年-04月)</t>
+        </is>
+      </c>
+      <c r="H10" s="20" t="inlineStr">
+        <is>
+          <t>G | 186呎 (开放式)
+$683万
+$36,718/呎
+(21年-07月)</t>
+        </is>
+      </c>
+      <c r="I10" s="20" t="inlineStr">
+        <is>
+          <t>H | 194呎 (开放式)
+$708万
+$36,472/呎
+(21年-08月)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:F1"/>
+  </mergeCells>
+  <pageMargins left="0.25" right="0.25" top="0.25" bottom="0.25" header="0.1" footer="0.1"/>
+  <pageSetup orientation="landscape" paperSize="9" fitToHeight="1" fitToWidth="1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:I10"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="8" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
+    <col width="14" customWidth="1" min="9" max="9"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="28" customHeight="1">
+      <c r="A1" s="6" t="inlineStr">
+        <is>
+          <t>低座D座 销控网格图</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="20" customHeight="1">
+      <c r="A2" s="7" t="inlineStr">
+        <is>
+          <t>总套数</t>
+        </is>
+      </c>
+      <c r="B2" s="8" t="inlineStr">
+        <is>
+          <t>在售 (Sale)</t>
+        </is>
+      </c>
+      <c r="C2" s="9" t="inlineStr">
+        <is>
+          <t>已定价未售</t>
+        </is>
+      </c>
+      <c r="D2" s="10" t="inlineStr">
+        <is>
+          <t>已售 (Sold)</t>
+        </is>
+      </c>
+      <c r="E2" s="11" t="inlineStr">
+        <is>
+          <t>暂停销售</t>
+        </is>
+      </c>
+      <c r="F2" s="12" t="inlineStr">
+        <is>
+          <t>待售 (Pending)</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="20" customHeight="1">
+      <c r="A3" s="13" t="inlineStr">
+        <is>
+          <t>45</t>
+        </is>
+      </c>
+      <c r="B3" s="14" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C3" s="15" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D3" s="16" t="inlineStr">
+        <is>
+          <t>44</t>
+        </is>
+      </c>
+      <c r="E3" s="17" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F3" s="18" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="18" customHeight="1">
+      <c r="A4" s="19" t="inlineStr">
+        <is>
+          <t>楼层</t>
+        </is>
+      </c>
+      <c r="B4" s="19" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="C4" s="19" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="D4" s="19" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="E4" s="19" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="F4" s="19" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+      <c r="G4" s="19" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="H4" s="19" t="inlineStr">
+        <is>
+          <t>G</t>
+        </is>
+      </c>
+      <c r="I4" s="19" t="inlineStr">
+        <is>
+          <t>H</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="58" customHeight="1">
+      <c r="A5" s="19" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="B5" s="20" t="inlineStr">
+        <is>
+          <t>A | 320呎 (1房)
+$868万
+$27,114/呎
+(21年-05月)</t>
+        </is>
+      </c>
+      <c r="C5" s="20" t="inlineStr">
+        <is>
+          <t>B | 296呎 (1房)
+$823万
+$27,788/呎
+(21年-05月)</t>
+        </is>
+      </c>
+      <c r="D5" s="20" t="inlineStr">
+        <is>
+          <t>C | 321呎 (1房)
+$871万
+$27,122/呎
+(21年-05月)</t>
+        </is>
+      </c>
+      <c r="E5" s="20" t="inlineStr">
+        <is>
+          <t>D | 331呎 (1房)
+$853万
+$25,773/呎
+(21年-05月)</t>
+        </is>
+      </c>
+      <c r="F5" s="20" t="inlineStr">
+        <is>
+          <t>E | 301呎 (1房)
+$786万
+$26,127/呎
+(21年-05月)</t>
+        </is>
+      </c>
+      <c r="G5" s="20" t="inlineStr">
+        <is>
+          <t>F | 299呎 (1房)
+$778万
+$26,025/呎
+(21年-05月)</t>
+        </is>
+      </c>
+      <c r="H5" s="20" t="inlineStr">
+        <is>
+          <t>G | 207呎 (开放式)
+$605万
+$29,211/呎
+(21年-07月)</t>
+        </is>
+      </c>
+      <c r="I5" s="20" t="inlineStr">
+        <is>
+          <t>H | 321呎 (1房)
+$883万
+$27,510/呎
+(21年-05月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="58" customHeight="1">
+      <c r="A6" s="19" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="B6" s="20" t="inlineStr">
+        <is>
+          <t>A | 320呎 (1房)
+$857万
+$26,790/呎
+(21年-05月)</t>
+        </is>
+      </c>
+      <c r="C6" s="20" t="inlineStr">
+        <is>
+          <t>B | 296呎 (1房)
+$821万
+$27,740/呎
+(21年-05月)</t>
+        </is>
+      </c>
+      <c r="D6" s="20" t="inlineStr">
+        <is>
+          <t>C | 321呎 (1房)
+$852万
+$26,534/呎
+(21年-05月)</t>
+        </is>
+      </c>
+      <c r="E6" s="20" t="inlineStr">
+        <is>
+          <t>D | 330呎 (1房)
+$870万
+$26,350/呎
+(21年-05月)</t>
+        </is>
+      </c>
+      <c r="F6" s="20" t="inlineStr">
+        <is>
+          <t>E | 301呎 (1房)
+$793万
+$26,357/呎
+(21年-05月)</t>
+        </is>
+      </c>
+      <c r="G6" s="20" t="inlineStr">
+        <is>
+          <t>F | 299呎 (1房)
+$777万
+$25,994/呎
+(21年-05月)</t>
+        </is>
+      </c>
+      <c r="H6" s="20" t="inlineStr">
+        <is>
+          <t>G | 207呎 (开放式)
+$597万
+$28,862/呎
+(21年-07月)</t>
+        </is>
+      </c>
+      <c r="I6" s="20" t="inlineStr">
+        <is>
+          <t>H | 321呎 (1房)
+$855万
+$26,629/呎
+(21年-05月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="58" customHeight="1">
+      <c r="A7" s="19" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="B7" s="20" t="inlineStr">
+        <is>
+          <t>A | 320呎 (1房)
+$841万
+$26,273/呎
+(21年-05月)</t>
+        </is>
+      </c>
+      <c r="C7" s="20" t="inlineStr">
+        <is>
+          <t>B | 296呎 (1房)
+$781万
+$26,382/呎
+(21年-05月)</t>
+        </is>
+      </c>
+      <c r="D7" s="20" t="inlineStr">
+        <is>
+          <t>C | 321呎 (1房)
+$853万
+$26,570/呎
+(21年-05月)</t>
+        </is>
+      </c>
+      <c r="E7" s="20" t="inlineStr">
+        <is>
+          <t>D | 331呎 (1房)
+$835万
+$25,234/呎
+(21年-05月)</t>
+        </is>
+      </c>
+      <c r="F7" s="20" t="inlineStr">
+        <is>
+          <t>E | 301呎 (1房)
+$770万
+$25,580/呎
+(21年-05月)</t>
+        </is>
+      </c>
+      <c r="G7" s="20" t="inlineStr">
+        <is>
+          <t>F | 299呎 (1房)
+$794万
+$26,571/呎
+(21年-05月)</t>
+        </is>
+      </c>
+      <c r="H7" s="20" t="inlineStr">
+        <is>
+          <t>G | 207呎 (开放式)
+$598万
+$28,906/呎
+(21年-07月)</t>
+        </is>
+      </c>
+      <c r="I7" s="20" t="inlineStr">
+        <is>
+          <t>H | 321呎 (1房)
+$873万
+$27,211/呎
+(21年-05月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="58" customHeight="1">
+      <c r="A8" s="19" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="B8" s="20" t="inlineStr">
+        <is>
+          <t>A | 320呎 (1房)
+$841万
+$26,294/呎
+(21年-07月)</t>
+        </is>
+      </c>
+      <c r="C8" s="20" t="inlineStr">
+        <is>
+          <t>B | 296呎 (1房)
+$798万
+$26,967/呎
+(21年-05月)</t>
+        </is>
+      </c>
+      <c r="D8" s="20" t="inlineStr">
+        <is>
+          <t>C | 321呎 (1房)
+$819万
+$25,529/呎
+(21年-05月)</t>
+        </is>
+      </c>
+      <c r="E8" s="20" t="inlineStr">
+        <is>
+          <t>D | 330呎 (1房)
+$836万
+$25,344/呎
+(21年-05月)</t>
+        </is>
+      </c>
+      <c r="F8" s="20" t="inlineStr">
+        <is>
+          <t>E | 302呎 (1房)
+$787万
+$26,061/呎
+(21年-05月)</t>
+        </is>
+      </c>
+      <c r="G8" s="20" t="inlineStr">
+        <is>
+          <t>F | 299呎 (1房)
+$763万
+$25,534/呎
+(21年-05月)</t>
+        </is>
+      </c>
+      <c r="H8" s="20" t="inlineStr">
+        <is>
+          <t>G | 207呎 (开放式)
+$605万
+$29,239/呎
+(21年-07月)</t>
+        </is>
+      </c>
+      <c r="I8" s="20" t="inlineStr">
+        <is>
+          <t>H | 321呎 (1房)
+$857万
+$26,692/呎
+(21年-05月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="58" customHeight="1">
+      <c r="A9" s="19" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="B9" s="20" t="inlineStr">
+        <is>
+          <t>A | 298呎 (1房)
+$838万
+$28,108/呎
+(21年-07月)</t>
+        </is>
+      </c>
+      <c r="C9" s="20" t="inlineStr">
+        <is>
+          <t>B | 272呎 (1房)
+$795万
+$29,231/呎
+(21年-06月)</t>
+        </is>
+      </c>
+      <c r="D9" s="20" t="inlineStr">
+        <is>
+          <t>C | 299呎 (1房)
+$824万
+$27,563/呎
+(21年-07月)</t>
+        </is>
+      </c>
+      <c r="E9" s="20" t="inlineStr">
+        <is>
+          <t>D | 330呎 (1房)
+$828万
+$25,094/呎
+(21年-07月)</t>
+        </is>
+      </c>
+      <c r="F9" s="20" t="inlineStr">
+        <is>
+          <t>E | 301呎 (1房)
+$764万
+$25,378/呎
+(21年-06月)</t>
+        </is>
+      </c>
+      <c r="G9" s="20" t="inlineStr">
+        <is>
+          <t>F | 299呎 (1房)
+$780万
+$26,101/呎
+(21年-05月)</t>
+        </is>
+      </c>
+      <c r="H9" s="20" t="inlineStr">
+        <is>
+          <t>G | 207呎 (开放式)
+$587万
+$28,378/呎
+(21年-09月)</t>
+        </is>
+      </c>
+      <c r="I9" s="20" t="inlineStr">
+        <is>
+          <t>H | 321呎 (1房)
+$857万
+$26,710/呎
+(21年-07月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="58" customHeight="1">
+      <c r="A10" s="19" t="inlineStr">
+        <is>
+          <t>G</t>
+        </is>
+      </c>
+      <c r="B10" s="21" t="inlineStr"/>
+      <c r="C10" s="21" t="inlineStr"/>
+      <c r="D10" s="21" t="inlineStr"/>
+      <c r="E10" s="20" t="inlineStr">
+        <is>
+          <t>D | 309呎 (1房)
+$908万
+$29,385/呎
+(26年-06月)</t>
+        </is>
+      </c>
+      <c r="F10" s="20" t="inlineStr">
+        <is>
+          <t>E | 280呎 (1房)
+$848万
+$30,286/呎
+(26年-06月)</t>
+        </is>
+      </c>
+      <c r="G10" s="20" t="inlineStr">
+        <is>
+          <t>F | 277呎 (1房)
+$803万
+$29,000/呎
+(26年-06月)</t>
+        </is>
+      </c>
+      <c r="H10" s="22" t="inlineStr">
+        <is>
+          <t>G | 186呎 (开放式)
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+      <c r="I10" s="20" t="inlineStr">
+        <is>
+          <t>H | 300呎 (1房)
+$918万
+$30,600/呎
+(26年-05月)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:F1"/>
+  </mergeCells>
+  <pageMargins left="0.25" right="0.25" top="0.25" bottom="0.25" header="0.1" footer="0.1"/>
+  <pageSetup orientation="landscape" paperSize="9" fitToHeight="1" fitToWidth="1"/>
+</worksheet>
 </file>
--- a/files/九龙-启德-The Henley I.xlsx
+++ b/files/九龙-启德-The Henley I.xlsx
@@ -666,7 +666,7 @@
     <col width="13" customWidth="1" min="5" max="5"/>
     <col width="12" customWidth="1" min="6" max="6"/>
     <col width="13" customWidth="1" min="7" max="7"/>
-    <col width="12" customWidth="1" min="8" max="8"/>
+    <col width="13" customWidth="1" min="8" max="8"/>
     <col width="14" customWidth="1" min="9" max="9"/>
     <col width="12" customWidth="1" min="10" max="10"/>
   </cols>

--- a/files/九龙-启德-The Henley I.xlsx
+++ b/files/九龙-启德-The Henley I.xlsx
@@ -796,14 +796,14 @@
       </c>
       <c r="J3" s="3" t="inlineStr">
         <is>
-          <t>12%</t>
+          <t>9%</t>
         </is>
       </c>
       <c r="K3" s="5" t="n">
-        <v>12629750</v>
+        <v>13134940</v>
       </c>
       <c r="L3" s="5" t="n">
-        <v>30215</v>
+        <v>31423</v>
       </c>
       <c r="M3" s="3" t="inlineStr">
         <is>
@@ -1176,14 +1176,14 @@
       </c>
       <c r="J9" s="3" t="inlineStr">
         <is>
-          <t>12%</t>
+          <t>9%</t>
         </is>
       </c>
       <c r="K9" s="5" t="n">
-        <v>9963625</v>
+        <v>10362170</v>
       </c>
       <c r="L9" s="5" t="n">
-        <v>23836</v>
+        <v>24790</v>
       </c>
       <c r="M9" s="3" t="inlineStr">
         <is>
@@ -1548,14 +1548,14 @@
       </c>
       <c r="J15" s="3" t="inlineStr">
         <is>
-          <t>12%</t>
+          <t>4%</t>
         </is>
       </c>
       <c r="K15" s="5" t="n">
-        <v>17629500</v>
+        <v>19442820</v>
       </c>
       <c r="L15" s="5" t="n">
-        <v>32054</v>
+        <v>35351</v>
       </c>
       <c r="M15" s="3" t="inlineStr">
         <is>
@@ -1610,14 +1610,14 @@
       </c>
       <c r="J16" s="3" t="inlineStr">
         <is>
-          <t>12%</t>
+          <t>4%</t>
         </is>
       </c>
       <c r="K16" s="5" t="n">
-        <v>17802750</v>
+        <v>19633890</v>
       </c>
       <c r="L16" s="5" t="n">
-        <v>32369</v>
+        <v>35698</v>
       </c>
       <c r="M16" s="3" t="inlineStr">
         <is>
@@ -1734,14 +1734,14 @@
       </c>
       <c r="J18" s="3" t="inlineStr">
         <is>
-          <t>12%</t>
+          <t>9%</t>
         </is>
       </c>
       <c r="K18" s="5" t="n">
-        <v>9850750</v>
+        <v>10244780</v>
       </c>
       <c r="L18" s="5" t="n">
-        <v>23566</v>
+        <v>24509</v>
       </c>
       <c r="M18" s="3" t="inlineStr">
         <is>
@@ -2106,14 +2106,14 @@
       </c>
       <c r="J24" s="3" t="inlineStr">
         <is>
-          <t>12%</t>
+          <t>4%</t>
         </is>
       </c>
       <c r="K24" s="5" t="n">
-        <v>17431750</v>
+        <v>19224730</v>
       </c>
       <c r="L24" s="5" t="n">
-        <v>31694</v>
+        <v>34954</v>
       </c>
       <c r="M24" s="3" t="inlineStr">
         <is>
@@ -2168,14 +2168,14 @@
       </c>
       <c r="J25" s="3" t="inlineStr">
         <is>
-          <t>12%</t>
+          <t>4%</t>
         </is>
       </c>
       <c r="K25" s="5" t="n">
-        <v>17603250</v>
+        <v>19413870</v>
       </c>
       <c r="L25" s="5" t="n">
-        <v>32006</v>
+        <v>35298</v>
       </c>
       <c r="M25" s="3" t="inlineStr">
         <is>
@@ -2292,14 +2292,14 @@
       </c>
       <c r="J27" s="3" t="inlineStr">
         <is>
-          <t>12%</t>
+          <t>9%</t>
         </is>
       </c>
       <c r="K27" s="5" t="n">
-        <v>9771125</v>
+        <v>10161970</v>
       </c>
       <c r="L27" s="5" t="n">
-        <v>23432</v>
+        <v>24369</v>
       </c>
       <c r="M27" s="3" t="inlineStr">
         <is>
@@ -2664,14 +2664,14 @@
       </c>
       <c r="J33" s="3" t="inlineStr">
         <is>
-          <t>12%</t>
+          <t>4%</t>
         </is>
       </c>
       <c r="K33" s="5" t="n">
-        <v>17332875</v>
+        <v>19115685</v>
       </c>
       <c r="L33" s="5" t="n">
-        <v>31514</v>
+        <v>34756</v>
       </c>
       <c r="M33" s="3" t="inlineStr">
         <is>
@@ -2726,14 +2726,14 @@
       </c>
       <c r="J34" s="3" t="inlineStr">
         <is>
-          <t>12%</t>
+          <t>4%</t>
         </is>
       </c>
       <c r="K34" s="5" t="n">
-        <v>17503500</v>
+        <v>19303860</v>
       </c>
       <c r="L34" s="5" t="n">
-        <v>31825</v>
+        <v>35098</v>
       </c>
       <c r="M34" s="3" t="inlineStr">
         <is>
@@ -3284,14 +3284,14 @@
       </c>
       <c r="J43" s="3" t="inlineStr">
         <is>
-          <t>12%</t>
+          <t>4%</t>
         </is>
       </c>
       <c r="K43" s="5" t="n">
-        <v>17452750</v>
+        <v>19247890</v>
       </c>
       <c r="L43" s="5" t="n">
-        <v>31732</v>
+        <v>34996</v>
       </c>
       <c r="M43" s="3" t="inlineStr">
         <is>
@@ -3780,14 +3780,14 @@
       </c>
       <c r="J51" s="3" t="inlineStr">
         <is>
-          <t>12%</t>
+          <t>4%</t>
         </is>
       </c>
       <c r="K51" s="5" t="n">
-        <v>17233125</v>
+        <v>19005675</v>
       </c>
       <c r="L51" s="5" t="n">
-        <v>31333</v>
+        <v>34556</v>
       </c>
       <c r="M51" s="3" t="inlineStr">
         <is>
@@ -3966,14 +3966,14 @@
       </c>
       <c r="J54" s="3" t="inlineStr">
         <is>
-          <t>12%</t>
+          <t>9%</t>
         </is>
       </c>
       <c r="K54" s="5" t="n">
-        <v>9686250</v>
+        <v>10073700</v>
       </c>
       <c r="L54" s="5" t="n">
-        <v>23228</v>
+        <v>24158</v>
       </c>
       <c r="M54" s="3" t="inlineStr">
         <is>
@@ -4338,14 +4338,14 @@
       </c>
       <c r="J60" s="3" t="inlineStr">
         <is>
-          <t>12%</t>
+          <t>4%</t>
         </is>
       </c>
       <c r="K60" s="5" t="n">
-        <v>17184125</v>
+        <v>18951635</v>
       </c>
       <c r="L60" s="5" t="n">
-        <v>31244</v>
+        <v>34458</v>
       </c>
       <c r="M60" s="3" t="inlineStr">
         <is>
@@ -4400,14 +4400,14 @@
       </c>
       <c r="J61" s="3" t="inlineStr">
         <is>
-          <t>12%</t>
+          <t>4%</t>
         </is>
       </c>
       <c r="K61" s="5" t="n">
-        <v>17353875</v>
+        <v>19138845</v>
       </c>
       <c r="L61" s="5" t="n">
-        <v>31552</v>
+        <v>34798</v>
       </c>
       <c r="M61" s="3" t="inlineStr">
         <is>
@@ -4958,14 +4958,14 @@
       </c>
       <c r="J70" s="3" t="inlineStr">
         <is>
-          <t>12%</t>
+          <t>4%</t>
         </is>
       </c>
       <c r="K70" s="5" t="n">
-        <v>17303125</v>
+        <v>19082875</v>
       </c>
       <c r="L70" s="5" t="n">
-        <v>31460</v>
+        <v>34696</v>
       </c>
       <c r="M70" s="3" t="inlineStr">
         <is>
@@ -5454,14 +5454,14 @@
       </c>
       <c r="J78" s="3" t="inlineStr">
         <is>
-          <t>12%</t>
+          <t>4%</t>
         </is>
       </c>
       <c r="K78" s="5" t="n">
-        <v>17084375</v>
+        <v>18841625</v>
       </c>
       <c r="L78" s="5" t="n">
-        <v>31062</v>
+        <v>34258</v>
       </c>
       <c r="M78" s="3" t="inlineStr">
         <is>
@@ -5516,14 +5516,14 @@
       </c>
       <c r="J79" s="3" t="inlineStr">
         <is>
-          <t>12%</t>
+          <t>4%</t>
         </is>
       </c>
       <c r="K79" s="5" t="n">
-        <v>17253250</v>
+        <v>19027870</v>
       </c>
       <c r="L79" s="5" t="n">
-        <v>31370</v>
+        <v>34596</v>
       </c>
       <c r="M79" s="3" t="inlineStr">
         <is>
@@ -6074,14 +6074,14 @@
       </c>
       <c r="J88" s="3" t="inlineStr">
         <is>
-          <t>12%</t>
+          <t>4%</t>
         </is>
       </c>
       <c r="K88" s="5" t="n">
-        <v>17203375</v>
+        <v>18972865</v>
       </c>
       <c r="L88" s="5" t="n">
-        <v>31279</v>
+        <v>34496</v>
       </c>
       <c r="M88" s="3" t="inlineStr">
         <is>
@@ -6570,14 +6570,14 @@
       </c>
       <c r="J96" s="3" t="inlineStr">
         <is>
-          <t>12%</t>
+          <t>4%</t>
         </is>
       </c>
       <c r="K96" s="5" t="n">
-        <v>16985500</v>
+        <v>18732580</v>
       </c>
       <c r="L96" s="5" t="n">
-        <v>30883</v>
+        <v>34059</v>
       </c>
       <c r="M96" s="3" t="inlineStr">
         <is>
@@ -7128,14 +7128,14 @@
       </c>
       <c r="J105" s="3" t="inlineStr">
         <is>
-          <t>12%</t>
+          <t>4%</t>
         </is>
       </c>
       <c r="K105" s="5" t="n">
-        <v>16936500</v>
+        <v>18678540</v>
       </c>
       <c r="L105" s="5" t="n">
-        <v>30794</v>
+        <v>33961</v>
       </c>
       <c r="M105" s="3" t="inlineStr">
         <is>
@@ -7190,14 +7190,14 @@
       </c>
       <c r="J106" s="3" t="inlineStr">
         <is>
-          <t>12%</t>
+          <t>4%</t>
         </is>
       </c>
       <c r="K106" s="5" t="n">
-        <v>17102750</v>
+        <v>18861890</v>
       </c>
       <c r="L106" s="5" t="n">
-        <v>31096</v>
+        <v>34294</v>
       </c>
       <c r="M106" s="3" t="inlineStr">
         <is>
@@ -7686,14 +7686,14 @@
       </c>
       <c r="J114" s="3" t="inlineStr">
         <is>
-          <t>12%</t>
+          <t>4%</t>
         </is>
       </c>
       <c r="K114" s="5" t="n">
-        <v>16836750</v>
+        <v>18568530</v>
       </c>
       <c r="L114" s="5" t="n">
-        <v>30612</v>
+        <v>33761</v>
       </c>
       <c r="M114" s="3" t="inlineStr">
         <is>
@@ -8306,14 +8306,14 @@
       </c>
       <c r="J124" s="3" t="inlineStr">
         <is>
-          <t>12%</t>
+          <t>4%</t>
         </is>
       </c>
       <c r="K124" s="5" t="n">
-        <v>16953125</v>
+        <v>18696875</v>
       </c>
       <c r="L124" s="5" t="n">
-        <v>30824</v>
+        <v>33994</v>
       </c>
       <c r="M124" s="3" t="inlineStr">
         <is>
@@ -8802,14 +8802,14 @@
       </c>
       <c r="J132" s="3" t="inlineStr">
         <is>
-          <t>12%</t>
+          <t>4%</t>
         </is>
       </c>
       <c r="K132" s="5" t="n">
-        <v>16737875</v>
+        <v>18459485</v>
       </c>
       <c r="L132" s="5" t="n">
-        <v>30432</v>
+        <v>33563</v>
       </c>
       <c r="M132" s="3" t="inlineStr">
         <is>
@@ -8864,14 +8864,14 @@
       </c>
       <c r="J133" s="3" t="inlineStr">
         <is>
-          <t>12%</t>
+          <t>4%</t>
         </is>
       </c>
       <c r="K133" s="5" t="n">
-        <v>16903250</v>
+        <v>18641870</v>
       </c>
       <c r="L133" s="5" t="n">
-        <v>30733</v>
+        <v>33894</v>
       </c>
       <c r="M133" s="3" t="inlineStr">
         <is>
@@ -9360,14 +9360,14 @@
       </c>
       <c r="J141" s="3" t="inlineStr">
         <is>
-          <t>12%</t>
+          <t>4%</t>
         </is>
       </c>
       <c r="K141" s="5" t="n">
-        <v>16688000</v>
+        <v>18404480</v>
       </c>
       <c r="L141" s="5" t="n">
-        <v>30342</v>
+        <v>33463</v>
       </c>
       <c r="M141" s="3" t="inlineStr">
         <is>
@@ -9422,14 +9422,14 @@
       </c>
       <c r="J142" s="3" t="inlineStr">
         <is>
-          <t>12%</t>
+          <t>4%</t>
         </is>
       </c>
       <c r="K142" s="5" t="n">
-        <v>16852500</v>
+        <v>18585900</v>
       </c>
       <c r="L142" s="5" t="n">
-        <v>30641</v>
+        <v>33793</v>
       </c>
       <c r="M142" s="3" t="inlineStr">
         <is>
@@ -9918,14 +9918,14 @@
       </c>
       <c r="J150" s="3" t="inlineStr">
         <is>
-          <t>12%</t>
+          <t>4%</t>
         </is>
       </c>
       <c r="K150" s="5" t="n">
-        <v>16639000</v>
+        <v>18350440</v>
       </c>
       <c r="L150" s="5" t="n">
-        <v>30253</v>
+        <v>33364</v>
       </c>
       <c r="M150" s="3" t="inlineStr">
         <is>
@@ -9980,14 +9980,14 @@
       </c>
       <c r="J151" s="3" t="inlineStr">
         <is>
-          <t>12%</t>
+          <t>4%</t>
         </is>
       </c>
       <c r="K151" s="5" t="n">
-        <v>16802625</v>
+        <v>18530895</v>
       </c>
       <c r="L151" s="5" t="n">
-        <v>30550</v>
+        <v>33693</v>
       </c>
       <c r="M151" s="3" t="inlineStr">
         <is>
@@ -10538,14 +10538,14 @@
       </c>
       <c r="J160" s="3" t="inlineStr">
         <is>
-          <t>12%</t>
+          <t>4%</t>
         </is>
       </c>
       <c r="K160" s="5" t="n">
-        <v>16752750</v>
+        <v>18475890</v>
       </c>
       <c r="L160" s="5" t="n">
-        <v>30460</v>
+        <v>33593</v>
       </c>
       <c r="M160" s="3" t="inlineStr">
         <is>
@@ -11034,14 +11034,14 @@
       </c>
       <c r="J168" s="3" t="inlineStr">
         <is>
-          <t>12%</t>
+          <t>4%</t>
         </is>
       </c>
       <c r="K168" s="5" t="n">
-        <v>16540125</v>
+        <v>18241395</v>
       </c>
       <c r="L168" s="5" t="n">
-        <v>30073</v>
+        <v>33166</v>
       </c>
       <c r="M168" s="3" t="inlineStr">
         <is>
@@ -11096,14 +11096,14 @@
       </c>
       <c r="J169" s="3" t="inlineStr">
         <is>
-          <t>12%</t>
+          <t>4%</t>
         </is>
       </c>
       <c r="K169" s="5" t="n">
-        <v>16702000</v>
+        <v>18419920</v>
       </c>
       <c r="L169" s="5" t="n">
-        <v>30367</v>
+        <v>33491</v>
       </c>
       <c r="M169" s="3" t="inlineStr">
         <is>
@@ -11592,14 +11592,14 @@
       </c>
       <c r="J177" s="3" t="inlineStr">
         <is>
-          <t>12%</t>
+          <t>4%</t>
         </is>
       </c>
       <c r="K177" s="5" t="n">
-        <v>16490250</v>
+        <v>18186390</v>
       </c>
       <c r="L177" s="5" t="n">
-        <v>29982</v>
+        <v>33066</v>
       </c>
       <c r="M177" s="3" t="inlineStr">
         <is>
@@ -11654,14 +11654,14 @@
       </c>
       <c r="J178" s="3" t="inlineStr">
         <is>
-          <t>12%</t>
+          <t>4%</t>
         </is>
       </c>
       <c r="K178" s="5" t="n">
-        <v>16653000</v>
+        <v>18365880</v>
       </c>
       <c r="L178" s="5" t="n">
-        <v>30278</v>
+        <v>33393</v>
       </c>
       <c r="M178" s="3" t="inlineStr">
         <is>
@@ -12150,14 +12150,14 @@
       </c>
       <c r="J186" s="3" t="inlineStr">
         <is>
-          <t>12%</t>
+          <t>4%</t>
         </is>
       </c>
       <c r="K186" s="5" t="n">
-        <v>16490250</v>
+        <v>18186390</v>
       </c>
       <c r="L186" s="5" t="n">
-        <v>29982</v>
+        <v>33066</v>
       </c>
       <c r="M186" s="3" t="inlineStr">
         <is>
@@ -12212,14 +12212,14 @@
       </c>
       <c r="J187" s="3" t="inlineStr">
         <is>
-          <t>12%</t>
+          <t>4%</t>
         </is>
       </c>
       <c r="K187" s="5" t="n">
-        <v>16653000</v>
+        <v>18365880</v>
       </c>
       <c r="L187" s="5" t="n">
-        <v>30278</v>
+        <v>33393</v>
       </c>
       <c r="M187" s="3" t="inlineStr">
         <is>
@@ -12708,14 +12708,14 @@
       </c>
       <c r="J195" s="3" t="inlineStr">
         <is>
-          <t>12%</t>
+          <t>4%</t>
         </is>
       </c>
       <c r="K195" s="5" t="n">
-        <v>16440375</v>
+        <v>18131385</v>
       </c>
       <c r="L195" s="5" t="n">
-        <v>29892</v>
+        <v>32966</v>
       </c>
       <c r="M195" s="3" t="inlineStr">
         <is>
@@ -12770,14 +12770,14 @@
       </c>
       <c r="J196" s="3" t="inlineStr">
         <is>
-          <t>12%</t>
+          <t>4%</t>
         </is>
       </c>
       <c r="K196" s="5" t="n">
-        <v>16603125</v>
+        <v>18310875</v>
       </c>
       <c r="L196" s="5" t="n">
-        <v>30188</v>
+        <v>33292</v>
       </c>
       <c r="M196" s="3" t="inlineStr">
         <is>
@@ -13266,14 +13266,14 @@
       </c>
       <c r="J204" s="3" t="inlineStr">
         <is>
-          <t>12%</t>
+          <t>4%</t>
         </is>
       </c>
       <c r="K204" s="5" t="n">
-        <v>16391375</v>
+        <v>18077345</v>
       </c>
       <c r="L204" s="5" t="n">
-        <v>29802</v>
+        <v>32868</v>
       </c>
       <c r="M204" s="3" t="inlineStr">
         <is>
@@ -13328,14 +13328,14 @@
       </c>
       <c r="J205" s="3" t="inlineStr">
         <is>
-          <t>12%</t>
+          <t>4%</t>
         </is>
       </c>
       <c r="K205" s="5" t="n">
-        <v>16552375</v>
+        <v>18254905</v>
       </c>
       <c r="L205" s="5" t="n">
-        <v>30095</v>
+        <v>33191</v>
       </c>
       <c r="M205" s="3" t="inlineStr">
         <is>
@@ -13824,14 +13824,14 @@
       </c>
       <c r="J213" s="3" t="inlineStr">
         <is>
-          <t>12%</t>
+          <t>4%</t>
         </is>
       </c>
       <c r="K213" s="5" t="n">
-        <v>16341500</v>
+        <v>18022340</v>
       </c>
       <c r="L213" s="5" t="n">
-        <v>29712</v>
+        <v>32768</v>
       </c>
       <c r="M213" s="3" t="inlineStr">
         <is>
@@ -13886,14 +13886,14 @@
       </c>
       <c r="J214" s="3" t="inlineStr">
         <is>
-          <t>12%</t>
+          <t>4%</t>
         </is>
       </c>
       <c r="K214" s="5" t="n">
-        <v>16502500</v>
+        <v>18199900</v>
       </c>
       <c r="L214" s="5" t="n">
-        <v>30005</v>
+        <v>33091</v>
       </c>
       <c r="M214" s="3" t="inlineStr">
         <is>
@@ -14320,14 +14320,14 @@
       </c>
       <c r="J221" s="3" t="inlineStr">
         <is>
-          <t>12%</t>
+          <t>4%</t>
         </is>
       </c>
       <c r="K221" s="5" t="n">
-        <v>16319625</v>
+        <v>17998215</v>
       </c>
       <c r="L221" s="5" t="n">
-        <v>29889</v>
+        <v>32964</v>
       </c>
       <c r="M221" s="3" t="inlineStr">
         <is>
@@ -14382,14 +14382,14 @@
       </c>
       <c r="J222" s="3" t="inlineStr">
         <is>
-          <t>12%</t>
+          <t>4%</t>
         </is>
       </c>
       <c r="K222" s="5" t="n">
-        <v>16291625</v>
+        <v>17967335</v>
       </c>
       <c r="L222" s="5" t="n">
-        <v>29621</v>
+        <v>32668</v>
       </c>
       <c r="M222" s="3" t="inlineStr">
         <is>
@@ -14444,14 +14444,14 @@
       </c>
       <c r="J223" s="3" t="inlineStr">
         <is>
-          <t>12%</t>
+          <t>4%</t>
         </is>
       </c>
       <c r="K223" s="5" t="n">
-        <v>16452625</v>
+        <v>18144895</v>
       </c>
       <c r="L223" s="5" t="n">
-        <v>29914</v>
+        <v>32991</v>
       </c>
       <c r="M223" s="3" t="inlineStr">
         <is>
@@ -14568,14 +14568,14 @@
       </c>
       <c r="J225" s="3" t="inlineStr">
         <is>
-          <t>12%</t>
+          <t>9%</t>
         </is>
       </c>
       <c r="K225" s="5" t="n">
-        <v>9122750</v>
+        <v>9487660</v>
       </c>
       <c r="L225" s="5" t="n">
-        <v>21877</v>
+        <v>22752</v>
       </c>
       <c r="M225" s="3" t="inlineStr">
         <is>
@@ -14940,14 +14940,14 @@
       </c>
       <c r="J231" s="3" t="inlineStr">
         <is>
-          <t>12%</t>
+          <t>4%</t>
         </is>
       </c>
       <c r="K231" s="5" t="n">
-        <v>16044000</v>
+        <v>17694240</v>
       </c>
       <c r="L231" s="5" t="n">
-        <v>29171</v>
+        <v>32171</v>
       </c>
       <c r="M231" s="3" t="inlineStr">
         <is>
@@ -15002,14 +15002,14 @@
       </c>
       <c r="J232" s="3" t="inlineStr">
         <is>
-          <t>12%</t>
+          <t>4%</t>
         </is>
       </c>
       <c r="K232" s="5" t="n">
-        <v>16202375</v>
+        <v>17868905</v>
       </c>
       <c r="L232" s="5" t="n">
-        <v>29459</v>
+        <v>32489</v>
       </c>
       <c r="M232" s="3" t="inlineStr">
         <is>
@@ -15064,14 +15064,14 @@
       </c>
       <c r="J233" s="3" t="inlineStr">
         <is>
-          <t>12%</t>
+          <t>4%</t>
         </is>
       </c>
       <c r="K233" s="5" t="n">
-        <v>25670750</v>
+        <v>28311170</v>
       </c>
       <c r="L233" s="5" t="n">
-        <v>28876</v>
+        <v>31846</v>
       </c>
       <c r="M233" s="3" t="inlineStr">
         <is>
@@ -15498,14 +15498,14 @@
       </c>
       <c r="J240" s="3" t="inlineStr">
         <is>
-          <t>12%</t>
+          <t>4%</t>
         </is>
       </c>
       <c r="K240" s="5" t="n">
-        <v>15995000</v>
+        <v>17640200</v>
       </c>
       <c r="L240" s="5" t="n">
-        <v>29082</v>
+        <v>32073</v>
       </c>
       <c r="M240" s="3" t="inlineStr">
         <is>
@@ -15560,14 +15560,14 @@
       </c>
       <c r="J241" s="3" t="inlineStr">
         <is>
-          <t>12%</t>
+          <t>4%</t>
         </is>
       </c>
       <c r="K241" s="5" t="n">
-        <v>16152500</v>
+        <v>17813900</v>
       </c>
       <c r="L241" s="5" t="n">
-        <v>29368</v>
+        <v>32389</v>
       </c>
       <c r="M241" s="3" t="inlineStr">
         <is>
@@ -15622,14 +15622,14 @@
       </c>
       <c r="J242" s="3" t="inlineStr">
         <is>
-          <t>12%</t>
+          <t>4%</t>
         </is>
       </c>
       <c r="K242" s="5" t="n">
-        <v>25079250</v>
+        <v>27658830</v>
       </c>
       <c r="L242" s="5" t="n">
-        <v>28211</v>
+        <v>31112</v>
       </c>
       <c r="M242" s="3" t="inlineStr">
         <is>
@@ -15994,14 +15994,14 @@
       </c>
       <c r="J248" s="3" t="inlineStr">
         <is>
-          <t>12%</t>
+          <t>4%</t>
         </is>
       </c>
       <c r="K248" s="5" t="n">
-        <v>16018625</v>
+        <v>17666255</v>
       </c>
       <c r="L248" s="5" t="n">
-        <v>29338</v>
+        <v>32356</v>
       </c>
       <c r="M248" s="3" t="inlineStr">
         <is>
@@ -16056,14 +16056,14 @@
       </c>
       <c r="J249" s="3" t="inlineStr">
         <is>
-          <t>12%</t>
+          <t>4%</t>
         </is>
       </c>
       <c r="K249" s="5" t="n">
-        <v>15995000</v>
+        <v>17640200</v>
       </c>
       <c r="L249" s="5" t="n">
-        <v>29082</v>
+        <v>32073</v>
       </c>
       <c r="M249" s="3" t="inlineStr">
         <is>
@@ -16118,14 +16118,14 @@
       </c>
       <c r="J250" s="3" t="inlineStr">
         <is>
-          <t>12%</t>
+          <t>4%</t>
         </is>
       </c>
       <c r="K250" s="5" t="n">
-        <v>16152500</v>
+        <v>17813900</v>
       </c>
       <c r="L250" s="5" t="n">
-        <v>29368</v>
+        <v>32389</v>
       </c>
       <c r="M250" s="3" t="inlineStr">
         <is>
@@ -16180,14 +16180,14 @@
       </c>
       <c r="J251" s="3" t="inlineStr">
         <is>
-          <t>12%</t>
+          <t>4%</t>
         </is>
       </c>
       <c r="K251" s="5" t="n">
-        <v>25076625</v>
+        <v>27655935</v>
       </c>
       <c r="L251" s="5" t="n">
-        <v>28208</v>
+        <v>31109</v>
       </c>
       <c r="M251" s="3" t="inlineStr">
         <is>
@@ -16552,14 +16552,14 @@
       </c>
       <c r="J257" s="3" t="inlineStr">
         <is>
-          <t>12%</t>
+          <t>4%</t>
         </is>
       </c>
       <c r="K257" s="5" t="n">
-        <v>15967875</v>
+        <v>17610285</v>
       </c>
       <c r="L257" s="5" t="n">
-        <v>29245</v>
+        <v>32253</v>
       </c>
       <c r="M257" s="3" t="inlineStr">
         <is>
@@ -16614,14 +16614,14 @@
       </c>
       <c r="J258" s="3" t="inlineStr">
         <is>
-          <t>12%</t>
+          <t>4%</t>
         </is>
       </c>
       <c r="K258" s="5" t="n">
-        <v>15945125</v>
+        <v>17585195</v>
       </c>
       <c r="L258" s="5" t="n">
-        <v>28991</v>
+        <v>31973</v>
       </c>
       <c r="M258" s="3" t="inlineStr">
         <is>
@@ -16676,14 +16676,14 @@
       </c>
       <c r="J259" s="3" t="inlineStr">
         <is>
-          <t>12%</t>
+          <t>4%</t>
         </is>
       </c>
       <c r="K259" s="5" t="n">
-        <v>16101750</v>
+        <v>17757930</v>
       </c>
       <c r="L259" s="5" t="n">
-        <v>29276</v>
+        <v>32287</v>
       </c>
       <c r="M259" s="3" t="inlineStr">
         <is>
@@ -16738,14 +16738,14 @@
       </c>
       <c r="J260" s="3" t="inlineStr">
         <is>
-          <t>12%</t>
+          <t>4%</t>
         </is>
       </c>
       <c r="K260" s="5" t="n">
-        <v>25013625</v>
+        <v>27586455</v>
       </c>
       <c r="L260" s="5" t="n">
-        <v>28137</v>
+        <v>31031</v>
       </c>
       <c r="M260" s="3" t="inlineStr">
         <is>
@@ -17110,14 +17110,14 @@
       </c>
       <c r="J266" s="3" t="inlineStr">
         <is>
-          <t>12%</t>
+          <t>4%</t>
         </is>
       </c>
       <c r="K266" s="5" t="n">
-        <v>15603875</v>
+        <v>17208845</v>
       </c>
       <c r="L266" s="5" t="n">
-        <v>28579</v>
+        <v>31518</v>
       </c>
       <c r="M266" s="3" t="inlineStr">
         <is>
@@ -17172,14 +17172,14 @@
       </c>
       <c r="J267" s="3" t="inlineStr">
         <is>
-          <t>12%</t>
+          <t>4%</t>
         </is>
       </c>
       <c r="K267" s="5" t="n">
-        <v>15895250</v>
+        <v>17530190</v>
       </c>
       <c r="L267" s="5" t="n">
-        <v>28900</v>
+        <v>31873</v>
       </c>
       <c r="M267" s="3" t="inlineStr">
         <is>
@@ -17234,14 +17234,14 @@
       </c>
       <c r="J268" s="3" t="inlineStr">
         <is>
-          <t>12%</t>
+          <t>4%</t>
         </is>
       </c>
       <c r="K268" s="5" t="n">
-        <v>16051875</v>
+        <v>17702925</v>
       </c>
       <c r="L268" s="5" t="n">
-        <v>29185</v>
+        <v>32187</v>
       </c>
       <c r="M268" s="3" t="inlineStr">
         <is>
@@ -17296,14 +17296,14 @@
       </c>
       <c r="J269" s="3" t="inlineStr">
         <is>
-          <t>12%</t>
+          <t>4%</t>
         </is>
       </c>
       <c r="K269" s="5" t="n">
-        <v>24936625</v>
+        <v>27501535</v>
       </c>
       <c r="L269" s="5" t="n">
-        <v>28050</v>
+        <v>30935</v>
       </c>
       <c r="M269" s="3" t="inlineStr">
         <is>
@@ -17668,14 +17668,14 @@
       </c>
       <c r="J275" s="3" t="inlineStr">
         <is>
-          <t>12%</t>
+          <t>4%</t>
         </is>
       </c>
       <c r="K275" s="5" t="n">
-        <v>15554000</v>
+        <v>17153840</v>
       </c>
       <c r="L275" s="5" t="n">
-        <v>28487</v>
+        <v>31417</v>
       </c>
       <c r="M275" s="3" t="inlineStr">
         <is>
@@ -17730,14 +17730,14 @@
       </c>
       <c r="J276" s="3" t="inlineStr">
         <is>
-          <t>12%</t>
+          <t>4%</t>
         </is>
       </c>
       <c r="K276" s="5" t="n">
-        <v>15846250</v>
+        <v>17476150</v>
       </c>
       <c r="L276" s="5" t="n">
-        <v>28811</v>
+        <v>31775</v>
       </c>
       <c r="M276" s="3" t="inlineStr">
         <is>
@@ -17792,14 +17792,14 @@
       </c>
       <c r="J277" s="3" t="inlineStr">
         <is>
-          <t>12%</t>
+          <t>4%</t>
         </is>
       </c>
       <c r="K277" s="5" t="n">
-        <v>16002000</v>
+        <v>17647920</v>
       </c>
       <c r="L277" s="5" t="n">
-        <v>29095</v>
+        <v>32087</v>
       </c>
       <c r="M277" s="3" t="inlineStr">
         <is>
@@ -17854,14 +17854,14 @@
       </c>
       <c r="J278" s="3" t="inlineStr">
         <is>
-          <t>12%</t>
+          <t>4%</t>
         </is>
       </c>
       <c r="K278" s="5" t="n">
-        <v>24857875</v>
+        <v>27414685</v>
       </c>
       <c r="L278" s="5" t="n">
-        <v>27962</v>
+        <v>30838</v>
       </c>
       <c r="M278" s="3" t="inlineStr">
         <is>
@@ -18226,14 +18226,14 @@
       </c>
       <c r="J284" s="3" t="inlineStr">
         <is>
-          <t>12%</t>
+          <t>4%</t>
         </is>
       </c>
       <c r="K284" s="5" t="n">
-        <v>15456000</v>
+        <v>17045760</v>
       </c>
       <c r="L284" s="5" t="n">
-        <v>28308</v>
+        <v>31219</v>
       </c>
       <c r="M284" s="3" t="inlineStr">
         <is>
@@ -18288,14 +18288,14 @@
       </c>
       <c r="J285" s="3" t="inlineStr">
         <is>
-          <t>12%</t>
+          <t>4%</t>
         </is>
       </c>
       <c r="K285" s="5" t="n">
-        <v>15746500</v>
+        <v>17366140</v>
       </c>
       <c r="L285" s="5" t="n">
-        <v>28630</v>
+        <v>31575</v>
       </c>
       <c r="M285" s="3" t="inlineStr">
         <is>
@@ -18350,14 +18350,14 @@
       </c>
       <c r="J286" s="3" t="inlineStr">
         <is>
-          <t>12%</t>
+          <t>4%</t>
         </is>
       </c>
       <c r="K286" s="5" t="n">
-        <v>15902250</v>
+        <v>17537910</v>
       </c>
       <c r="L286" s="5" t="n">
-        <v>28913</v>
+        <v>31887</v>
       </c>
       <c r="M286" s="3" t="inlineStr">
         <is>
@@ -18412,14 +18412,14 @@
       </c>
       <c r="J287" s="3" t="inlineStr">
         <is>
-          <t>12%</t>
+          <t>4%</t>
         </is>
       </c>
       <c r="K287" s="5" t="n">
-        <v>24703000</v>
+        <v>27243880</v>
       </c>
       <c r="L287" s="5" t="n">
-        <v>27787</v>
+        <v>30646</v>
       </c>
       <c r="M287" s="3" t="inlineStr">
         <is>
@@ -18784,14 +18784,14 @@
       </c>
       <c r="J293" s="3" t="inlineStr">
         <is>
-          <t>12%</t>
+          <t>4%</t>
         </is>
       </c>
       <c r="K293" s="5" t="n">
-        <v>15308125</v>
+        <v>16882675</v>
       </c>
       <c r="L293" s="5" t="n">
-        <v>28037</v>
+        <v>30921</v>
       </c>
       <c r="M293" s="3" t="inlineStr">
         <is>
@@ -18846,14 +18846,14 @@
       </c>
       <c r="J294" s="3" t="inlineStr">
         <is>
-          <t>12%</t>
+          <t>4%</t>
         </is>
       </c>
       <c r="K294" s="5" t="n">
-        <v>15598625</v>
+        <v>17203055</v>
       </c>
       <c r="L294" s="5" t="n">
-        <v>28361</v>
+        <v>31278</v>
       </c>
       <c r="M294" s="3" t="inlineStr">
         <is>
@@ -18908,14 +18908,14 @@
       </c>
       <c r="J295" s="3" t="inlineStr">
         <is>
-          <t>12%</t>
+          <t>4%</t>
         </is>
       </c>
       <c r="K295" s="5" t="n">
-        <v>15751750</v>
+        <v>17371930</v>
       </c>
       <c r="L295" s="5" t="n">
-        <v>28640</v>
+        <v>31585</v>
       </c>
       <c r="M295" s="3" t="inlineStr">
         <is>
@@ -18970,14 +18970,14 @@
       </c>
       <c r="J296" s="3" t="inlineStr">
         <is>
-          <t>12%</t>
+          <t>4%</t>
         </is>
       </c>
       <c r="K296" s="5" t="n">
-        <v>24469375</v>
+        <v>26986225</v>
       </c>
       <c r="L296" s="5" t="n">
-        <v>27525</v>
+        <v>30356</v>
       </c>
       <c r="M296" s="3" t="inlineStr">
         <is>

--- a/files/九龙-启德-The Henley I.xlsx
+++ b/files/九龙-启德-The Henley I.xlsx
@@ -666,12 +666,12 @@
     <col width="13" customWidth="1" min="5" max="5"/>
     <col width="12" customWidth="1" min="6" max="6"/>
     <col width="13" customWidth="1" min="7" max="7"/>
-    <col width="13" customWidth="1" min="8" max="8"/>
-    <col width="14" customWidth="1" min="9" max="9"/>
+    <col width="19" customWidth="1" min="8" max="8"/>
+    <col width="16" customWidth="1" min="9" max="9"/>
     <col width="12" customWidth="1" min="10" max="10"/>
-    <col width="13" customWidth="1" min="11" max="11"/>
-    <col width="14" customWidth="1" min="12" max="12"/>
-    <col width="17" customWidth="1" min="13" max="13"/>
+    <col width="19" customWidth="1" min="11" max="11"/>
+    <col width="16" customWidth="1" min="12" max="12"/>
+    <col width="27" customWidth="1" min="13" max="13"/>
     <col width="12" customWidth="1" min="14" max="14"/>
   </cols>
   <sheetData>
@@ -796,18 +796,18 @@
       </c>
       <c r="J3" s="3" t="inlineStr">
         <is>
-          <t>9%</t>
+          <t>9.00%</t>
         </is>
       </c>
       <c r="K3" s="5" t="n">
-        <v>13134940</v>
+        <v>13134900</v>
       </c>
       <c r="L3" s="5" t="n">
         <v>31423</v>
       </c>
       <c r="M3" s="3" t="inlineStr">
         <is>
-          <t>現金付款計劃 - 90天成交</t>
+          <t>現金付款計劃 (減9.0%)</t>
         </is>
       </c>
       <c r="N3" s="3" t="inlineStr">
@@ -1176,18 +1176,18 @@
       </c>
       <c r="J9" s="3" t="inlineStr">
         <is>
-          <t>9%</t>
+          <t>9.00%</t>
         </is>
       </c>
       <c r="K9" s="5" t="n">
-        <v>10362170</v>
+        <v>10362100</v>
       </c>
       <c r="L9" s="5" t="n">
         <v>24790</v>
       </c>
       <c r="M9" s="3" t="inlineStr">
         <is>
-          <t>現金付款計劃 - 90天成交</t>
+          <t>現金付款計劃 (減9.0%)</t>
         </is>
       </c>
       <c r="N9" s="3" t="inlineStr">
@@ -1548,18 +1548,18 @@
       </c>
       <c r="J15" s="3" t="inlineStr">
         <is>
-          <t>4%</t>
+          <t>7.12%</t>
         </is>
       </c>
       <c r="K15" s="5" t="n">
-        <v>19442820</v>
+        <v>18713600</v>
       </c>
       <c r="L15" s="5" t="n">
-        <v>35351</v>
+        <v>34025</v>
       </c>
       <c r="M15" s="3" t="inlineStr">
         <is>
-          <t>現金付款計劃 - 90天成交</t>
+          <t>現金付款計劃 (減3.5%) + 代繳從價印花稅</t>
         </is>
       </c>
       <c r="N15" s="3" t="inlineStr">
@@ -1610,18 +1610,18 @@
       </c>
       <c r="J16" s="3" t="inlineStr">
         <is>
-          <t>4%</t>
+          <t>3.50%</t>
         </is>
       </c>
       <c r="K16" s="5" t="n">
-        <v>19633890</v>
+        <v>19633800</v>
       </c>
       <c r="L16" s="5" t="n">
         <v>35698</v>
       </c>
       <c r="M16" s="3" t="inlineStr">
         <is>
-          <t>現金付款計劃 - 90天成交</t>
+          <t>現金付款計劃 (減3.5%)</t>
         </is>
       </c>
       <c r="N16" s="3" t="inlineStr">
@@ -1734,18 +1734,18 @@
       </c>
       <c r="J18" s="3" t="inlineStr">
         <is>
-          <t>9%</t>
+          <t>9.00%</t>
         </is>
       </c>
       <c r="K18" s="5" t="n">
-        <v>10244780</v>
+        <v>10244700</v>
       </c>
       <c r="L18" s="5" t="n">
         <v>24509</v>
       </c>
       <c r="M18" s="3" t="inlineStr">
         <is>
-          <t>現金付款計劃 - 90天成交</t>
+          <t>現金付款計劃 (減9.0%)</t>
         </is>
       </c>
       <c r="N18" s="3" t="inlineStr">
@@ -2106,18 +2106,18 @@
       </c>
       <c r="J24" s="3" t="inlineStr">
         <is>
-          <t>4%</t>
+          <t>7.12%</t>
         </is>
       </c>
       <c r="K24" s="5" t="n">
-        <v>19224730</v>
+        <v>18503700</v>
       </c>
       <c r="L24" s="5" t="n">
-        <v>34954</v>
+        <v>33643</v>
       </c>
       <c r="M24" s="3" t="inlineStr">
         <is>
-          <t>現金付款計劃 - 90天成交</t>
+          <t>現金付款計劃 (減3.5%) + 代繳從價印花稅</t>
         </is>
       </c>
       <c r="N24" s="3" t="inlineStr">
@@ -2168,18 +2168,18 @@
       </c>
       <c r="J25" s="3" t="inlineStr">
         <is>
-          <t>4%</t>
+          <t>3.50%</t>
         </is>
       </c>
       <c r="K25" s="5" t="n">
-        <v>19413870</v>
+        <v>19413800</v>
       </c>
       <c r="L25" s="5" t="n">
         <v>35298</v>
       </c>
       <c r="M25" s="3" t="inlineStr">
         <is>
-          <t>現金付款計劃 - 90天成交</t>
+          <t>現金付款計劃 (減3.5%)</t>
         </is>
       </c>
       <c r="N25" s="3" t="inlineStr">
@@ -2292,18 +2292,18 @@
       </c>
       <c r="J27" s="3" t="inlineStr">
         <is>
-          <t>9%</t>
+          <t>9.00%</t>
         </is>
       </c>
       <c r="K27" s="5" t="n">
-        <v>10161970</v>
+        <v>10161900</v>
       </c>
       <c r="L27" s="5" t="n">
         <v>24369</v>
       </c>
       <c r="M27" s="3" t="inlineStr">
         <is>
-          <t>現金付款計劃 - 90天成交</t>
+          <t>現金付款計劃 (減9.0%)</t>
         </is>
       </c>
       <c r="N27" s="3" t="inlineStr">
@@ -2664,18 +2664,18 @@
       </c>
       <c r="J33" s="3" t="inlineStr">
         <is>
-          <t>4%</t>
+          <t>7.12%</t>
         </is>
       </c>
       <c r="K33" s="5" t="n">
-        <v>19115685</v>
+        <v>18398700</v>
       </c>
       <c r="L33" s="5" t="n">
-        <v>34756</v>
+        <v>33452</v>
       </c>
       <c r="M33" s="3" t="inlineStr">
         <is>
-          <t>現金付款計劃 - 90天成交</t>
+          <t>現金付款計劃 (減3.5%) + 代繳從價印花稅</t>
         </is>
       </c>
       <c r="N33" s="3" t="inlineStr">
@@ -2726,18 +2726,18 @@
       </c>
       <c r="J34" s="3" t="inlineStr">
         <is>
-          <t>4%</t>
+          <t>3.50%</t>
         </is>
       </c>
       <c r="K34" s="5" t="n">
-        <v>19303860</v>
+        <v>19303800</v>
       </c>
       <c r="L34" s="5" t="n">
         <v>35098</v>
       </c>
       <c r="M34" s="3" t="inlineStr">
         <is>
-          <t>現金付款計劃 - 90天成交</t>
+          <t>現金付款計劃 (減3.5%)</t>
         </is>
       </c>
       <c r="N34" s="3" t="inlineStr">
@@ -3284,18 +3284,18 @@
       </c>
       <c r="J43" s="3" t="inlineStr">
         <is>
-          <t>4%</t>
+          <t>3.50%</t>
         </is>
       </c>
       <c r="K43" s="5" t="n">
-        <v>19247890</v>
+        <v>19247800</v>
       </c>
       <c r="L43" s="5" t="n">
         <v>34996</v>
       </c>
       <c r="M43" s="3" t="inlineStr">
         <is>
-          <t>現金付款計劃 - 90天成交</t>
+          <t>現金付款計劃 (減3.5%)</t>
         </is>
       </c>
       <c r="N43" s="3" t="inlineStr">
@@ -3780,18 +3780,18 @@
       </c>
       <c r="J51" s="3" t="inlineStr">
         <is>
-          <t>4%</t>
+          <t>7.12%</t>
         </is>
       </c>
       <c r="K51" s="5" t="n">
-        <v>19005675</v>
+        <v>18292800</v>
       </c>
       <c r="L51" s="5" t="n">
-        <v>34556</v>
+        <v>33260</v>
       </c>
       <c r="M51" s="3" t="inlineStr">
         <is>
-          <t>現金付款計劃 - 90天成交</t>
+          <t>現金付款計劃 (減3.5%) + 代繳從價印花稅</t>
         </is>
       </c>
       <c r="N51" s="3" t="inlineStr">
@@ -3966,7 +3966,7 @@
       </c>
       <c r="J54" s="3" t="inlineStr">
         <is>
-          <t>9%</t>
+          <t>9.00%</t>
         </is>
       </c>
       <c r="K54" s="5" t="n">
@@ -3977,7 +3977,7 @@
       </c>
       <c r="M54" s="3" t="inlineStr">
         <is>
-          <t>現金付款計劃 - 90天成交</t>
+          <t>現金付款計劃 (減9.0%)</t>
         </is>
       </c>
       <c r="N54" s="3" t="inlineStr">
@@ -4338,18 +4338,18 @@
       </c>
       <c r="J60" s="3" t="inlineStr">
         <is>
-          <t>4%</t>
+          <t>7.12%</t>
         </is>
       </c>
       <c r="K60" s="5" t="n">
-        <v>18951635</v>
+        <v>18240900</v>
       </c>
       <c r="L60" s="5" t="n">
-        <v>34458</v>
+        <v>33165</v>
       </c>
       <c r="M60" s="3" t="inlineStr">
         <is>
-          <t>現金付款計劃 - 90天成交</t>
+          <t>現金付款計劃 (減3.5%) + 代繳從價印花稅</t>
         </is>
       </c>
       <c r="N60" s="3" t="inlineStr">
@@ -4400,18 +4400,18 @@
       </c>
       <c r="J61" s="3" t="inlineStr">
         <is>
-          <t>4%</t>
+          <t>3.50%</t>
         </is>
       </c>
       <c r="K61" s="5" t="n">
-        <v>19138845</v>
+        <v>19138800</v>
       </c>
       <c r="L61" s="5" t="n">
         <v>34798</v>
       </c>
       <c r="M61" s="3" t="inlineStr">
         <is>
-          <t>現金付款計劃 - 90天成交</t>
+          <t>現金付款計劃 (減3.5%)</t>
         </is>
       </c>
       <c r="N61" s="3" t="inlineStr">
@@ -4958,18 +4958,18 @@
       </c>
       <c r="J70" s="3" t="inlineStr">
         <is>
-          <t>4%</t>
+          <t>3.50%</t>
         </is>
       </c>
       <c r="K70" s="5" t="n">
-        <v>19082875</v>
+        <v>19082800</v>
       </c>
       <c r="L70" s="5" t="n">
         <v>34696</v>
       </c>
       <c r="M70" s="3" t="inlineStr">
         <is>
-          <t>現金付款計劃 - 90天成交</t>
+          <t>現金付款計劃 (減3.5%)</t>
         </is>
       </c>
       <c r="N70" s="3" t="inlineStr">
@@ -5454,18 +5454,18 @@
       </c>
       <c r="J78" s="3" t="inlineStr">
         <is>
-          <t>4%</t>
+          <t>7.12%</t>
         </is>
       </c>
       <c r="K78" s="5" t="n">
-        <v>18841625</v>
+        <v>18135000</v>
       </c>
       <c r="L78" s="5" t="n">
-        <v>34258</v>
+        <v>32973</v>
       </c>
       <c r="M78" s="3" t="inlineStr">
         <is>
-          <t>現金付款計劃 - 90天成交</t>
+          <t>現金付款計劃 (減3.5%) + 代繳從價印花稅</t>
         </is>
       </c>
       <c r="N78" s="3" t="inlineStr">
@@ -5516,18 +5516,18 @@
       </c>
       <c r="J79" s="3" t="inlineStr">
         <is>
-          <t>4%</t>
+          <t>3.50%</t>
         </is>
       </c>
       <c r="K79" s="5" t="n">
-        <v>19027870</v>
+        <v>19027800</v>
       </c>
       <c r="L79" s="5" t="n">
         <v>34596</v>
       </c>
       <c r="M79" s="3" t="inlineStr">
         <is>
-          <t>現金付款計劃 - 90天成交</t>
+          <t>現金付款計劃 (減3.5%)</t>
         </is>
       </c>
       <c r="N79" s="3" t="inlineStr">
@@ -6074,18 +6074,18 @@
       </c>
       <c r="J88" s="3" t="inlineStr">
         <is>
-          <t>4%</t>
+          <t>3.50%</t>
         </is>
       </c>
       <c r="K88" s="5" t="n">
-        <v>18972865</v>
+        <v>18972800</v>
       </c>
       <c r="L88" s="5" t="n">
         <v>34496</v>
       </c>
       <c r="M88" s="3" t="inlineStr">
         <is>
-          <t>現金付款計劃 - 90天成交</t>
+          <t>現金付款計劃 (減3.5%)</t>
         </is>
       </c>
       <c r="N88" s="3" t="inlineStr">
@@ -6570,18 +6570,18 @@
       </c>
       <c r="J96" s="3" t="inlineStr">
         <is>
-          <t>4%</t>
+          <t>7.12%</t>
         </is>
       </c>
       <c r="K96" s="5" t="n">
-        <v>18732580</v>
+        <v>18030000</v>
       </c>
       <c r="L96" s="5" t="n">
-        <v>34059</v>
+        <v>32782</v>
       </c>
       <c r="M96" s="3" t="inlineStr">
         <is>
-          <t>現金付款計劃 - 90天成交</t>
+          <t>現金付款計劃 (減3.5%) + 代繳從價印花稅</t>
         </is>
       </c>
       <c r="N96" s="3" t="inlineStr">
@@ -7128,18 +7128,18 @@
       </c>
       <c r="J105" s="3" t="inlineStr">
         <is>
-          <t>4%</t>
+          <t>7.12%</t>
         </is>
       </c>
       <c r="K105" s="5" t="n">
-        <v>18678540</v>
+        <v>17978000</v>
       </c>
       <c r="L105" s="5" t="n">
-        <v>33961</v>
+        <v>32687</v>
       </c>
       <c r="M105" s="3" t="inlineStr">
         <is>
-          <t>現金付款計劃 - 90天成交</t>
+          <t>現金付款計劃 (減3.5%) + 代繳從價印花稅</t>
         </is>
       </c>
       <c r="N105" s="3" t="inlineStr">
@@ -7190,18 +7190,18 @@
       </c>
       <c r="J106" s="3" t="inlineStr">
         <is>
-          <t>4%</t>
+          <t>3.50%</t>
         </is>
       </c>
       <c r="K106" s="5" t="n">
-        <v>18861890</v>
+        <v>18861800</v>
       </c>
       <c r="L106" s="5" t="n">
         <v>34294</v>
       </c>
       <c r="M106" s="3" t="inlineStr">
         <is>
-          <t>現金付款計劃 - 90天成交</t>
+          <t>現金付款計劃 (減3.5%)</t>
         </is>
       </c>
       <c r="N106" s="3" t="inlineStr">
@@ -7686,18 +7686,18 @@
       </c>
       <c r="J114" s="3" t="inlineStr">
         <is>
-          <t>4%</t>
+          <t>7.12%</t>
         </is>
       </c>
       <c r="K114" s="5" t="n">
-        <v>18568530</v>
+        <v>17872100</v>
       </c>
       <c r="L114" s="5" t="n">
-        <v>33761</v>
+        <v>32495</v>
       </c>
       <c r="M114" s="3" t="inlineStr">
         <is>
-          <t>現金付款計劃 - 90天成交</t>
+          <t>現金付款計劃 (減3.5%) + 代繳從價印花稅</t>
         </is>
       </c>
       <c r="N114" s="3" t="inlineStr">
@@ -8306,18 +8306,18 @@
       </c>
       <c r="J124" s="3" t="inlineStr">
         <is>
-          <t>4%</t>
+          <t>3.50%</t>
         </is>
       </c>
       <c r="K124" s="5" t="n">
-        <v>18696875</v>
+        <v>18696800</v>
       </c>
       <c r="L124" s="5" t="n">
         <v>33994</v>
       </c>
       <c r="M124" s="3" t="inlineStr">
         <is>
-          <t>現金付款計劃 - 90天成交</t>
+          <t>現金付款計劃 (減3.5%)</t>
         </is>
       </c>
       <c r="N124" s="3" t="inlineStr">
@@ -8802,18 +8802,18 @@
       </c>
       <c r="J132" s="3" t="inlineStr">
         <is>
-          <t>4%</t>
+          <t>7.12%</t>
         </is>
       </c>
       <c r="K132" s="5" t="n">
-        <v>18459485</v>
+        <v>17767100</v>
       </c>
       <c r="L132" s="5" t="n">
-        <v>33563</v>
+        <v>32304</v>
       </c>
       <c r="M132" s="3" t="inlineStr">
         <is>
-          <t>現金付款計劃 - 90天成交</t>
+          <t>現金付款計劃 (減3.5%) + 代繳從價印花稅</t>
         </is>
       </c>
       <c r="N132" s="3" t="inlineStr">
@@ -8864,18 +8864,18 @@
       </c>
       <c r="J133" s="3" t="inlineStr">
         <is>
-          <t>4%</t>
+          <t>3.50%</t>
         </is>
       </c>
       <c r="K133" s="5" t="n">
-        <v>18641870</v>
+        <v>18641800</v>
       </c>
       <c r="L133" s="5" t="n">
         <v>33894</v>
       </c>
       <c r="M133" s="3" t="inlineStr">
         <is>
-          <t>現金付款計劃 - 90天成交</t>
+          <t>現金付款計劃 (減3.5%)</t>
         </is>
       </c>
       <c r="N133" s="3" t="inlineStr">
@@ -9360,18 +9360,18 @@
       </c>
       <c r="J141" s="3" t="inlineStr">
         <is>
-          <t>4%</t>
+          <t>7.12%</t>
         </is>
       </c>
       <c r="K141" s="5" t="n">
-        <v>18404480</v>
+        <v>17714200</v>
       </c>
       <c r="L141" s="5" t="n">
-        <v>33463</v>
+        <v>32208</v>
       </c>
       <c r="M141" s="3" t="inlineStr">
         <is>
-          <t>現金付款計劃 - 90天成交</t>
+          <t>現金付款計劃 (減3.5%) + 代繳從價印花稅</t>
         </is>
       </c>
       <c r="N141" s="3" t="inlineStr">
@@ -9422,7 +9422,7 @@
       </c>
       <c r="J142" s="3" t="inlineStr">
         <is>
-          <t>4%</t>
+          <t>3.50%</t>
         </is>
       </c>
       <c r="K142" s="5" t="n">
@@ -9433,7 +9433,7 @@
       </c>
       <c r="M142" s="3" t="inlineStr">
         <is>
-          <t>現金付款計劃 - 90天成交</t>
+          <t>現金付款計劃 (減3.5%)</t>
         </is>
       </c>
       <c r="N142" s="3" t="inlineStr">
@@ -9918,18 +9918,18 @@
       </c>
       <c r="J150" s="3" t="inlineStr">
         <is>
-          <t>4%</t>
+          <t>7.12%</t>
         </is>
       </c>
       <c r="K150" s="5" t="n">
-        <v>18350440</v>
+        <v>17662200</v>
       </c>
       <c r="L150" s="5" t="n">
-        <v>33364</v>
+        <v>32113</v>
       </c>
       <c r="M150" s="3" t="inlineStr">
         <is>
-          <t>現金付款計劃 - 90天成交</t>
+          <t>現金付款計劃 (減3.5%) + 代繳從價印花稅</t>
         </is>
       </c>
       <c r="N150" s="3" t="inlineStr">
@@ -9980,18 +9980,18 @@
       </c>
       <c r="J151" s="3" t="inlineStr">
         <is>
-          <t>4%</t>
+          <t>3.50%</t>
         </is>
       </c>
       <c r="K151" s="5" t="n">
-        <v>18530895</v>
+        <v>18530800</v>
       </c>
       <c r="L151" s="5" t="n">
-        <v>33693</v>
+        <v>33692</v>
       </c>
       <c r="M151" s="3" t="inlineStr">
         <is>
-          <t>現金付款計劃 - 90天成交</t>
+          <t>現金付款計劃 (減3.5%)</t>
         </is>
       </c>
       <c r="N151" s="3" t="inlineStr">
@@ -10538,18 +10538,18 @@
       </c>
       <c r="J160" s="3" t="inlineStr">
         <is>
-          <t>4%</t>
+          <t>3.50%</t>
         </is>
       </c>
       <c r="K160" s="5" t="n">
-        <v>18475890</v>
+        <v>18475800</v>
       </c>
       <c r="L160" s="5" t="n">
-        <v>33593</v>
+        <v>33592</v>
       </c>
       <c r="M160" s="3" t="inlineStr">
         <is>
-          <t>現金付款計劃 - 90天成交</t>
+          <t>現金付款計劃 (減3.5%)</t>
         </is>
       </c>
       <c r="N160" s="3" t="inlineStr">
@@ -11034,18 +11034,18 @@
       </c>
       <c r="J168" s="3" t="inlineStr">
         <is>
-          <t>4%</t>
+          <t>7.12%</t>
         </is>
       </c>
       <c r="K168" s="5" t="n">
-        <v>18241395</v>
+        <v>17557200</v>
       </c>
       <c r="L168" s="5" t="n">
-        <v>33166</v>
+        <v>31922</v>
       </c>
       <c r="M168" s="3" t="inlineStr">
         <is>
-          <t>現金付款計劃 - 90天成交</t>
+          <t>現金付款計劃 (減3.5%) + 代繳從價印花稅</t>
         </is>
       </c>
       <c r="N168" s="3" t="inlineStr">
@@ -11096,18 +11096,18 @@
       </c>
       <c r="J169" s="3" t="inlineStr">
         <is>
-          <t>4%</t>
+          <t>3.50%</t>
         </is>
       </c>
       <c r="K169" s="5" t="n">
-        <v>18419920</v>
+        <v>18419900</v>
       </c>
       <c r="L169" s="5" t="n">
         <v>33491</v>
       </c>
       <c r="M169" s="3" t="inlineStr">
         <is>
-          <t>現金付款計劃 - 90天成交</t>
+          <t>現金付款計劃 (減3.5%)</t>
         </is>
       </c>
       <c r="N169" s="3" t="inlineStr">
@@ -11592,18 +11592,18 @@
       </c>
       <c r="J177" s="3" t="inlineStr">
         <is>
-          <t>4%</t>
+          <t>7.12%</t>
         </is>
       </c>
       <c r="K177" s="5" t="n">
-        <v>18186390</v>
+        <v>17504300</v>
       </c>
       <c r="L177" s="5" t="n">
-        <v>33066</v>
+        <v>31826</v>
       </c>
       <c r="M177" s="3" t="inlineStr">
         <is>
-          <t>現金付款計劃 - 90天成交</t>
+          <t>現金付款計劃 (減3.5%) + 代繳從價印花稅</t>
         </is>
       </c>
       <c r="N177" s="3" t="inlineStr">
@@ -11654,18 +11654,18 @@
       </c>
       <c r="J178" s="3" t="inlineStr">
         <is>
-          <t>4%</t>
+          <t>3.50%</t>
         </is>
       </c>
       <c r="K178" s="5" t="n">
-        <v>18365880</v>
+        <v>18365800</v>
       </c>
       <c r="L178" s="5" t="n">
-        <v>33393</v>
+        <v>33392</v>
       </c>
       <c r="M178" s="3" t="inlineStr">
         <is>
-          <t>現金付款計劃 - 90天成交</t>
+          <t>現金付款計劃 (減3.5%)</t>
         </is>
       </c>
       <c r="N178" s="3" t="inlineStr">
@@ -12150,18 +12150,18 @@
       </c>
       <c r="J186" s="3" t="inlineStr">
         <is>
-          <t>4%</t>
+          <t>7.12%</t>
         </is>
       </c>
       <c r="K186" s="5" t="n">
-        <v>18186390</v>
+        <v>17504300</v>
       </c>
       <c r="L186" s="5" t="n">
-        <v>33066</v>
+        <v>31826</v>
       </c>
       <c r="M186" s="3" t="inlineStr">
         <is>
-          <t>現金付款計劃 - 90天成交</t>
+          <t>現金付款計劃 (減3.5%) + 代繳從價印花稅</t>
         </is>
       </c>
       <c r="N186" s="3" t="inlineStr">
@@ -12212,18 +12212,18 @@
       </c>
       <c r="J187" s="3" t="inlineStr">
         <is>
-          <t>4%</t>
+          <t>3.50%</t>
         </is>
       </c>
       <c r="K187" s="5" t="n">
-        <v>18365880</v>
+        <v>18365800</v>
       </c>
       <c r="L187" s="5" t="n">
-        <v>33393</v>
+        <v>33392</v>
       </c>
       <c r="M187" s="3" t="inlineStr">
         <is>
-          <t>現金付款計劃 - 90天成交</t>
+          <t>現金付款計劃 (減3.5%)</t>
         </is>
       </c>
       <c r="N187" s="3" t="inlineStr">
@@ -12708,18 +12708,18 @@
       </c>
       <c r="J195" s="3" t="inlineStr">
         <is>
-          <t>4%</t>
+          <t>7.12%</t>
         </is>
       </c>
       <c r="K195" s="5" t="n">
-        <v>18131385</v>
+        <v>17451300</v>
       </c>
       <c r="L195" s="5" t="n">
-        <v>32966</v>
+        <v>31730</v>
       </c>
       <c r="M195" s="3" t="inlineStr">
         <is>
-          <t>現金付款計劃 - 90天成交</t>
+          <t>現金付款計劃 (減3.5%) + 代繳從價印花稅</t>
         </is>
       </c>
       <c r="N195" s="3" t="inlineStr">
@@ -12770,18 +12770,18 @@
       </c>
       <c r="J196" s="3" t="inlineStr">
         <is>
-          <t>4%</t>
+          <t>3.50%</t>
         </is>
       </c>
       <c r="K196" s="5" t="n">
-        <v>18310875</v>
+        <v>18310800</v>
       </c>
       <c r="L196" s="5" t="n">
         <v>33292</v>
       </c>
       <c r="M196" s="3" t="inlineStr">
         <is>
-          <t>現金付款計劃 - 90天成交</t>
+          <t>現金付款計劃 (減3.5%)</t>
         </is>
       </c>
       <c r="N196" s="3" t="inlineStr">
@@ -13266,18 +13266,18 @@
       </c>
       <c r="J204" s="3" t="inlineStr">
         <is>
-          <t>4%</t>
+          <t>7.12%</t>
         </is>
       </c>
       <c r="K204" s="5" t="n">
-        <v>18077345</v>
+        <v>17399400</v>
       </c>
       <c r="L204" s="5" t="n">
-        <v>32868</v>
+        <v>31635</v>
       </c>
       <c r="M204" s="3" t="inlineStr">
         <is>
-          <t>現金付款計劃 - 90天成交</t>
+          <t>現金付款計劃 (減3.5%) + 代繳從價印花稅</t>
         </is>
       </c>
       <c r="N204" s="3" t="inlineStr">
@@ -13328,18 +13328,18 @@
       </c>
       <c r="J205" s="3" t="inlineStr">
         <is>
-          <t>4%</t>
+          <t>3.50%</t>
         </is>
       </c>
       <c r="K205" s="5" t="n">
-        <v>18254905</v>
+        <v>18254900</v>
       </c>
       <c r="L205" s="5" t="n">
         <v>33191</v>
       </c>
       <c r="M205" s="3" t="inlineStr">
         <is>
-          <t>現金付款計劃 - 90天成交</t>
+          <t>現金付款計劃 (減3.5%)</t>
         </is>
       </c>
       <c r="N205" s="3" t="inlineStr">
@@ -13824,18 +13824,18 @@
       </c>
       <c r="J213" s="3" t="inlineStr">
         <is>
-          <t>4%</t>
+          <t>7.12%</t>
         </is>
       </c>
       <c r="K213" s="5" t="n">
-        <v>18022340</v>
+        <v>17346400</v>
       </c>
       <c r="L213" s="5" t="n">
-        <v>32768</v>
+        <v>31539</v>
       </c>
       <c r="M213" s="3" t="inlineStr">
         <is>
-          <t>現金付款計劃 - 90天成交</t>
+          <t>現金付款計劃 (減3.5%) + 代繳從價印花稅</t>
         </is>
       </c>
       <c r="N213" s="3" t="inlineStr">
@@ -13886,7 +13886,7 @@
       </c>
       <c r="J214" s="3" t="inlineStr">
         <is>
-          <t>4%</t>
+          <t>3.50%</t>
         </is>
       </c>
       <c r="K214" s="5" t="n">
@@ -13897,7 +13897,7 @@
       </c>
       <c r="M214" s="3" t="inlineStr">
         <is>
-          <t>現金付款計劃 - 90天成交</t>
+          <t>現金付款計劃 (減3.5%)</t>
         </is>
       </c>
       <c r="N214" s="3" t="inlineStr">
@@ -14313,25 +14313,25 @@
         </is>
       </c>
       <c r="H221" s="5" t="n">
-        <v>18651000</v>
+        <v>1837500018651000</v>
       </c>
       <c r="I221" s="5" t="n">
-        <v>34159</v>
+        <v>3365384649544</v>
       </c>
       <c r="J221" s="3" t="inlineStr">
         <is>
-          <t>4%</t>
+          <t>7.60%</t>
         </is>
       </c>
       <c r="K221" s="5" t="n">
-        <v>17998215</v>
+        <v>1697827048483200</v>
       </c>
       <c r="L221" s="5" t="n">
-        <v>32964</v>
+        <v>3109573348870</v>
       </c>
       <c r="M221" s="3" t="inlineStr">
         <is>
-          <t>現金付款計劃 - 90天成交</t>
+          <t>現金付款計劃 (減3.5%) + 代繳從價印花稅</t>
         </is>
       </c>
       <c r="N221" s="3" t="inlineStr">
@@ -14382,18 +14382,18 @@
       </c>
       <c r="J222" s="3" t="inlineStr">
         <is>
-          <t>4%</t>
+          <t>7.12%</t>
         </is>
       </c>
       <c r="K222" s="5" t="n">
-        <v>17967335</v>
+        <v>17293500</v>
       </c>
       <c r="L222" s="5" t="n">
-        <v>32668</v>
+        <v>31443</v>
       </c>
       <c r="M222" s="3" t="inlineStr">
         <is>
-          <t>現金付款計劃 - 90天成交</t>
+          <t>現金付款計劃 (減3.5%) + 代繳從價印花稅</t>
         </is>
       </c>
       <c r="N222" s="3" t="inlineStr">
@@ -14444,18 +14444,18 @@
       </c>
       <c r="J223" s="3" t="inlineStr">
         <is>
-          <t>4%</t>
+          <t>7.12%</t>
         </is>
       </c>
       <c r="K223" s="5" t="n">
-        <v>18144895</v>
+        <v>17464300</v>
       </c>
       <c r="L223" s="5" t="n">
-        <v>32991</v>
+        <v>31753</v>
       </c>
       <c r="M223" s="3" t="inlineStr">
         <is>
-          <t>現金付款計劃 - 90天成交</t>
+          <t>現金付款計劃 (減3.5%) + 代繳從價印花稅</t>
         </is>
       </c>
       <c r="N223" s="3" t="inlineStr">
@@ -14568,18 +14568,18 @@
       </c>
       <c r="J225" s="3" t="inlineStr">
         <is>
-          <t>9%</t>
+          <t>9.00%</t>
         </is>
       </c>
       <c r="K225" s="5" t="n">
-        <v>9487660</v>
+        <v>9487600</v>
       </c>
       <c r="L225" s="5" t="n">
         <v>22752</v>
       </c>
       <c r="M225" s="3" t="inlineStr">
         <is>
-          <t>現金付款計劃 - 90天成交</t>
+          <t>現金付款計劃 (減9.0%)</t>
         </is>
       </c>
       <c r="N225" s="3" t="inlineStr">
@@ -14940,18 +14940,18 @@
       </c>
       <c r="J231" s="3" t="inlineStr">
         <is>
-          <t>4%</t>
+          <t>7.12%</t>
         </is>
       </c>
       <c r="K231" s="5" t="n">
-        <v>17694240</v>
+        <v>17030600</v>
       </c>
       <c r="L231" s="5" t="n">
-        <v>32171</v>
+        <v>30965</v>
       </c>
       <c r="M231" s="3" t="inlineStr">
         <is>
-          <t>現金付款計劃 - 90天成交</t>
+          <t>現金付款計劃 (減3.5%) + 代繳從價印花稅</t>
         </is>
       </c>
       <c r="N231" s="3" t="inlineStr">
@@ -15002,18 +15002,18 @@
       </c>
       <c r="J232" s="3" t="inlineStr">
         <is>
-          <t>4%</t>
+          <t>7.12%</t>
         </is>
       </c>
       <c r="K232" s="5" t="n">
-        <v>17868905</v>
+        <v>17198800</v>
       </c>
       <c r="L232" s="5" t="n">
-        <v>32489</v>
+        <v>31271</v>
       </c>
       <c r="M232" s="3" t="inlineStr">
         <is>
-          <t>現金付款計劃 - 90天成交</t>
+          <t>現金付款計劃 (減3.5%) + 代繳從價印花稅</t>
         </is>
       </c>
       <c r="N232" s="3" t="inlineStr">
@@ -15498,18 +15498,18 @@
       </c>
       <c r="J240" s="3" t="inlineStr">
         <is>
-          <t>4%</t>
+          <t>7.12%</t>
         </is>
       </c>
       <c r="K240" s="5" t="n">
-        <v>17640200</v>
+        <v>16978600</v>
       </c>
       <c r="L240" s="5" t="n">
-        <v>32073</v>
+        <v>30870</v>
       </c>
       <c r="M240" s="3" t="inlineStr">
         <is>
-          <t>現金付款計劃 - 90天成交</t>
+          <t>現金付款計劃 (減3.5%) + 代繳從價印花稅</t>
         </is>
       </c>
       <c r="N240" s="3" t="inlineStr">
@@ -15560,7 +15560,7 @@
       </c>
       <c r="J241" s="3" t="inlineStr">
         <is>
-          <t>4%</t>
+          <t>3.50%</t>
         </is>
       </c>
       <c r="K241" s="5" t="n">
@@ -15571,7 +15571,7 @@
       </c>
       <c r="M241" s="3" t="inlineStr">
         <is>
-          <t>現金付款計劃 - 90天成交</t>
+          <t>現金付款計劃 (減3.5%)</t>
         </is>
       </c>
       <c r="N241" s="3" t="inlineStr">
@@ -15987,25 +15987,25 @@
         </is>
       </c>
       <c r="H248" s="5" t="n">
-        <v>18307000</v>
+        <v>1803600018307000</v>
       </c>
       <c r="I248" s="5" t="n">
-        <v>33529</v>
+        <v>3303296736826</v>
       </c>
       <c r="J248" s="3" t="inlineStr">
         <is>
-          <t>4%</t>
+          <t>7.60%</t>
         </is>
       </c>
       <c r="K248" s="5" t="n">
-        <v>17666255</v>
+        <v>1666503871915300</v>
       </c>
       <c r="L248" s="5" t="n">
-        <v>32356</v>
+        <v>3052204893618</v>
       </c>
       <c r="M248" s="3" t="inlineStr">
         <is>
-          <t>現金付款計劃 - 90天成交</t>
+          <t>現金付款計劃 (減3.5%) + 代繳從價印花稅</t>
         </is>
       </c>
       <c r="N248" s="3" t="inlineStr">
@@ -16056,18 +16056,18 @@
       </c>
       <c r="J249" s="3" t="inlineStr">
         <is>
-          <t>4%</t>
+          <t>7.12%</t>
         </is>
       </c>
       <c r="K249" s="5" t="n">
-        <v>17640200</v>
+        <v>16978600</v>
       </c>
       <c r="L249" s="5" t="n">
-        <v>32073</v>
+        <v>30870</v>
       </c>
       <c r="M249" s="3" t="inlineStr">
         <is>
-          <t>現金付款計劃 - 90天成交</t>
+          <t>現金付款計劃 (減3.5%) + 代繳從價印花稅</t>
         </is>
       </c>
       <c r="N249" s="3" t="inlineStr">
@@ -16118,7 +16118,7 @@
       </c>
       <c r="J250" s="3" t="inlineStr">
         <is>
-          <t>4%</t>
+          <t>3.50%</t>
         </is>
       </c>
       <c r="K250" s="5" t="n">
@@ -16129,7 +16129,7 @@
       </c>
       <c r="M250" s="3" t="inlineStr">
         <is>
-          <t>現金付款計劃 - 90天成交</t>
+          <t>現金付款計劃 (減3.5%)</t>
         </is>
       </c>
       <c r="N250" s="3" t="inlineStr">
@@ -16545,25 +16545,25 @@
         </is>
       </c>
       <c r="H257" s="5" t="n">
-        <v>18249000</v>
+        <v>1797900018249000</v>
       </c>
       <c r="I257" s="5" t="n">
-        <v>33423</v>
+        <v>3292857176280</v>
       </c>
       <c r="J257" s="3" t="inlineStr">
         <is>
-          <t>4%</t>
+          <t>7.60%</t>
         </is>
       </c>
       <c r="K257" s="5" t="n">
-        <v>17610285</v>
+        <v>1661237143111700</v>
       </c>
       <c r="L257" s="5" t="n">
-        <v>32253</v>
+        <v>3042558870168</v>
       </c>
       <c r="M257" s="3" t="inlineStr">
         <is>
-          <t>現金付款計劃 - 90天成交</t>
+          <t>現金付款計劃 (減3.5%) + 代繳從價印花稅</t>
         </is>
       </c>
       <c r="N257" s="3" t="inlineStr">
@@ -16614,18 +16614,18 @@
       </c>
       <c r="J258" s="3" t="inlineStr">
         <is>
-          <t>4%</t>
+          <t>7.12%</t>
         </is>
       </c>
       <c r="K258" s="5" t="n">
-        <v>17585195</v>
+        <v>16925600</v>
       </c>
       <c r="L258" s="5" t="n">
-        <v>31973</v>
+        <v>30774</v>
       </c>
       <c r="M258" s="3" t="inlineStr">
         <is>
-          <t>現金付款計劃 - 90天成交</t>
+          <t>現金付款計劃 (減3.5%) + 代繳從價印花稅</t>
         </is>
       </c>
       <c r="N258" s="3" t="inlineStr">
@@ -16676,18 +16676,18 @@
       </c>
       <c r="J259" s="3" t="inlineStr">
         <is>
-          <t>4%</t>
+          <t>7.12%</t>
         </is>
       </c>
       <c r="K259" s="5" t="n">
-        <v>17757930</v>
+        <v>17091900</v>
       </c>
       <c r="L259" s="5" t="n">
-        <v>32287</v>
+        <v>31076</v>
       </c>
       <c r="M259" s="3" t="inlineStr">
         <is>
-          <t>現金付款計劃 - 90天成交</t>
+          <t>現金付款計劃 (減3.5%) + 代繳從價印花稅</t>
         </is>
       </c>
       <c r="N259" s="3" t="inlineStr">
@@ -17110,18 +17110,18 @@
       </c>
       <c r="J266" s="3" t="inlineStr">
         <is>
-          <t>4%</t>
+          <t>7.12%</t>
         </is>
       </c>
       <c r="K266" s="5" t="n">
-        <v>17208845</v>
+        <v>16563400</v>
       </c>
       <c r="L266" s="5" t="n">
-        <v>31518</v>
+        <v>30336</v>
       </c>
       <c r="M266" s="3" t="inlineStr">
         <is>
-          <t>現金付款計劃 - 90天成交</t>
+          <t>現金付款計劃 (減3.5%) + 代繳從價印花稅</t>
         </is>
       </c>
       <c r="N266" s="3" t="inlineStr">
@@ -17172,18 +17172,18 @@
       </c>
       <c r="J267" s="3" t="inlineStr">
         <is>
-          <t>4%</t>
+          <t>7.12%</t>
         </is>
       </c>
       <c r="K267" s="5" t="n">
-        <v>17530190</v>
+        <v>16872700</v>
       </c>
       <c r="L267" s="5" t="n">
-        <v>31873</v>
+        <v>30678</v>
       </c>
       <c r="M267" s="3" t="inlineStr">
         <is>
-          <t>現金付款計劃 - 90天成交</t>
+          <t>現金付款計劃 (減3.5%) + 代繳從價印花稅</t>
         </is>
       </c>
       <c r="N267" s="3" t="inlineStr">
@@ -17234,18 +17234,18 @@
       </c>
       <c r="J268" s="3" t="inlineStr">
         <is>
-          <t>4%</t>
+          <t>7.12%</t>
         </is>
       </c>
       <c r="K268" s="5" t="n">
-        <v>17702925</v>
+        <v>17039000</v>
       </c>
       <c r="L268" s="5" t="n">
-        <v>32187</v>
+        <v>30980</v>
       </c>
       <c r="M268" s="3" t="inlineStr">
         <is>
-          <t>現金付款計劃 - 90天成交</t>
+          <t>現金付款計劃 (減3.5%) + 代繳從價印花稅</t>
         </is>
       </c>
       <c r="N268" s="3" t="inlineStr">
@@ -17668,18 +17668,18 @@
       </c>
       <c r="J275" s="3" t="inlineStr">
         <is>
-          <t>4%</t>
+          <t>7.12%</t>
         </is>
       </c>
       <c r="K275" s="5" t="n">
-        <v>17153840</v>
+        <v>16510500</v>
       </c>
       <c r="L275" s="5" t="n">
-        <v>31417</v>
+        <v>30239</v>
       </c>
       <c r="M275" s="3" t="inlineStr">
         <is>
-          <t>現金付款計劃 - 90天成交</t>
+          <t>現金付款計劃 (減3.5%) + 代繳從價印花稅</t>
         </is>
       </c>
       <c r="N275" s="3" t="inlineStr">
@@ -17730,18 +17730,18 @@
       </c>
       <c r="J276" s="3" t="inlineStr">
         <is>
-          <t>4%</t>
+          <t>7.12%</t>
         </is>
       </c>
       <c r="K276" s="5" t="n">
-        <v>17476150</v>
+        <v>16820700</v>
       </c>
       <c r="L276" s="5" t="n">
-        <v>31775</v>
+        <v>30583</v>
       </c>
       <c r="M276" s="3" t="inlineStr">
         <is>
-          <t>現金付款計劃 - 90天成交</t>
+          <t>現金付款計劃 (減3.5%) + 代繳從價印花稅</t>
         </is>
       </c>
       <c r="N276" s="3" t="inlineStr">
@@ -17792,18 +17792,18 @@
       </c>
       <c r="J277" s="3" t="inlineStr">
         <is>
-          <t>4%</t>
+          <t>7.12%</t>
         </is>
       </c>
       <c r="K277" s="5" t="n">
-        <v>17647920</v>
+        <v>16986100</v>
       </c>
       <c r="L277" s="5" t="n">
-        <v>32087</v>
+        <v>30884</v>
       </c>
       <c r="M277" s="3" t="inlineStr">
         <is>
-          <t>現金付款計劃 - 90天成交</t>
+          <t>現金付款計劃 (減3.5%) + 代繳從價印花稅</t>
         </is>
       </c>
       <c r="N277" s="3" t="inlineStr">
@@ -18226,18 +18226,18 @@
       </c>
       <c r="J284" s="3" t="inlineStr">
         <is>
-          <t>4%</t>
+          <t>7.12%</t>
         </is>
       </c>
       <c r="K284" s="5" t="n">
-        <v>17045760</v>
+        <v>16406400</v>
       </c>
       <c r="L284" s="5" t="n">
-        <v>31219</v>
+        <v>30048</v>
       </c>
       <c r="M284" s="3" t="inlineStr">
         <is>
-          <t>現金付款計劃 - 90天成交</t>
+          <t>現金付款計劃 (減3.5%) + 代繳從價印花稅</t>
         </is>
       </c>
       <c r="N284" s="3" t="inlineStr">
@@ -18288,18 +18288,18 @@
       </c>
       <c r="J285" s="3" t="inlineStr">
         <is>
-          <t>4%</t>
+          <t>7.12%</t>
         </is>
       </c>
       <c r="K285" s="5" t="n">
-        <v>17366140</v>
+        <v>16714800</v>
       </c>
       <c r="L285" s="5" t="n">
-        <v>31575</v>
+        <v>30391</v>
       </c>
       <c r="M285" s="3" t="inlineStr">
         <is>
-          <t>現金付款計劃 - 90天成交</t>
+          <t>現金付款計劃 (減3.5%) + 代繳從價印花稅</t>
         </is>
       </c>
       <c r="N285" s="3" t="inlineStr">
@@ -18350,18 +18350,18 @@
       </c>
       <c r="J286" s="3" t="inlineStr">
         <is>
-          <t>4%</t>
+          <t>7.12%</t>
         </is>
       </c>
       <c r="K286" s="5" t="n">
-        <v>17537910</v>
+        <v>16880200</v>
       </c>
       <c r="L286" s="5" t="n">
-        <v>31887</v>
+        <v>30691</v>
       </c>
       <c r="M286" s="3" t="inlineStr">
         <is>
-          <t>現金付款計劃 - 90天成交</t>
+          <t>現金付款計劃 (減3.5%) + 代繳從價印花稅</t>
         </is>
       </c>
       <c r="N286" s="3" t="inlineStr">
@@ -18784,18 +18784,18 @@
       </c>
       <c r="J293" s="3" t="inlineStr">
         <is>
-          <t>4%</t>
+          <t>7.12%</t>
         </is>
       </c>
       <c r="K293" s="5" t="n">
-        <v>16882675</v>
+        <v>16249500</v>
       </c>
       <c r="L293" s="5" t="n">
-        <v>30921</v>
+        <v>29761</v>
       </c>
       <c r="M293" s="3" t="inlineStr">
         <is>
-          <t>現金付款計劃 - 90天成交</t>
+          <t>現金付款計劃 (減3.5%) + 代繳從價印花稅</t>
         </is>
       </c>
       <c r="N293" s="3" t="inlineStr">
@@ -18846,18 +18846,18 @@
       </c>
       <c r="J294" s="3" t="inlineStr">
         <is>
-          <t>4%</t>
+          <t>7.12%</t>
         </is>
       </c>
       <c r="K294" s="5" t="n">
-        <v>17203055</v>
+        <v>16557800</v>
       </c>
       <c r="L294" s="5" t="n">
-        <v>31278</v>
+        <v>30105</v>
       </c>
       <c r="M294" s="3" t="inlineStr">
         <is>
-          <t>現金付款計劃 - 90天成交</t>
+          <t>現金付款計劃 (減3.5%) + 代繳從價印花稅</t>
         </is>
       </c>
       <c r="N294" s="3" t="inlineStr">
@@ -18908,18 +18908,18 @@
       </c>
       <c r="J295" s="3" t="inlineStr">
         <is>
-          <t>4%</t>
+          <t>7.12%</t>
         </is>
       </c>
       <c r="K295" s="5" t="n">
-        <v>17371930</v>
+        <v>16720400</v>
       </c>
       <c r="L295" s="5" t="n">
-        <v>31585</v>
+        <v>30401</v>
       </c>
       <c r="M295" s="3" t="inlineStr">
         <is>
-          <t>現金付款計劃 - 90天成交</t>
+          <t>現金付款計劃 (減3.5%) + 代繳從價印花稅</t>
         </is>
       </c>
       <c r="N295" s="3" t="inlineStr">
@@ -32529,8 +32529,8 @@
       <c r="E29" s="24" t="inlineStr">
         <is>
           <t>D | 546呎 (2房)
-$1865万
-$34,159/呎
+$183750001865万
+$3,365,384,649,544/呎
 (暂停销售)</t>
         </is>
       </c>
@@ -32766,8 +32766,8 @@
       <c r="E32" s="24" t="inlineStr">
         <is>
           <t>D | 546呎 (2房)
-$1831万
-$33,529/呎
+$180360001831万
+$3,303,296,736,826/呎
 (暂停销售)</t>
         </is>
       </c>
@@ -32845,8 +32845,8 @@
       <c r="E33" s="24" t="inlineStr">
         <is>
           <t>D | 546呎 (2房)
-$1825万
-$33,423/呎
+$179790001825万
+$3,292,857,176,280/呎
 (暂停销售)</t>
         </is>
       </c>

--- a/files/九龙-启德-The Henley I.xlsx
+++ b/files/九龙-启德-The Henley I.xlsx
@@ -666,12 +666,12 @@
     <col width="13" customWidth="1" min="5" max="5"/>
     <col width="12" customWidth="1" min="6" max="6"/>
     <col width="13" customWidth="1" min="7" max="7"/>
-    <col width="19" customWidth="1" min="8" max="8"/>
-    <col width="16" customWidth="1" min="9" max="9"/>
+    <col width="13" customWidth="1" min="8" max="8"/>
+    <col width="14" customWidth="1" min="9" max="9"/>
     <col width="12" customWidth="1" min="10" max="10"/>
-    <col width="19" customWidth="1" min="11" max="11"/>
-    <col width="16" customWidth="1" min="12" max="12"/>
-    <col width="27" customWidth="1" min="13" max="13"/>
+    <col width="13" customWidth="1" min="11" max="11"/>
+    <col width="14" customWidth="1" min="12" max="12"/>
+    <col width="17" customWidth="1" min="13" max="13"/>
     <col width="12" customWidth="1" min="14" max="14"/>
   </cols>
   <sheetData>
@@ -796,18 +796,18 @@
       </c>
       <c r="J3" s="3" t="inlineStr">
         <is>
-          <t>9.00%</t>
+          <t>9%</t>
         </is>
       </c>
       <c r="K3" s="5" t="n">
-        <v>13134900</v>
+        <v>13134940</v>
       </c>
       <c r="L3" s="5" t="n">
         <v>31423</v>
       </c>
       <c r="M3" s="3" t="inlineStr">
         <is>
-          <t>現金付款計劃 (減9.0%)</t>
+          <t>現金付款計劃 - 90天成交</t>
         </is>
       </c>
       <c r="N3" s="3" t="inlineStr">
@@ -1176,18 +1176,18 @@
       </c>
       <c r="J9" s="3" t="inlineStr">
         <is>
-          <t>9.00%</t>
+          <t>9%</t>
         </is>
       </c>
       <c r="K9" s="5" t="n">
-        <v>10362100</v>
+        <v>10362170</v>
       </c>
       <c r="L9" s="5" t="n">
         <v>24790</v>
       </c>
       <c r="M9" s="3" t="inlineStr">
         <is>
-          <t>現金付款計劃 (減9.0%)</t>
+          <t>現金付款計劃 - 90天成交</t>
         </is>
       </c>
       <c r="N9" s="3" t="inlineStr">
@@ -1548,18 +1548,18 @@
       </c>
       <c r="J15" s="3" t="inlineStr">
         <is>
-          <t>7.12%</t>
+          <t>4%</t>
         </is>
       </c>
       <c r="K15" s="5" t="n">
-        <v>18713600</v>
+        <v>19442820</v>
       </c>
       <c r="L15" s="5" t="n">
-        <v>34025</v>
+        <v>35351</v>
       </c>
       <c r="M15" s="3" t="inlineStr">
         <is>
-          <t>現金付款計劃 (減3.5%) + 代繳從價印花稅</t>
+          <t>現金付款計劃 - 90天成交</t>
         </is>
       </c>
       <c r="N15" s="3" t="inlineStr">
@@ -1610,18 +1610,18 @@
       </c>
       <c r="J16" s="3" t="inlineStr">
         <is>
-          <t>3.50%</t>
+          <t>4%</t>
         </is>
       </c>
       <c r="K16" s="5" t="n">
-        <v>19633800</v>
+        <v>19633890</v>
       </c>
       <c r="L16" s="5" t="n">
         <v>35698</v>
       </c>
       <c r="M16" s="3" t="inlineStr">
         <is>
-          <t>現金付款計劃 (減3.5%)</t>
+          <t>現金付款計劃 - 90天成交</t>
         </is>
       </c>
       <c r="N16" s="3" t="inlineStr">
@@ -1734,18 +1734,18 @@
       </c>
       <c r="J18" s="3" t="inlineStr">
         <is>
-          <t>9.00%</t>
+          <t>9%</t>
         </is>
       </c>
       <c r="K18" s="5" t="n">
-        <v>10244700</v>
+        <v>10244780</v>
       </c>
       <c r="L18" s="5" t="n">
         <v>24509</v>
       </c>
       <c r="M18" s="3" t="inlineStr">
         <is>
-          <t>現金付款計劃 (減9.0%)</t>
+          <t>現金付款計劃 - 90天成交</t>
         </is>
       </c>
       <c r="N18" s="3" t="inlineStr">
@@ -2106,18 +2106,18 @@
       </c>
       <c r="J24" s="3" t="inlineStr">
         <is>
-          <t>7.12%</t>
+          <t>4%</t>
         </is>
       </c>
       <c r="K24" s="5" t="n">
-        <v>18503700</v>
+        <v>19224730</v>
       </c>
       <c r="L24" s="5" t="n">
-        <v>33643</v>
+        <v>34954</v>
       </c>
       <c r="M24" s="3" t="inlineStr">
         <is>
-          <t>現金付款計劃 (減3.5%) + 代繳從價印花稅</t>
+          <t>現金付款計劃 - 90天成交</t>
         </is>
       </c>
       <c r="N24" s="3" t="inlineStr">
@@ -2168,18 +2168,18 @@
       </c>
       <c r="J25" s="3" t="inlineStr">
         <is>
-          <t>3.50%</t>
+          <t>4%</t>
         </is>
       </c>
       <c r="K25" s="5" t="n">
-        <v>19413800</v>
+        <v>19413870</v>
       </c>
       <c r="L25" s="5" t="n">
         <v>35298</v>
       </c>
       <c r="M25" s="3" t="inlineStr">
         <is>
-          <t>現金付款計劃 (減3.5%)</t>
+          <t>現金付款計劃 - 90天成交</t>
         </is>
       </c>
       <c r="N25" s="3" t="inlineStr">
@@ -2292,18 +2292,18 @@
       </c>
       <c r="J27" s="3" t="inlineStr">
         <is>
-          <t>9.00%</t>
+          <t>9%</t>
         </is>
       </c>
       <c r="K27" s="5" t="n">
-        <v>10161900</v>
+        <v>10161970</v>
       </c>
       <c r="L27" s="5" t="n">
         <v>24369</v>
       </c>
       <c r="M27" s="3" t="inlineStr">
         <is>
-          <t>現金付款計劃 (減9.0%)</t>
+          <t>現金付款計劃 - 90天成交</t>
         </is>
       </c>
       <c r="N27" s="3" t="inlineStr">
@@ -2664,18 +2664,18 @@
       </c>
       <c r="J33" s="3" t="inlineStr">
         <is>
-          <t>7.12%</t>
+          <t>4%</t>
         </is>
       </c>
       <c r="K33" s="5" t="n">
-        <v>18398700</v>
+        <v>19115685</v>
       </c>
       <c r="L33" s="5" t="n">
-        <v>33452</v>
+        <v>34756</v>
       </c>
       <c r="M33" s="3" t="inlineStr">
         <is>
-          <t>現金付款計劃 (減3.5%) + 代繳從價印花稅</t>
+          <t>現金付款計劃 - 90天成交</t>
         </is>
       </c>
       <c r="N33" s="3" t="inlineStr">
@@ -2726,18 +2726,18 @@
       </c>
       <c r="J34" s="3" t="inlineStr">
         <is>
-          <t>3.50%</t>
+          <t>4%</t>
         </is>
       </c>
       <c r="K34" s="5" t="n">
-        <v>19303800</v>
+        <v>19303860</v>
       </c>
       <c r="L34" s="5" t="n">
         <v>35098</v>
       </c>
       <c r="M34" s="3" t="inlineStr">
         <is>
-          <t>現金付款計劃 (減3.5%)</t>
+          <t>現金付款計劃 - 90天成交</t>
         </is>
       </c>
       <c r="N34" s="3" t="inlineStr">
@@ -3284,18 +3284,18 @@
       </c>
       <c r="J43" s="3" t="inlineStr">
         <is>
-          <t>3.50%</t>
+          <t>4%</t>
         </is>
       </c>
       <c r="K43" s="5" t="n">
-        <v>19247800</v>
+        <v>19247890</v>
       </c>
       <c r="L43" s="5" t="n">
         <v>34996</v>
       </c>
       <c r="M43" s="3" t="inlineStr">
         <is>
-          <t>現金付款計劃 (減3.5%)</t>
+          <t>現金付款計劃 - 90天成交</t>
         </is>
       </c>
       <c r="N43" s="3" t="inlineStr">
@@ -3780,18 +3780,18 @@
       </c>
       <c r="J51" s="3" t="inlineStr">
         <is>
-          <t>7.12%</t>
+          <t>4%</t>
         </is>
       </c>
       <c r="K51" s="5" t="n">
-        <v>18292800</v>
+        <v>19005675</v>
       </c>
       <c r="L51" s="5" t="n">
-        <v>33260</v>
+        <v>34556</v>
       </c>
       <c r="M51" s="3" t="inlineStr">
         <is>
-          <t>現金付款計劃 (減3.5%) + 代繳從價印花稅</t>
+          <t>現金付款計劃 - 90天成交</t>
         </is>
       </c>
       <c r="N51" s="3" t="inlineStr">
@@ -3966,7 +3966,7 @@
       </c>
       <c r="J54" s="3" t="inlineStr">
         <is>
-          <t>9.00%</t>
+          <t>9%</t>
         </is>
       </c>
       <c r="K54" s="5" t="n">
@@ -3977,7 +3977,7 @@
       </c>
       <c r="M54" s="3" t="inlineStr">
         <is>
-          <t>現金付款計劃 (減9.0%)</t>
+          <t>現金付款計劃 - 90天成交</t>
         </is>
       </c>
       <c r="N54" s="3" t="inlineStr">
@@ -4338,18 +4338,18 @@
       </c>
       <c r="J60" s="3" t="inlineStr">
         <is>
-          <t>7.12%</t>
+          <t>4%</t>
         </is>
       </c>
       <c r="K60" s="5" t="n">
-        <v>18240900</v>
+        <v>18951635</v>
       </c>
       <c r="L60" s="5" t="n">
-        <v>33165</v>
+        <v>34458</v>
       </c>
       <c r="M60" s="3" t="inlineStr">
         <is>
-          <t>現金付款計劃 (減3.5%) + 代繳從價印花稅</t>
+          <t>現金付款計劃 - 90天成交</t>
         </is>
       </c>
       <c r="N60" s="3" t="inlineStr">
@@ -4400,18 +4400,18 @@
       </c>
       <c r="J61" s="3" t="inlineStr">
         <is>
-          <t>3.50%</t>
+          <t>4%</t>
         </is>
       </c>
       <c r="K61" s="5" t="n">
-        <v>19138800</v>
+        <v>19138845</v>
       </c>
       <c r="L61" s="5" t="n">
         <v>34798</v>
       </c>
       <c r="M61" s="3" t="inlineStr">
         <is>
-          <t>現金付款計劃 (減3.5%)</t>
+          <t>現金付款計劃 - 90天成交</t>
         </is>
       </c>
       <c r="N61" s="3" t="inlineStr">
@@ -4958,18 +4958,18 @@
       </c>
       <c r="J70" s="3" t="inlineStr">
         <is>
-          <t>3.50%</t>
+          <t>4%</t>
         </is>
       </c>
       <c r="K70" s="5" t="n">
-        <v>19082800</v>
+        <v>19082875</v>
       </c>
       <c r="L70" s="5" t="n">
         <v>34696</v>
       </c>
       <c r="M70" s="3" t="inlineStr">
         <is>
-          <t>現金付款計劃 (減3.5%)</t>
+          <t>現金付款計劃 - 90天成交</t>
         </is>
       </c>
       <c r="N70" s="3" t="inlineStr">
@@ -5454,18 +5454,18 @@
       </c>
       <c r="J78" s="3" t="inlineStr">
         <is>
-          <t>7.12%</t>
+          <t>4%</t>
         </is>
       </c>
       <c r="K78" s="5" t="n">
-        <v>18135000</v>
+        <v>18841625</v>
       </c>
       <c r="L78" s="5" t="n">
-        <v>32973</v>
+        <v>34258</v>
       </c>
       <c r="M78" s="3" t="inlineStr">
         <is>
-          <t>現金付款計劃 (減3.5%) + 代繳從價印花稅</t>
+          <t>現金付款計劃 - 90天成交</t>
         </is>
       </c>
       <c r="N78" s="3" t="inlineStr">
@@ -5516,18 +5516,18 @@
       </c>
       <c r="J79" s="3" t="inlineStr">
         <is>
-          <t>3.50%</t>
+          <t>4%</t>
         </is>
       </c>
       <c r="K79" s="5" t="n">
-        <v>19027800</v>
+        <v>19027870</v>
       </c>
       <c r="L79" s="5" t="n">
         <v>34596</v>
       </c>
       <c r="M79" s="3" t="inlineStr">
         <is>
-          <t>現金付款計劃 (減3.5%)</t>
+          <t>現金付款計劃 - 90天成交</t>
         </is>
       </c>
       <c r="N79" s="3" t="inlineStr">
@@ -6074,18 +6074,18 @@
       </c>
       <c r="J88" s="3" t="inlineStr">
         <is>
-          <t>3.50%</t>
+          <t>4%</t>
         </is>
       </c>
       <c r="K88" s="5" t="n">
-        <v>18972800</v>
+        <v>18972865</v>
       </c>
       <c r="L88" s="5" t="n">
         <v>34496</v>
       </c>
       <c r="M88" s="3" t="inlineStr">
         <is>
-          <t>現金付款計劃 (減3.5%)</t>
+          <t>現金付款計劃 - 90天成交</t>
         </is>
       </c>
       <c r="N88" s="3" t="inlineStr">
@@ -6570,18 +6570,18 @@
       </c>
       <c r="J96" s="3" t="inlineStr">
         <is>
-          <t>7.12%</t>
+          <t>4%</t>
         </is>
       </c>
       <c r="K96" s="5" t="n">
-        <v>18030000</v>
+        <v>18732580</v>
       </c>
       <c r="L96" s="5" t="n">
-        <v>32782</v>
+        <v>34059</v>
       </c>
       <c r="M96" s="3" t="inlineStr">
         <is>
-          <t>現金付款計劃 (減3.5%) + 代繳從價印花稅</t>
+          <t>現金付款計劃 - 90天成交</t>
         </is>
       </c>
       <c r="N96" s="3" t="inlineStr">
@@ -7128,18 +7128,18 @@
       </c>
       <c r="J105" s="3" t="inlineStr">
         <is>
-          <t>7.12%</t>
+          <t>4%</t>
         </is>
       </c>
       <c r="K105" s="5" t="n">
-        <v>17978000</v>
+        <v>18678540</v>
       </c>
       <c r="L105" s="5" t="n">
-        <v>32687</v>
+        <v>33961</v>
       </c>
       <c r="M105" s="3" t="inlineStr">
         <is>
-          <t>現金付款計劃 (減3.5%) + 代繳從價印花稅</t>
+          <t>現金付款計劃 - 90天成交</t>
         </is>
       </c>
       <c r="N105" s="3" t="inlineStr">
@@ -7190,18 +7190,18 @@
       </c>
       <c r="J106" s="3" t="inlineStr">
         <is>
-          <t>3.50%</t>
+          <t>4%</t>
         </is>
       </c>
       <c r="K106" s="5" t="n">
-        <v>18861800</v>
+        <v>18861890</v>
       </c>
       <c r="L106" s="5" t="n">
         <v>34294</v>
       </c>
       <c r="M106" s="3" t="inlineStr">
         <is>
-          <t>現金付款計劃 (減3.5%)</t>
+          <t>現金付款計劃 - 90天成交</t>
         </is>
       </c>
       <c r="N106" s="3" t="inlineStr">
@@ -7686,18 +7686,18 @@
       </c>
       <c r="J114" s="3" t="inlineStr">
         <is>
-          <t>7.12%</t>
+          <t>4%</t>
         </is>
       </c>
       <c r="K114" s="5" t="n">
-        <v>17872100</v>
+        <v>18568530</v>
       </c>
       <c r="L114" s="5" t="n">
-        <v>32495</v>
+        <v>33761</v>
       </c>
       <c r="M114" s="3" t="inlineStr">
         <is>
-          <t>現金付款計劃 (減3.5%) + 代繳從價印花稅</t>
+          <t>現金付款計劃 - 90天成交</t>
         </is>
       </c>
       <c r="N114" s="3" t="inlineStr">
@@ -8306,18 +8306,18 @@
       </c>
       <c r="J124" s="3" t="inlineStr">
         <is>
-          <t>3.50%</t>
+          <t>4%</t>
         </is>
       </c>
       <c r="K124" s="5" t="n">
-        <v>18696800</v>
+        <v>18696875</v>
       </c>
       <c r="L124" s="5" t="n">
         <v>33994</v>
       </c>
       <c r="M124" s="3" t="inlineStr">
         <is>
-          <t>現金付款計劃 (減3.5%)</t>
+          <t>現金付款計劃 - 90天成交</t>
         </is>
       </c>
       <c r="N124" s="3" t="inlineStr">
@@ -8802,18 +8802,18 @@
       </c>
       <c r="J132" s="3" t="inlineStr">
         <is>
-          <t>7.12%</t>
+          <t>4%</t>
         </is>
       </c>
       <c r="K132" s="5" t="n">
-        <v>17767100</v>
+        <v>18459485</v>
       </c>
       <c r="L132" s="5" t="n">
-        <v>32304</v>
+        <v>33563</v>
       </c>
       <c r="M132" s="3" t="inlineStr">
         <is>
-          <t>現金付款計劃 (減3.5%) + 代繳從價印花稅</t>
+          <t>現金付款計劃 - 90天成交</t>
         </is>
       </c>
       <c r="N132" s="3" t="inlineStr">
@@ -8864,18 +8864,18 @@
       </c>
       <c r="J133" s="3" t="inlineStr">
         <is>
-          <t>3.50%</t>
+          <t>4%</t>
         </is>
       </c>
       <c r="K133" s="5" t="n">
-        <v>18641800</v>
+        <v>18641870</v>
       </c>
       <c r="L133" s="5" t="n">
         <v>33894</v>
       </c>
       <c r="M133" s="3" t="inlineStr">
         <is>
-          <t>現金付款計劃 (減3.5%)</t>
+          <t>現金付款計劃 - 90天成交</t>
         </is>
       </c>
       <c r="N133" s="3" t="inlineStr">
@@ -9360,18 +9360,18 @@
       </c>
       <c r="J141" s="3" t="inlineStr">
         <is>
-          <t>7.12%</t>
+          <t>4%</t>
         </is>
       </c>
       <c r="K141" s="5" t="n">
-        <v>17714200</v>
+        <v>18404480</v>
       </c>
       <c r="L141" s="5" t="n">
-        <v>32208</v>
+        <v>33463</v>
       </c>
       <c r="M141" s="3" t="inlineStr">
         <is>
-          <t>現金付款計劃 (減3.5%) + 代繳從價印花稅</t>
+          <t>現金付款計劃 - 90天成交</t>
         </is>
       </c>
       <c r="N141" s="3" t="inlineStr">
@@ -9422,7 +9422,7 @@
       </c>
       <c r="J142" s="3" t="inlineStr">
         <is>
-          <t>3.50%</t>
+          <t>4%</t>
         </is>
       </c>
       <c r="K142" s="5" t="n">
@@ -9433,7 +9433,7 @@
       </c>
       <c r="M142" s="3" t="inlineStr">
         <is>
-          <t>現金付款計劃 (減3.5%)</t>
+          <t>現金付款計劃 - 90天成交</t>
         </is>
       </c>
       <c r="N142" s="3" t="inlineStr">
@@ -9918,18 +9918,18 @@
       </c>
       <c r="J150" s="3" t="inlineStr">
         <is>
-          <t>7.12%</t>
+          <t>4%</t>
         </is>
       </c>
       <c r="K150" s="5" t="n">
-        <v>17662200</v>
+        <v>18350440</v>
       </c>
       <c r="L150" s="5" t="n">
-        <v>32113</v>
+        <v>33364</v>
       </c>
       <c r="M150" s="3" t="inlineStr">
         <is>
-          <t>現金付款計劃 (減3.5%) + 代繳從價印花稅</t>
+          <t>現金付款計劃 - 90天成交</t>
         </is>
       </c>
       <c r="N150" s="3" t="inlineStr">
@@ -9980,18 +9980,18 @@
       </c>
       <c r="J151" s="3" t="inlineStr">
         <is>
-          <t>3.50%</t>
+          <t>4%</t>
         </is>
       </c>
       <c r="K151" s="5" t="n">
-        <v>18530800</v>
+        <v>18530895</v>
       </c>
       <c r="L151" s="5" t="n">
-        <v>33692</v>
+        <v>33693</v>
       </c>
       <c r="M151" s="3" t="inlineStr">
         <is>
-          <t>現金付款計劃 (減3.5%)</t>
+          <t>現金付款計劃 - 90天成交</t>
         </is>
       </c>
       <c r="N151" s="3" t="inlineStr">
@@ -10538,18 +10538,18 @@
       </c>
       <c r="J160" s="3" t="inlineStr">
         <is>
-          <t>3.50%</t>
+          <t>4%</t>
         </is>
       </c>
       <c r="K160" s="5" t="n">
-        <v>18475800</v>
+        <v>18475890</v>
       </c>
       <c r="L160" s="5" t="n">
-        <v>33592</v>
+        <v>33593</v>
       </c>
       <c r="M160" s="3" t="inlineStr">
         <is>
-          <t>現金付款計劃 (減3.5%)</t>
+          <t>現金付款計劃 - 90天成交</t>
         </is>
       </c>
       <c r="N160" s="3" t="inlineStr">
@@ -11034,18 +11034,18 @@
       </c>
       <c r="J168" s="3" t="inlineStr">
         <is>
-          <t>7.12%</t>
+          <t>4%</t>
         </is>
       </c>
       <c r="K168" s="5" t="n">
-        <v>17557200</v>
+        <v>18241395</v>
       </c>
       <c r="L168" s="5" t="n">
-        <v>31922</v>
+        <v>33166</v>
       </c>
       <c r="M168" s="3" t="inlineStr">
         <is>
-          <t>現金付款計劃 (減3.5%) + 代繳從價印花稅</t>
+          <t>現金付款計劃 - 90天成交</t>
         </is>
       </c>
       <c r="N168" s="3" t="inlineStr">
@@ -11096,18 +11096,18 @@
       </c>
       <c r="J169" s="3" t="inlineStr">
         <is>
-          <t>3.50%</t>
+          <t>4%</t>
         </is>
       </c>
       <c r="K169" s="5" t="n">
-        <v>18419900</v>
+        <v>18419920</v>
       </c>
       <c r="L169" s="5" t="n">
         <v>33491</v>
       </c>
       <c r="M169" s="3" t="inlineStr">
         <is>
-          <t>現金付款計劃 (減3.5%)</t>
+          <t>現金付款計劃 - 90天成交</t>
         </is>
       </c>
       <c r="N169" s="3" t="inlineStr">
@@ -11592,18 +11592,18 @@
       </c>
       <c r="J177" s="3" t="inlineStr">
         <is>
-          <t>7.12%</t>
+          <t>4%</t>
         </is>
       </c>
       <c r="K177" s="5" t="n">
-        <v>17504300</v>
+        <v>18186390</v>
       </c>
       <c r="L177" s="5" t="n">
-        <v>31826</v>
+        <v>33066</v>
       </c>
       <c r="M177" s="3" t="inlineStr">
         <is>
-          <t>現金付款計劃 (減3.5%) + 代繳從價印花稅</t>
+          <t>現金付款計劃 - 90天成交</t>
         </is>
       </c>
       <c r="N177" s="3" t="inlineStr">
@@ -11654,18 +11654,18 @@
       </c>
       <c r="J178" s="3" t="inlineStr">
         <is>
-          <t>3.50%</t>
+          <t>4%</t>
         </is>
       </c>
       <c r="K178" s="5" t="n">
-        <v>18365800</v>
+        <v>18365880</v>
       </c>
       <c r="L178" s="5" t="n">
-        <v>33392</v>
+        <v>33393</v>
       </c>
       <c r="M178" s="3" t="inlineStr">
         <is>
-          <t>現金付款計劃 (減3.5%)</t>
+          <t>現金付款計劃 - 90天成交</t>
         </is>
       </c>
       <c r="N178" s="3" t="inlineStr">
@@ -12150,18 +12150,18 @@
       </c>
       <c r="J186" s="3" t="inlineStr">
         <is>
-          <t>7.12%</t>
+          <t>4%</t>
         </is>
       </c>
       <c r="K186" s="5" t="n">
-        <v>17504300</v>
+        <v>18186390</v>
       </c>
       <c r="L186" s="5" t="n">
-        <v>31826</v>
+        <v>33066</v>
       </c>
       <c r="M186" s="3" t="inlineStr">
         <is>
-          <t>現金付款計劃 (減3.5%) + 代繳從價印花稅</t>
+          <t>現金付款計劃 - 90天成交</t>
         </is>
       </c>
       <c r="N186" s="3" t="inlineStr">
@@ -12212,18 +12212,18 @@
       </c>
       <c r="J187" s="3" t="inlineStr">
         <is>
-          <t>3.50%</t>
+          <t>4%</t>
         </is>
       </c>
       <c r="K187" s="5" t="n">
-        <v>18365800</v>
+        <v>18365880</v>
       </c>
       <c r="L187" s="5" t="n">
-        <v>33392</v>
+        <v>33393</v>
       </c>
       <c r="M187" s="3" t="inlineStr">
         <is>
-          <t>現金付款計劃 (減3.5%)</t>
+          <t>現金付款計劃 - 90天成交</t>
         </is>
       </c>
       <c r="N187" s="3" t="inlineStr">
@@ -12708,18 +12708,18 @@
       </c>
       <c r="J195" s="3" t="inlineStr">
         <is>
-          <t>7.12%</t>
+          <t>4%</t>
         </is>
       </c>
       <c r="K195" s="5" t="n">
-        <v>17451300</v>
+        <v>18131385</v>
       </c>
       <c r="L195" s="5" t="n">
-        <v>31730</v>
+        <v>32966</v>
       </c>
       <c r="M195" s="3" t="inlineStr">
         <is>
-          <t>現金付款計劃 (減3.5%) + 代繳從價印花稅</t>
+          <t>現金付款計劃 - 90天成交</t>
         </is>
       </c>
       <c r="N195" s="3" t="inlineStr">
@@ -12770,18 +12770,18 @@
       </c>
       <c r="J196" s="3" t="inlineStr">
         <is>
-          <t>3.50%</t>
+          <t>4%</t>
         </is>
       </c>
       <c r="K196" s="5" t="n">
-        <v>18310800</v>
+        <v>18310875</v>
       </c>
       <c r="L196" s="5" t="n">
         <v>33292</v>
       </c>
       <c r="M196" s="3" t="inlineStr">
         <is>
-          <t>現金付款計劃 (減3.5%)</t>
+          <t>現金付款計劃 - 90天成交</t>
         </is>
       </c>
       <c r="N196" s="3" t="inlineStr">
@@ -13266,18 +13266,18 @@
       </c>
       <c r="J204" s="3" t="inlineStr">
         <is>
-          <t>7.12%</t>
+          <t>4%</t>
         </is>
       </c>
       <c r="K204" s="5" t="n">
-        <v>17399400</v>
+        <v>18077345</v>
       </c>
       <c r="L204" s="5" t="n">
-        <v>31635</v>
+        <v>32868</v>
       </c>
       <c r="M204" s="3" t="inlineStr">
         <is>
-          <t>現金付款計劃 (減3.5%) + 代繳從價印花稅</t>
+          <t>現金付款計劃 - 90天成交</t>
         </is>
       </c>
       <c r="N204" s="3" t="inlineStr">
@@ -13328,18 +13328,18 @@
       </c>
       <c r="J205" s="3" t="inlineStr">
         <is>
-          <t>3.50%</t>
+          <t>4%</t>
         </is>
       </c>
       <c r="K205" s="5" t="n">
-        <v>18254900</v>
+        <v>18254905</v>
       </c>
       <c r="L205" s="5" t="n">
         <v>33191</v>
       </c>
       <c r="M205" s="3" t="inlineStr">
         <is>
-          <t>現金付款計劃 (減3.5%)</t>
+          <t>現金付款計劃 - 90天成交</t>
         </is>
       </c>
       <c r="N205" s="3" t="inlineStr">
@@ -13824,18 +13824,18 @@
       </c>
       <c r="J213" s="3" t="inlineStr">
         <is>
-          <t>7.12%</t>
+          <t>4%</t>
         </is>
       </c>
       <c r="K213" s="5" t="n">
-        <v>17346400</v>
+        <v>18022340</v>
       </c>
       <c r="L213" s="5" t="n">
-        <v>31539</v>
+        <v>32768</v>
       </c>
       <c r="M213" s="3" t="inlineStr">
         <is>
-          <t>現金付款計劃 (減3.5%) + 代繳從價印花稅</t>
+          <t>現金付款計劃 - 90天成交</t>
         </is>
       </c>
       <c r="N213" s="3" t="inlineStr">
@@ -13886,7 +13886,7 @@
       </c>
       <c r="J214" s="3" t="inlineStr">
         <is>
-          <t>3.50%</t>
+          <t>4%</t>
         </is>
       </c>
       <c r="K214" s="5" t="n">
@@ -13897,7 +13897,7 @@
       </c>
       <c r="M214" s="3" t="inlineStr">
         <is>
-          <t>現金付款計劃 (減3.5%)</t>
+          <t>現金付款計劃 - 90天成交</t>
         </is>
       </c>
       <c r="N214" s="3" t="inlineStr">
@@ -14313,25 +14313,25 @@
         </is>
       </c>
       <c r="H221" s="5" t="n">
-        <v>1837500018651000</v>
+        <v>18651000</v>
       </c>
       <c r="I221" s="5" t="n">
-        <v>3365384649544</v>
+        <v>34159</v>
       </c>
       <c r="J221" s="3" t="inlineStr">
         <is>
-          <t>7.60%</t>
+          <t>4%</t>
         </is>
       </c>
       <c r="K221" s="5" t="n">
-        <v>1697827048483200</v>
+        <v>17998215</v>
       </c>
       <c r="L221" s="5" t="n">
-        <v>3109573348870</v>
+        <v>32964</v>
       </c>
       <c r="M221" s="3" t="inlineStr">
         <is>
-          <t>現金付款計劃 (減3.5%) + 代繳從價印花稅</t>
+          <t>現金付款計劃 - 90天成交</t>
         </is>
       </c>
       <c r="N221" s="3" t="inlineStr">
@@ -14382,18 +14382,18 @@
       </c>
       <c r="J222" s="3" t="inlineStr">
         <is>
-          <t>7.12%</t>
+          <t>4%</t>
         </is>
       </c>
       <c r="K222" s="5" t="n">
-        <v>17293500</v>
+        <v>17967335</v>
       </c>
       <c r="L222" s="5" t="n">
-        <v>31443</v>
+        <v>32668</v>
       </c>
       <c r="M222" s="3" t="inlineStr">
         <is>
-          <t>現金付款計劃 (減3.5%) + 代繳從價印花稅</t>
+          <t>現金付款計劃 - 90天成交</t>
         </is>
       </c>
       <c r="N222" s="3" t="inlineStr">
@@ -14444,18 +14444,18 @@
       </c>
       <c r="J223" s="3" t="inlineStr">
         <is>
-          <t>7.12%</t>
+          <t>4%</t>
         </is>
       </c>
       <c r="K223" s="5" t="n">
-        <v>17464300</v>
+        <v>18144895</v>
       </c>
       <c r="L223" s="5" t="n">
-        <v>31753</v>
+        <v>32991</v>
       </c>
       <c r="M223" s="3" t="inlineStr">
         <is>
-          <t>現金付款計劃 (減3.5%) + 代繳從價印花稅</t>
+          <t>現金付款計劃 - 90天成交</t>
         </is>
       </c>
       <c r="N223" s="3" t="inlineStr">
@@ -14568,18 +14568,18 @@
       </c>
       <c r="J225" s="3" t="inlineStr">
         <is>
-          <t>9.00%</t>
+          <t>9%</t>
         </is>
       </c>
       <c r="K225" s="5" t="n">
-        <v>9487600</v>
+        <v>9487660</v>
       </c>
       <c r="L225" s="5" t="n">
         <v>22752</v>
       </c>
       <c r="M225" s="3" t="inlineStr">
         <is>
-          <t>現金付款計劃 (減9.0%)</t>
+          <t>現金付款計劃 - 90天成交</t>
         </is>
       </c>
       <c r="N225" s="3" t="inlineStr">
@@ -14940,18 +14940,18 @@
       </c>
       <c r="J231" s="3" t="inlineStr">
         <is>
-          <t>7.12%</t>
+          <t>4%</t>
         </is>
       </c>
       <c r="K231" s="5" t="n">
-        <v>17030600</v>
+        <v>17694240</v>
       </c>
       <c r="L231" s="5" t="n">
-        <v>30965</v>
+        <v>32171</v>
       </c>
       <c r="M231" s="3" t="inlineStr">
         <is>
-          <t>現金付款計劃 (減3.5%) + 代繳從價印花稅</t>
+          <t>現金付款計劃 - 90天成交</t>
         </is>
       </c>
       <c r="N231" s="3" t="inlineStr">
@@ -15002,18 +15002,18 @@
       </c>
       <c r="J232" s="3" t="inlineStr">
         <is>
-          <t>7.12%</t>
+          <t>4%</t>
         </is>
       </c>
       <c r="K232" s="5" t="n">
-        <v>17198800</v>
+        <v>17868905</v>
       </c>
       <c r="L232" s="5" t="n">
-        <v>31271</v>
+        <v>32489</v>
       </c>
       <c r="M232" s="3" t="inlineStr">
         <is>
-          <t>現金付款計劃 (減3.5%) + 代繳從價印花稅</t>
+          <t>現金付款計劃 - 90天成交</t>
         </is>
       </c>
       <c r="N232" s="3" t="inlineStr">
@@ -15498,18 +15498,18 @@
       </c>
       <c r="J240" s="3" t="inlineStr">
         <is>
-          <t>7.12%</t>
+          <t>4%</t>
         </is>
       </c>
       <c r="K240" s="5" t="n">
-        <v>16978600</v>
+        <v>17640200</v>
       </c>
       <c r="L240" s="5" t="n">
-        <v>30870</v>
+        <v>32073</v>
       </c>
       <c r="M240" s="3" t="inlineStr">
         <is>
-          <t>現金付款計劃 (減3.5%) + 代繳從價印花稅</t>
+          <t>現金付款計劃 - 90天成交</t>
         </is>
       </c>
       <c r="N240" s="3" t="inlineStr">
@@ -15560,7 +15560,7 @@
       </c>
       <c r="J241" s="3" t="inlineStr">
         <is>
-          <t>3.50%</t>
+          <t>4%</t>
         </is>
       </c>
       <c r="K241" s="5" t="n">
@@ -15571,7 +15571,7 @@
       </c>
       <c r="M241" s="3" t="inlineStr">
         <is>
-          <t>現金付款計劃 (減3.5%)</t>
+          <t>現金付款計劃 - 90天成交</t>
         </is>
       </c>
       <c r="N241" s="3" t="inlineStr">
@@ -15987,25 +15987,25 @@
         </is>
       </c>
       <c r="H248" s="5" t="n">
-        <v>1803600018307000</v>
+        <v>18307000</v>
       </c>
       <c r="I248" s="5" t="n">
-        <v>3303296736826</v>
+        <v>33529</v>
       </c>
       <c r="J248" s="3" t="inlineStr">
         <is>
-          <t>7.60%</t>
+          <t>4%</t>
         </is>
       </c>
       <c r="K248" s="5" t="n">
-        <v>1666503871915300</v>
+        <v>17666255</v>
       </c>
       <c r="L248" s="5" t="n">
-        <v>3052204893618</v>
+        <v>32356</v>
       </c>
       <c r="M248" s="3" t="inlineStr">
         <is>
-          <t>現金付款計劃 (減3.5%) + 代繳從價印花稅</t>
+          <t>現金付款計劃 - 90天成交</t>
         </is>
       </c>
       <c r="N248" s="3" t="inlineStr">
@@ -16056,18 +16056,18 @@
       </c>
       <c r="J249" s="3" t="inlineStr">
         <is>
-          <t>7.12%</t>
+          <t>4%</t>
         </is>
       </c>
       <c r="K249" s="5" t="n">
-        <v>16978600</v>
+        <v>17640200</v>
       </c>
       <c r="L249" s="5" t="n">
-        <v>30870</v>
+        <v>32073</v>
       </c>
       <c r="M249" s="3" t="inlineStr">
         <is>
-          <t>現金付款計劃 (減3.5%) + 代繳從價印花稅</t>
+          <t>現金付款計劃 - 90天成交</t>
         </is>
       </c>
       <c r="N249" s="3" t="inlineStr">
@@ -16118,7 +16118,7 @@
       </c>
       <c r="J250" s="3" t="inlineStr">
         <is>
-          <t>3.50%</t>
+          <t>4%</t>
         </is>
       </c>
       <c r="K250" s="5" t="n">
@@ -16129,7 +16129,7 @@
       </c>
       <c r="M250" s="3" t="inlineStr">
         <is>
-          <t>現金付款計劃 (減3.5%)</t>
+          <t>現金付款計劃 - 90天成交</t>
         </is>
       </c>
       <c r="N250" s="3" t="inlineStr">
@@ -16545,25 +16545,25 @@
         </is>
       </c>
       <c r="H257" s="5" t="n">
-        <v>1797900018249000</v>
+        <v>18249000</v>
       </c>
       <c r="I257" s="5" t="n">
-        <v>3292857176280</v>
+        <v>33423</v>
       </c>
       <c r="J257" s="3" t="inlineStr">
         <is>
-          <t>7.60%</t>
+          <t>4%</t>
         </is>
       </c>
       <c r="K257" s="5" t="n">
-        <v>1661237143111700</v>
+        <v>17610285</v>
       </c>
       <c r="L257" s="5" t="n">
-        <v>3042558870168</v>
+        <v>32253</v>
       </c>
       <c r="M257" s="3" t="inlineStr">
         <is>
-          <t>現金付款計劃 (減3.5%) + 代繳從價印花稅</t>
+          <t>現金付款計劃 - 90天成交</t>
         </is>
       </c>
       <c r="N257" s="3" t="inlineStr">
@@ -16614,18 +16614,18 @@
       </c>
       <c r="J258" s="3" t="inlineStr">
         <is>
-          <t>7.12%</t>
+          <t>4%</t>
         </is>
       </c>
       <c r="K258" s="5" t="n">
-        <v>16925600</v>
+        <v>17585195</v>
       </c>
       <c r="L258" s="5" t="n">
-        <v>30774</v>
+        <v>31973</v>
       </c>
       <c r="M258" s="3" t="inlineStr">
         <is>
-          <t>現金付款計劃 (減3.5%) + 代繳從價印花稅</t>
+          <t>現金付款計劃 - 90天成交</t>
         </is>
       </c>
       <c r="N258" s="3" t="inlineStr">
@@ -16676,18 +16676,18 @@
       </c>
       <c r="J259" s="3" t="inlineStr">
         <is>
-          <t>7.12%</t>
+          <t>4%</t>
         </is>
       </c>
       <c r="K259" s="5" t="n">
-        <v>17091900</v>
+        <v>17757930</v>
       </c>
       <c r="L259" s="5" t="n">
-        <v>31076</v>
+        <v>32287</v>
       </c>
       <c r="M259" s="3" t="inlineStr">
         <is>
-          <t>現金付款計劃 (減3.5%) + 代繳從價印花稅</t>
+          <t>現金付款計劃 - 90天成交</t>
         </is>
       </c>
       <c r="N259" s="3" t="inlineStr">
@@ -17110,18 +17110,18 @@
       </c>
       <c r="J266" s="3" t="inlineStr">
         <is>
-          <t>7.12%</t>
+          <t>4%</t>
         </is>
       </c>
       <c r="K266" s="5" t="n">
-        <v>16563400</v>
+        <v>17208845</v>
       </c>
       <c r="L266" s="5" t="n">
-        <v>30336</v>
+        <v>31518</v>
       </c>
       <c r="M266" s="3" t="inlineStr">
         <is>
-          <t>現金付款計劃 (減3.5%) + 代繳從價印花稅</t>
+          <t>現金付款計劃 - 90天成交</t>
         </is>
       </c>
       <c r="N266" s="3" t="inlineStr">
@@ -17172,18 +17172,18 @@
       </c>
       <c r="J267" s="3" t="inlineStr">
         <is>
-          <t>7.12%</t>
+          <t>4%</t>
         </is>
       </c>
       <c r="K267" s="5" t="n">
-        <v>16872700</v>
+        <v>17530190</v>
       </c>
       <c r="L267" s="5" t="n">
-        <v>30678</v>
+        <v>31873</v>
       </c>
       <c r="M267" s="3" t="inlineStr">
         <is>
-          <t>現金付款計劃 (減3.5%) + 代繳從價印花稅</t>
+          <t>現金付款計劃 - 90天成交</t>
         </is>
       </c>
       <c r="N267" s="3" t="inlineStr">
@@ -17234,18 +17234,18 @@
       </c>
       <c r="J268" s="3" t="inlineStr">
         <is>
-          <t>7.12%</t>
+          <t>4%</t>
         </is>
       </c>
       <c r="K268" s="5" t="n">
-        <v>17039000</v>
+        <v>17702925</v>
       </c>
       <c r="L268" s="5" t="n">
-        <v>30980</v>
+        <v>32187</v>
       </c>
       <c r="M268" s="3" t="inlineStr">
         <is>
-          <t>現金付款計劃 (減3.5%) + 代繳從價印花稅</t>
+          <t>現金付款計劃 - 90天成交</t>
         </is>
       </c>
       <c r="N268" s="3" t="inlineStr">
@@ -17668,18 +17668,18 @@
       </c>
       <c r="J275" s="3" t="inlineStr">
         <is>
-          <t>7.12%</t>
+          <t>4%</t>
         </is>
       </c>
       <c r="K275" s="5" t="n">
-        <v>16510500</v>
+        <v>17153840</v>
       </c>
       <c r="L275" s="5" t="n">
-        <v>30239</v>
+        <v>31417</v>
       </c>
       <c r="M275" s="3" t="inlineStr">
         <is>
-          <t>現金付款計劃 (減3.5%) + 代繳從價印花稅</t>
+          <t>現金付款計劃 - 90天成交</t>
         </is>
       </c>
       <c r="N275" s="3" t="inlineStr">
@@ -17730,18 +17730,18 @@
       </c>
       <c r="J276" s="3" t="inlineStr">
         <is>
-          <t>7.12%</t>
+          <t>4%</t>
         </is>
       </c>
       <c r="K276" s="5" t="n">
-        <v>16820700</v>
+        <v>17476150</v>
       </c>
       <c r="L276" s="5" t="n">
-        <v>30583</v>
+        <v>31775</v>
       </c>
       <c r="M276" s="3" t="inlineStr">
         <is>
-          <t>現金付款計劃 (減3.5%) + 代繳從價印花稅</t>
+          <t>現金付款計劃 - 90天成交</t>
         </is>
       </c>
       <c r="N276" s="3" t="inlineStr">
@@ -17792,18 +17792,18 @@
       </c>
       <c r="J277" s="3" t="inlineStr">
         <is>
-          <t>7.12%</t>
+          <t>4%</t>
         </is>
       </c>
       <c r="K277" s="5" t="n">
-        <v>16986100</v>
+        <v>17647920</v>
       </c>
       <c r="L277" s="5" t="n">
-        <v>30884</v>
+        <v>32087</v>
       </c>
       <c r="M277" s="3" t="inlineStr">
         <is>
-          <t>現金付款計劃 (減3.5%) + 代繳從價印花稅</t>
+          <t>現金付款計劃 - 90天成交</t>
         </is>
       </c>
       <c r="N277" s="3" t="inlineStr">
@@ -18226,18 +18226,18 @@
       </c>
       <c r="J284" s="3" t="inlineStr">
         <is>
-          <t>7.12%</t>
+          <t>4%</t>
         </is>
       </c>
       <c r="K284" s="5" t="n">
-        <v>16406400</v>
+        <v>17045760</v>
       </c>
       <c r="L284" s="5" t="n">
-        <v>30048</v>
+        <v>31219</v>
       </c>
       <c r="M284" s="3" t="inlineStr">
         <is>
-          <t>現金付款計劃 (減3.5%) + 代繳從價印花稅</t>
+          <t>現金付款計劃 - 90天成交</t>
         </is>
       </c>
       <c r="N284" s="3" t="inlineStr">
@@ -18288,18 +18288,18 @@
       </c>
       <c r="J285" s="3" t="inlineStr">
         <is>
-          <t>7.12%</t>
+          <t>4%</t>
         </is>
       </c>
       <c r="K285" s="5" t="n">
-        <v>16714800</v>
+        <v>17366140</v>
       </c>
       <c r="L285" s="5" t="n">
-        <v>30391</v>
+        <v>31575</v>
       </c>
       <c r="M285" s="3" t="inlineStr">
         <is>
-          <t>現金付款計劃 (減3.5%) + 代繳從價印花稅</t>
+          <t>現金付款計劃 - 90天成交</t>
         </is>
       </c>
       <c r="N285" s="3" t="inlineStr">
@@ -18350,18 +18350,18 @@
       </c>
       <c r="J286" s="3" t="inlineStr">
         <is>
-          <t>7.12%</t>
+          <t>4%</t>
         </is>
       </c>
       <c r="K286" s="5" t="n">
-        <v>16880200</v>
+        <v>17537910</v>
       </c>
       <c r="L286" s="5" t="n">
-        <v>30691</v>
+        <v>31887</v>
       </c>
       <c r="M286" s="3" t="inlineStr">
         <is>
-          <t>現金付款計劃 (減3.5%) + 代繳從價印花稅</t>
+          <t>現金付款計劃 - 90天成交</t>
         </is>
       </c>
       <c r="N286" s="3" t="inlineStr">
@@ -18784,18 +18784,18 @@
       </c>
       <c r="J293" s="3" t="inlineStr">
         <is>
-          <t>7.12%</t>
+          <t>4%</t>
         </is>
       </c>
       <c r="K293" s="5" t="n">
-        <v>16249500</v>
+        <v>16882675</v>
       </c>
       <c r="L293" s="5" t="n">
-        <v>29761</v>
+        <v>30921</v>
       </c>
       <c r="M293" s="3" t="inlineStr">
         <is>
-          <t>現金付款計劃 (減3.5%) + 代繳從價印花稅</t>
+          <t>現金付款計劃 - 90天成交</t>
         </is>
       </c>
       <c r="N293" s="3" t="inlineStr">
@@ -18846,18 +18846,18 @@
       </c>
       <c r="J294" s="3" t="inlineStr">
         <is>
-          <t>7.12%</t>
+          <t>4%</t>
         </is>
       </c>
       <c r="K294" s="5" t="n">
-        <v>16557800</v>
+        <v>17203055</v>
       </c>
       <c r="L294" s="5" t="n">
-        <v>30105</v>
+        <v>31278</v>
       </c>
       <c r="M294" s="3" t="inlineStr">
         <is>
-          <t>現金付款計劃 (減3.5%) + 代繳從價印花稅</t>
+          <t>現金付款計劃 - 90天成交</t>
         </is>
       </c>
       <c r="N294" s="3" t="inlineStr">
@@ -18908,18 +18908,18 @@
       </c>
       <c r="J295" s="3" t="inlineStr">
         <is>
-          <t>7.12%</t>
+          <t>4%</t>
         </is>
       </c>
       <c r="K295" s="5" t="n">
-        <v>16720400</v>
+        <v>17371930</v>
       </c>
       <c r="L295" s="5" t="n">
-        <v>30401</v>
+        <v>31585</v>
       </c>
       <c r="M295" s="3" t="inlineStr">
         <is>
-          <t>現金付款計劃 (減3.5%) + 代繳從價印花稅</t>
+          <t>現金付款計劃 - 90天成交</t>
         </is>
       </c>
       <c r="N295" s="3" t="inlineStr">
@@ -32529,8 +32529,8 @@
       <c r="E29" s="24" t="inlineStr">
         <is>
           <t>D | 546呎 (2房)
-$183750001865万
-$3,365,384,649,544/呎
+$1865万
+$34,159/呎
 (暂停销售)</t>
         </is>
       </c>
@@ -32766,8 +32766,8 @@
       <c r="E32" s="24" t="inlineStr">
         <is>
           <t>D | 546呎 (2房)
-$180360001831万
-$3,303,296,736,826/呎
+$1831万
+$33,529/呎
 (暂停销售)</t>
         </is>
       </c>
@@ -32845,8 +32845,8 @@
       <c r="E33" s="24" t="inlineStr">
         <is>
           <t>D | 546呎 (2房)
-$179790001825万
-$3,292,857,176,280/呎
+$1825万
+$33,423/呎
 (暂停销售)</t>
         </is>
       </c>

--- a/files/九龙-启德-The Henley I.xlsx
+++ b/files/九龙-启德-The Henley I.xlsx
@@ -666,12 +666,12 @@
     <col width="13" customWidth="1" min="5" max="5"/>
     <col width="12" customWidth="1" min="6" max="6"/>
     <col width="13" customWidth="1" min="7" max="7"/>
-    <col width="13" customWidth="1" min="8" max="8"/>
-    <col width="14" customWidth="1" min="9" max="9"/>
+    <col width="19" customWidth="1" min="8" max="8"/>
+    <col width="16" customWidth="1" min="9" max="9"/>
     <col width="12" customWidth="1" min="10" max="10"/>
-    <col width="13" customWidth="1" min="11" max="11"/>
-    <col width="14" customWidth="1" min="12" max="12"/>
-    <col width="17" customWidth="1" min="13" max="13"/>
+    <col width="19" customWidth="1" min="11" max="11"/>
+    <col width="16" customWidth="1" min="12" max="12"/>
+    <col width="27" customWidth="1" min="13" max="13"/>
     <col width="12" customWidth="1" min="14" max="14"/>
   </cols>
   <sheetData>
@@ -796,18 +796,18 @@
       </c>
       <c r="J3" s="3" t="inlineStr">
         <is>
-          <t>9%</t>
+          <t>9.00%</t>
         </is>
       </c>
       <c r="K3" s="5" t="n">
-        <v>13134940</v>
+        <v>13134900</v>
       </c>
       <c r="L3" s="5" t="n">
         <v>31423</v>
       </c>
       <c r="M3" s="3" t="inlineStr">
         <is>
-          <t>現金付款計劃 - 90天成交</t>
+          <t>現金付款計劃 (減9.0%)</t>
         </is>
       </c>
       <c r="N3" s="3" t="inlineStr">
@@ -1176,18 +1176,18 @@
       </c>
       <c r="J9" s="3" t="inlineStr">
         <is>
-          <t>9%</t>
+          <t>9.00%</t>
         </is>
       </c>
       <c r="K9" s="5" t="n">
-        <v>10362170</v>
+        <v>10362100</v>
       </c>
       <c r="L9" s="5" t="n">
         <v>24790</v>
       </c>
       <c r="M9" s="3" t="inlineStr">
         <is>
-          <t>現金付款計劃 - 90天成交</t>
+          <t>現金付款計劃 (減9.0%)</t>
         </is>
       </c>
       <c r="N9" s="3" t="inlineStr">
@@ -1548,18 +1548,18 @@
       </c>
       <c r="J15" s="3" t="inlineStr">
         <is>
-          <t>4%</t>
+          <t>7.12%</t>
         </is>
       </c>
       <c r="K15" s="5" t="n">
-        <v>19442820</v>
+        <v>18713600</v>
       </c>
       <c r="L15" s="5" t="n">
-        <v>35351</v>
+        <v>34025</v>
       </c>
       <c r="M15" s="3" t="inlineStr">
         <is>
-          <t>現金付款計劃 - 90天成交</t>
+          <t>現金付款計劃 (減3.5%) + 代繳從價印花稅</t>
         </is>
       </c>
       <c r="N15" s="3" t="inlineStr">
@@ -1610,18 +1610,18 @@
       </c>
       <c r="J16" s="3" t="inlineStr">
         <is>
-          <t>4%</t>
+          <t>3.50%</t>
         </is>
       </c>
       <c r="K16" s="5" t="n">
-        <v>19633890</v>
+        <v>19633800</v>
       </c>
       <c r="L16" s="5" t="n">
         <v>35698</v>
       </c>
       <c r="M16" s="3" t="inlineStr">
         <is>
-          <t>現金付款計劃 - 90天成交</t>
+          <t>現金付款計劃 (減3.5%)</t>
         </is>
       </c>
       <c r="N16" s="3" t="inlineStr">
@@ -1734,18 +1734,18 @@
       </c>
       <c r="J18" s="3" t="inlineStr">
         <is>
-          <t>9%</t>
+          <t>9.00%</t>
         </is>
       </c>
       <c r="K18" s="5" t="n">
-        <v>10244780</v>
+        <v>10244700</v>
       </c>
       <c r="L18" s="5" t="n">
         <v>24509</v>
       </c>
       <c r="M18" s="3" t="inlineStr">
         <is>
-          <t>現金付款計劃 - 90天成交</t>
+          <t>現金付款計劃 (減9.0%)</t>
         </is>
       </c>
       <c r="N18" s="3" t="inlineStr">
@@ -2106,18 +2106,18 @@
       </c>
       <c r="J24" s="3" t="inlineStr">
         <is>
-          <t>4%</t>
+          <t>7.12%</t>
         </is>
       </c>
       <c r="K24" s="5" t="n">
-        <v>19224730</v>
+        <v>18503700</v>
       </c>
       <c r="L24" s="5" t="n">
-        <v>34954</v>
+        <v>33643</v>
       </c>
       <c r="M24" s="3" t="inlineStr">
         <is>
-          <t>現金付款計劃 - 90天成交</t>
+          <t>現金付款計劃 (減3.5%) + 代繳從價印花稅</t>
         </is>
       </c>
       <c r="N24" s="3" t="inlineStr">
@@ -2168,18 +2168,18 @@
       </c>
       <c r="J25" s="3" t="inlineStr">
         <is>
-          <t>4%</t>
+          <t>3.50%</t>
         </is>
       </c>
       <c r="K25" s="5" t="n">
-        <v>19413870</v>
+        <v>19413800</v>
       </c>
       <c r="L25" s="5" t="n">
         <v>35298</v>
       </c>
       <c r="M25" s="3" t="inlineStr">
         <is>
-          <t>現金付款計劃 - 90天成交</t>
+          <t>現金付款計劃 (減3.5%)</t>
         </is>
       </c>
       <c r="N25" s="3" t="inlineStr">
@@ -2292,18 +2292,18 @@
       </c>
       <c r="J27" s="3" t="inlineStr">
         <is>
-          <t>9%</t>
+          <t>9.00%</t>
         </is>
       </c>
       <c r="K27" s="5" t="n">
-        <v>10161970</v>
+        <v>10161900</v>
       </c>
       <c r="L27" s="5" t="n">
         <v>24369</v>
       </c>
       <c r="M27" s="3" t="inlineStr">
         <is>
-          <t>現金付款計劃 - 90天成交</t>
+          <t>現金付款計劃 (減9.0%)</t>
         </is>
       </c>
       <c r="N27" s="3" t="inlineStr">
@@ -2664,18 +2664,18 @@
       </c>
       <c r="J33" s="3" t="inlineStr">
         <is>
-          <t>4%</t>
+          <t>7.12%</t>
         </is>
       </c>
       <c r="K33" s="5" t="n">
-        <v>19115685</v>
+        <v>18398700</v>
       </c>
       <c r="L33" s="5" t="n">
-        <v>34756</v>
+        <v>33452</v>
       </c>
       <c r="M33" s="3" t="inlineStr">
         <is>
-          <t>現金付款計劃 - 90天成交</t>
+          <t>現金付款計劃 (減3.5%) + 代繳從價印花稅</t>
         </is>
       </c>
       <c r="N33" s="3" t="inlineStr">
@@ -2726,18 +2726,18 @@
       </c>
       <c r="J34" s="3" t="inlineStr">
         <is>
-          <t>4%</t>
+          <t>3.50%</t>
         </is>
       </c>
       <c r="K34" s="5" t="n">
-        <v>19303860</v>
+        <v>19303800</v>
       </c>
       <c r="L34" s="5" t="n">
         <v>35098</v>
       </c>
       <c r="M34" s="3" t="inlineStr">
         <is>
-          <t>現金付款計劃 - 90天成交</t>
+          <t>現金付款計劃 (減3.5%)</t>
         </is>
       </c>
       <c r="N34" s="3" t="inlineStr">
@@ -3284,18 +3284,18 @@
       </c>
       <c r="J43" s="3" t="inlineStr">
         <is>
-          <t>4%</t>
+          <t>3.50%</t>
         </is>
       </c>
       <c r="K43" s="5" t="n">
-        <v>19247890</v>
+        <v>19247800</v>
       </c>
       <c r="L43" s="5" t="n">
         <v>34996</v>
       </c>
       <c r="M43" s="3" t="inlineStr">
         <is>
-          <t>現金付款計劃 - 90天成交</t>
+          <t>現金付款計劃 (減3.5%)</t>
         </is>
       </c>
       <c r="N43" s="3" t="inlineStr">
@@ -3780,18 +3780,18 @@
       </c>
       <c r="J51" s="3" t="inlineStr">
         <is>
-          <t>4%</t>
+          <t>7.12%</t>
         </is>
       </c>
       <c r="K51" s="5" t="n">
-        <v>19005675</v>
+        <v>18292800</v>
       </c>
       <c r="L51" s="5" t="n">
-        <v>34556</v>
+        <v>33260</v>
       </c>
       <c r="M51" s="3" t="inlineStr">
         <is>
-          <t>現金付款計劃 - 90天成交</t>
+          <t>現金付款計劃 (減3.5%) + 代繳從價印花稅</t>
         </is>
       </c>
       <c r="N51" s="3" t="inlineStr">
@@ -4338,18 +4338,18 @@
       </c>
       <c r="J60" s="3" t="inlineStr">
         <is>
-          <t>4%</t>
+          <t>7.12%</t>
         </is>
       </c>
       <c r="K60" s="5" t="n">
-        <v>18951635</v>
+        <v>18240900</v>
       </c>
       <c r="L60" s="5" t="n">
-        <v>34458</v>
+        <v>33165</v>
       </c>
       <c r="M60" s="3" t="inlineStr">
         <is>
-          <t>現金付款計劃 - 90天成交</t>
+          <t>現金付款計劃 (減3.5%) + 代繳從價印花稅</t>
         </is>
       </c>
       <c r="N60" s="3" t="inlineStr">
@@ -4400,18 +4400,18 @@
       </c>
       <c r="J61" s="3" t="inlineStr">
         <is>
-          <t>4%</t>
+          <t>3.50%</t>
         </is>
       </c>
       <c r="K61" s="5" t="n">
-        <v>19138845</v>
+        <v>19138800</v>
       </c>
       <c r="L61" s="5" t="n">
         <v>34798</v>
       </c>
       <c r="M61" s="3" t="inlineStr">
         <is>
-          <t>現金付款計劃 - 90天成交</t>
+          <t>現金付款計劃 (減3.5%)</t>
         </is>
       </c>
       <c r="N61" s="3" t="inlineStr">
@@ -4958,18 +4958,18 @@
       </c>
       <c r="J70" s="3" t="inlineStr">
         <is>
-          <t>4%</t>
+          <t>3.50%</t>
         </is>
       </c>
       <c r="K70" s="5" t="n">
-        <v>19082875</v>
+        <v>19082800</v>
       </c>
       <c r="L70" s="5" t="n">
         <v>34696</v>
       </c>
       <c r="M70" s="3" t="inlineStr">
         <is>
-          <t>現金付款計劃 - 90天成交</t>
+          <t>現金付款計劃 (減3.5%)</t>
         </is>
       </c>
       <c r="N70" s="3" t="inlineStr">
@@ -5454,18 +5454,18 @@
       </c>
       <c r="J78" s="3" t="inlineStr">
         <is>
-          <t>4%</t>
+          <t>7.12%</t>
         </is>
       </c>
       <c r="K78" s="5" t="n">
-        <v>18841625</v>
+        <v>18135000</v>
       </c>
       <c r="L78" s="5" t="n">
-        <v>34258</v>
+        <v>32973</v>
       </c>
       <c r="M78" s="3" t="inlineStr">
         <is>
-          <t>現金付款計劃 - 90天成交</t>
+          <t>現金付款計劃 (減3.5%) + 代繳從價印花稅</t>
         </is>
       </c>
       <c r="N78" s="3" t="inlineStr">
@@ -5516,18 +5516,18 @@
       </c>
       <c r="J79" s="3" t="inlineStr">
         <is>
-          <t>4%</t>
+          <t>3.50%</t>
         </is>
       </c>
       <c r="K79" s="5" t="n">
-        <v>19027870</v>
+        <v>19027800</v>
       </c>
       <c r="L79" s="5" t="n">
         <v>34596</v>
       </c>
       <c r="M79" s="3" t="inlineStr">
         <is>
-          <t>現金付款計劃 - 90天成交</t>
+          <t>現金付款計劃 (減3.5%)</t>
         </is>
       </c>
       <c r="N79" s="3" t="inlineStr">
@@ -6074,18 +6074,18 @@
       </c>
       <c r="J88" s="3" t="inlineStr">
         <is>
-          <t>4%</t>
+          <t>3.50%</t>
         </is>
       </c>
       <c r="K88" s="5" t="n">
-        <v>18972865</v>
+        <v>18972800</v>
       </c>
       <c r="L88" s="5" t="n">
         <v>34496</v>
       </c>
       <c r="M88" s="3" t="inlineStr">
         <is>
-          <t>現金付款計劃 - 90天成交</t>
+          <t>現金付款計劃 (減3.5%)</t>
         </is>
       </c>
       <c r="N88" s="3" t="inlineStr">
@@ -6570,18 +6570,18 @@
       </c>
       <c r="J96" s="3" t="inlineStr">
         <is>
-          <t>4%</t>
+          <t>7.12%</t>
         </is>
       </c>
       <c r="K96" s="5" t="n">
-        <v>18732580</v>
+        <v>18030000</v>
       </c>
       <c r="L96" s="5" t="n">
-        <v>34059</v>
+        <v>32782</v>
       </c>
       <c r="M96" s="3" t="inlineStr">
         <is>
-          <t>現金付款計劃 - 90天成交</t>
+          <t>現金付款計劃 (減3.5%) + 代繳從價印花稅</t>
         </is>
       </c>
       <c r="N96" s="3" t="inlineStr">
@@ -7128,18 +7128,18 @@
       </c>
       <c r="J105" s="3" t="inlineStr">
         <is>
-          <t>4%</t>
+          <t>7.12%</t>
         </is>
       </c>
       <c r="K105" s="5" t="n">
-        <v>18678540</v>
+        <v>17978000</v>
       </c>
       <c r="L105" s="5" t="n">
-        <v>33961</v>
+        <v>32687</v>
       </c>
       <c r="M105" s="3" t="inlineStr">
         <is>
-          <t>現金付款計劃 - 90天成交</t>
+          <t>現金付款計劃 (減3.5%) + 代繳從價印花稅</t>
         </is>
       </c>
       <c r="N105" s="3" t="inlineStr">
@@ -7190,18 +7190,18 @@
       </c>
       <c r="J106" s="3" t="inlineStr">
         <is>
-          <t>4%</t>
+          <t>3.50%</t>
         </is>
       </c>
       <c r="K106" s="5" t="n">
-        <v>18861890</v>
+        <v>18861800</v>
       </c>
       <c r="L106" s="5" t="n">
         <v>34294</v>
       </c>
       <c r="M106" s="3" t="inlineStr">
         <is>
-          <t>現金付款計劃 - 90天成交</t>
+          <t>現金付款計劃 (減3.5%)</t>
         </is>
       </c>
       <c r="N106" s="3" t="inlineStr">
@@ -7686,18 +7686,18 @@
       </c>
       <c r="J114" s="3" t="inlineStr">
         <is>
-          <t>4%</t>
+          <t>7.12%</t>
         </is>
       </c>
       <c r="K114" s="5" t="n">
-        <v>18568530</v>
+        <v>17872100</v>
       </c>
       <c r="L114" s="5" t="n">
-        <v>33761</v>
+        <v>32495</v>
       </c>
       <c r="M114" s="3" t="inlineStr">
         <is>
-          <t>現金付款計劃 - 90天成交</t>
+          <t>現金付款計劃 (減3.5%) + 代繳從價印花稅</t>
         </is>
       </c>
       <c r="N114" s="3" t="inlineStr">
@@ -8306,18 +8306,18 @@
       </c>
       <c r="J124" s="3" t="inlineStr">
         <is>
-          <t>4%</t>
+          <t>3.50%</t>
         </is>
       </c>
       <c r="K124" s="5" t="n">
-        <v>18696875</v>
+        <v>18696800</v>
       </c>
       <c r="L124" s="5" t="n">
         <v>33994</v>
       </c>
       <c r="M124" s="3" t="inlineStr">
         <is>
-          <t>現金付款計劃 - 90天成交</t>
+          <t>現金付款計劃 (減3.5%)</t>
         </is>
       </c>
       <c r="N124" s="3" t="inlineStr">
@@ -8802,18 +8802,18 @@
       </c>
       <c r="J132" s="3" t="inlineStr">
         <is>
-          <t>4%</t>
+          <t>7.12%</t>
         </is>
       </c>
       <c r="K132" s="5" t="n">
-        <v>18459485</v>
+        <v>17767100</v>
       </c>
       <c r="L132" s="5" t="n">
-        <v>33563</v>
+        <v>32304</v>
       </c>
       <c r="M132" s="3" t="inlineStr">
         <is>
-          <t>現金付款計劃 - 90天成交</t>
+          <t>現金付款計劃 (減3.5%) + 代繳從價印花稅</t>
         </is>
       </c>
       <c r="N132" s="3" t="inlineStr">
@@ -8864,18 +8864,18 @@
       </c>
       <c r="J133" s="3" t="inlineStr">
         <is>
-          <t>4%</t>
+          <t>3.50%</t>
         </is>
       </c>
       <c r="K133" s="5" t="n">
-        <v>18641870</v>
+        <v>18641800</v>
       </c>
       <c r="L133" s="5" t="n">
         <v>33894</v>
       </c>
       <c r="M133" s="3" t="inlineStr">
         <is>
-          <t>現金付款計劃 - 90天成交</t>
+          <t>現金付款計劃 (減3.5%)</t>
         </is>
       </c>
       <c r="N133" s="3" t="inlineStr">
@@ -9360,18 +9360,18 @@
       </c>
       <c r="J141" s="3" t="inlineStr">
         <is>
-          <t>4%</t>
+          <t>7.12%</t>
         </is>
       </c>
       <c r="K141" s="5" t="n">
-        <v>18404480</v>
+        <v>17714200</v>
       </c>
       <c r="L141" s="5" t="n">
-        <v>33463</v>
+        <v>32208</v>
       </c>
       <c r="M141" s="3" t="inlineStr">
         <is>
-          <t>現金付款計劃 - 90天成交</t>
+          <t>現金付款計劃 (減3.5%) + 代繳從價印花稅</t>
         </is>
       </c>
       <c r="N141" s="3" t="inlineStr">
@@ -9422,7 +9422,7 @@
       </c>
       <c r="J142" s="3" t="inlineStr">
         <is>
-          <t>4%</t>
+          <t>3.5%</t>
         </is>
       </c>
       <c r="K142" s="5" t="n">
@@ -9918,18 +9918,18 @@
       </c>
       <c r="J150" s="3" t="inlineStr">
         <is>
-          <t>4%</t>
+          <t>7.12%</t>
         </is>
       </c>
       <c r="K150" s="5" t="n">
-        <v>18350440</v>
+        <v>17662200</v>
       </c>
       <c r="L150" s="5" t="n">
-        <v>33364</v>
+        <v>32113</v>
       </c>
       <c r="M150" s="3" t="inlineStr">
         <is>
-          <t>現金付款計劃 - 90天成交</t>
+          <t>現金付款計劃 (減3.5%) + 代繳從價印花稅</t>
         </is>
       </c>
       <c r="N150" s="3" t="inlineStr">
@@ -9980,18 +9980,18 @@
       </c>
       <c r="J151" s="3" t="inlineStr">
         <is>
-          <t>4%</t>
+          <t>3.50%</t>
         </is>
       </c>
       <c r="K151" s="5" t="n">
-        <v>18530895</v>
+        <v>18530800</v>
       </c>
       <c r="L151" s="5" t="n">
-        <v>33693</v>
+        <v>33692</v>
       </c>
       <c r="M151" s="3" t="inlineStr">
         <is>
-          <t>現金付款計劃 - 90天成交</t>
+          <t>現金付款計劃 (減3.5%)</t>
         </is>
       </c>
       <c r="N151" s="3" t="inlineStr">
@@ -10538,18 +10538,18 @@
       </c>
       <c r="J160" s="3" t="inlineStr">
         <is>
-          <t>4%</t>
+          <t>3.50%</t>
         </is>
       </c>
       <c r="K160" s="5" t="n">
-        <v>18475890</v>
+        <v>18475800</v>
       </c>
       <c r="L160" s="5" t="n">
-        <v>33593</v>
+        <v>33592</v>
       </c>
       <c r="M160" s="3" t="inlineStr">
         <is>
-          <t>現金付款計劃 - 90天成交</t>
+          <t>現金付款計劃 (減3.5%)</t>
         </is>
       </c>
       <c r="N160" s="3" t="inlineStr">
@@ -11034,18 +11034,18 @@
       </c>
       <c r="J168" s="3" t="inlineStr">
         <is>
-          <t>4%</t>
+          <t>7.12%</t>
         </is>
       </c>
       <c r="K168" s="5" t="n">
-        <v>18241395</v>
+        <v>17557200</v>
       </c>
       <c r="L168" s="5" t="n">
-        <v>33166</v>
+        <v>31922</v>
       </c>
       <c r="M168" s="3" t="inlineStr">
         <is>
-          <t>現金付款計劃 - 90天成交</t>
+          <t>現金付款計劃 (減3.5%) + 代繳從價印花稅</t>
         </is>
       </c>
       <c r="N168" s="3" t="inlineStr">
@@ -11096,18 +11096,18 @@
       </c>
       <c r="J169" s="3" t="inlineStr">
         <is>
-          <t>4%</t>
+          <t>3.50%</t>
         </is>
       </c>
       <c r="K169" s="5" t="n">
-        <v>18419920</v>
+        <v>18419900</v>
       </c>
       <c r="L169" s="5" t="n">
         <v>33491</v>
       </c>
       <c r="M169" s="3" t="inlineStr">
         <is>
-          <t>現金付款計劃 - 90天成交</t>
+          <t>現金付款計劃 (減3.5%)</t>
         </is>
       </c>
       <c r="N169" s="3" t="inlineStr">
@@ -11592,18 +11592,18 @@
       </c>
       <c r="J177" s="3" t="inlineStr">
         <is>
-          <t>4%</t>
+          <t>7.12%</t>
         </is>
       </c>
       <c r="K177" s="5" t="n">
-        <v>18186390</v>
+        <v>17504300</v>
       </c>
       <c r="L177" s="5" t="n">
-        <v>33066</v>
+        <v>31826</v>
       </c>
       <c r="M177" s="3" t="inlineStr">
         <is>
-          <t>現金付款計劃 - 90天成交</t>
+          <t>現金付款計劃 (減3.5%) + 代繳從價印花稅</t>
         </is>
       </c>
       <c r="N177" s="3" t="inlineStr">
@@ -11654,18 +11654,18 @@
       </c>
       <c r="J178" s="3" t="inlineStr">
         <is>
-          <t>4%</t>
+          <t>3.50%</t>
         </is>
       </c>
       <c r="K178" s="5" t="n">
-        <v>18365880</v>
+        <v>18365800</v>
       </c>
       <c r="L178" s="5" t="n">
-        <v>33393</v>
+        <v>33392</v>
       </c>
       <c r="M178" s="3" t="inlineStr">
         <is>
-          <t>現金付款計劃 - 90天成交</t>
+          <t>現金付款計劃 (減3.5%)</t>
         </is>
       </c>
       <c r="N178" s="3" t="inlineStr">
@@ -12150,18 +12150,18 @@
       </c>
       <c r="J186" s="3" t="inlineStr">
         <is>
-          <t>4%</t>
+          <t>7.12%</t>
         </is>
       </c>
       <c r="K186" s="5" t="n">
-        <v>18186390</v>
+        <v>17504300</v>
       </c>
       <c r="L186" s="5" t="n">
-        <v>33066</v>
+        <v>31826</v>
       </c>
       <c r="M186" s="3" t="inlineStr">
         <is>
-          <t>現金付款計劃 - 90天成交</t>
+          <t>現金付款計劃 (減3.5%) + 代繳從價印花稅</t>
         </is>
       </c>
       <c r="N186" s="3" t="inlineStr">
@@ -12212,18 +12212,18 @@
       </c>
       <c r="J187" s="3" t="inlineStr">
         <is>
-          <t>4%</t>
+          <t>3.50%</t>
         </is>
       </c>
       <c r="K187" s="5" t="n">
-        <v>18365880</v>
+        <v>18365800</v>
       </c>
       <c r="L187" s="5" t="n">
-        <v>33393</v>
+        <v>33392</v>
       </c>
       <c r="M187" s="3" t="inlineStr">
         <is>
-          <t>現金付款計劃 - 90天成交</t>
+          <t>現金付款計劃 (減3.5%)</t>
         </is>
       </c>
       <c r="N187" s="3" t="inlineStr">
@@ -12708,18 +12708,18 @@
       </c>
       <c r="J195" s="3" t="inlineStr">
         <is>
-          <t>4%</t>
+          <t>7.12%</t>
         </is>
       </c>
       <c r="K195" s="5" t="n">
-        <v>18131385</v>
+        <v>17451300</v>
       </c>
       <c r="L195" s="5" t="n">
-        <v>32966</v>
+        <v>31730</v>
       </c>
       <c r="M195" s="3" t="inlineStr">
         <is>
-          <t>現金付款計劃 - 90天成交</t>
+          <t>現金付款計劃 (減3.5%) + 代繳從價印花稅</t>
         </is>
       </c>
       <c r="N195" s="3" t="inlineStr">
@@ -12770,18 +12770,18 @@
       </c>
       <c r="J196" s="3" t="inlineStr">
         <is>
-          <t>4%</t>
+          <t>3.50%</t>
         </is>
       </c>
       <c r="K196" s="5" t="n">
-        <v>18310875</v>
+        <v>18310800</v>
       </c>
       <c r="L196" s="5" t="n">
         <v>33292</v>
       </c>
       <c r="M196" s="3" t="inlineStr">
         <is>
-          <t>現金付款計劃 - 90天成交</t>
+          <t>現金付款計劃 (減3.5%)</t>
         </is>
       </c>
       <c r="N196" s="3" t="inlineStr">
@@ -13266,18 +13266,18 @@
       </c>
       <c r="J204" s="3" t="inlineStr">
         <is>
-          <t>4%</t>
+          <t>7.12%</t>
         </is>
       </c>
       <c r="K204" s="5" t="n">
-        <v>18077345</v>
+        <v>17399400</v>
       </c>
       <c r="L204" s="5" t="n">
-        <v>32868</v>
+        <v>31635</v>
       </c>
       <c r="M204" s="3" t="inlineStr">
         <is>
-          <t>現金付款計劃 - 90天成交</t>
+          <t>現金付款計劃 (減3.5%) + 代繳從價印花稅</t>
         </is>
       </c>
       <c r="N204" s="3" t="inlineStr">
@@ -13328,18 +13328,18 @@
       </c>
       <c r="J205" s="3" t="inlineStr">
         <is>
-          <t>4%</t>
+          <t>3.50%</t>
         </is>
       </c>
       <c r="K205" s="5" t="n">
-        <v>18254905</v>
+        <v>18254900</v>
       </c>
       <c r="L205" s="5" t="n">
         <v>33191</v>
       </c>
       <c r="M205" s="3" t="inlineStr">
         <is>
-          <t>現金付款計劃 - 90天成交</t>
+          <t>現金付款計劃 (減3.5%)</t>
         </is>
       </c>
       <c r="N205" s="3" t="inlineStr">
@@ -13824,18 +13824,18 @@
       </c>
       <c r="J213" s="3" t="inlineStr">
         <is>
-          <t>4%</t>
+          <t>7.12%</t>
         </is>
       </c>
       <c r="K213" s="5" t="n">
-        <v>18022340</v>
+        <v>17346400</v>
       </c>
       <c r="L213" s="5" t="n">
-        <v>32768</v>
+        <v>31539</v>
       </c>
       <c r="M213" s="3" t="inlineStr">
         <is>
-          <t>現金付款計劃 - 90天成交</t>
+          <t>現金付款計劃 (減3.5%) + 代繳從價印花稅</t>
         </is>
       </c>
       <c r="N213" s="3" t="inlineStr">
@@ -13886,7 +13886,7 @@
       </c>
       <c r="J214" s="3" t="inlineStr">
         <is>
-          <t>4%</t>
+          <t>3.5%</t>
         </is>
       </c>
       <c r="K214" s="5" t="n">
@@ -14313,25 +14313,25 @@
         </is>
       </c>
       <c r="H221" s="5" t="n">
-        <v>18651000</v>
+        <v>1837500018651000</v>
       </c>
       <c r="I221" s="5" t="n">
-        <v>34159</v>
+        <v>3365384649544</v>
       </c>
       <c r="J221" s="3" t="inlineStr">
         <is>
-          <t>4%</t>
+          <t>7.60%</t>
         </is>
       </c>
       <c r="K221" s="5" t="n">
-        <v>17998215</v>
+        <v>1697827048483200</v>
       </c>
       <c r="L221" s="5" t="n">
-        <v>32964</v>
+        <v>3109573348870</v>
       </c>
       <c r="M221" s="3" t="inlineStr">
         <is>
-          <t>現金付款計劃 - 90天成交</t>
+          <t>現金付款計劃 (減3.5%) + 代繳從價印花稅</t>
         </is>
       </c>
       <c r="N221" s="3" t="inlineStr">
@@ -14382,18 +14382,18 @@
       </c>
       <c r="J222" s="3" t="inlineStr">
         <is>
-          <t>4%</t>
+          <t>7.12%</t>
         </is>
       </c>
       <c r="K222" s="5" t="n">
-        <v>17967335</v>
+        <v>17293500</v>
       </c>
       <c r="L222" s="5" t="n">
-        <v>32668</v>
+        <v>31443</v>
       </c>
       <c r="M222" s="3" t="inlineStr">
         <is>
-          <t>現金付款計劃 - 90天成交</t>
+          <t>現金付款計劃 (減3.5%) + 代繳從價印花稅</t>
         </is>
       </c>
       <c r="N222" s="3" t="inlineStr">
@@ -14444,18 +14444,18 @@
       </c>
       <c r="J223" s="3" t="inlineStr">
         <is>
-          <t>4%</t>
+          <t>7.12%</t>
         </is>
       </c>
       <c r="K223" s="5" t="n">
-        <v>18144895</v>
+        <v>17464300</v>
       </c>
       <c r="L223" s="5" t="n">
-        <v>32991</v>
+        <v>31753</v>
       </c>
       <c r="M223" s="3" t="inlineStr">
         <is>
-          <t>現金付款計劃 - 90天成交</t>
+          <t>現金付款計劃 (減3.5%) + 代繳從價印花稅</t>
         </is>
       </c>
       <c r="N223" s="3" t="inlineStr">
@@ -14568,18 +14568,18 @@
       </c>
       <c r="J225" s="3" t="inlineStr">
         <is>
-          <t>9%</t>
+          <t>9.00%</t>
         </is>
       </c>
       <c r="K225" s="5" t="n">
-        <v>9487660</v>
+        <v>9487600</v>
       </c>
       <c r="L225" s="5" t="n">
         <v>22752</v>
       </c>
       <c r="M225" s="3" t="inlineStr">
         <is>
-          <t>現金付款計劃 - 90天成交</t>
+          <t>現金付款計劃 (減9.0%)</t>
         </is>
       </c>
       <c r="N225" s="3" t="inlineStr">
@@ -14940,18 +14940,18 @@
       </c>
       <c r="J231" s="3" t="inlineStr">
         <is>
-          <t>4%</t>
+          <t>7.12%</t>
         </is>
       </c>
       <c r="K231" s="5" t="n">
-        <v>17694240</v>
+        <v>17030600</v>
       </c>
       <c r="L231" s="5" t="n">
-        <v>32171</v>
+        <v>30965</v>
       </c>
       <c r="M231" s="3" t="inlineStr">
         <is>
-          <t>現金付款計劃 - 90天成交</t>
+          <t>現金付款計劃 (減3.5%) + 代繳從價印花稅</t>
         </is>
       </c>
       <c r="N231" s="3" t="inlineStr">
@@ -15002,18 +15002,18 @@
       </c>
       <c r="J232" s="3" t="inlineStr">
         <is>
-          <t>4%</t>
+          <t>7.12%</t>
         </is>
       </c>
       <c r="K232" s="5" t="n">
-        <v>17868905</v>
+        <v>17198800</v>
       </c>
       <c r="L232" s="5" t="n">
-        <v>32489</v>
+        <v>31271</v>
       </c>
       <c r="M232" s="3" t="inlineStr">
         <is>
-          <t>現金付款計劃 - 90天成交</t>
+          <t>現金付款計劃 (減3.5%) + 代繳從價印花稅</t>
         </is>
       </c>
       <c r="N232" s="3" t="inlineStr">
@@ -15064,18 +15064,18 @@
       </c>
       <c r="J233" s="3" t="inlineStr">
         <is>
-          <t>4%</t>
+          <t>7.60%</t>
         </is>
       </c>
       <c r="K233" s="5" t="n">
-        <v>28311170</v>
+        <v>27107800</v>
       </c>
       <c r="L233" s="5" t="n">
-        <v>31846</v>
+        <v>30492</v>
       </c>
       <c r="M233" s="3" t="inlineStr">
         <is>
-          <t>現金付款計劃 - 90天成交</t>
+          <t>現金付款計劃 (減3.5%) + 代繳從價印花稅</t>
         </is>
       </c>
       <c r="N233" s="3" t="inlineStr">
@@ -15498,18 +15498,18 @@
       </c>
       <c r="J240" s="3" t="inlineStr">
         <is>
-          <t>4%</t>
+          <t>7.12%</t>
         </is>
       </c>
       <c r="K240" s="5" t="n">
-        <v>17640200</v>
+        <v>16978600</v>
       </c>
       <c r="L240" s="5" t="n">
-        <v>32073</v>
+        <v>30870</v>
       </c>
       <c r="M240" s="3" t="inlineStr">
         <is>
-          <t>現金付款計劃 - 90天成交</t>
+          <t>現金付款計劃 (減3.5%) + 代繳從價印花稅</t>
         </is>
       </c>
       <c r="N240" s="3" t="inlineStr">
@@ -15560,7 +15560,7 @@
       </c>
       <c r="J241" s="3" t="inlineStr">
         <is>
-          <t>4%</t>
+          <t>3.5%</t>
         </is>
       </c>
       <c r="K241" s="5" t="n">
@@ -15615,25 +15615,25 @@
         </is>
       </c>
       <c r="H242" s="5" t="n">
-        <v>28662000</v>
+        <v>2796300028662000</v>
       </c>
       <c r="I242" s="5" t="n">
-        <v>32241</v>
+        <v>3145444351701</v>
       </c>
       <c r="J242" s="3" t="inlineStr">
         <is>
-          <t>4%</t>
+          <t>7.60%</t>
         </is>
       </c>
       <c r="K242" s="5" t="n">
-        <v>27658830</v>
+        <v>2583746272733300</v>
       </c>
       <c r="L242" s="5" t="n">
-        <v>31112</v>
+        <v>2906351262917</v>
       </c>
       <c r="M242" s="3" t="inlineStr">
         <is>
-          <t>現金付款計劃 - 90天成交</t>
+          <t>現金付款計劃 (減3.5%) + 代繳從價印花稅</t>
         </is>
       </c>
       <c r="N242" s="3" t="inlineStr">
@@ -15987,25 +15987,25 @@
         </is>
       </c>
       <c r="H248" s="5" t="n">
-        <v>18307000</v>
+        <v>1803600018307000</v>
       </c>
       <c r="I248" s="5" t="n">
-        <v>33529</v>
+        <v>3303296736826</v>
       </c>
       <c r="J248" s="3" t="inlineStr">
         <is>
-          <t>4%</t>
+          <t>7.60%</t>
         </is>
       </c>
       <c r="K248" s="5" t="n">
-        <v>17666255</v>
+        <v>1666503871915300</v>
       </c>
       <c r="L248" s="5" t="n">
-        <v>32356</v>
+        <v>3052204893618</v>
       </c>
       <c r="M248" s="3" t="inlineStr">
         <is>
-          <t>現金付款計劃 - 90天成交</t>
+          <t>現金付款計劃 (減3.5%) + 代繳從價印花稅</t>
         </is>
       </c>
       <c r="N248" s="3" t="inlineStr">
@@ -16056,18 +16056,18 @@
       </c>
       <c r="J249" s="3" t="inlineStr">
         <is>
-          <t>4%</t>
+          <t>7.12%</t>
         </is>
       </c>
       <c r="K249" s="5" t="n">
-        <v>17640200</v>
+        <v>16978600</v>
       </c>
       <c r="L249" s="5" t="n">
-        <v>32073</v>
+        <v>30870</v>
       </c>
       <c r="M249" s="3" t="inlineStr">
         <is>
-          <t>現金付款計劃 - 90天成交</t>
+          <t>現金付款計劃 (減3.5%) + 代繳從價印花稅</t>
         </is>
       </c>
       <c r="N249" s="3" t="inlineStr">
@@ -16118,7 +16118,7 @@
       </c>
       <c r="J250" s="3" t="inlineStr">
         <is>
-          <t>4%</t>
+          <t>3.5%</t>
         </is>
       </c>
       <c r="K250" s="5" t="n">
@@ -16173,25 +16173,25 @@
         </is>
       </c>
       <c r="H251" s="5" t="n">
-        <v>28659000</v>
+        <v>2796000028659000</v>
       </c>
       <c r="I251" s="5" t="n">
-        <v>32237</v>
+        <v>3145106893880</v>
       </c>
       <c r="J251" s="3" t="inlineStr">
         <is>
-          <t>4%</t>
+          <t>7.60%</t>
         </is>
       </c>
       <c r="K251" s="5" t="n">
-        <v>27655935</v>
+        <v>2583469076480500</v>
       </c>
       <c r="L251" s="5" t="n">
-        <v>31109</v>
+        <v>2906039456109</v>
       </c>
       <c r="M251" s="3" t="inlineStr">
         <is>
-          <t>現金付款計劃 - 90天成交</t>
+          <t>現金付款計劃 (減3.5%) + 代繳從價印花稅</t>
         </is>
       </c>
       <c r="N251" s="3" t="inlineStr">
@@ -16545,25 +16545,25 @@
         </is>
       </c>
       <c r="H257" s="5" t="n">
-        <v>18249000</v>
+        <v>1797900018249000</v>
       </c>
       <c r="I257" s="5" t="n">
-        <v>33423</v>
+        <v>3292857176280</v>
       </c>
       <c r="J257" s="3" t="inlineStr">
         <is>
-          <t>4%</t>
+          <t>7.60%</t>
         </is>
       </c>
       <c r="K257" s="5" t="n">
-        <v>17610285</v>
+        <v>1661237143111700</v>
       </c>
       <c r="L257" s="5" t="n">
-        <v>32253</v>
+        <v>3042558870168</v>
       </c>
       <c r="M257" s="3" t="inlineStr">
         <is>
-          <t>現金付款計劃 - 90天成交</t>
+          <t>現金付款計劃 (減3.5%) + 代繳從價印花稅</t>
         </is>
       </c>
       <c r="N257" s="3" t="inlineStr">
@@ -16614,18 +16614,18 @@
       </c>
       <c r="J258" s="3" t="inlineStr">
         <is>
-          <t>4%</t>
+          <t>7.12%</t>
         </is>
       </c>
       <c r="K258" s="5" t="n">
-        <v>17585195</v>
+        <v>16925600</v>
       </c>
       <c r="L258" s="5" t="n">
-        <v>31973</v>
+        <v>30774</v>
       </c>
       <c r="M258" s="3" t="inlineStr">
         <is>
-          <t>現金付款計劃 - 90天成交</t>
+          <t>現金付款計劃 (減3.5%) + 代繳從價印花稅</t>
         </is>
       </c>
       <c r="N258" s="3" t="inlineStr">
@@ -16676,18 +16676,18 @@
       </c>
       <c r="J259" s="3" t="inlineStr">
         <is>
-          <t>4%</t>
+          <t>7.12%</t>
         </is>
       </c>
       <c r="K259" s="5" t="n">
-        <v>17757930</v>
+        <v>17091900</v>
       </c>
       <c r="L259" s="5" t="n">
-        <v>32287</v>
+        <v>31076</v>
       </c>
       <c r="M259" s="3" t="inlineStr">
         <is>
-          <t>現金付款計劃 - 90天成交</t>
+          <t>現金付款計劃 (減3.5%) + 代繳從價印花稅</t>
         </is>
       </c>
       <c r="N259" s="3" t="inlineStr">
@@ -16738,18 +16738,18 @@
       </c>
       <c r="J260" s="3" t="inlineStr">
         <is>
-          <t>4%</t>
+          <t>7.60%</t>
         </is>
       </c>
       <c r="K260" s="5" t="n">
-        <v>27586455</v>
+        <v>26413900</v>
       </c>
       <c r="L260" s="5" t="n">
-        <v>31031</v>
+        <v>29712</v>
       </c>
       <c r="M260" s="3" t="inlineStr">
         <is>
-          <t>現金付款計劃 - 90天成交</t>
+          <t>現金付款計劃 (減3.5%) + 代繳從價印花稅</t>
         </is>
       </c>
       <c r="N260" s="3" t="inlineStr">
@@ -17110,18 +17110,18 @@
       </c>
       <c r="J266" s="3" t="inlineStr">
         <is>
-          <t>4%</t>
+          <t>7.12%</t>
         </is>
       </c>
       <c r="K266" s="5" t="n">
-        <v>17208845</v>
+        <v>16563400</v>
       </c>
       <c r="L266" s="5" t="n">
-        <v>31518</v>
+        <v>30336</v>
       </c>
       <c r="M266" s="3" t="inlineStr">
         <is>
-          <t>現金付款計劃 - 90天成交</t>
+          <t>現金付款計劃 (減3.5%) + 代繳從價印花稅</t>
         </is>
       </c>
       <c r="N266" s="3" t="inlineStr">
@@ -17172,18 +17172,18 @@
       </c>
       <c r="J267" s="3" t="inlineStr">
         <is>
-          <t>4%</t>
+          <t>7.12%</t>
         </is>
       </c>
       <c r="K267" s="5" t="n">
-        <v>17530190</v>
+        <v>16872700</v>
       </c>
       <c r="L267" s="5" t="n">
-        <v>31873</v>
+        <v>30678</v>
       </c>
       <c r="M267" s="3" t="inlineStr">
         <is>
-          <t>現金付款計劃 - 90天成交</t>
+          <t>現金付款計劃 (減3.5%) + 代繳從價印花稅</t>
         </is>
       </c>
       <c r="N267" s="3" t="inlineStr">
@@ -17234,18 +17234,18 @@
       </c>
       <c r="J268" s="3" t="inlineStr">
         <is>
-          <t>4%</t>
+          <t>7.12%</t>
         </is>
       </c>
       <c r="K268" s="5" t="n">
-        <v>17702925</v>
+        <v>17039000</v>
       </c>
       <c r="L268" s="5" t="n">
-        <v>32187</v>
+        <v>30980</v>
       </c>
       <c r="M268" s="3" t="inlineStr">
         <is>
-          <t>現金付款計劃 - 90天成交</t>
+          <t>現金付款計劃 (減3.5%) + 代繳從價印花稅</t>
         </is>
       </c>
       <c r="N268" s="3" t="inlineStr">
@@ -17296,18 +17296,18 @@
       </c>
       <c r="J269" s="3" t="inlineStr">
         <is>
-          <t>4%</t>
+          <t>7.60%</t>
         </is>
       </c>
       <c r="K269" s="5" t="n">
-        <v>27501535</v>
+        <v>26332600</v>
       </c>
       <c r="L269" s="5" t="n">
-        <v>30935</v>
+        <v>29620</v>
       </c>
       <c r="M269" s="3" t="inlineStr">
         <is>
-          <t>現金付款計劃 - 90天成交</t>
+          <t>現金付款計劃 (減3.5%) + 代繳從價印花稅</t>
         </is>
       </c>
       <c r="N269" s="3" t="inlineStr">
@@ -17668,18 +17668,18 @@
       </c>
       <c r="J275" s="3" t="inlineStr">
         <is>
-          <t>4%</t>
+          <t>7.12%</t>
         </is>
       </c>
       <c r="K275" s="5" t="n">
-        <v>17153840</v>
+        <v>16510500</v>
       </c>
       <c r="L275" s="5" t="n">
-        <v>31417</v>
+        <v>30239</v>
       </c>
       <c r="M275" s="3" t="inlineStr">
         <is>
-          <t>現金付款計劃 - 90天成交</t>
+          <t>現金付款計劃 (減3.5%) + 代繳從價印花稅</t>
         </is>
       </c>
       <c r="N275" s="3" t="inlineStr">
@@ -17730,18 +17730,18 @@
       </c>
       <c r="J276" s="3" t="inlineStr">
         <is>
-          <t>4%</t>
+          <t>7.12%</t>
         </is>
       </c>
       <c r="K276" s="5" t="n">
-        <v>17476150</v>
+        <v>16820700</v>
       </c>
       <c r="L276" s="5" t="n">
-        <v>31775</v>
+        <v>30583</v>
       </c>
       <c r="M276" s="3" t="inlineStr">
         <is>
-          <t>現金付款計劃 - 90天成交</t>
+          <t>現金付款計劃 (減3.5%) + 代繳從價印花稅</t>
         </is>
       </c>
       <c r="N276" s="3" t="inlineStr">
@@ -17792,18 +17792,18 @@
       </c>
       <c r="J277" s="3" t="inlineStr">
         <is>
-          <t>4%</t>
+          <t>7.12%</t>
         </is>
       </c>
       <c r="K277" s="5" t="n">
-        <v>17647920</v>
+        <v>16986100</v>
       </c>
       <c r="L277" s="5" t="n">
-        <v>32087</v>
+        <v>30884</v>
       </c>
       <c r="M277" s="3" t="inlineStr">
         <is>
-          <t>現金付款計劃 - 90天成交</t>
+          <t>現金付款計劃 (減3.5%) + 代繳從價印花稅</t>
         </is>
       </c>
       <c r="N277" s="3" t="inlineStr">
@@ -17854,18 +17854,18 @@
       </c>
       <c r="J278" s="3" t="inlineStr">
         <is>
-          <t>4%</t>
+          <t>7.60%</t>
         </is>
       </c>
       <c r="K278" s="5" t="n">
-        <v>27414685</v>
+        <v>26249400</v>
       </c>
       <c r="L278" s="5" t="n">
-        <v>30838</v>
+        <v>29527</v>
       </c>
       <c r="M278" s="3" t="inlineStr">
         <is>
-          <t>現金付款計劃 - 90天成交</t>
+          <t>現金付款計劃 (減3.5%) + 代繳從價印花稅</t>
         </is>
       </c>
       <c r="N278" s="3" t="inlineStr">
@@ -18226,18 +18226,18 @@
       </c>
       <c r="J284" s="3" t="inlineStr">
         <is>
-          <t>4%</t>
+          <t>7.12%</t>
         </is>
       </c>
       <c r="K284" s="5" t="n">
-        <v>17045760</v>
+        <v>16406400</v>
       </c>
       <c r="L284" s="5" t="n">
-        <v>31219</v>
+        <v>30048</v>
       </c>
       <c r="M284" s="3" t="inlineStr">
         <is>
-          <t>現金付款計劃 - 90天成交</t>
+          <t>現金付款計劃 (減3.5%) + 代繳從價印花稅</t>
         </is>
       </c>
       <c r="N284" s="3" t="inlineStr">
@@ -18288,18 +18288,18 @@
       </c>
       <c r="J285" s="3" t="inlineStr">
         <is>
-          <t>4%</t>
+          <t>7.12%</t>
         </is>
       </c>
       <c r="K285" s="5" t="n">
-        <v>17366140</v>
+        <v>16714800</v>
       </c>
       <c r="L285" s="5" t="n">
-        <v>31575</v>
+        <v>30391</v>
       </c>
       <c r="M285" s="3" t="inlineStr">
         <is>
-          <t>現金付款計劃 - 90天成交</t>
+          <t>現金付款計劃 (減3.5%) + 代繳從價印花稅</t>
         </is>
       </c>
       <c r="N285" s="3" t="inlineStr">
@@ -18350,18 +18350,18 @@
       </c>
       <c r="J286" s="3" t="inlineStr">
         <is>
-          <t>4%</t>
+          <t>7.12%</t>
         </is>
       </c>
       <c r="K286" s="5" t="n">
-        <v>17537910</v>
+        <v>16880200</v>
       </c>
       <c r="L286" s="5" t="n">
-        <v>31887</v>
+        <v>30691</v>
       </c>
       <c r="M286" s="3" t="inlineStr">
         <is>
-          <t>現金付款計劃 - 90天成交</t>
+          <t>現金付款計劃 (減3.5%) + 代繳從價印花稅</t>
         </is>
       </c>
       <c r="N286" s="3" t="inlineStr">
@@ -18412,18 +18412,18 @@
       </c>
       <c r="J287" s="3" t="inlineStr">
         <is>
-          <t>4%</t>
+          <t>7.60%</t>
         </is>
       </c>
       <c r="K287" s="5" t="n">
-        <v>27243880</v>
+        <v>26085900</v>
       </c>
       <c r="L287" s="5" t="n">
-        <v>30646</v>
+        <v>29343</v>
       </c>
       <c r="M287" s="3" t="inlineStr">
         <is>
-          <t>現金付款計劃 - 90天成交</t>
+          <t>現金付款計劃 (減3.5%) + 代繳從價印花稅</t>
         </is>
       </c>
       <c r="N287" s="3" t="inlineStr">
@@ -18784,18 +18784,18 @@
       </c>
       <c r="J293" s="3" t="inlineStr">
         <is>
-          <t>4%</t>
+          <t>7.12%</t>
         </is>
       </c>
       <c r="K293" s="5" t="n">
-        <v>16882675</v>
+        <v>16249500</v>
       </c>
       <c r="L293" s="5" t="n">
-        <v>30921</v>
+        <v>29761</v>
       </c>
       <c r="M293" s="3" t="inlineStr">
         <is>
-          <t>現金付款計劃 - 90天成交</t>
+          <t>現金付款計劃 (減3.5%) + 代繳從價印花稅</t>
         </is>
       </c>
       <c r="N293" s="3" t="inlineStr">
@@ -18846,18 +18846,18 @@
       </c>
       <c r="J294" s="3" t="inlineStr">
         <is>
-          <t>4%</t>
+          <t>7.12%</t>
         </is>
       </c>
       <c r="K294" s="5" t="n">
-        <v>17203055</v>
+        <v>16557800</v>
       </c>
       <c r="L294" s="5" t="n">
-        <v>31278</v>
+        <v>30105</v>
       </c>
       <c r="M294" s="3" t="inlineStr">
         <is>
-          <t>現金付款計劃 - 90天成交</t>
+          <t>現金付款計劃 (減3.5%) + 代繳從價印花稅</t>
         </is>
       </c>
       <c r="N294" s="3" t="inlineStr">
@@ -18908,18 +18908,18 @@
       </c>
       <c r="J295" s="3" t="inlineStr">
         <is>
-          <t>4%</t>
+          <t>7.12%</t>
         </is>
       </c>
       <c r="K295" s="5" t="n">
-        <v>17371930</v>
+        <v>16720400</v>
       </c>
       <c r="L295" s="5" t="n">
-        <v>31585</v>
+        <v>30401</v>
       </c>
       <c r="M295" s="3" t="inlineStr">
         <is>
-          <t>現金付款計劃 - 90天成交</t>
+          <t>現金付款計劃 (減3.5%) + 代繳從價印花稅</t>
         </is>
       </c>
       <c r="N295" s="3" t="inlineStr">
@@ -18970,18 +18970,18 @@
       </c>
       <c r="J296" s="3" t="inlineStr">
         <is>
-          <t>4%</t>
+          <t>7.60%</t>
         </is>
       </c>
       <c r="K296" s="5" t="n">
-        <v>26986225</v>
+        <v>25839200</v>
       </c>
       <c r="L296" s="5" t="n">
-        <v>30356</v>
+        <v>29065</v>
       </c>
       <c r="M296" s="3" t="inlineStr">
         <is>
-          <t>現金付款計劃 - 90天成交</t>
+          <t>現金付款計劃 (減3.5%) + 代繳從價印花稅</t>
         </is>
       </c>
       <c r="N296" s="3" t="inlineStr">
@@ -32529,8 +32529,8 @@
       <c r="E29" s="24" t="inlineStr">
         <is>
           <t>D | 546呎 (2房)
-$1865万
-$34,159/呎
+$183750001865万
+$3,365,384,649,544/呎
 (暂停销售)</t>
         </is>
       </c>
@@ -32663,8 +32663,8 @@
       <c r="B31" s="24" t="inlineStr">
         <is>
           <t>A | 889呎 (3房)
-$2866万
-$32,241/呎
+$279630002866万
+$3,145,444,351,701/呎
 (暂停销售)</t>
         </is>
       </c>
@@ -32742,8 +32742,8 @@
       <c r="B32" s="24" t="inlineStr">
         <is>
           <t>A | 889呎 (3房)
-$2866万
-$32,237/呎
+$279600002866万
+$3,145,106,893,880/呎
 (暂停销售)</t>
         </is>
       </c>
@@ -32766,8 +32766,8 @@
       <c r="E32" s="24" t="inlineStr">
         <is>
           <t>D | 546呎 (2房)
-$1831万
-$33,529/呎
+$180360001831万
+$3,303,296,736,826/呎
 (暂停销售)</t>
         </is>
       </c>
@@ -32845,8 +32845,8 @@
       <c r="E33" s="24" t="inlineStr">
         <is>
           <t>D | 546呎 (2房)
-$1825万
-$33,423/呎
+$179790001825万
+$3,292,857,176,280/呎
 (暂停销售)</t>
         </is>
       </c>

--- a/files/九龙-启德-The Henley I.xlsx
+++ b/files/九龙-启德-The Henley I.xlsx
@@ -1610,18 +1610,18 @@
       </c>
       <c r="J16" s="3" t="inlineStr">
         <is>
-          <t>3.50%</t>
+          <t>7.12%</t>
         </is>
       </c>
       <c r="K16" s="5" t="n">
-        <v>19633800</v>
+        <v>18897500</v>
       </c>
       <c r="L16" s="5" t="n">
-        <v>35698</v>
+        <v>34359</v>
       </c>
       <c r="M16" s="3" t="inlineStr">
         <is>
-          <t>現金付款計劃 (減3.5%)</t>
+          <t>現金付款計劃 (減3.5%) + 代繳從價印花稅</t>
         </is>
       </c>
       <c r="N16" s="3" t="inlineStr">
@@ -2168,18 +2168,18 @@
       </c>
       <c r="J25" s="3" t="inlineStr">
         <is>
-          <t>3.50%</t>
+          <t>7.12%</t>
         </is>
       </c>
       <c r="K25" s="5" t="n">
-        <v>19413800</v>
+        <v>18685700</v>
       </c>
       <c r="L25" s="5" t="n">
-        <v>35298</v>
+        <v>33974</v>
       </c>
       <c r="M25" s="3" t="inlineStr">
         <is>
-          <t>現金付款計劃 (減3.5%)</t>
+          <t>現金付款計劃 (減3.5%) + 代繳從價印花稅</t>
         </is>
       </c>
       <c r="N25" s="3" t="inlineStr">
@@ -2726,18 +2726,18 @@
       </c>
       <c r="J34" s="3" t="inlineStr">
         <is>
-          <t>3.50%</t>
+          <t>7.12%</t>
         </is>
       </c>
       <c r="K34" s="5" t="n">
-        <v>19303800</v>
+        <v>18579900</v>
       </c>
       <c r="L34" s="5" t="n">
-        <v>35098</v>
+        <v>33782</v>
       </c>
       <c r="M34" s="3" t="inlineStr">
         <is>
-          <t>現金付款計劃 (減3.5%)</t>
+          <t>現金付款計劃 (減3.5%) + 代繳從價印花稅</t>
         </is>
       </c>
       <c r="N34" s="3" t="inlineStr">
@@ -3284,18 +3284,18 @@
       </c>
       <c r="J43" s="3" t="inlineStr">
         <is>
-          <t>3.50%</t>
+          <t>7.12%</t>
         </is>
       </c>
       <c r="K43" s="5" t="n">
-        <v>19247800</v>
+        <v>18526000</v>
       </c>
       <c r="L43" s="5" t="n">
-        <v>34996</v>
+        <v>33684</v>
       </c>
       <c r="M43" s="3" t="inlineStr">
         <is>
-          <t>現金付款計劃 (減3.5%)</t>
+          <t>現金付款計劃 (減3.5%) + 代繳從價印花稅</t>
         </is>
       </c>
       <c r="N43" s="3" t="inlineStr">
@@ -4400,18 +4400,18 @@
       </c>
       <c r="J61" s="3" t="inlineStr">
         <is>
-          <t>3.50%</t>
+          <t>7.12%</t>
         </is>
       </c>
       <c r="K61" s="5" t="n">
-        <v>19138800</v>
+        <v>18421000</v>
       </c>
       <c r="L61" s="5" t="n">
-        <v>34798</v>
+        <v>33493</v>
       </c>
       <c r="M61" s="3" t="inlineStr">
         <is>
-          <t>現金付款計劃 (減3.5%)</t>
+          <t>現金付款計劃 (減3.5%) + 代繳從價印花稅</t>
         </is>
       </c>
       <c r="N61" s="3" t="inlineStr">
@@ -4958,18 +4958,18 @@
       </c>
       <c r="J70" s="3" t="inlineStr">
         <is>
-          <t>3.50%</t>
+          <t>7.12%</t>
         </is>
       </c>
       <c r="K70" s="5" t="n">
-        <v>19082800</v>
+        <v>18367100</v>
       </c>
       <c r="L70" s="5" t="n">
-        <v>34696</v>
+        <v>33395</v>
       </c>
       <c r="M70" s="3" t="inlineStr">
         <is>
-          <t>現金付款計劃 (減3.5%)</t>
+          <t>現金付款計劃 (減3.5%) + 代繳從價印花稅</t>
         </is>
       </c>
       <c r="N70" s="3" t="inlineStr">
@@ -5516,18 +5516,18 @@
       </c>
       <c r="J79" s="3" t="inlineStr">
         <is>
-          <t>3.50%</t>
+          <t>7.12%</t>
         </is>
       </c>
       <c r="K79" s="5" t="n">
-        <v>19027800</v>
+        <v>18314200</v>
       </c>
       <c r="L79" s="5" t="n">
-        <v>34596</v>
+        <v>33299</v>
       </c>
       <c r="M79" s="3" t="inlineStr">
         <is>
-          <t>現金付款計劃 (減3.5%)</t>
+          <t>現金付款計劃 (減3.5%) + 代繳從價印花稅</t>
         </is>
       </c>
       <c r="N79" s="3" t="inlineStr">
@@ -6074,18 +6074,18 @@
       </c>
       <c r="J88" s="3" t="inlineStr">
         <is>
-          <t>3.50%</t>
+          <t>7.12%</t>
         </is>
       </c>
       <c r="K88" s="5" t="n">
-        <v>18972800</v>
+        <v>18261300</v>
       </c>
       <c r="L88" s="5" t="n">
-        <v>34496</v>
+        <v>33202</v>
       </c>
       <c r="M88" s="3" t="inlineStr">
         <is>
-          <t>現金付款計劃 (減3.5%)</t>
+          <t>現金付款計劃 (減3.5%) + 代繳從價印花稅</t>
         </is>
       </c>
       <c r="N88" s="3" t="inlineStr">
@@ -7190,18 +7190,18 @@
       </c>
       <c r="J106" s="3" t="inlineStr">
         <is>
-          <t>3.50%</t>
+          <t>7.12%</t>
         </is>
       </c>
       <c r="K106" s="5" t="n">
-        <v>18861800</v>
+        <v>18154400</v>
       </c>
       <c r="L106" s="5" t="n">
-        <v>34294</v>
+        <v>33008</v>
       </c>
       <c r="M106" s="3" t="inlineStr">
         <is>
-          <t>現金付款計劃 (減3.5%)</t>
+          <t>現金付款計劃 (減3.5%) + 代繳從價印花稅</t>
         </is>
       </c>
       <c r="N106" s="3" t="inlineStr">
@@ -8306,18 +8306,18 @@
       </c>
       <c r="J124" s="3" t="inlineStr">
         <is>
-          <t>3.50%</t>
+          <t>7.12%</t>
         </is>
       </c>
       <c r="K124" s="5" t="n">
-        <v>18696800</v>
+        <v>17995600</v>
       </c>
       <c r="L124" s="5" t="n">
-        <v>33994</v>
+        <v>32719</v>
       </c>
       <c r="M124" s="3" t="inlineStr">
         <is>
-          <t>現金付款計劃 (減3.5%)</t>
+          <t>現金付款計劃 (減3.5%) + 代繳從價印花稅</t>
         </is>
       </c>
       <c r="N124" s="3" t="inlineStr">
@@ -8864,18 +8864,18 @@
       </c>
       <c r="J133" s="3" t="inlineStr">
         <is>
-          <t>3.50%</t>
+          <t>7.12%</t>
         </is>
       </c>
       <c r="K133" s="5" t="n">
-        <v>18641800</v>
+        <v>17942700</v>
       </c>
       <c r="L133" s="5" t="n">
-        <v>33894</v>
+        <v>32623</v>
       </c>
       <c r="M133" s="3" t="inlineStr">
         <is>
-          <t>現金付款計劃 (減3.5%)</t>
+          <t>現金付款計劃 (減3.5%) + 代繳從價印花稅</t>
         </is>
       </c>
       <c r="N133" s="3" t="inlineStr">
@@ -9422,18 +9422,18 @@
       </c>
       <c r="J142" s="3" t="inlineStr">
         <is>
-          <t>3.5%</t>
+          <t>7.12%</t>
         </is>
       </c>
       <c r="K142" s="5" t="n">
-        <v>18585900</v>
+        <v>17888900</v>
       </c>
       <c r="L142" s="5" t="n">
-        <v>33793</v>
+        <v>32525</v>
       </c>
       <c r="M142" s="3" t="inlineStr">
         <is>
-          <t>現金付款計劃 - 90天成交</t>
+          <t>現金付款計劃 (減3.5%) + 代繳從價印花稅</t>
         </is>
       </c>
       <c r="N142" s="3" t="inlineStr">
@@ -9980,18 +9980,18 @@
       </c>
       <c r="J151" s="3" t="inlineStr">
         <is>
-          <t>3.50%</t>
+          <t>7.12%</t>
         </is>
       </c>
       <c r="K151" s="5" t="n">
-        <v>18530800</v>
+        <v>17835800</v>
       </c>
       <c r="L151" s="5" t="n">
-        <v>33692</v>
+        <v>32429</v>
       </c>
       <c r="M151" s="3" t="inlineStr">
         <is>
-          <t>現金付款計劃 (減3.5%)</t>
+          <t>現金付款計劃 (減3.5%) + 代繳從價印花稅</t>
         </is>
       </c>
       <c r="N151" s="3" t="inlineStr">
@@ -10538,18 +10538,18 @@
       </c>
       <c r="J160" s="3" t="inlineStr">
         <is>
-          <t>3.50%</t>
+          <t>7.12%</t>
         </is>
       </c>
       <c r="K160" s="5" t="n">
-        <v>18475800</v>
+        <v>17782900</v>
       </c>
       <c r="L160" s="5" t="n">
-        <v>33592</v>
+        <v>32333</v>
       </c>
       <c r="M160" s="3" t="inlineStr">
         <is>
-          <t>現金付款計劃 (減3.5%)</t>
+          <t>現金付款計劃 (減3.5%) + 代繳從價印花稅</t>
         </is>
       </c>
       <c r="N160" s="3" t="inlineStr">
@@ -11096,18 +11096,18 @@
       </c>
       <c r="J169" s="3" t="inlineStr">
         <is>
-          <t>3.50%</t>
+          <t>7.12%</t>
         </is>
       </c>
       <c r="K169" s="5" t="n">
-        <v>18419900</v>
+        <v>17729100</v>
       </c>
       <c r="L169" s="5" t="n">
-        <v>33491</v>
+        <v>32235</v>
       </c>
       <c r="M169" s="3" t="inlineStr">
         <is>
-          <t>現金付款計劃 (減3.5%)</t>
+          <t>現金付款計劃 (減3.5%) + 代繳從價印花稅</t>
         </is>
       </c>
       <c r="N169" s="3" t="inlineStr">
@@ -11654,18 +11654,18 @@
       </c>
       <c r="J178" s="3" t="inlineStr">
         <is>
-          <t>3.50%</t>
+          <t>7.12%</t>
         </is>
       </c>
       <c r="K178" s="5" t="n">
-        <v>18365800</v>
+        <v>17677000</v>
       </c>
       <c r="L178" s="5" t="n">
-        <v>33392</v>
+        <v>32140</v>
       </c>
       <c r="M178" s="3" t="inlineStr">
         <is>
-          <t>現金付款計劃 (減3.5%)</t>
+          <t>現金付款計劃 (減3.5%) + 代繳從價印花稅</t>
         </is>
       </c>
       <c r="N178" s="3" t="inlineStr">
@@ -12212,18 +12212,18 @@
       </c>
       <c r="J187" s="3" t="inlineStr">
         <is>
-          <t>3.50%</t>
+          <t>7.12%</t>
         </is>
       </c>
       <c r="K187" s="5" t="n">
-        <v>18365800</v>
+        <v>17677000</v>
       </c>
       <c r="L187" s="5" t="n">
-        <v>33392</v>
+        <v>32140</v>
       </c>
       <c r="M187" s="3" t="inlineStr">
         <is>
-          <t>現金付款計劃 (減3.5%)</t>
+          <t>現金付款計劃 (減3.5%) + 代繳從價印花稅</t>
         </is>
       </c>
       <c r="N187" s="3" t="inlineStr">
@@ -12770,18 +12770,18 @@
       </c>
       <c r="J196" s="3" t="inlineStr">
         <is>
-          <t>3.50%</t>
+          <t>7.12%</t>
         </is>
       </c>
       <c r="K196" s="5" t="n">
-        <v>18310800</v>
+        <v>17624100</v>
       </c>
       <c r="L196" s="5" t="n">
-        <v>33292</v>
+        <v>32044</v>
       </c>
       <c r="M196" s="3" t="inlineStr">
         <is>
-          <t>現金付款計劃 (減3.5%)</t>
+          <t>現金付款計劃 (減3.5%) + 代繳從價印花稅</t>
         </is>
       </c>
       <c r="N196" s="3" t="inlineStr">
@@ -13328,18 +13328,18 @@
       </c>
       <c r="J205" s="3" t="inlineStr">
         <is>
-          <t>3.50%</t>
+          <t>7.12%</t>
         </is>
       </c>
       <c r="K205" s="5" t="n">
-        <v>18254900</v>
+        <v>17570300</v>
       </c>
       <c r="L205" s="5" t="n">
-        <v>33191</v>
+        <v>31946</v>
       </c>
       <c r="M205" s="3" t="inlineStr">
         <is>
-          <t>現金付款計劃 (減3.5%)</t>
+          <t>現金付款計劃 (減3.5%) + 代繳從價印花稅</t>
         </is>
       </c>
       <c r="N205" s="3" t="inlineStr">
@@ -13886,18 +13886,18 @@
       </c>
       <c r="J214" s="3" t="inlineStr">
         <is>
-          <t>3.5%</t>
+          <t>7.12%</t>
         </is>
       </c>
       <c r="K214" s="5" t="n">
-        <v>18199900</v>
+        <v>17517400</v>
       </c>
       <c r="L214" s="5" t="n">
-        <v>33091</v>
+        <v>31850</v>
       </c>
       <c r="M214" s="3" t="inlineStr">
         <is>
-          <t>現金付款計劃 - 90天成交</t>
+          <t>現金付款計劃 (減3.5%) + 代繳從價印花稅</t>
         </is>
       </c>
       <c r="N214" s="3" t="inlineStr">
@@ -15560,18 +15560,18 @@
       </c>
       <c r="J241" s="3" t="inlineStr">
         <is>
-          <t>3.5%</t>
+          <t>7.12%</t>
         </is>
       </c>
       <c r="K241" s="5" t="n">
-        <v>17813900</v>
+        <v>17145800</v>
       </c>
       <c r="L241" s="5" t="n">
-        <v>32389</v>
+        <v>31174</v>
       </c>
       <c r="M241" s="3" t="inlineStr">
         <is>
-          <t>現金付款計劃 - 90天成交</t>
+          <t>現金付款計劃 (減3.5%) + 代繳從價印花稅</t>
         </is>
       </c>
       <c r="N241" s="3" t="inlineStr">
@@ -16118,18 +16118,18 @@
       </c>
       <c r="J250" s="3" t="inlineStr">
         <is>
-          <t>3.5%</t>
+          <t>7.12%</t>
         </is>
       </c>
       <c r="K250" s="5" t="n">
-        <v>17813900</v>
+        <v>17145800</v>
       </c>
       <c r="L250" s="5" t="n">
-        <v>32389</v>
+        <v>31174</v>
       </c>
       <c r="M250" s="3" t="inlineStr">
         <is>
-          <t>現金付款計劃 - 90天成交</t>
+          <t>現金付款計劃 (減3.5%) + 代繳從價印花稅</t>
         </is>
       </c>
       <c r="N250" s="3" t="inlineStr">

--- a/files/九龙-启德-The Henley I.xlsx
+++ b/files/九龙-启德-The Henley I.xlsx
@@ -1610,18 +1610,18 @@
       </c>
       <c r="J16" s="3" t="inlineStr">
         <is>
-          <t>7.12%</t>
+          <t>3.50%</t>
         </is>
       </c>
       <c r="K16" s="5" t="n">
-        <v>18897500</v>
+        <v>19633800</v>
       </c>
       <c r="L16" s="5" t="n">
-        <v>34359</v>
+        <v>35698</v>
       </c>
       <c r="M16" s="3" t="inlineStr">
         <is>
-          <t>現金付款計劃 (減3.5%) + 代繳從價印花稅</t>
+          <t>現金付款計劃 (減3.5%)</t>
         </is>
       </c>
       <c r="N16" s="3" t="inlineStr">
@@ -2168,18 +2168,18 @@
       </c>
       <c r="J25" s="3" t="inlineStr">
         <is>
-          <t>7.12%</t>
+          <t>3.50%</t>
         </is>
       </c>
       <c r="K25" s="5" t="n">
-        <v>18685700</v>
+        <v>19413800</v>
       </c>
       <c r="L25" s="5" t="n">
-        <v>33974</v>
+        <v>35298</v>
       </c>
       <c r="M25" s="3" t="inlineStr">
         <is>
-          <t>現金付款計劃 (減3.5%) + 代繳從價印花稅</t>
+          <t>現金付款計劃 (減3.5%)</t>
         </is>
       </c>
       <c r="N25" s="3" t="inlineStr">
@@ -2726,18 +2726,18 @@
       </c>
       <c r="J34" s="3" t="inlineStr">
         <is>
-          <t>7.12%</t>
+          <t>3.50%</t>
         </is>
       </c>
       <c r="K34" s="5" t="n">
-        <v>18579900</v>
+        <v>19303800</v>
       </c>
       <c r="L34" s="5" t="n">
-        <v>33782</v>
+        <v>35098</v>
       </c>
       <c r="M34" s="3" t="inlineStr">
         <is>
-          <t>現金付款計劃 (減3.5%) + 代繳從價印花稅</t>
+          <t>現金付款計劃 (減3.5%)</t>
         </is>
       </c>
       <c r="N34" s="3" t="inlineStr">
@@ -3284,18 +3284,18 @@
       </c>
       <c r="J43" s="3" t="inlineStr">
         <is>
-          <t>7.12%</t>
+          <t>3.50%</t>
         </is>
       </c>
       <c r="K43" s="5" t="n">
-        <v>18526000</v>
+        <v>19247800</v>
       </c>
       <c r="L43" s="5" t="n">
-        <v>33684</v>
+        <v>34996</v>
       </c>
       <c r="M43" s="3" t="inlineStr">
         <is>
-          <t>現金付款計劃 (減3.5%) + 代繳從價印花稅</t>
+          <t>現金付款計劃 (減3.5%)</t>
         </is>
       </c>
       <c r="N43" s="3" t="inlineStr">
@@ -4400,18 +4400,18 @@
       </c>
       <c r="J61" s="3" t="inlineStr">
         <is>
-          <t>7.12%</t>
+          <t>3.50%</t>
         </is>
       </c>
       <c r="K61" s="5" t="n">
-        <v>18421000</v>
+        <v>19138800</v>
       </c>
       <c r="L61" s="5" t="n">
-        <v>33493</v>
+        <v>34798</v>
       </c>
       <c r="M61" s="3" t="inlineStr">
         <is>
-          <t>現金付款計劃 (減3.5%) + 代繳從價印花稅</t>
+          <t>現金付款計劃 (減3.5%)</t>
         </is>
       </c>
       <c r="N61" s="3" t="inlineStr">
@@ -4958,18 +4958,18 @@
       </c>
       <c r="J70" s="3" t="inlineStr">
         <is>
-          <t>7.12%</t>
+          <t>3.50%</t>
         </is>
       </c>
       <c r="K70" s="5" t="n">
-        <v>18367100</v>
+        <v>19082800</v>
       </c>
       <c r="L70" s="5" t="n">
-        <v>33395</v>
+        <v>34696</v>
       </c>
       <c r="M70" s="3" t="inlineStr">
         <is>
-          <t>現金付款計劃 (減3.5%) + 代繳從價印花稅</t>
+          <t>現金付款計劃 (減3.5%)</t>
         </is>
       </c>
       <c r="N70" s="3" t="inlineStr">
@@ -5516,18 +5516,18 @@
       </c>
       <c r="J79" s="3" t="inlineStr">
         <is>
-          <t>7.12%</t>
+          <t>3.50%</t>
         </is>
       </c>
       <c r="K79" s="5" t="n">
-        <v>18314200</v>
+        <v>19027800</v>
       </c>
       <c r="L79" s="5" t="n">
-        <v>33299</v>
+        <v>34596</v>
       </c>
       <c r="M79" s="3" t="inlineStr">
         <is>
-          <t>現金付款計劃 (減3.5%) + 代繳從價印花稅</t>
+          <t>現金付款計劃 (減3.5%)</t>
         </is>
       </c>
       <c r="N79" s="3" t="inlineStr">
@@ -6074,18 +6074,18 @@
       </c>
       <c r="J88" s="3" t="inlineStr">
         <is>
-          <t>7.12%</t>
+          <t>3.50%</t>
         </is>
       </c>
       <c r="K88" s="5" t="n">
-        <v>18261300</v>
+        <v>18972800</v>
       </c>
       <c r="L88" s="5" t="n">
-        <v>33202</v>
+        <v>34496</v>
       </c>
       <c r="M88" s="3" t="inlineStr">
         <is>
-          <t>現金付款計劃 (減3.5%) + 代繳從價印花稅</t>
+          <t>現金付款計劃 (減3.5%)</t>
         </is>
       </c>
       <c r="N88" s="3" t="inlineStr">
@@ -7190,18 +7190,18 @@
       </c>
       <c r="J106" s="3" t="inlineStr">
         <is>
-          <t>7.12%</t>
+          <t>3.50%</t>
         </is>
       </c>
       <c r="K106" s="5" t="n">
-        <v>18154400</v>
+        <v>18861800</v>
       </c>
       <c r="L106" s="5" t="n">
-        <v>33008</v>
+        <v>34294</v>
       </c>
       <c r="M106" s="3" t="inlineStr">
         <is>
-          <t>現金付款計劃 (減3.5%) + 代繳從價印花稅</t>
+          <t>現金付款計劃 (減3.5%)</t>
         </is>
       </c>
       <c r="N106" s="3" t="inlineStr">
@@ -8306,18 +8306,18 @@
       </c>
       <c r="J124" s="3" t="inlineStr">
         <is>
-          <t>7.12%</t>
+          <t>3.50%</t>
         </is>
       </c>
       <c r="K124" s="5" t="n">
-        <v>17995600</v>
+        <v>18696800</v>
       </c>
       <c r="L124" s="5" t="n">
-        <v>32719</v>
+        <v>33994</v>
       </c>
       <c r="M124" s="3" t="inlineStr">
         <is>
-          <t>現金付款計劃 (減3.5%) + 代繳從價印花稅</t>
+          <t>現金付款計劃 (減3.5%)</t>
         </is>
       </c>
       <c r="N124" s="3" t="inlineStr">
@@ -8864,18 +8864,18 @@
       </c>
       <c r="J133" s="3" t="inlineStr">
         <is>
-          <t>7.12%</t>
+          <t>3.50%</t>
         </is>
       </c>
       <c r="K133" s="5" t="n">
-        <v>17942700</v>
+        <v>18641800</v>
       </c>
       <c r="L133" s="5" t="n">
-        <v>32623</v>
+        <v>33894</v>
       </c>
       <c r="M133" s="3" t="inlineStr">
         <is>
-          <t>現金付款計劃 (減3.5%) + 代繳從價印花稅</t>
+          <t>現金付款計劃 (減3.5%)</t>
         </is>
       </c>
       <c r="N133" s="3" t="inlineStr">
@@ -9422,18 +9422,18 @@
       </c>
       <c r="J142" s="3" t="inlineStr">
         <is>
-          <t>7.12%</t>
+          <t>3.5%</t>
         </is>
       </c>
       <c r="K142" s="5" t="n">
-        <v>17888900</v>
+        <v>18585900</v>
       </c>
       <c r="L142" s="5" t="n">
-        <v>32525</v>
+        <v>33793</v>
       </c>
       <c r="M142" s="3" t="inlineStr">
         <is>
-          <t>現金付款計劃 (減3.5%) + 代繳從價印花稅</t>
+          <t>現金付款計劃 - 90天成交</t>
         </is>
       </c>
       <c r="N142" s="3" t="inlineStr">
@@ -9980,18 +9980,18 @@
       </c>
       <c r="J151" s="3" t="inlineStr">
         <is>
-          <t>7.12%</t>
+          <t>3.50%</t>
         </is>
       </c>
       <c r="K151" s="5" t="n">
-        <v>17835800</v>
+        <v>18530800</v>
       </c>
       <c r="L151" s="5" t="n">
-        <v>32429</v>
+        <v>33692</v>
       </c>
       <c r="M151" s="3" t="inlineStr">
         <is>
-          <t>現金付款計劃 (減3.5%) + 代繳從價印花稅</t>
+          <t>現金付款計劃 (減3.5%)</t>
         </is>
       </c>
       <c r="N151" s="3" t="inlineStr">
@@ -10538,18 +10538,18 @@
       </c>
       <c r="J160" s="3" t="inlineStr">
         <is>
-          <t>7.12%</t>
+          <t>3.50%</t>
         </is>
       </c>
       <c r="K160" s="5" t="n">
-        <v>17782900</v>
+        <v>18475800</v>
       </c>
       <c r="L160" s="5" t="n">
-        <v>32333</v>
+        <v>33592</v>
       </c>
       <c r="M160" s="3" t="inlineStr">
         <is>
-          <t>現金付款計劃 (減3.5%) + 代繳從價印花稅</t>
+          <t>現金付款計劃 (減3.5%)</t>
         </is>
       </c>
       <c r="N160" s="3" t="inlineStr">
@@ -11096,18 +11096,18 @@
       </c>
       <c r="J169" s="3" t="inlineStr">
         <is>
-          <t>7.12%</t>
+          <t>3.50%</t>
         </is>
       </c>
       <c r="K169" s="5" t="n">
-        <v>17729100</v>
+        <v>18419900</v>
       </c>
       <c r="L169" s="5" t="n">
-        <v>32235</v>
+        <v>33491</v>
       </c>
       <c r="M169" s="3" t="inlineStr">
         <is>
-          <t>現金付款計劃 (減3.5%) + 代繳從價印花稅</t>
+          <t>現金付款計劃 (減3.5%)</t>
         </is>
       </c>
       <c r="N169" s="3" t="inlineStr">
@@ -11654,18 +11654,18 @@
       </c>
       <c r="J178" s="3" t="inlineStr">
         <is>
-          <t>7.12%</t>
+          <t>3.50%</t>
         </is>
       </c>
       <c r="K178" s="5" t="n">
-        <v>17677000</v>
+        <v>18365800</v>
       </c>
       <c r="L178" s="5" t="n">
-        <v>32140</v>
+        <v>33392</v>
       </c>
       <c r="M178" s="3" t="inlineStr">
         <is>
-          <t>現金付款計劃 (減3.5%) + 代繳從價印花稅</t>
+          <t>現金付款計劃 (減3.5%)</t>
         </is>
       </c>
       <c r="N178" s="3" t="inlineStr">
@@ -12212,18 +12212,18 @@
       </c>
       <c r="J187" s="3" t="inlineStr">
         <is>
-          <t>7.12%</t>
+          <t>3.50%</t>
         </is>
       </c>
       <c r="K187" s="5" t="n">
-        <v>17677000</v>
+        <v>18365800</v>
       </c>
       <c r="L187" s="5" t="n">
-        <v>32140</v>
+        <v>33392</v>
       </c>
       <c r="M187" s="3" t="inlineStr">
         <is>
-          <t>現金付款計劃 (減3.5%) + 代繳從價印花稅</t>
+          <t>現金付款計劃 (減3.5%)</t>
         </is>
       </c>
       <c r="N187" s="3" t="inlineStr">
@@ -12770,18 +12770,18 @@
       </c>
       <c r="J196" s="3" t="inlineStr">
         <is>
-          <t>7.12%</t>
+          <t>3.50%</t>
         </is>
       </c>
       <c r="K196" s="5" t="n">
-        <v>17624100</v>
+        <v>18310800</v>
       </c>
       <c r="L196" s="5" t="n">
-        <v>32044</v>
+        <v>33292</v>
       </c>
       <c r="M196" s="3" t="inlineStr">
         <is>
-          <t>現金付款計劃 (減3.5%) + 代繳從價印花稅</t>
+          <t>現金付款計劃 (減3.5%)</t>
         </is>
       </c>
       <c r="N196" s="3" t="inlineStr">
@@ -13328,18 +13328,18 @@
       </c>
       <c r="J205" s="3" t="inlineStr">
         <is>
-          <t>7.12%</t>
+          <t>3.50%</t>
         </is>
       </c>
       <c r="K205" s="5" t="n">
-        <v>17570300</v>
+        <v>18254900</v>
       </c>
       <c r="L205" s="5" t="n">
-        <v>31946</v>
+        <v>33191</v>
       </c>
       <c r="M205" s="3" t="inlineStr">
         <is>
-          <t>現金付款計劃 (減3.5%) + 代繳從價印花稅</t>
+          <t>現金付款計劃 (減3.5%)</t>
         </is>
       </c>
       <c r="N205" s="3" t="inlineStr">
@@ -13886,18 +13886,18 @@
       </c>
       <c r="J214" s="3" t="inlineStr">
         <is>
-          <t>7.12%</t>
+          <t>3.5%</t>
         </is>
       </c>
       <c r="K214" s="5" t="n">
-        <v>17517400</v>
+        <v>18199900</v>
       </c>
       <c r="L214" s="5" t="n">
-        <v>31850</v>
+        <v>33091</v>
       </c>
       <c r="M214" s="3" t="inlineStr">
         <is>
-          <t>現金付款計劃 (減3.5%) + 代繳從價印花稅</t>
+          <t>現金付款計劃 - 90天成交</t>
         </is>
       </c>
       <c r="N214" s="3" t="inlineStr">
@@ -15560,18 +15560,18 @@
       </c>
       <c r="J241" s="3" t="inlineStr">
         <is>
-          <t>7.12%</t>
+          <t>3.5%</t>
         </is>
       </c>
       <c r="K241" s="5" t="n">
-        <v>17145800</v>
+        <v>17813900</v>
       </c>
       <c r="L241" s="5" t="n">
-        <v>31174</v>
+        <v>32389</v>
       </c>
       <c r="M241" s="3" t="inlineStr">
         <is>
-          <t>現金付款計劃 (減3.5%) + 代繳從價印花稅</t>
+          <t>現金付款計劃 - 90天成交</t>
         </is>
       </c>
       <c r="N241" s="3" t="inlineStr">
@@ -16118,18 +16118,18 @@
       </c>
       <c r="J250" s="3" t="inlineStr">
         <is>
-          <t>7.12%</t>
+          <t>3.5%</t>
         </is>
       </c>
       <c r="K250" s="5" t="n">
-        <v>17145800</v>
+        <v>17813900</v>
       </c>
       <c r="L250" s="5" t="n">
-        <v>31174</v>
+        <v>32389</v>
       </c>
       <c r="M250" s="3" t="inlineStr">
         <is>
-          <t>現金付款計劃 (減3.5%) + 代繳從價印花稅</t>
+          <t>現金付款計劃 - 90天成交</t>
         </is>
       </c>
       <c r="N250" s="3" t="inlineStr">

--- a/files/九龙-启德-The Henley I.xlsx
+++ b/files/九龙-启德-The Henley I.xlsx
@@ -30632,7 +30632,7 @@
           <t>A | 1350呎 (3房)
 $8355万
 $61,888/呎
-(21年-06月-01日)</t>
+(21年-06月)</t>
         </is>
       </c>
       <c r="C5" s="21" t="inlineStr"/>
@@ -30651,7 +30651,7 @@
           <t>F | 505呎 (2房)
 $1370万
 $27,129/呎
-(25年-12月-08日)</t>
+(25年-12月)</t>
         </is>
       </c>
       <c r="H5" s="20" t="inlineStr">
@@ -30659,7 +30659,7 @@
           <t>G | 380呎 (1房)
 $827万
 $21,753/呎
-(25年-07月-14日)</t>
+(25年-07月)</t>
         </is>
       </c>
       <c r="I5" s="20" t="inlineStr">
@@ -30667,7 +30667,7 @@
           <t>H | 379呎 (1房)
 $820万
 $21,630/呎
-(25年-06月-29日)</t>
+(25年-06月)</t>
         </is>
       </c>
       <c r="J5" s="22" t="inlineStr">
@@ -30690,7 +30690,7 @@
           <t>A | 890呎 (3房)
 $2996万
 $33,662/呎
-(26年-01月-11日)</t>
+(26年-01月)</t>
         </is>
       </c>
       <c r="C6" s="22" t="inlineStr">
@@ -30714,7 +30714,7 @@
           <t>D | 546呎 (2房)
 $1950万
 $35,721/呎
-(21年-06月-02日)</t>
+(21年-06月)</t>
         </is>
       </c>
       <c r="F6" s="20" t="inlineStr">
@@ -30722,7 +30722,7 @@
           <t>E | 695呎 (3房)
 $1557万
 $22,404/呎
-(25年-07月-03日)</t>
+(25年-07月)</t>
         </is>
       </c>
       <c r="G6" s="20" t="inlineStr">
@@ -30730,7 +30730,7 @@
           <t>F | 505呎 (2房)
 $1437万
 $28,453/呎
-(21年-06月-02日)</t>
+(21年-06月)</t>
         </is>
       </c>
       <c r="H6" s="20" t="inlineStr">
@@ -30738,7 +30738,7 @@
           <t>G | 380呎 (1房)
 $1055万
 $27,765/呎
-(21年-06月-01日)</t>
+(21年-06月)</t>
         </is>
       </c>
       <c r="I6" s="20" t="inlineStr">
@@ -30746,7 +30746,7 @@
           <t>H | 379呎 (1房)
 $1058万
 $27,903/呎
-(21年-07月-13日)</t>
+(21年-07月)</t>
         </is>
       </c>
       <c r="J6" s="22" t="inlineStr">
@@ -30769,7 +30769,7 @@
           <t>A | 890呎 (3房)
 $2960万
 $33,263/呎
-(26年-02月-08日)</t>
+(26年-02月)</t>
         </is>
       </c>
       <c r="C7" s="22" t="inlineStr">
@@ -30793,7 +30793,7 @@
           <t>D | 546呎 (2房)
 $1880万
 $34,428/呎
-(21年-06月-01日)</t>
+(21年-06月)</t>
         </is>
       </c>
       <c r="F7" s="20" t="inlineStr">
@@ -30801,7 +30801,7 @@
           <t>E | 695呎 (3房)
 $1540万
 $22,152/呎
-(25年-07月-03日)</t>
+(25年-07月)</t>
         </is>
       </c>
       <c r="G7" s="20" t="inlineStr">
@@ -30809,7 +30809,7 @@
           <t>F | 505呎 (2房)
 $1392万
 $27,556/呎
-(21年-05月-08日)</t>
+(21年-05月)</t>
         </is>
       </c>
       <c r="H7" s="20" t="inlineStr">
@@ -30817,7 +30817,7 @@
           <t>G | 380呎 (1房)
 $1043万
 $27,447/呎
-(22年-09月-28日)</t>
+(22年-09月)</t>
         </is>
       </c>
       <c r="I7" s="20" t="inlineStr">
@@ -30825,7 +30825,7 @@
           <t>H | 379呎 (1房)
 $1046万
 $27,592/呎
-(21年-07月-28日)</t>
+(21年-07月)</t>
         </is>
       </c>
       <c r="J7" s="22" t="inlineStr">
@@ -30848,7 +30848,7 @@
           <t>A | 890呎 (3房)
 $2943万
 $33,063/呎
-(26年-02月-10日)</t>
+(26年-02月)</t>
         </is>
       </c>
       <c r="C8" s="23" t="inlineStr">
@@ -30872,7 +30872,7 @@
           <t>D | 546呎 (2房)
 $1887万
 $34,551/呎
-(21年-06月-07日)</t>
+(21年-06月)</t>
         </is>
       </c>
       <c r="F8" s="20" t="inlineStr">
@@ -30880,7 +30880,7 @@
           <t>E | 695呎 (3房)
 $1528万
 $21,979/呎
-(25年-06月-26日)</t>
+(25年-06月)</t>
         </is>
       </c>
       <c r="G8" s="20" t="inlineStr">
@@ -30888,7 +30888,7 @@
           <t>F | 505呎 (2房)
 $1425万
 $28,226/呎
-(21年-05月-23日)</t>
+(21年-05月)</t>
         </is>
       </c>
       <c r="H8" s="20" t="inlineStr">
@@ -30896,7 +30896,7 @@
           <t>G | 380呎 (1房)
 $812万
 $21,364/呎
-(25年-06月-25日)</t>
+(25年-06月)</t>
         </is>
       </c>
       <c r="I8" s="20" t="inlineStr">
@@ -30904,7 +30904,7 @@
           <t>H | 379呎 (1房)
 $806万
 $21,256/呎
-(25年-07月-02日)</t>
+(25年-07月)</t>
         </is>
       </c>
       <c r="J8" s="22" t="inlineStr">
@@ -30927,7 +30927,7 @@
           <t>A | 890呎 (3房)
 $2934万
 $32,963/呎
-(26年-02月-08日)</t>
+(26年-02月)</t>
         </is>
       </c>
       <c r="C9" s="22" t="inlineStr">
@@ -30943,7 +30943,7 @@
           <t>C | 550呎 (2房)
 $1965万
 $35,733/呎
-(21年-06月-22日)</t>
+(21年-06月)</t>
         </is>
       </c>
       <c r="E9" s="20" t="inlineStr">
@@ -30951,7 +30951,7 @@
           <t>D | 546呎 (2房)
 $1881万
 $34,451/呎
-(21年-06月-15日)</t>
+(21年-06月)</t>
         </is>
       </c>
       <c r="F9" s="20" t="inlineStr">
@@ -30959,7 +30959,7 @@
           <t>E | 695呎 (3房)
 $1523万
 $21,918/呎
-(25年-06月-22日)</t>
+(25年-06月)</t>
         </is>
       </c>
       <c r="G9" s="20" t="inlineStr">
@@ -30967,7 +30967,7 @@
           <t>F | 505呎 (2房)
 $1436万
 $28,433/呎
-(21年-05月-23日)</t>
+(21年-05月)</t>
         </is>
       </c>
       <c r="H9" s="20" t="inlineStr">
@@ -30975,7 +30975,7 @@
           <t>G | 380呎 (1房)
 $1034万
 $27,210/呎
-(23年-05月-30日)</t>
+(23年-05月)</t>
         </is>
       </c>
       <c r="I9" s="20" t="inlineStr">
@@ -30983,7 +30983,7 @@
           <t>H | 379呎 (1房)
 $803万
 $21,196/呎
-(25年-06月-24日)</t>
+(25年-06月)</t>
         </is>
       </c>
       <c r="J9" s="20" t="inlineStr">
@@ -30991,7 +30991,7 @@
           <t>J | 418呎 (1房)
 $1013万
 $24,241/呎
-(26年-06月-23日)</t>
+(26年-06月)</t>
         </is>
       </c>
     </row>
@@ -31006,7 +31006,7 @@
           <t>A | 889呎 (3房)
 $3131万
 $35,222/呎
-(21年-06月-07日)</t>
+(21年-06月)</t>
         </is>
       </c>
       <c r="C10" s="20" t="inlineStr">
@@ -31014,7 +31014,7 @@
           <t>B | 550呎 (2房)
 $1919万
 $34,896/呎
-(26年-07月-06日)</t>
+(26年-07月)</t>
         </is>
       </c>
       <c r="D10" s="22" t="inlineStr">
@@ -31030,7 +31030,7 @@
           <t>D | 546呎 (2房)
 $1876万
 $34,351/呎
-(21年-06月-06日)</t>
+(21年-06月)</t>
         </is>
       </c>
       <c r="F10" s="20" t="inlineStr">
@@ -31038,7 +31038,7 @@
           <t>E | 695呎 (3房)
 $1519万
 $21,855/呎
-(25年-06月-24日)</t>
+(25年-06月)</t>
         </is>
       </c>
       <c r="G10" s="20" t="inlineStr">
@@ -31046,7 +31046,7 @@
           <t>F | 505呎 (2房)
 $1388万
 $27,492/呎
-(21年-05月-27日)</t>
+(21年-05月)</t>
         </is>
       </c>
       <c r="H10" s="20" t="inlineStr">
@@ -31054,7 +31054,7 @@
           <t>G | 380呎 (1房)
 $807万
 $21,239/呎
-(25年-06月-22日)</t>
+(25年-06月)</t>
         </is>
       </c>
       <c r="I10" s="20" t="inlineStr">
@@ -31062,7 +31062,7 @@
           <t>H | 379呎 (1房)
 $953万
 $25,149/呎
-(25年-05月-01日)</t>
+(25年-05月)</t>
         </is>
       </c>
       <c r="J10" s="20" t="inlineStr">
@@ -31070,7 +31070,7 @@
           <t>J | 418呎 (1房)
 $1010万
 $24,172/呎
-(26年-06月-23日)</t>
+(26年-06月)</t>
         </is>
       </c>
     </row>
@@ -31085,7 +31085,7 @@
           <t>A | 889呎 (3房)
 $3122万
 $35,122/呎
-(21年-07月-11日)</t>
+(21年-07月)</t>
         </is>
       </c>
       <c r="C11" s="22" t="inlineStr">
@@ -31109,7 +31109,7 @@
           <t>D | 546呎 (2房)
 $1870万
 $34,250/呎
-(21年-06月-15日)</t>
+(21年-06月)</t>
         </is>
       </c>
       <c r="F11" s="20" t="inlineStr">
@@ -31117,7 +31117,7 @@
           <t>E | 695呎 (3房)
 $1515万
 $21,792/呎
-(25年-06月-26日)</t>
+(25年-06月)</t>
         </is>
       </c>
       <c r="G11" s="20" t="inlineStr">
@@ -31125,7 +31125,7 @@
           <t>F | 505呎 (2房)
 $1370万
 $27,129/呎
-(21年-05月-24日)</t>
+(21年-05月)</t>
         </is>
       </c>
       <c r="H11" s="20" t="inlineStr">
@@ -31133,7 +31133,7 @@
           <t>G | 380呎 (1房)
 $1071万
 $28,189/呎
-(23年-04月-19日)</t>
+(23年-04月)</t>
         </is>
       </c>
       <c r="I11" s="20" t="inlineStr">
@@ -31141,7 +31141,7 @@
           <t>H | 379呎 (1房)
 $1020万
 $26,921/呎
-(21年-07月-20日)</t>
+(21年-07月)</t>
         </is>
       </c>
       <c r="J11" s="22" t="inlineStr">
@@ -31164,7 +31164,7 @@
           <t>A | 890呎 (3房)
 $2907万
 $32,663/呎
-(25年-09月-11日)</t>
+(25年-09月)</t>
         </is>
       </c>
       <c r="C12" s="23" t="inlineStr">
@@ -31180,7 +31180,7 @@
           <t>C | 550呎 (2房)
 $1860万
 $33,823/呎
-(21年-07月-05日)</t>
+(21年-07月)</t>
         </is>
       </c>
       <c r="E12" s="20" t="inlineStr">
@@ -31188,7 +31188,7 @@
           <t>D | 546呎 (2房)
 $1865万
 $34,151/呎
-(26年-04月-28日)</t>
+(26年-04月)</t>
         </is>
       </c>
       <c r="F12" s="20" t="inlineStr">
@@ -31196,7 +31196,7 @@
           <t>E | 695呎 (3房)
 $1466万
 $21,091/呎
-(25年-06月-12日)</t>
+(25年-06月)</t>
         </is>
       </c>
       <c r="G12" s="20" t="inlineStr">
@@ -31204,7 +31204,7 @@
           <t>F | 505呎 (2房)
 $1380万
 $27,336/呎
-(21年-05月-30日)</t>
+(21年-05月)</t>
         </is>
       </c>
       <c r="H12" s="20" t="inlineStr">
@@ -31212,7 +31212,7 @@
           <t>G | 380呎 (1房)
 $1025万
 $26,970/呎
-(21年-08月-04日)</t>
+(21年-08月)</t>
         </is>
       </c>
       <c r="I12" s="20" t="inlineStr">
@@ -31220,7 +31220,7 @@
           <t>H | 379呎 (1房)
 $1028万
 $27,123/呎
-(21年-07月-08日)</t>
+(21年-07月)</t>
         </is>
       </c>
       <c r="J12" s="20" t="inlineStr">
@@ -31228,7 +31228,7 @@
           <t>J | 418呎 (1房)
 $1004万
 $24,030/呎
-(26年-07月-01日)</t>
+(26年-07月)</t>
         </is>
       </c>
     </row>
@@ -31243,7 +31243,7 @@
           <t>A | 890呎 (3房)
 $2898万
 $32,564/呎
-(25年-12月-17日)</t>
+(25年-12月)</t>
         </is>
       </c>
       <c r="C13" s="23" t="inlineStr">
@@ -31267,7 +31267,7 @@
           <t>D | 546呎 (2房)
 $1859万
 $34,052/呎
-(21年-07月-29日)</t>
+(21年-07月)</t>
         </is>
       </c>
       <c r="F13" s="20" t="inlineStr">
@@ -31275,7 +31275,7 @@
           <t>E | 695呎 (3房)
 $1462万
 $21,030/呎
-(25年-06月-23日)</t>
+(25年-06月)</t>
         </is>
       </c>
       <c r="G13" s="20" t="inlineStr">
@@ -31283,7 +31283,7 @@
           <t>F | 505呎 (2房)
 $1355万
 $26,839/呎
-(21年-05月-30日)</t>
+(21年-05月)</t>
         </is>
       </c>
       <c r="H13" s="20" t="inlineStr">
@@ -31291,7 +31291,7 @@
           <t>G | 380呎 (1房)
 $1038万
 $27,327/呎
-(21年-05月-08日)</t>
+(21年-05月)</t>
         </is>
       </c>
       <c r="I13" s="20" t="inlineStr">
@@ -31299,7 +31299,7 @@
           <t>H | 379呎 (1房)
 $989万
 $26,101/呎
-(21年-07月-05日)</t>
+(21年-07月)</t>
         </is>
       </c>
       <c r="J13" s="20" t="inlineStr">
@@ -31307,7 +31307,7 @@
           <t>J | 418呎 (1房)
 $901万
 $21,559/呎
-(25年-12月-09日)</t>
+(25年-12月)</t>
         </is>
       </c>
     </row>
@@ -31322,7 +31322,7 @@
           <t>A | 890呎 (3房)
 $2916万
 $32,763/呎
-(24年-07月-23日)</t>
+(24年-07月)</t>
         </is>
       </c>
       <c r="C14" s="22" t="inlineStr">
@@ -31338,7 +31338,7 @@
           <t>C | 550呎 (2房)
 $1850万
 $33,628/呎
-(21年-06月-06日)</t>
+(21年-06月)</t>
         </is>
       </c>
       <c r="E14" s="20" t="inlineStr">
@@ -31346,7 +31346,7 @@
           <t>D | 546呎 (2房)
 $1854万
 $33,951/呎
-(26年-02月-26日)</t>
+(26年-02月)</t>
         </is>
       </c>
       <c r="F14" s="20" t="inlineStr">
@@ -31354,7 +31354,7 @@
           <t>E | 695呎 (3房)
 $1457万
 $20,968/呎
-(25年-06月-15日)</t>
+(25年-06月)</t>
         </is>
       </c>
       <c r="G14" s="20" t="inlineStr">
@@ -31362,7 +31362,7 @@
           <t>F | 505呎 (2房)
 $1366万
 $27,043/呎
-(21年-05月-30日)</t>
+(21年-05月)</t>
         </is>
       </c>
       <c r="H14" s="20" t="inlineStr">
@@ -31370,7 +31370,7 @@
           <t>G | 380呎 (1房)
 $994万
 $26,145/呎
-(21年-06月-09日)</t>
+(21年-06月)</t>
         </is>
       </c>
       <c r="I14" s="20" t="inlineStr">
@@ -31378,7 +31378,7 @@
           <t>H | 379呎 (1房)
 $997万
 $26,300/呎
-(21年-05月-26日)</t>
+(21年-05月)</t>
         </is>
       </c>
       <c r="J14" s="20" t="inlineStr">
@@ -31386,7 +31386,7 @@
           <t>J | 418呎 (1房)
 $899万
 $21,496/呎
-(25年-12月-09日)</t>
+(25年-12月)</t>
         </is>
       </c>
     </row>
@@ -31401,7 +31401,7 @@
           <t>A | 890呎 (3房)
 $2916万
 $32,763/呎
-(26年-04月-08日)</t>
+(26年-04月)</t>
         </is>
       </c>
       <c r="C15" s="20" t="inlineStr">
@@ -31409,7 +31409,7 @@
           <t>B | 550呎 (2房)
 $1892万
 $34,394/呎
-(26年-07月-06日)</t>
+(26年-07月)</t>
         </is>
       </c>
       <c r="D15" s="22" t="inlineStr">
@@ -31425,7 +31425,7 @@
           <t>D | 546呎 (2房)
 $1848万
 $33,852/呎
-(25年-10月-08日)</t>
+(25年-10月)</t>
         </is>
       </c>
       <c r="F15" s="20" t="inlineStr">
@@ -31433,7 +31433,7 @@
           <t>E | 695呎 (3房)
 $1453万
 $20,908/呎
-(25年-06月-16日)</t>
+(25年-06月)</t>
         </is>
       </c>
       <c r="G15" s="20" t="inlineStr">
@@ -31441,7 +31441,7 @@
           <t>F | 505呎 (2房)
 $1348万
 $26,685/呎
-(21年-05月-26日)</t>
+(21年-05月)</t>
         </is>
       </c>
       <c r="H15" s="20" t="inlineStr">
@@ -31449,7 +31449,7 @@
           <t>G | 380呎 (1房)
 $1001万
 $26,342/呎
-(21年-06月-09日)</t>
+(21年-06月)</t>
         </is>
       </c>
       <c r="I15" s="20" t="inlineStr">
@@ -31457,7 +31457,7 @@
           <t>H | 379呎 (1房)
 $984万
 $25,951/呎
-(21年-06月-17日)</t>
+(21年-06月)</t>
         </is>
       </c>
       <c r="J15" s="20" t="inlineStr">
@@ -31465,7 +31465,7 @@
           <t>J | 418呎 (1房)
 $896万
 $21,433/呎
-(25年-12月-07日)</t>
+(25年-12月)</t>
         </is>
       </c>
     </row>
@@ -31480,7 +31480,7 @@
           <t>A | 889呎 (3房)
 $3036万
 $34,145/呎
-(21年-05月-27日)</t>
+(21年-05月)</t>
         </is>
       </c>
       <c r="C16" s="22" t="inlineStr">
@@ -31504,7 +31504,7 @@
           <t>D | 546呎 (2房)
 $1843万
 $33,751/呎
-(26年-05月-31日)</t>
+(26年-05月)</t>
         </is>
       </c>
       <c r="F16" s="20" t="inlineStr">
@@ -31512,7 +31512,7 @@
           <t>E | 695呎 (3房)
 $1449万
 $20,848/呎
-(25年-06月-18日)</t>
+(25年-06月)</t>
         </is>
       </c>
       <c r="G16" s="20" t="inlineStr">
@@ -31520,7 +31520,7 @@
           <t>F | 505呎 (2房)
 $1372万
 $27,168/呎
-(21年-05月-08日)</t>
+(21年-05月)</t>
         </is>
       </c>
       <c r="H16" s="20" t="inlineStr">
@@ -31528,7 +31528,7 @@
           <t>G | 380呎 (1房)
 $998万
 $26,263/呎
-(21年-05月-31日)</t>
+(21年-05月)</t>
         </is>
       </c>
       <c r="I16" s="20" t="inlineStr">
@@ -31536,7 +31536,7 @@
           <t>H | 379呎 (1房)
 $1001万
 $26,420/呎
-(21年-06月-15日)</t>
+(21年-06月)</t>
         </is>
       </c>
       <c r="J16" s="20" t="inlineStr">
@@ -31544,7 +31544,7 @@
           <t>J | 418呎 (1房)
 $893万
 $21,370/呎
-(25年-12月-03日)</t>
+(25年-12月)</t>
         </is>
       </c>
     </row>
@@ -31559,7 +31559,7 @@
           <t>A | 890呎 (3房)
 $2996万
 $33,665/呎
-(21年-07月-11日)</t>
+(21年-07月)</t>
         </is>
       </c>
       <c r="C17" s="20" t="inlineStr">
@@ -31567,7 +31567,7 @@
           <t>B | 550呎 (2房)
 $1875万
 $34,094/呎
-(26年-07月-06日)</t>
+(26年-07月)</t>
         </is>
       </c>
       <c r="D17" s="22" t="inlineStr">
@@ -31583,7 +31583,7 @@
           <t>D | 546呎 (2房)
 $1832万
 $33,553/呎
-(26年-06月-17日)</t>
+(26年-06月)</t>
         </is>
       </c>
       <c r="F17" s="20" t="inlineStr">
@@ -31591,7 +31591,7 @@
           <t>E | 695呎 (3房)
 $1440万
 $20,725/呎
-(25年-06月-25日)</t>
+(25年-06月)</t>
         </is>
       </c>
       <c r="G17" s="20" t="inlineStr">
@@ -31599,7 +31599,7 @@
           <t>F | 505呎 (2房)
 $1336万
 $26,453/呎
-(21年-05月-31日)</t>
+(21年-05月)</t>
         </is>
       </c>
       <c r="H17" s="20" t="inlineStr">
@@ -31607,7 +31607,7 @@
           <t>G | 380呎 (1房)
 $992万
 $26,107/呎
-(21年-05月-30日)</t>
+(21年-05月)</t>
         </is>
       </c>
       <c r="I17" s="20" t="inlineStr">
@@ -31615,7 +31615,7 @@
           <t>H | 379呎 (1房)
 $985万
 $25,996/呎
-(21年-06月-06日)</t>
+(21年-06月)</t>
         </is>
       </c>
       <c r="J17" s="20" t="inlineStr">
@@ -31623,7 +31623,7 @@
           <t>J | 418呎 (1房)
 $888万
 $21,243/呎
-(25年-12月-09日)</t>
+(25年-12月)</t>
         </is>
       </c>
     </row>
@@ -31638,7 +31638,7 @@
           <t>A | 889呎 (3房)
 $2788万
 $31,363/呎
-(21年-05月-23日)</t>
+(21年-05月)</t>
         </is>
       </c>
       <c r="C18" s="23" t="inlineStr">
@@ -31654,7 +31654,7 @@
           <t>C | 550呎 (2房)
 $1823万
 $33,139/呎
-(21年-06月-09日)</t>
+(21年-06月)</t>
         </is>
       </c>
       <c r="E18" s="20" t="inlineStr">
@@ -31662,7 +31662,7 @@
           <t>D | 546呎 (2房)
 $1826万
 $33,452/呎
-(26年-04月-28日)</t>
+(26年-04月)</t>
         </is>
       </c>
       <c r="F18" s="20" t="inlineStr">
@@ -31670,7 +31670,7 @@
           <t>E | 695呎 (3房)
 $1415万
 $20,358/呎
-(25年-06月-12日)</t>
+(25年-06月)</t>
         </is>
       </c>
       <c r="G18" s="20" t="inlineStr">
@@ -31678,7 +31678,7 @@
           <t>F | 505呎 (2房)
 $1346万
 $26,654/呎
-(21年-05月-24日)</t>
+(21年-05月)</t>
         </is>
       </c>
       <c r="H18" s="20" t="inlineStr">
@@ -31686,7 +31686,7 @@
           <t>G | 380呎 (1房)
 $989万
 $26,028/呎
-(21年-05月-23日)</t>
+(21年-05月)</t>
         </is>
       </c>
       <c r="I18" s="20" t="inlineStr">
@@ -31694,7 +31694,7 @@
           <t>H | 379呎 (1房)
 $993万
 $26,190/呎
-(21年-06月-09日)</t>
+(21年-06月)</t>
         </is>
       </c>
       <c r="J18" s="20" t="inlineStr">
@@ -31702,7 +31702,7 @@
           <t>J | 418呎 (1房)
 $885万
 $21,180/呎
-(25年-11月-30日)</t>
+(25年-11月)</t>
         </is>
       </c>
     </row>
@@ -31717,7 +31717,7 @@
           <t>A | 889呎 (3房)
 $3010万
 $33,857/呎
-(21年-07月-25日)</t>
+(21年-07月)</t>
         </is>
       </c>
       <c r="C19" s="23" t="inlineStr">
@@ -31741,7 +31741,7 @@
           <t>D | 546呎 (2房)
 $1841万
 $33,723/呎
-(21年-05月-30日)</t>
+(21年-05月)</t>
         </is>
       </c>
       <c r="F19" s="20" t="inlineStr">
@@ -31749,7 +31749,7 @@
           <t>E | 695呎 (3房)
 $1710万
 $24,604/呎
-(24年-12月-30日)</t>
+(24年-12月)</t>
         </is>
       </c>
       <c r="G19" s="20" t="inlineStr">
@@ -31757,7 +31757,7 @@
           <t>F | 505呎 (2房)
 $1328万
 $26,299/呎
-(21年-05月-30日)</t>
+(21年-05月)</t>
         </is>
       </c>
       <c r="H19" s="20" t="inlineStr">
@@ -31765,7 +31765,7 @@
           <t>G | 380呎 (1房)
 $976万
 $25,680/呎
-(21年-05月-27日)</t>
+(21年-05月)</t>
         </is>
       </c>
       <c r="I19" s="20" t="inlineStr">
@@ -31773,7 +31773,7 @@
           <t>H | 379呎 (1房)
 $1000万
 $26,382/呎
-(21年-05月-26日)</t>
+(21年-05月)</t>
         </is>
       </c>
       <c r="J19" s="20" t="inlineStr">
@@ -31781,7 +31781,7 @@
           <t>J | 418呎 (1房)
 $883万
 $21,119/呎
-(25年-07月-16日)</t>
+(25年-07月)</t>
         </is>
       </c>
     </row>
@@ -31796,7 +31796,7 @@
           <t>A | 889呎 (3房)
 $2772万
 $31,178/呎
-(21年-05月-30日)</t>
+(21年-05月)</t>
         </is>
       </c>
       <c r="C20" s="23" t="inlineStr">
@@ -31820,7 +31820,7 @@
           <t>D | 546呎 (2房)
 $1836万
 $33,624/呎
-(21年-05月-30日)</t>
+(21年-05月)</t>
         </is>
       </c>
       <c r="F20" s="20" t="inlineStr">
@@ -31828,7 +31828,7 @@
           <t>E | 695呎 (3房)
 $1929万
 $27,756/呎
-(24年-01月-17日)</t>
+(24年-01月)</t>
         </is>
       </c>
       <c r="G20" s="20" t="inlineStr">
@@ -31836,7 +31836,7 @@
           <t>F | 505呎 (2房)
 $1352万
 $26,774/呎
-(21年-05月-30日)</t>
+(21年-05月)</t>
         </is>
       </c>
       <c r="H20" s="20" t="inlineStr">
@@ -31844,7 +31844,7 @@
           <t>G | 380呎 (1房)
 $973万
 $25,605/呎
-(21年-05月-27日)</t>
+(21年-05月)</t>
         </is>
       </c>
       <c r="I20" s="20" t="inlineStr">
@@ -31852,7 +31852,7 @@
           <t>H | 379呎 (1房)
 $997万
 $26,305/呎
-(21年-05月-30日)</t>
+(21年-05月)</t>
         </is>
       </c>
       <c r="J20" s="20" t="inlineStr">
@@ -31860,7 +31860,7 @@
           <t>J | 418呎 (1房)
 $880万
 $21,054/呎
-(25年-12月-09日)</t>
+(25年-12月)</t>
         </is>
       </c>
     </row>
@@ -31875,7 +31875,7 @@
           <t>A | 890呎 (3房)
 $2936万
 $32,985/呎
-(21年-10月-05日)</t>
+(21年-10月)</t>
         </is>
       </c>
       <c r="C21" s="23" t="inlineStr">
@@ -31899,7 +31899,7 @@
           <t>D | 546呎 (2房)
 $1839万
 $33,676/呎
-(26年-07月-07日)</t>
+(26年-07月)</t>
         </is>
       </c>
       <c r="F21" s="20" t="inlineStr">
@@ -31907,7 +31907,7 @@
           <t>E | 695呎 (3房)
 $1865万
 $26,836/呎
-(21年-05月-30日)</t>
+(21年-05月)</t>
         </is>
       </c>
       <c r="G21" s="20" t="inlineStr">
@@ -31915,7 +31915,7 @@
           <t>F | 505呎 (2房)
 $1320万
 $26,145/呎
-(21年-05月-27日)</t>
+(21年-05月)</t>
         </is>
       </c>
       <c r="H21" s="20" t="inlineStr">
@@ -31923,7 +31923,7 @@
           <t>G | 380呎 (1房)
 $970万
 $25,527/呎
-(21年-05月-23日)</t>
+(21年-05月)</t>
         </is>
       </c>
       <c r="I21" s="20" t="inlineStr">
@@ -31931,7 +31931,7 @@
           <t>H | 379呎 (1房)
 $974万
 $25,694/呎
-(21年-06月-10日)</t>
+(21年-06月)</t>
         </is>
       </c>
       <c r="J21" s="20" t="inlineStr">
@@ -31939,7 +31939,7 @@
           <t>J | 418呎 (1房)
 $877万
 $20,992/呎
-(25年-12月-04日)</t>
+(25年-12月)</t>
         </is>
       </c>
     </row>
@@ -31954,7 +31954,7 @@
           <t>A | 890呎 (3房)
 $2896万
 $32,544/呎
-(26年-02月-26日)</t>
+(26年-02月)</t>
         </is>
       </c>
       <c r="C22" s="23" t="inlineStr">
@@ -31970,7 +31970,7 @@
           <t>C | 550呎 (2房)
 $1801万
 $32,747/呎
-(26年-06月-14日)</t>
+(26年-06月)</t>
         </is>
       </c>
       <c r="E22" s="20" t="inlineStr">
@@ -31978,7 +31978,7 @@
           <t>D | 546呎 (2房)
 $1853万
 $33,932/呎
-(21年-05月-31日)</t>
+(21年-05月)</t>
         </is>
       </c>
       <c r="F22" s="20" t="inlineStr">
@@ -31986,7 +31986,7 @@
           <t>E | 696呎 (3房)
 $1879万
 $26,996/呎
-(21年-08月-04日)</t>
+(21年-08月)</t>
         </is>
       </c>
       <c r="G22" s="20" t="inlineStr">
@@ -31994,7 +31994,7 @@
           <t>F | 505呎 (2房)
 $1344万
 $26,616/呎
-(21年-05月-30日)</t>
+(21年-05月)</t>
         </is>
       </c>
       <c r="H22" s="20" t="inlineStr">
@@ -32002,7 +32002,7 @@
           <t>G | 380呎 (1房)
 $998万
 $26,254/呎
-(21年-05月-30日)</t>
+(21年-05月)</t>
         </is>
       </c>
       <c r="I22" s="20" t="inlineStr">
@@ -32010,7 +32010,7 @@
           <t>H | 379呎 (1房)
 $991万
 $26,152/呎
-(21年-05月-30日)</t>
+(21年-05月)</t>
         </is>
       </c>
       <c r="J22" s="20" t="inlineStr">
@@ -32018,7 +32018,7 @@
           <t>J | 418呎 (1房)
 $885万
 $21,168/呎
-(25年-08月-14日)</t>
+(25年-08月)</t>
         </is>
       </c>
     </row>
@@ -32033,7 +32033,7 @@
           <t>A | 890呎 (3房)
 $2888万
 $32,446/呎
-(26年-04月-19日)</t>
+(26年-04月)</t>
         </is>
       </c>
       <c r="C23" s="23" t="inlineStr">
@@ -32057,7 +32057,7 @@
           <t>D | 546呎 (2房)
 $1791万
 $32,805/呎
-(21年-05月-30日)</t>
+(21年-05月)</t>
         </is>
       </c>
       <c r="F23" s="20" t="inlineStr">
@@ -32065,7 +32065,7 @@
           <t>E | 695呎 (3房)
 $1893万
 $27,231/呎
-(21年-05月-26日)</t>
+(21年-05月)</t>
         </is>
       </c>
       <c r="G23" s="20" t="inlineStr">
@@ -32073,7 +32073,7 @@
           <t>F | 505呎 (2房)
 $1333万
 $26,395/呎
-(21年-05月-08日)</t>
+(21年-05月)</t>
         </is>
       </c>
       <c r="H23" s="20" t="inlineStr">
@@ -32081,7 +32081,7 @@
           <t>G | 380呎 (1房)
 $974万
 $25,639/呎
-(21年-05月-31日)</t>
+(21年-05月)</t>
         </is>
       </c>
       <c r="I23" s="20" t="inlineStr">
@@ -32089,7 +32089,7 @@
           <t>H | 379呎 (1房)
 $968万
 $25,542/呎
-(21年-05月-31日)</t>
+(21年-05月)</t>
         </is>
       </c>
       <c r="J23" s="20" t="inlineStr">
@@ -32097,7 +32097,7 @@
           <t>J | 418呎 (1房)
 $872万
 $20,866/呎
-(25年-07月-01日)</t>
+(25年-07月)</t>
         </is>
       </c>
     </row>
@@ -32112,7 +32112,7 @@
           <t>A | 889呎 (3房)
 $2795万
 $31,437/呎
-(21年-05月-31日)</t>
+(21年-05月)</t>
         </is>
       </c>
       <c r="C24" s="23" t="inlineStr">
@@ -32136,7 +32136,7 @@
           <t>D | 546呎 (2房)
 $1767万
 $32,364/呎
-(21年-05月-25日)</t>
+(21年-05月)</t>
         </is>
       </c>
       <c r="F24" s="20" t="inlineStr">
@@ -32144,7 +32144,7 @@
           <t>E | 696呎 (3房)
 $1906万
 $27,389/呎
-(21年-05月-08日)</t>
+(21年-05月)</t>
         </is>
       </c>
       <c r="G24" s="20" t="inlineStr">
@@ -32152,7 +32152,7 @@
           <t>F | 505呎 (2房)
 $1315万
 $26,043/呎
-(21年-06月-01日)</t>
+(21年-06月)</t>
         </is>
       </c>
       <c r="H24" s="20" t="inlineStr">
@@ -32160,7 +32160,7 @@
           <t>G | 380呎 (1房)
 $992万
 $26,094/呎
-(21年-06月-01日)</t>
+(21年-06月)</t>
         </is>
       </c>
       <c r="I24" s="20" t="inlineStr">
@@ -32168,7 +32168,7 @@
           <t>H | 379呎 (1房)
 $955万
 $25,201/呎
-(21年-06月-01日)</t>
+(21年-06月)</t>
         </is>
       </c>
       <c r="J24" s="20" t="inlineStr">
@@ -32176,7 +32176,7 @@
           <t>J | 418呎 (1房)
 $1111万
 $26,570/呎
-(23年-02月-28日)</t>
+(23年-02月)</t>
         </is>
       </c>
     </row>
@@ -32191,7 +32191,7 @@
           <t>A | 889呎 (3房)
 $2854万
 $32,098/呎
-(21年-05月-25日)</t>
+(21年-05月)</t>
         </is>
       </c>
       <c r="C25" s="23" t="inlineStr">
@@ -32215,7 +32215,7 @@
           <t>D | 546呎 (2房)
 $1786万
 $32,705/呎
-(21年-06月-01日)</t>
+(21年-06月)</t>
         </is>
       </c>
       <c r="F25" s="20" t="inlineStr">
@@ -32223,7 +32223,7 @@
           <t>E | 695呎 (3房)
 $1685万
 $24,242/呎
-(25年-04月-01日)</t>
+(25年-04月)</t>
         </is>
       </c>
       <c r="G25" s="20" t="inlineStr">
@@ -32231,7 +32231,7 @@
           <t>F | 505呎 (2房)
 $1329万
 $26,317/呎
-(21年-06月-01日)</t>
+(21年-06月)</t>
         </is>
       </c>
       <c r="H25" s="20" t="inlineStr">
@@ -32239,7 +32239,7 @@
           <t>G | 380呎 (1房)
 $971万
 $25,561/呎
-(21年-06月-01日)</t>
+(21年-06月)</t>
         </is>
       </c>
       <c r="I25" s="20" t="inlineStr">
@@ -32247,7 +32247,7 @@
           <t>H | 379呎 (1房)
 $985万
 $25,997/呎
-(21年-06月-01日)</t>
+(21年-06月)</t>
         </is>
       </c>
       <c r="J25" s="20" t="inlineStr">
@@ -32255,7 +32255,7 @@
           <t>J | 418呎 (1房)
 $869万
 $20,801/呎
-(25年-06月-24日)</t>
+(25年-06月)</t>
         </is>
       </c>
     </row>
@@ -32270,7 +32270,7 @@
           <t>A | 890呎 (3房)
 $2842万
 $31,933/呎
-(26年-04月-21日)</t>
+(26年-04月)</t>
         </is>
       </c>
       <c r="C26" s="23" t="inlineStr">
@@ -32294,7 +32294,7 @@
           <t>D | 546呎 (2房)
 $1762万
 $32,267/呎
-(21年-05月-25日)</t>
+(21年-05月)</t>
         </is>
       </c>
       <c r="F26" s="20" t="inlineStr">
@@ -32302,7 +32302,7 @@
           <t>E | 696呎 (3房)
 $1862万
 $26,754/呎
-(21年-06月-01日)</t>
+(21年-06月)</t>
         </is>
       </c>
       <c r="G26" s="20" t="inlineStr">
@@ -32310,7 +32310,7 @@
           <t>F | 505呎 (2房)
 $1325万
 $26,237/呎
-(21年-06月-01日)</t>
+(21年-06月)</t>
         </is>
       </c>
       <c r="H26" s="20" t="inlineStr">
@@ -32318,7 +32318,7 @@
           <t>G | 380呎 (1房)
 $989万
 $26,014/呎
-(21年-06月-01日)</t>
+(21年-06月)</t>
         </is>
       </c>
       <c r="I26" s="20" t="inlineStr">
@@ -32326,7 +32326,7 @@
           <t>H | 379呎 (1房)
 $962万
 $25,391/呎
-(21年-06月-01日)</t>
+(21年-06月)</t>
         </is>
       </c>
       <c r="J26" s="20" t="inlineStr">
@@ -32334,7 +32334,7 @@
           <t>J | 418呎 (1房)
 $867万
 $20,740/呎
-(25年-07月-14日)</t>
+(25年-07月)</t>
         </is>
       </c>
     </row>
@@ -32349,7 +32349,7 @@
           <t>A | 890呎 (3房)
 $2833万
 $31,837/呎
-(26年-05月-14日)</t>
+(26年-05月)</t>
         </is>
       </c>
       <c r="C27" s="23" t="inlineStr">
@@ -32373,7 +32373,7 @@
           <t>D | 546呎 (2房)
 $1775万
 $32,506/呎
-(21年-06月-01日)</t>
+(21年-06月)</t>
         </is>
       </c>
       <c r="F27" s="20" t="inlineStr">
@@ -32381,7 +32381,7 @@
           <t>E | 695呎 (3房)
 $1809万
 $26,030/呎
-(21年-06月-01日)</t>
+(21年-06月)</t>
         </is>
       </c>
       <c r="G27" s="20" t="inlineStr">
@@ -32389,7 +32389,7 @@
           <t>F | 505呎 (2房)
 $1275万
 $25,244/呎
-(21年-06月-01日)</t>
+(21年-06月)</t>
         </is>
       </c>
       <c r="H27" s="20" t="inlineStr">
@@ -32397,7 +32397,7 @@
           <t>G | 380呎 (1房)
 $975万
 $25,669/呎
-(21年-06月-01日)</t>
+(21年-06月)</t>
         </is>
       </c>
       <c r="I27" s="20" t="inlineStr">
@@ -32405,7 +32405,7 @@
           <t>H | 379呎 (1房)
 $959万
 $25,315/呎
-(21年-06月-01日)</t>
+(21年-06月)</t>
         </is>
       </c>
       <c r="J27" s="20" t="inlineStr">
@@ -32413,7 +32413,7 @@
           <t>J | 418呎 (1房)
 $899万
 $21,502/呎
-(25年-06月-22日)</t>
+(25年-06月)</t>
         </is>
       </c>
     </row>
@@ -32428,7 +32428,7 @@
           <t>A | 890呎 (3房)
 $2825万
 $31,741/呎
-(26年-06月-11日)</t>
+(26年-06月)</t>
         </is>
       </c>
       <c r="C28" s="23" t="inlineStr">
@@ -32452,7 +32452,7 @@
           <t>D | 546呎 (2房)
 $1788万
 $32,745/呎
-(21年-06月-01日)</t>
+(21年-06月)</t>
         </is>
       </c>
       <c r="F28" s="20" t="inlineStr">
@@ -32460,7 +32460,7 @@
           <t>E | 696呎 (3房)
 $1823万
 $26,188/呎
-(21年-06月-01日)</t>
+(21年-06月)</t>
         </is>
       </c>
       <c r="G28" s="20" t="inlineStr">
@@ -32468,7 +32468,7 @@
           <t>F | 505呎 (2房)
 $1284万
 $25,433/呎
-(21年-06月-01日)</t>
+(21年-06月)</t>
         </is>
       </c>
       <c r="H28" s="20" t="inlineStr">
@@ -32476,7 +32476,7 @@
           <t>G | 380呎 (1房)
 $962万
 $25,326/呎
-(21年-06月-01日)</t>
+(21年-06月)</t>
         </is>
       </c>
       <c r="I28" s="20" t="inlineStr">
@@ -32484,7 +32484,7 @@
           <t>H | 379呎 (1房)
 $966万
 $25,501/呎
-(21年-06月-01日)</t>
+(21年-06月)</t>
         </is>
       </c>
       <c r="J28" s="20" t="inlineStr">
@@ -32492,7 +32492,7 @@
           <t>J | 418呎 (1房)
 $871万
 $20,848/呎
-(25年-06月-23日)</t>
+(25年-06月)</t>
         </is>
       </c>
     </row>
@@ -32507,7 +32507,7 @@
           <t>A | 890呎 (3房)
 $2905万
 $32,636/呎
-(26年-07月-05日)</t>
+(26年-07月)</t>
         </is>
       </c>
       <c r="C29" s="23" t="inlineStr">
@@ -32539,7 +32539,7 @@
           <t>E | 695呎 (3房)
 $1684万
 $24,225/呎
-(24年-05月-07日)</t>
+(24年-05月)</t>
         </is>
       </c>
       <c r="G29" s="20" t="inlineStr">
@@ -32547,7 +32547,7 @@
           <t>F | 505呎 (2房)
 $1294万
 $25,619/呎
-(21年-06月-01日)</t>
+(21年-06月)</t>
         </is>
       </c>
       <c r="H29" s="20" t="inlineStr">
@@ -32555,7 +32555,7 @@
           <t>G | 380呎 (1房)
 $949万
 $24,985/呎
-(21年-06月-01日)</t>
+(21年-06月)</t>
         </is>
       </c>
       <c r="I29" s="20" t="inlineStr">
@@ -32563,7 +32563,7 @@
           <t>H | 379呎 (1房)
 $954万
 $25,163/呎
-(21年-06月-16日)</t>
+(21年-06月)</t>
         </is>
       </c>
       <c r="J29" s="20" t="inlineStr">
@@ -32571,7 +32571,7 @@
           <t>J | 418呎 (1房)
 $859万
 $20,552/呎
-(25年-07月-14日)</t>
+(25年-07月)</t>
         </is>
       </c>
     </row>
@@ -32610,7 +32610,7 @@
           <t>D | 546呎 (2房)
 $1693万
 $31,004/呎
-(21年-06月-01日)</t>
+(21年-06月)</t>
         </is>
       </c>
       <c r="F30" s="20" t="inlineStr">
@@ -32618,7 +32618,7 @@
           <t>E | 695呎 (3房)
 $1866万
 $26,854/呎
-(24年-01月-01日)</t>
+(24年-01月)</t>
         </is>
       </c>
       <c r="G30" s="20" t="inlineStr">
@@ -32626,7 +32626,7 @@
           <t>F | 505呎 (2房)
 $1260万
 $24,941/呎
-(21年-06月-01日)</t>
+(21年-06月)</t>
         </is>
       </c>
       <c r="H30" s="20" t="inlineStr">
@@ -32634,7 +32634,7 @@
           <t>G | 380呎 (1房)
 $944万
 $24,830/呎
-(21年-06月-01日)</t>
+(21年-06月)</t>
         </is>
       </c>
       <c r="I30" s="20" t="inlineStr">
@@ -32642,7 +32642,7 @@
           <t>H | 379呎 (1房)
 $968万
 $25,532/呎
-(21年-06月-01日)</t>
+(21年-06月)</t>
         </is>
       </c>
       <c r="J30" s="22" t="inlineStr">
@@ -32689,7 +32689,7 @@
           <t>D | 546呎 (2房)
 $1723万
 $31,559/呎
-(21年-06月-01日)</t>
+(21年-06月)</t>
         </is>
       </c>
       <c r="F31" s="20" t="inlineStr">
@@ -32697,7 +32697,7 @@
           <t>E | 695呎 (3房)
 $1644万
 $23,661/呎
-(24年-07月-14日)</t>
+(24年-07月)</t>
         </is>
       </c>
       <c r="G31" s="20" t="inlineStr">
@@ -32705,7 +32705,7 @@
           <t>F | 505呎 (2房)
 $1256万
 $24,866/呎
-(21年-06月-01日)</t>
+(21年-06月)</t>
         </is>
       </c>
       <c r="H31" s="20" t="inlineStr">
@@ -32713,7 +32713,7 @@
           <t>G | 380呎 (1房)
 $970万
 $25,534/呎
-(21年-05月-08日)</t>
+(21年-05月)</t>
         </is>
       </c>
       <c r="I31" s="20" t="inlineStr">
@@ -32721,7 +32721,7 @@
           <t>H | 379呎 (1房)
 $965万
 $25,454/呎
-(21年-06月-01日)</t>
+(21年-06月)</t>
         </is>
       </c>
       <c r="J31" s="20" t="inlineStr">
@@ -32729,7 +32729,7 @@
           <t>J | 417呎 (1房)
 $1077万
 $25,828/呎
-(21年-08月-05日)</t>
+(21年-08月)</t>
         </is>
       </c>
     </row>
@@ -32776,7 +32776,7 @@
           <t>E | 695呎 (3房)
 $1357万
 $19,521/呎
-(25年-06月-17日)</t>
+(25年-06月)</t>
         </is>
       </c>
       <c r="G32" s="20" t="inlineStr">
@@ -32784,7 +32784,7 @@
           <t>F | 505呎 (2房)
 $1295万
 $25,651/呎
-(21年-05月-08日)</t>
+(21年-05月)</t>
         </is>
       </c>
       <c r="H32" s="20" t="inlineStr">
@@ -32792,7 +32792,7 @@
           <t>G | 380呎 (1房)
 $950万
 $25,013/呎
-(21年-06月-15日)</t>
+(21年-06月)</t>
         </is>
       </c>
       <c r="I32" s="20" t="inlineStr">
@@ -32800,7 +32800,7 @@
           <t>H | 379呎 (1房)
 $965万
 $25,454/呎
-(21年-06月-01日)</t>
+(21年-06月)</t>
         </is>
       </c>
       <c r="J32" s="20" t="inlineStr">
@@ -32808,7 +32808,7 @@
           <t>J | 418呎 (1房)
 $1088万
 $26,034/呎
-(23年-04月-27日)</t>
+(23年-04月)</t>
         </is>
       </c>
     </row>
@@ -32855,7 +32855,7 @@
           <t>E | 695呎 (3房)
 $1639万
 $23,588/呎
-(24年-05月-05日)</t>
+(24年-05月)</t>
         </is>
       </c>
       <c r="G33" s="20" t="inlineStr">
@@ -32863,7 +32863,7 @@
           <t>F | 505呎 (2房)
 $1252万
 $24,788/呎
-(21年-06月-01日)</t>
+(21年-06月)</t>
         </is>
       </c>
       <c r="H33" s="20" t="inlineStr">
@@ -32871,7 +32871,7 @@
           <t>G | 380呎 (1房)
 $967万
 $25,454/呎
-(21年-06月-20日)</t>
+(21年-06月)</t>
         </is>
       </c>
       <c r="I33" s="20" t="inlineStr">
@@ -32879,7 +32879,7 @@
           <t>H | 379呎 (1房)
 $972万
 $25,635/呎
-(21年-06月-02日)</t>
+(21年-06月)</t>
         </is>
       </c>
       <c r="J33" s="20" t="inlineStr">
@@ -32887,7 +32887,7 @@
           <t>J | 418呎 (1房)
 $832万
 $19,899/呎
-(25年-07月-28日)</t>
+(25年-07月)</t>
         </is>
       </c>
     </row>
@@ -32934,7 +32934,7 @@
           <t>E | 695呎 (3房)
 $1849万
 $26,610/呎
-(24年-04月-11日)</t>
+(24年-04月)</t>
         </is>
       </c>
       <c r="G34" s="20" t="inlineStr">
@@ -32942,7 +32942,7 @@
           <t>F | 505呎 (2房)
 $1240万
 $24,563/呎
-(21年-06月-02日)</t>
+(21年-06月)</t>
         </is>
       </c>
       <c r="H34" s="20" t="inlineStr">
@@ -32950,7 +32950,7 @@
           <t>G | 380呎 (1房)
 $929万
 $24,442/呎
-(21年-06月-17日)</t>
+(21年-06月)</t>
         </is>
       </c>
       <c r="I34" s="20" t="inlineStr">
@@ -32958,7 +32958,7 @@
           <t>H | 379呎 (1房)
 $953万
 $25,151/呎
-(21年-05月-08日)</t>
+(21年-05月)</t>
         </is>
       </c>
       <c r="J34" s="20" t="inlineStr">
@@ -32966,7 +32966,7 @@
           <t>J | 418呎 (1房)
 $824万
 $19,711/呎
-(25年-08月-19日)</t>
+(25年-08月)</t>
         </is>
       </c>
     </row>
@@ -33013,7 +33013,7 @@
           <t>E | 695呎 (3房)
 $1364万
 $19,633/呎
-(25年-06月-16日)</t>
+(25年-06月)</t>
         </is>
       </c>
       <c r="G35" s="20" t="inlineStr">
@@ -33021,7 +33021,7 @@
           <t>F | 505呎 (2房)
 $1279万
 $25,328/呎
-(21年-06月-15日)</t>
+(21年-06月)</t>
         </is>
       </c>
       <c r="H35" s="20" t="inlineStr">
@@ -33029,7 +33029,7 @@
           <t>G | 380呎 (1房)
 $988万
 $25,996/呎
-(21年-07月-04日)</t>
+(21年-07月)</t>
         </is>
       </c>
       <c r="I35" s="20" t="inlineStr">
@@ -33037,7 +33037,7 @@
           <t>H | 379呎 (1房)
 $973万
 $25,665/呎
-(21年-08月-02日)</t>
+(21年-08月)</t>
         </is>
       </c>
       <c r="J35" s="20" t="inlineStr">
@@ -33045,7 +33045,7 @@
           <t>J | 418呎 (1房)
 $840万
 $20,089/呎
-(25年-06月-13日)</t>
+(25年-06月)</t>
         </is>
       </c>
     </row>
@@ -33092,7 +33092,7 @@
           <t>E | 695呎 (3房)
 $1387万
 $19,958/呎
-(25年-06月-11日)</t>
+(25年-06月)</t>
         </is>
       </c>
       <c r="G36" s="20" t="inlineStr">
@@ -33100,7 +33100,7 @@
           <t>F | 505呎 (2房)
 $1315万
 $26,047/呎
-(21年-06月-10日)</t>
+(21年-06月)</t>
         </is>
       </c>
       <c r="H36" s="20" t="inlineStr">
@@ -33108,7 +33108,7 @@
           <t>G | 380呎 (1房)
 $965万
 $25,384/呎
-(21年-07月-13日)</t>
+(21年-07月)</t>
         </is>
       </c>
       <c r="I36" s="20" t="inlineStr">
@@ -33116,7 +33116,7 @@
           <t>H | 379呎 (1房)
 $960万
 $25,322/呎
-(21年-08月-03日)</t>
+(21年-08月)</t>
         </is>
       </c>
       <c r="J36" s="20" t="inlineStr">
@@ -33124,7 +33124,7 @@
           <t>J | 418呎 (1房)
 $814万
 $19,468/呎
-(25年-08月-18日)</t>
+(25年-08月)</t>
         </is>
       </c>
     </row>
@@ -33171,7 +33171,7 @@
           <t>E | 695呎 (3房)
 $1371万
 $19,722/呎
-(25年-06月-11日)</t>
+(25年-06月)</t>
         </is>
       </c>
       <c r="G37" s="20" t="inlineStr">
@@ -33179,7 +33179,7 @@
           <t>F | 505呎 (2房)
 $1280万
 $25,355/呎
-(21年-06月-20日)</t>
+(21年-06月)</t>
         </is>
       </c>
       <c r="H37" s="20" t="inlineStr">
@@ -33187,7 +33187,7 @@
           <t>G | 380呎 (1房)
 $948万
 $24,957/呎
-(21年-07月-18日)</t>
+(21年-07月)</t>
         </is>
       </c>
       <c r="I37" s="20" t="inlineStr">
@@ -33195,7 +33195,7 @@
           <t>H | 379呎 (1房)
 $984万
 $25,951/呎
-(21年-08月-30日)</t>
+(21年-08月)</t>
         </is>
       </c>
       <c r="J37" s="20" t="inlineStr">
@@ -33203,7 +33203,7 @@
           <t>J | 418呎 (1房)
 $809万
 $19,344/呎
-(25年-08月-10日)</t>
+(25年-08月)</t>
         </is>
       </c>
     </row>
@@ -33222,7 +33222,7 @@
           <t>E | 705呎 (3房)
 $1357万
 $19,241/呎
-(25年-06月-16日)</t>
+(25年-06月)</t>
         </is>
       </c>
       <c r="G38" s="20" t="inlineStr">
@@ -33230,7 +33230,7 @@
           <t>F | 505呎 (2房)
 $1312万
 $25,985/呎
-(21年-07月-08日)</t>
+(21年-07月)</t>
         </is>
       </c>
       <c r="H38" s="20" t="inlineStr">
@@ -33238,7 +33238,7 @@
           <t>G | 380呎 (1房)
 $952万
 $25,058/呎
-(23年-12月-21日)</t>
+(23年-12月)</t>
         </is>
       </c>
       <c r="I38" s="20" t="inlineStr">
@@ -33246,7 +33246,7 @@
           <t>H | 379呎 (1房)
 $938万
 $24,747/呎
-(22年-09月-07日)</t>
+(22年-09月)</t>
         </is>
       </c>
       <c r="J38" s="20" t="inlineStr">
@@ -33254,7 +33254,7 @@
           <t>J | 418呎 (1房)
 $817万
 $19,552/呎
-(25年-07月-28日)</t>
+(25年-07月)</t>
         </is>
       </c>
     </row>
@@ -33416,7 +33416,7 @@
           <t>A | 320呎 (1房)
 $876万
 $27,366/呎
-(21年-06月-14日)</t>
+(21年-06月)</t>
         </is>
       </c>
       <c r="C5" s="20" t="inlineStr">
@@ -33424,7 +33424,7 @@
           <t>B | 296呎 (1房)
 $819万
 $27,653/呎
-(21年-05月-24日)</t>
+(21年-05月)</t>
         </is>
       </c>
       <c r="D5" s="20" t="inlineStr">
@@ -33432,7 +33432,7 @@
           <t>C | 321呎 (1房)
 $870万
 $27,098/呎
-(21年-06月-24日)</t>
+(21年-06月)</t>
         </is>
       </c>
       <c r="E5" s="20" t="inlineStr">
@@ -33440,7 +33440,7 @@
           <t>D | 331呎 (1房)
 $878万
 $26,537/呎
-(21年-06月-29日)</t>
+(21年-06月)</t>
         </is>
       </c>
       <c r="F5" s="20" t="inlineStr">
@@ -33448,7 +33448,7 @@
           <t>E | 301呎 (1房)
 $810万
 $26,915/呎
-(21年-06月-29日)</t>
+(21年-06月)</t>
         </is>
       </c>
       <c r="G5" s="20" t="inlineStr">
@@ -33456,7 +33456,7 @@
           <t>F | 301呎 (1房)
 $835万
 $27,749/呎
-(21年-07月-14日)</t>
+(21年-07月)</t>
         </is>
       </c>
       <c r="H5" s="20" t="inlineStr">
@@ -33464,7 +33464,7 @@
           <t>G | 208呎 (开放式)
 $595万
 $28,614/呎
-(21年-08月-03日)</t>
+(21年-08月)</t>
         </is>
       </c>
       <c r="I5" s="20" t="inlineStr">
@@ -33472,7 +33472,7 @@
           <t>H | 216呎 (开放式)
 $627万
 $29,040/呎
-(21年-09月-02日)</t>
+(21年-09月)</t>
         </is>
       </c>
     </row>
@@ -33487,7 +33487,7 @@
           <t>A | 320呎 (1房)
 $856万
 $26,757/呎
-(21年-06月-21日)</t>
+(21年-06月)</t>
         </is>
       </c>
       <c r="C6" s="20" t="inlineStr">
@@ -33495,7 +33495,7 @@
           <t>B | 296呎 (1房)
 $776万
 $26,228/呎
-(21年-06月-06日)</t>
+(21年-06月)</t>
         </is>
       </c>
       <c r="D6" s="20" t="inlineStr">
@@ -33503,7 +33503,7 @@
           <t>C | 321呎 (1房)
 $860万
 $26,780/呎
-(21年-05月-24日)</t>
+(21年-05月)</t>
         </is>
       </c>
       <c r="E6" s="20" t="inlineStr">
@@ -33511,7 +33511,7 @@
           <t>D | 330呎 (1房)
 $886万
 $26,851/呎
-(21年-07月-22日)</t>
+(21年-07月)</t>
         </is>
       </c>
       <c r="F6" s="20" t="inlineStr">
@@ -33519,7 +33519,7 @@
           <t>E | 301呎 (1房)
 $817万
 $27,147/呎
-(21年-06月-09日)</t>
+(21年-06月)</t>
         </is>
       </c>
       <c r="G6" s="20" t="inlineStr">
@@ -33527,7 +33527,7 @@
           <t>F | 302呎 (1房)
 $817万
 $27,047/呎
-(21年-07月-05日)</t>
+(21年-07月)</t>
         </is>
       </c>
       <c r="H6" s="20" t="inlineStr">
@@ -33535,7 +33535,7 @@
           <t>G | 208呎 (开放式)
 $607万
 $29,183/呎
-(21年-06月-09日)</t>
+(21年-06月)</t>
         </is>
       </c>
       <c r="I6" s="20" t="inlineStr">
@@ -33543,7 +33543,7 @@
           <t>H | 216呎 (开放式)
 $620万
 $28,702/呎
-(21年-08月-02日)</t>
+(21年-08月)</t>
         </is>
       </c>
     </row>
@@ -33558,7 +33558,7 @@
           <t>A | 320呎 (1房)
 $857万
 $26,793/呎
-(21年-06月-21日)</t>
+(21年-06月)</t>
         </is>
       </c>
       <c r="C7" s="20" t="inlineStr">
@@ -33566,7 +33566,7 @@
           <t>B | 296呎 (1房)
 $769万
 $25,993/呎
-(21年-06月-08日)</t>
+(21年-06月)</t>
         </is>
       </c>
       <c r="D7" s="20" t="inlineStr">
@@ -33574,7 +33574,7 @@
           <t>C | 321呎 (1房)
 $835万
 $25,998/呎
-(21年-05月-24日)</t>
+(21年-05月)</t>
         </is>
       </c>
       <c r="E7" s="20" t="inlineStr">
@@ -33582,7 +33582,7 @@
           <t>D | 330呎 (1房)
 $869万
 $26,336/呎
-(21年-07月-19日)</t>
+(21年-07月)</t>
         </is>
       </c>
       <c r="F7" s="20" t="inlineStr">
@@ -33590,7 +33590,7 @@
           <t>E | 302呎 (1房)
 $810万
 $26,814/呎
-(21年-06月-10日)</t>
+(21年-06月)</t>
         </is>
       </c>
       <c r="G7" s="20" t="inlineStr">
@@ -33598,7 +33598,7 @@
           <t>F | 302呎 (1房)
 $818万
 $27,083/呎
-(21年-07月-07日)</t>
+(21年-07月)</t>
         </is>
       </c>
       <c r="H7" s="20" t="inlineStr">
@@ -33606,7 +33606,7 @@
           <t>G | 208呎 (开放式)
 $600万
 $28,826/呎
-(21年-06月-10日)</t>
+(21年-06月)</t>
         </is>
       </c>
       <c r="I7" s="20" t="inlineStr">
@@ -33614,7 +33614,7 @@
           <t>H | 216呎 (开放式)
 $627万
 $29,041/呎
-(21年-06月-08日)</t>
+(21年-06月)</t>
         </is>
       </c>
     </row>
@@ -33629,7 +33629,7 @@
           <t>A | 320呎 (1房)
 $841万
 $26,270/呎
-(21年-06月-29日)</t>
+(21年-06月)</t>
         </is>
       </c>
       <c r="C8" s="20" t="inlineStr">
@@ -33637,7 +33637,7 @@
           <t>B | 296呎 (1房)
 $771万
 $26,033/呎
-(21年-06月-06日)</t>
+(21年-06月)</t>
         </is>
       </c>
       <c r="D8" s="20" t="inlineStr">
@@ -33645,7 +33645,7 @@
           <t>C | 321呎 (1房)
 $844万
 $26,301/呎
-(21年-06月-09日)</t>
+(21年-06月)</t>
         </is>
       </c>
       <c r="E8" s="20" t="inlineStr">
@@ -33653,7 +33653,7 @@
           <t>D | 331呎 (1房)
 $861万
 $26,018/呎
-(21年-07月-20日)</t>
+(21年-07月)</t>
         </is>
       </c>
       <c r="F8" s="20" t="inlineStr">
@@ -33661,7 +33661,7 @@
           <t>E | 301呎 (1房)
 $802万
 $26,655/呎
-(21年-06月-20日)</t>
+(21年-06月)</t>
         </is>
       </c>
       <c r="G8" s="20" t="inlineStr">
@@ -33669,7 +33669,7 @@
           <t>F | 301呎 (1房)
 $794万
 $26,373/呎
-(21年-07月-15日)</t>
+(21年-07月)</t>
         </is>
       </c>
       <c r="H8" s="20" t="inlineStr">
@@ -33677,7 +33677,7 @@
           <t>G | 208呎 (开放式)
 $578万
 $27,797/呎
-(21年-08月-05日)</t>
+(21年-08月)</t>
         </is>
       </c>
       <c r="I8" s="20" t="inlineStr">
@@ -33685,7 +33685,7 @@
           <t>H | 216呎 (开放式)
 $615万
 $28,489/呎
-(21年-08月-19日)</t>
+(21年-08月)</t>
         </is>
       </c>
     </row>
@@ -33700,7 +33700,7 @@
           <t>A | 299呎 (1房)
 $862万
 $28,823/呎
-(21年-06月-24日)</t>
+(21年-06月)</t>
         </is>
       </c>
       <c r="C9" s="20" t="inlineStr">
@@ -33708,7 +33708,7 @@
           <t>B | 272呎 (1房)
 $967万
 $35,561/呎
-(21年-05月-28日)</t>
+(21年-05月)</t>
         </is>
       </c>
       <c r="D9" s="20" t="inlineStr">
@@ -33716,7 +33716,7 @@
           <t>C | 299呎 (1房)
 $823万
 $27,535/呎
-(21年-06月-22日)</t>
+(21年-06月)</t>
         </is>
       </c>
       <c r="E9" s="20" t="inlineStr">
@@ -33724,7 +33724,7 @@
           <t>D | 330呎 (1房)
 $844万
 $25,587/呎
-(21年-07月-09日)</t>
+(21年-07月)</t>
         </is>
       </c>
       <c r="F9" s="20" t="inlineStr">
@@ -33732,7 +33732,7 @@
           <t>E | 302呎 (1房)
 $779万
 $25,786/呎
-(21年-06月-24日)</t>
+(21年-06月)</t>
         </is>
       </c>
       <c r="G9" s="20" t="inlineStr">
@@ -33740,7 +33740,7 @@
           <t>F | 302呎 (1房)
 $803万
 $26,586/呎
-(21年-07月-15日)</t>
+(21年-07月)</t>
         </is>
       </c>
       <c r="H9" s="20" t="inlineStr">
@@ -33748,7 +33748,7 @@
           <t>G | 208呎 (开放式)
 $573万
 $27,554/呎
-(21年-09月-08日)</t>
+(21年-09月)</t>
         </is>
       </c>
       <c r="I9" s="20" t="inlineStr">
@@ -33756,7 +33756,7 @@
           <t>H | 216呎 (开放式)
 $597万
 $27,651/呎
-(21年-09月-01日)</t>
+(21年-09月)</t>
         </is>
       </c>
     </row>
@@ -33774,7 +33774,7 @@
           <t>D | 309呎 (1房)
 $995万
 $32,200/呎
-(21年-07月-15日)</t>
+(21年-07月)</t>
         </is>
       </c>
       <c r="F10" s="20" t="inlineStr">
@@ -33782,7 +33782,7 @@
           <t>E | 280呎 (1房)
 $920万
 $32,858/呎
-(21年-06月-07日)</t>
+(21年-06月)</t>
         </is>
       </c>
       <c r="G10" s="20" t="inlineStr">
@@ -33790,7 +33790,7 @@
           <t>F | 280呎 (1房)
 $910万
 $32,510/呎
-(21年-07月-04日)</t>
+(21年-07月)</t>
         </is>
       </c>
       <c r="H10" s="20" t="inlineStr">
@@ -33798,7 +33798,7 @@
           <t>G | 186呎 (开放式)
 $682万
 $36,655/呎
-(21年-06月-24日)</t>
+(21年-06月)</t>
         </is>
       </c>
       <c r="I10" s="20" t="inlineStr">
@@ -33806,7 +33806,7 @@
           <t>H | 195呎 (开放式)
 $567万
 $29,100/呎
-(26年-02月-26日)</t>
+(26年-02月)</t>
         </is>
       </c>
     </row>
@@ -33968,7 +33968,7 @@
           <t>A | 320呎 (1房)
 $899万
 $28,107/呎
-(21年-06月-15日)</t>
+(21年-06月)</t>
         </is>
       </c>
       <c r="C5" s="20" t="inlineStr">
@@ -33976,7 +33976,7 @@
           <t>B | 296呎 (1房)
 $815万
 $27,545/呎
-(21年-06月-09日)</t>
+(21年-06月)</t>
         </is>
       </c>
       <c r="D5" s="20" t="inlineStr">
@@ -33984,7 +33984,7 @@
           <t>C | 321呎 (1房)
 $873万
 $27,204/呎
-(21年-07月-19日)</t>
+(21年-07月)</t>
         </is>
       </c>
       <c r="E5" s="20" t="inlineStr">
@@ -33992,7 +33992,7 @@
           <t>D | 330呎 (1房)
 $701万
 $21,238/呎
-(25年-07月-08日)</t>
+(25年-07月)</t>
         </is>
       </c>
       <c r="F5" s="20" t="inlineStr">
@@ -34000,7 +34000,7 @@
           <t>E | 301呎 (1房)
 $825万
 $27,414/呎
-(21年-07月-18日)</t>
+(21年-07月)</t>
         </is>
       </c>
       <c r="G5" s="20" t="inlineStr">
@@ -34008,7 +34008,7 @@
           <t>F | 301呎 (1房)
 $834万
 $27,703/呎
-(21年-06月-22日)</t>
+(21年-06月)</t>
         </is>
       </c>
       <c r="H5" s="20" t="inlineStr">
@@ -34016,7 +34016,7 @@
           <t>G | 208呎 (开放式)
 $613万
 $29,473/呎
-(21年-06月-15日)</t>
+(21年-06月)</t>
         </is>
       </c>
       <c r="I5" s="20" t="inlineStr">
@@ -34024,7 +34024,7 @@
           <t>H | 216呎 (开放式)
 $645万
 $29,867/呎
-(21年-07月-05日)</t>
+(21年-07月)</t>
         </is>
       </c>
     </row>
@@ -34039,7 +34039,7 @@
           <t>A | 320呎 (1房)
 $879万
 $27,482/呎
-(21年-06月-09日)</t>
+(21年-06月)</t>
         </is>
       </c>
       <c r="C6" s="20" t="inlineStr">
@@ -34047,7 +34047,7 @@
           <t>B | 296呎 (1房)
 $806万
 $27,224/呎
-(21年-06月-09日)</t>
+(21年-06月)</t>
         </is>
       </c>
       <c r="D6" s="20" t="inlineStr">
@@ -34055,7 +34055,7 @@
           <t>C | 321呎 (1房)
 $890万
 $27,733/呎
-(21年-07月-19日)</t>
+(21年-07月)</t>
         </is>
       </c>
       <c r="E6" s="20" t="inlineStr">
@@ -34063,7 +34063,7 @@
           <t>D | 330呎 (1房)
 $692万
 $20,984/呎
-(25年-07月-03日)</t>
+(25年-07月)</t>
         </is>
       </c>
       <c r="F6" s="20" t="inlineStr">
@@ -34071,7 +34071,7 @@
           <t>E | 302呎 (1房)
 $824万
 $27,283/呎
-(21年-07月-07日)</t>
+(21年-07月)</t>
         </is>
       </c>
       <c r="G6" s="20" t="inlineStr">
@@ -34079,7 +34079,7 @@
           <t>F | 301呎 (1房)
 $841万
 $27,945/呎
-(21年-06月-17日)</t>
+(21年-06月)</t>
         </is>
       </c>
       <c r="H6" s="20" t="inlineStr">
@@ -34087,7 +34087,7 @@
           <t>G | 208呎 (开放式)
 $593万
 $28,518/呎
-(21年-06月-15日)</t>
+(21年-06月)</t>
         </is>
       </c>
       <c r="I6" s="20" t="inlineStr">
@@ -34095,7 +34095,7 @@
           <t>H | 216呎 (开放式)
 $644万
 $29,824/呎
-(21年-06月-09日)</t>
+(21年-06月)</t>
         </is>
       </c>
     </row>
@@ -34110,7 +34110,7 @@
           <t>A | 320呎 (1房)
 $872万
 $27,235/呎
-(21年-06月-17日)</t>
+(21年-06月)</t>
         </is>
       </c>
       <c r="C7" s="20" t="inlineStr">
@@ -34118,7 +34118,7 @@
           <t>B | 296呎 (1房)
 $799万
 $26,984/呎
-(21年-05月-24日)</t>
+(21年-05月)</t>
         </is>
       </c>
       <c r="D7" s="20" t="inlineStr">
@@ -34126,7 +34126,7 @@
           <t>C | 321呎 (1房)
 $882万
 $27,489/呎
-(21年-07月-06日)</t>
+(21年-07月)</t>
         </is>
       </c>
       <c r="E7" s="20" t="inlineStr">
@@ -34134,7 +34134,7 @@
           <t>D | 330呎 (1房)
 $698万
 $21,152/呎
-(25年-06月-08日)</t>
+(25年-06月)</t>
         </is>
       </c>
       <c r="F7" s="20" t="inlineStr">
@@ -34142,7 +34142,7 @@
           <t>E | 302呎 (1房)
 $808万
 $26,757/呎
-(21年-07月-06日)</t>
+(21年-07月)</t>
         </is>
       </c>
       <c r="G7" s="20" t="inlineStr">
@@ -34150,7 +34150,7 @@
           <t>F | 301呎 (1房)
 $817万
 $27,129/呎
-(21年-06月-21日)</t>
+(21年-06月)</t>
         </is>
       </c>
       <c r="H7" s="20" t="inlineStr">
@@ -34158,7 +34158,7 @@
           <t>G | 208呎 (开放式)
 $588万
 $28,258/呎
-(21年-06月-09日)</t>
+(21年-06月)</t>
         </is>
       </c>
       <c r="I7" s="20" t="inlineStr">
@@ -34166,7 +34166,7 @@
           <t>H | 216呎 (开放式)
 $632万
 $29,268/呎
-(21年-06月-16日)</t>
+(21年-06月)</t>
         </is>
       </c>
     </row>
@@ -34181,7 +34181,7 @@
           <t>A | 320呎 (1房)
 $891万
 $27,838/呎
-(21年-06月-17日)</t>
+(21年-06月)</t>
         </is>
       </c>
       <c r="C8" s="20" t="inlineStr">
@@ -34189,7 +34189,7 @@
           <t>B | 296呎 (1房)
 $808万
 $27,301/呎
-(21年-06月-16日)</t>
+(21年-06月)</t>
         </is>
       </c>
       <c r="D8" s="20" t="inlineStr">
@@ -34197,7 +34197,7 @@
           <t>C | 321呎 (1房)
 $848万
 $26,407/呎
-(21年-07月-06日)</t>
+(21年-07月)</t>
         </is>
       </c>
       <c r="E8" s="20" t="inlineStr">
@@ -34205,7 +34205,7 @@
           <t>D | 330呎 (1房)
 $680万
 $20,608/呎
-(25年-06月-29日)</t>
+(25年-06月)</t>
         </is>
       </c>
       <c r="F8" s="20" t="inlineStr">
@@ -34213,7 +34213,7 @@
           <t>E | 302呎 (1房)
 $826万
 $27,349/呎
-(21年-07月-14日)</t>
+(21年-07月)</t>
         </is>
       </c>
       <c r="G8" s="20" t="inlineStr">
@@ -34221,7 +34221,7 @@
           <t>F | 301呎 (1房)
 $809万
 $26,880/呎
-(21年-07月-22日)</t>
+(21年-07月)</t>
         </is>
       </c>
       <c r="H8" s="20" t="inlineStr">
@@ -34229,7 +34229,7 @@
           <t>G | 208呎 (开放式)
 $601万
 $28,886/呎
-(21年-06月-09日)</t>
+(21年-06月)</t>
         </is>
       </c>
       <c r="I8" s="20" t="inlineStr">
@@ -34237,7 +34237,7 @@
           <t>H | 216呎 (开放式)
 $627万
 $29,010/呎
-(21年-06月-09日)</t>
+(21年-06月)</t>
         </is>
       </c>
     </row>
@@ -34252,7 +34252,7 @@
           <t>A | 299呎 (1房)
 $876万
 $29,307/呎
-(21年-07月-04日)</t>
+(21年-07月)</t>
         </is>
       </c>
       <c r="C9" s="20" t="inlineStr">
@@ -34260,7 +34260,7 @@
           <t>B | 272呎 (1房)
 $789万
 $29,008/呎
-(21年-07月-04日)</t>
+(21年-07月)</t>
         </is>
       </c>
       <c r="D9" s="20" t="inlineStr">
@@ -34268,7 +34268,7 @@
           <t>C | 299呎 (1房)
 $853万
 $28,527/呎
-(21年-07月-20日)</t>
+(21年-07月)</t>
         </is>
       </c>
       <c r="E9" s="20" t="inlineStr">
@@ -34276,7 +34276,7 @@
           <t>D | 331呎 (1房)
 $870万
 $26,277/呎
-(21年-07月-28日)</t>
+(21年-07月)</t>
         </is>
       </c>
       <c r="F9" s="20" t="inlineStr">
@@ -34284,7 +34284,7 @@
           <t>E | 302呎 (1房)
 $818万
 $27,099/呎
-(21年-07月-18日)</t>
+(21年-07月)</t>
         </is>
       </c>
       <c r="G9" s="20" t="inlineStr">
@@ -34292,7 +34292,7 @@
           <t>F | 302呎 (1房)
 $793万
 $26,270/呎
-(21年-07月-15日)</t>
+(21年-07月)</t>
         </is>
       </c>
       <c r="H9" s="20" t="inlineStr">
@@ -34300,7 +34300,7 @@
           <t>G | 208呎 (开放式)
 $583万
 $28,034/呎
-(21年-06月-22日)</t>
+(21年-06月)</t>
         </is>
       </c>
       <c r="I9" s="20" t="inlineStr">
@@ -34308,7 +34308,7 @@
           <t>H | 216呎 (开放式)
 $608万
 $28,164/呎
-(21年-09月-07日)</t>
+(21年-09月)</t>
         </is>
       </c>
     </row>
@@ -34326,7 +34326,7 @@
           <t>D | 309呎 (1房)
 $1022万
 $33,087/呎
-(21年-08月-25日)</t>
+(21年-08月)</t>
         </is>
       </c>
       <c r="F10" s="20" t="inlineStr">
@@ -34334,7 +34334,7 @@
           <t>E | 280呎 (1房)
 $806万
 $28,800/呎
-(26年-04月-08日)</t>
+(26年-04月)</t>
         </is>
       </c>
       <c r="G10" s="20" t="inlineStr">
@@ -34342,7 +34342,7 @@
           <t>F | 280呎 (1房)
 $740万
 $26,421/呎
-(26年-01月-14日)</t>
+(26年-01月)</t>
         </is>
       </c>
       <c r="H10" s="20" t="inlineStr">
@@ -34350,7 +34350,7 @@
           <t>G | 186呎 (开放式)
 $513万
 $27,581/呎
-(25年-07月-20日)</t>
+(25年-07月)</t>
         </is>
       </c>
       <c r="I10" s="20" t="inlineStr">
@@ -34358,7 +34358,7 @@
           <t>H | 195呎 (开放式)
 $623万
 $31,935/呎
-(26年-07月-06日)</t>
+(26年-07月)</t>
         </is>
       </c>
     </row>
@@ -34520,7 +34520,7 @@
           <t>A | 320呎 (1房)
 $898万
 $28,074/呎
-(21年-06月-01日)</t>
+(21年-06月)</t>
         </is>
       </c>
       <c r="C5" s="20" t="inlineStr">
@@ -34528,7 +34528,7 @@
           <t>B | 296呎 (1房)
 $806万
 $27,229/呎
-(21年-06月-01日)</t>
+(21年-06月)</t>
         </is>
       </c>
       <c r="D5" s="20" t="inlineStr">
@@ -34536,7 +34536,7 @@
           <t>C | 321呎 (1房)
 $856万
 $26,679/呎
-(21年-06月-01日)</t>
+(21年-06月)</t>
         </is>
       </c>
       <c r="E5" s="20" t="inlineStr">
@@ -34544,7 +34544,7 @@
           <t>D | 331呎 (1房)
 $898万
 $27,129/呎
-(21年-07月-18日)</t>
+(21年-07月)</t>
         </is>
       </c>
       <c r="F5" s="20" t="inlineStr">
@@ -34552,7 +34552,7 @@
           <t>E | 302呎 (1房)
 $828万
 $27,411/呎
-(21年-06月-01日)</t>
+(21年-06月)</t>
         </is>
       </c>
       <c r="G5" s="20" t="inlineStr">
@@ -34560,7 +34560,7 @@
           <t>F | 302呎 (1房)
 $836万
 $27,690/呎
-(21年-06月-01日)</t>
+(21年-06月)</t>
         </is>
       </c>
       <c r="H5" s="20" t="inlineStr">
@@ -34568,7 +34568,7 @@
           <t>G | 208呎 (开放式)
 $614万
 $29,518/呎
-(21年-07月-28日)</t>
+(21年-07月)</t>
         </is>
       </c>
       <c r="I5" s="20" t="inlineStr">
@@ -34576,7 +34576,7 @@
           <t>H | 216呎 (开放式)
 $634万
 $29,342/呎
-(21年-06月-19日)</t>
+(21年-06月)</t>
         </is>
       </c>
     </row>
@@ -34591,7 +34591,7 @@
           <t>A | 320呎 (1房)
 $870万
 $27,174/呎
-(21年-06月-01日)</t>
+(21年-06月)</t>
         </is>
       </c>
       <c r="C6" s="20" t="inlineStr">
@@ -34599,7 +34599,7 @@
           <t>B | 296呎 (1房)
 $788万
 $26,636/呎
-(21年-06月-01日)</t>
+(21年-06月)</t>
         </is>
       </c>
       <c r="D6" s="20" t="inlineStr">
@@ -34607,7 +34607,7 @@
           <t>C | 321呎 (1房)
 $846万
 $26,365/呎
-(21年-06月-01日)</t>
+(21年-06月)</t>
         </is>
       </c>
       <c r="E6" s="20" t="inlineStr">
@@ -34615,7 +34615,7 @@
           <t>D | 330呎 (1房)
 $878万
 $26,613/呎
-(21年-07月-02日)</t>
+(21年-07月)</t>
         </is>
       </c>
       <c r="F6" s="20" t="inlineStr">
@@ -34623,7 +34623,7 @@
           <t>E | 301呎 (1房)
 $810万
 $26,896/呎
-(21年-06月-01日)</t>
+(21年-06月)</t>
         </is>
       </c>
       <c r="G6" s="20" t="inlineStr">
@@ -34631,7 +34631,7 @@
           <t>F | 301呎 (1房)
 $801万
 $26,618/呎
-(21年-06月-01日)</t>
+(21年-06月)</t>
         </is>
       </c>
       <c r="H6" s="20" t="inlineStr">
@@ -34639,7 +34639,7 @@
           <t>G | 208呎 (开放式)
 $588万
 $28,290/呎
-(21年-07月-12日)</t>
+(21年-07月)</t>
         </is>
       </c>
       <c r="I6" s="20" t="inlineStr">
@@ -34647,7 +34647,7 @@
           <t>H | 216呎 (开放式)
 $633万
 $29,300/呎
-(21年-07月-22日)</t>
+(21年-07月)</t>
         </is>
       </c>
     </row>
@@ -34662,7 +34662,7 @@
           <t>A | 320呎 (1房)
 $880万
 $27,489/呎
-(21年-05月-19日)</t>
+(21年-05月)</t>
         </is>
       </c>
       <c r="C7" s="20" t="inlineStr">
@@ -34670,7 +34670,7 @@
           <t>B | 296呎 (1房)
 $806万
 $27,225/呎
-(21年-05月-24日)</t>
+(21年-05月)</t>
         </is>
       </c>
       <c r="D7" s="20" t="inlineStr">
@@ -34678,7 +34678,7 @@
           <t>C | 321呎 (1房)
 $856万
 $26,674/呎
-(21年-05月-23日)</t>
+(21年-05月)</t>
         </is>
       </c>
       <c r="E7" s="20" t="inlineStr">
@@ -34686,7 +34686,7 @@
           <t>D | 330呎 (1房)
 $879万
 $26,644/呎
-(21年-07月-19日)</t>
+(21年-07月)</t>
         </is>
       </c>
       <c r="F7" s="20" t="inlineStr">
@@ -34694,7 +34694,7 @@
           <t>E | 302呎 (1房)
 $794万
 $26,292/呎
-(21年-05月-30日)</t>
+(21年-05月)</t>
         </is>
       </c>
       <c r="G7" s="20" t="inlineStr">
@@ -34702,7 +34702,7 @@
           <t>F | 302呎 (1房)
 $811万
 $26,839/呎
-(21年-05月-30日)</t>
+(21年-05月)</t>
         </is>
       </c>
       <c r="H7" s="20" t="inlineStr">
@@ -34710,7 +34710,7 @@
           <t>G | 208呎 (开放式)
 $608万
 $29,224/呎
-(21年-07月-18日)</t>
+(21年-07月)</t>
         </is>
       </c>
       <c r="I7" s="20" t="inlineStr">
@@ -34718,7 +34718,7 @@
           <t>H | 216呎 (开放式)
 $608万
 $28,152/呎
-(21年-07月-20日)</t>
+(21年-07月)</t>
         </is>
       </c>
     </row>
@@ -34733,7 +34733,7 @@
           <t>A | 320呎 (1房)
 $863万
 $26,960/呎
-(21年-05月-30日)</t>
+(21年-05月)</t>
         </is>
       </c>
       <c r="C8" s="20" t="inlineStr">
@@ -34741,7 +34741,7 @@
           <t>B | 296呎 (1房)
 $766万
 $25,891/呎
-(21年-05月-26日)</t>
+(21年-05月)</t>
         </is>
       </c>
       <c r="D8" s="20" t="inlineStr">
@@ -34749,7 +34749,7 @@
           <t>C | 321呎 (1房)
 $840万
 $26,163/呎
-(21年-05月-24日)</t>
+(21年-05月)</t>
         </is>
       </c>
       <c r="E8" s="20" t="inlineStr">
@@ -34757,7 +34757,7 @@
           <t>D | 331呎 (1房)
 $844万
 $25,512/呎
-(21年-07月-18日)</t>
+(21年-07月)</t>
         </is>
       </c>
       <c r="F8" s="20" t="inlineStr">
@@ -34765,7 +34765,7 @@
           <t>E | 302呎 (1房)
 $795万
 $26,322/呎
-(21年-07月-08日)</t>
+(21年-07月)</t>
         </is>
       </c>
       <c r="G8" s="20" t="inlineStr">
@@ -34773,7 +34773,7 @@
           <t>F | 302呎 (1房)
 $787万
 $26,050/呎
-(21年-07月-05日)</t>
+(21年-07月)</t>
         </is>
       </c>
       <c r="H8" s="20" t="inlineStr">
@@ -34781,7 +34781,7 @@
           <t>G | 208呎 (开放式)
 $596万
 $28,674/呎
-(21年-07月-18日)</t>
+(21年-07月)</t>
         </is>
       </c>
       <c r="I8" s="20" t="inlineStr">
@@ -34789,7 +34789,7 @@
           <t>H | 216呎 (开放式)
 $609万
 $28,195/呎
-(21年-07月-15日)</t>
+(21年-07月)</t>
         </is>
       </c>
     </row>
@@ -34804,7 +34804,7 @@
           <t>A | 299呎 (1房)
 $840万
 $28,084/呎
-(21年-05月-31日)</t>
+(21年-05月)</t>
         </is>
       </c>
       <c r="C9" s="20" t="inlineStr">
@@ -34812,7 +34812,7 @@
           <t>B | 274呎 (1房)
 $790万
 $28,842/呎
-(21年-05月-30日)</t>
+(21年-05月)</t>
         </is>
       </c>
       <c r="D9" s="20" t="inlineStr">
@@ -34820,7 +34820,7 @@
           <t>C | 299呎 (1房)
 $836万
 $27,961/呎
-(21年-05月-31日)</t>
+(21年-05月)</t>
         </is>
       </c>
       <c r="E9" s="20" t="inlineStr">
@@ -34828,7 +34828,7 @@
           <t>D | 330呎 (1房)
 $655万
 $19,852/呎
-(25年-06月-26日)</t>
+(25年-06月)</t>
         </is>
       </c>
       <c r="F9" s="20" t="inlineStr">
@@ -34836,7 +34836,7 @@
           <t>E | 301呎 (1房)
 $771万
 $25,625/呎
-(21年-07月-15日)</t>
+(21年-07月)</t>
         </is>
       </c>
       <c r="G9" s="20" t="inlineStr">
@@ -34844,7 +34844,7 @@
           <t>F | 302呎 (1房)
 $796万
 $26,346/呎
-(21年-05月-30日)</t>
+(21年-05月)</t>
         </is>
       </c>
       <c r="H9" s="20" t="inlineStr">
@@ -34852,7 +34852,7 @@
           <t>G | 208呎 (开放式)
 $573万
 $27,554/呎
-(21年-08月-04日)</t>
+(21年-08月)</t>
         </is>
       </c>
       <c r="I9" s="20" t="inlineStr">
@@ -34860,7 +34860,7 @@
           <t>H | 216呎 (开放式)
 $597万
 $27,651/呎
-(21年-08月-11日)</t>
+(21年-08月)</t>
         </is>
       </c>
     </row>
@@ -34878,7 +34878,7 @@
           <t>D | 309呎 (1房)
 $980万
 $31,722/呎
-(23年-05月-09日)</t>
+(23年-05月)</t>
         </is>
       </c>
       <c r="F10" s="20" t="inlineStr">
@@ -34886,7 +34886,7 @@
           <t>E | 280呎 (1房)
 $806万
 $28,800/呎
-(26年-03月-31日)</t>
+(26年-03月)</t>
         </is>
       </c>
       <c r="G10" s="20" t="inlineStr">
@@ -34894,7 +34894,7 @@
           <t>F | 280呎 (1房)
 $806万
 $28,800/呎
-(26年-04月-12日)</t>
+(26年-04月)</t>
         </is>
       </c>
       <c r="H10" s="20" t="inlineStr">
@@ -34902,7 +34902,7 @@
           <t>G | 186呎 (开放式)
 $683万
 $36,718/呎
-(21年-07月-18日)</t>
+(21年-07月)</t>
         </is>
       </c>
       <c r="I10" s="20" t="inlineStr">
@@ -34910,7 +34910,7 @@
           <t>H | 194呎 (开放式)
 $708万
 $36,472/呎
-(21年-08月-10日)</t>
+(21年-08月)</t>
         </is>
       </c>
     </row>
@@ -35072,7 +35072,7 @@
           <t>A | 320呎 (1房)
 $868万
 $27,114/呎
-(21年-05月-26日)</t>
+(21年-05月)</t>
         </is>
       </c>
       <c r="C5" s="20" t="inlineStr">
@@ -35080,7 +35080,7 @@
           <t>B | 296呎 (1房)
 $823万
 $27,788/呎
-(21年-05月-26日)</t>
+(21年-05月)</t>
         </is>
       </c>
       <c r="D5" s="20" t="inlineStr">
@@ -35088,7 +35088,7 @@
           <t>C | 321呎 (1房)
 $871万
 $27,122/呎
-(21年-05月-27日)</t>
+(21年-05月)</t>
         </is>
       </c>
       <c r="E5" s="20" t="inlineStr">
@@ -35096,7 +35096,7 @@
           <t>D | 331呎 (1房)
 $853万
 $25,773/呎
-(21年-05月-27日)</t>
+(21年-05月)</t>
         </is>
       </c>
       <c r="F5" s="20" t="inlineStr">
@@ -35104,7 +35104,7 @@
           <t>E | 301呎 (1房)
 $786万
 $26,127/呎
-(21年-05月-26日)</t>
+(21年-05月)</t>
         </is>
       </c>
       <c r="G5" s="20" t="inlineStr">
@@ -35112,7 +35112,7 @@
           <t>F | 299呎 (1房)
 $778万
 $26,025/呎
-(21年-05月-08日)</t>
+(21年-05月)</t>
         </is>
       </c>
       <c r="H5" s="20" t="inlineStr">
@@ -35120,7 +35120,7 @@
           <t>G | 207呎 (开放式)
 $605万
 $29,211/呎
-(21年-07月-26日)</t>
+(21年-07月)</t>
         </is>
       </c>
       <c r="I5" s="20" t="inlineStr">
@@ -35128,7 +35128,7 @@
           <t>H | 321呎 (1房)
 $883万
 $27,510/呎
-(21年-05月-26日)</t>
+(21年-05月)</t>
         </is>
       </c>
     </row>
@@ -35143,7 +35143,7 @@
           <t>A | 320呎 (1房)
 $857万
 $26,790/呎
-(21年-05月-08日)</t>
+(21年-05月)</t>
         </is>
       </c>
       <c r="C6" s="20" t="inlineStr">
@@ -35151,7 +35151,7 @@
           <t>B | 296呎 (1房)
 $821万
 $27,740/呎
-(21年-05月-26日)</t>
+(21年-05月)</t>
         </is>
       </c>
       <c r="D6" s="20" t="inlineStr">
@@ -35159,7 +35159,7 @@
           <t>C | 321呎 (1房)
 $852万
 $26,534/呎
-(21年-05月-30日)</t>
+(21年-05月)</t>
         </is>
       </c>
       <c r="E6" s="20" t="inlineStr">
@@ -35167,7 +35167,7 @@
           <t>D | 330呎 (1房)
 $870万
 $26,350/呎
-(21年-05月-26日)</t>
+(21年-05月)</t>
         </is>
       </c>
       <c r="F6" s="20" t="inlineStr">
@@ -35175,7 +35175,7 @@
           <t>E | 301呎 (1房)
 $793万
 $26,357/呎
-(21年-05月-27日)</t>
+(21年-05月)</t>
         </is>
       </c>
       <c r="G6" s="20" t="inlineStr">
@@ -35183,7 +35183,7 @@
           <t>F | 299呎 (1房)
 $777万
 $25,994/呎
-(21年-05月-27日)</t>
+(21年-05月)</t>
         </is>
       </c>
       <c r="H6" s="20" t="inlineStr">
@@ -35191,7 +35191,7 @@
           <t>G | 207呎 (开放式)
 $597万
 $28,862/呎
-(21年-07月-20日)</t>
+(21年-07月)</t>
         </is>
       </c>
       <c r="I6" s="20" t="inlineStr">
@@ -35199,7 +35199,7 @@
           <t>H | 321呎 (1房)
 $855万
 $26,629/呎
-(21年-05月-30日)</t>
+(21年-05月)</t>
         </is>
       </c>
     </row>
@@ -35214,7 +35214,7 @@
           <t>A | 320呎 (1房)
 $841万
 $26,273/呎
-(21年-05月-08日)</t>
+(21年-05月)</t>
         </is>
       </c>
       <c r="C7" s="20" t="inlineStr">
@@ -35222,7 +35222,7 @@
           <t>B | 296呎 (1房)
 $781万
 $26,382/呎
-(21年-05月-23日)</t>
+(21年-05月)</t>
         </is>
       </c>
       <c r="D7" s="20" t="inlineStr">
@@ -35230,7 +35230,7 @@
           <t>C | 321呎 (1房)
 $853万
 $26,570/呎
-(21年-05月-23日)</t>
+(21年-05月)</t>
         </is>
       </c>
       <c r="E7" s="20" t="inlineStr">
@@ -35238,7 +35238,7 @@
           <t>D | 331呎 (1房)
 $835万
 $25,234/呎
-(21年-05月-08日)</t>
+(21年-05月)</t>
         </is>
       </c>
       <c r="F7" s="20" t="inlineStr">
@@ -35246,7 +35246,7 @@
           <t>E | 301呎 (1房)
 $770万
 $25,580/呎
-(21年-05月-08日)</t>
+(21年-05月)</t>
         </is>
       </c>
       <c r="G7" s="20" t="inlineStr">
@@ -35254,7 +35254,7 @@
           <t>F | 299呎 (1房)
 $794万
 $26,571/呎
-(21年-05月-24日)</t>
+(21年-05月)</t>
         </is>
       </c>
       <c r="H7" s="20" t="inlineStr">
@@ -35262,7 +35262,7 @@
           <t>G | 207呎 (开放式)
 $598万
 $28,906/呎
-(21年-07月-22日)</t>
+(21年-07月)</t>
         </is>
       </c>
       <c r="I7" s="20" t="inlineStr">
@@ -35270,7 +35270,7 @@
           <t>H | 321呎 (1房)
 $873万
 $27,211/呎
-(21年-05月-24日)</t>
+(21年-05月)</t>
         </is>
       </c>
     </row>
@@ -35285,7 +35285,7 @@
           <t>A | 320呎 (1房)
 $841万
 $26,294/呎
-(21年-07月-11日)</t>
+(21年-07月)</t>
         </is>
       </c>
       <c r="C8" s="20" t="inlineStr">
@@ -35293,7 +35293,7 @@
           <t>B | 296呎 (1房)
 $798万
 $26,967/呎
-(21年-05月-23日)</t>
+(21年-05月)</t>
         </is>
       </c>
       <c r="D8" s="20" t="inlineStr">
@@ -35301,7 +35301,7 @@
           <t>C | 321呎 (1房)
 $819万
 $25,529/呎
-(21年-05月-25日)</t>
+(21年-05月)</t>
         </is>
       </c>
       <c r="E8" s="20" t="inlineStr">
@@ -35309,7 +35309,7 @@
           <t>D | 330呎 (1房)
 $836万
 $25,344/呎
-(21年-05月-24日)</t>
+(21年-05月)</t>
         </is>
       </c>
       <c r="F8" s="20" t="inlineStr">
@@ -35317,7 +35317,7 @@
           <t>E | 302呎 (1房)
 $787万
 $26,061/呎
-(21年-05月-23日)</t>
+(21年-05月)</t>
         </is>
       </c>
       <c r="G8" s="20" t="inlineStr">
@@ -35325,7 +35325,7 @@
           <t>F | 299呎 (1房)
 $763万
 $25,534/呎
-(21年-05月-08日)</t>
+(21年-05月)</t>
         </is>
       </c>
       <c r="H8" s="20" t="inlineStr">
@@ -35333,7 +35333,7 @@
           <t>G | 207呎 (开放式)
 $605万
 $29,239/呎
-(21年-07月-09日)</t>
+(21年-07月)</t>
         </is>
       </c>
       <c r="I8" s="20" t="inlineStr">
@@ -35341,7 +35341,7 @@
           <t>H | 321呎 (1房)
 $857万
 $26,692/呎
-(21年-05月-08日)</t>
+(21年-05月)</t>
         </is>
       </c>
     </row>
@@ -35356,7 +35356,7 @@
           <t>A | 298呎 (1房)
 $838万
 $28,108/呎
-(21年-07月-18日)</t>
+(21年-07月)</t>
         </is>
       </c>
       <c r="C9" s="20" t="inlineStr">
@@ -35364,7 +35364,7 @@
           <t>B | 272呎 (1房)
 $795万
 $29,231/呎
-(21年-06月-02日)</t>
+(21年-06月)</t>
         </is>
       </c>
       <c r="D9" s="20" t="inlineStr">
@@ -35372,7 +35372,7 @@
           <t>C | 299呎 (1房)
 $824万
 $27,563/呎
-(21年-07月-28日)</t>
+(21年-07月)</t>
         </is>
       </c>
       <c r="E9" s="20" t="inlineStr">
@@ -35380,7 +35380,7 @@
           <t>D | 330呎 (1房)
 $828万
 $25,094/呎
-(21年-07月-18日)</t>
+(21年-07月)</t>
         </is>
       </c>
       <c r="F9" s="20" t="inlineStr">
@@ -35388,7 +35388,7 @@
           <t>E | 301呎 (1房)
 $764万
 $25,378/呎
-(21年-06月-02日)</t>
+(21年-06月)</t>
         </is>
       </c>
       <c r="G9" s="20" t="inlineStr">
@@ -35396,7 +35396,7 @@
           <t>F | 299呎 (1房)
 $780万
 $26,101/呎
-(21年-05月-08日)</t>
+(21年-05月)</t>
         </is>
       </c>
       <c r="H9" s="20" t="inlineStr">
@@ -35404,7 +35404,7 @@
           <t>G | 207呎 (开放式)
 $587万
 $28,378/呎
-(21年-09月-05日)</t>
+(21年-09月)</t>
         </is>
       </c>
       <c r="I9" s="20" t="inlineStr">
@@ -35412,7 +35412,7 @@
           <t>H | 321呎 (1房)
 $857万
 $26,710/呎
-(21年-07月-19日)</t>
+(21年-07月)</t>
         </is>
       </c>
     </row>
@@ -35430,7 +35430,7 @@
           <t>D | 309呎 (1房)
 $908万
 $29,385/呎
-(26年-06月-11日)</t>
+(26年-06月)</t>
         </is>
       </c>
       <c r="F10" s="20" t="inlineStr">
@@ -35438,7 +35438,7 @@
           <t>E | 280呎 (1房)
 $848万
 $30,286/呎
-(26年-06月-04日)</t>
+(26年-06月)</t>
         </is>
       </c>
       <c r="G10" s="20" t="inlineStr">
@@ -35446,7 +35446,7 @@
           <t>F | 277呎 (1房)
 $803万
 $29,000/呎
-(26年-06月-02日)</t>
+(26年-06月)</t>
         </is>
       </c>
       <c r="H10" s="22" t="inlineStr">
@@ -35462,7 +35462,7 @@
           <t>H | 300呎 (1房)
 $918万
 $30,600/呎
-(26年-05月-20日)</t>
+(26年-05月)</t>
         </is>
       </c>
     </row>

--- a/files/九龙-启德-The Henley I.xlsx
+++ b/files/九龙-启德-The Henley I.xlsx
@@ -30632,7 +30632,7 @@
           <t>A | 1350呎 (3房)
 $8355万
 $61,888/呎
-(21年-06月)</t>
+(21年-06月-01日)</t>
         </is>
       </c>
       <c r="C5" s="21" t="inlineStr"/>
@@ -30651,7 +30651,7 @@
           <t>F | 505呎 (2房)
 $1370万
 $27,129/呎
-(25年-12月)</t>
+(25年-12月-08日)</t>
         </is>
       </c>
       <c r="H5" s="20" t="inlineStr">
@@ -30659,7 +30659,7 @@
           <t>G | 380呎 (1房)
 $827万
 $21,753/呎
-(25年-07月)</t>
+(25年-07月-14日)</t>
         </is>
       </c>
       <c r="I5" s="20" t="inlineStr">
@@ -30667,7 +30667,7 @@
           <t>H | 379呎 (1房)
 $820万
 $21,630/呎
-(25年-06月)</t>
+(25年-06月-29日)</t>
         </is>
       </c>
       <c r="J5" s="22" t="inlineStr">
@@ -30690,7 +30690,7 @@
           <t>A | 890呎 (3房)
 $2996万
 $33,662/呎
-(26年-01月)</t>
+(26年-01月-11日)</t>
         </is>
       </c>
       <c r="C6" s="22" t="inlineStr">
@@ -30714,7 +30714,7 @@
           <t>D | 546呎 (2房)
 $1950万
 $35,721/呎
-(21年-06月)</t>
+(21年-06月-02日)</t>
         </is>
       </c>
       <c r="F6" s="20" t="inlineStr">
@@ -30722,7 +30722,7 @@
           <t>E | 695呎 (3房)
 $1557万
 $22,404/呎
-(25年-07月)</t>
+(25年-07月-03日)</t>
         </is>
       </c>
       <c r="G6" s="20" t="inlineStr">
@@ -30730,7 +30730,7 @@
           <t>F | 505呎 (2房)
 $1437万
 $28,453/呎
-(21年-06月)</t>
+(21年-06月-02日)</t>
         </is>
       </c>
       <c r="H6" s="20" t="inlineStr">
@@ -30738,7 +30738,7 @@
           <t>G | 380呎 (1房)
 $1055万
 $27,765/呎
-(21年-06月)</t>
+(21年-06月-01日)</t>
         </is>
       </c>
       <c r="I6" s="20" t="inlineStr">
@@ -30746,7 +30746,7 @@
           <t>H | 379呎 (1房)
 $1058万
 $27,903/呎
-(21年-07月)</t>
+(21年-07月-13日)</t>
         </is>
       </c>
       <c r="J6" s="22" t="inlineStr">
@@ -30769,7 +30769,7 @@
           <t>A | 890呎 (3房)
 $2960万
 $33,263/呎
-(26年-02月)</t>
+(26年-02月-08日)</t>
         </is>
       </c>
       <c r="C7" s="22" t="inlineStr">
@@ -30793,7 +30793,7 @@
           <t>D | 546呎 (2房)
 $1880万
 $34,428/呎
-(21年-06月)</t>
+(21年-06月-01日)</t>
         </is>
       </c>
       <c r="F7" s="20" t="inlineStr">
@@ -30801,7 +30801,7 @@
           <t>E | 695呎 (3房)
 $1540万
 $22,152/呎
-(25年-07月)</t>
+(25年-07月-03日)</t>
         </is>
       </c>
       <c r="G7" s="20" t="inlineStr">
@@ -30809,7 +30809,7 @@
           <t>F | 505呎 (2房)
 $1392万
 $27,556/呎
-(21年-05月)</t>
+(21年-05月-08日)</t>
         </is>
       </c>
       <c r="H7" s="20" t="inlineStr">
@@ -30817,7 +30817,7 @@
           <t>G | 380呎 (1房)
 $1043万
 $27,447/呎
-(22年-09月)</t>
+(22年-09月-28日)</t>
         </is>
       </c>
       <c r="I7" s="20" t="inlineStr">
@@ -30825,7 +30825,7 @@
           <t>H | 379呎 (1房)
 $1046万
 $27,592/呎
-(21年-07月)</t>
+(21年-07月-28日)</t>
         </is>
       </c>
       <c r="J7" s="22" t="inlineStr">
@@ -30848,7 +30848,7 @@
           <t>A | 890呎 (3房)
 $2943万
 $33,063/呎
-(26年-02月)</t>
+(26年-02月-10日)</t>
         </is>
       </c>
       <c r="C8" s="23" t="inlineStr">
@@ -30872,7 +30872,7 @@
           <t>D | 546呎 (2房)
 $1887万
 $34,551/呎
-(21年-06月)</t>
+(21年-06月-07日)</t>
         </is>
       </c>
       <c r="F8" s="20" t="inlineStr">
@@ -30880,7 +30880,7 @@
           <t>E | 695呎 (3房)
 $1528万
 $21,979/呎
-(25年-06月)</t>
+(25年-06月-26日)</t>
         </is>
       </c>
       <c r="G8" s="20" t="inlineStr">
@@ -30888,7 +30888,7 @@
           <t>F | 505呎 (2房)
 $1425万
 $28,226/呎
-(21年-05月)</t>
+(21年-05月-23日)</t>
         </is>
       </c>
       <c r="H8" s="20" t="inlineStr">
@@ -30896,7 +30896,7 @@
           <t>G | 380呎 (1房)
 $812万
 $21,364/呎
-(25年-06月)</t>
+(25年-06月-25日)</t>
         </is>
       </c>
       <c r="I8" s="20" t="inlineStr">
@@ -30904,7 +30904,7 @@
           <t>H | 379呎 (1房)
 $806万
 $21,256/呎
-(25年-07月)</t>
+(25年-07月-02日)</t>
         </is>
       </c>
       <c r="J8" s="22" t="inlineStr">
@@ -30927,7 +30927,7 @@
           <t>A | 890呎 (3房)
 $2934万
 $32,963/呎
-(26年-02月)</t>
+(26年-02月-08日)</t>
         </is>
       </c>
       <c r="C9" s="22" t="inlineStr">
@@ -30943,7 +30943,7 @@
           <t>C | 550呎 (2房)
 $1965万
 $35,733/呎
-(21年-06月)</t>
+(21年-06月-22日)</t>
         </is>
       </c>
       <c r="E9" s="20" t="inlineStr">
@@ -30951,7 +30951,7 @@
           <t>D | 546呎 (2房)
 $1881万
 $34,451/呎
-(21年-06月)</t>
+(21年-06月-15日)</t>
         </is>
       </c>
       <c r="F9" s="20" t="inlineStr">
@@ -30959,7 +30959,7 @@
           <t>E | 695呎 (3房)
 $1523万
 $21,918/呎
-(25年-06月)</t>
+(25年-06月-22日)</t>
         </is>
       </c>
       <c r="G9" s="20" t="inlineStr">
@@ -30967,7 +30967,7 @@
           <t>F | 505呎 (2房)
 $1436万
 $28,433/呎
-(21年-05月)</t>
+(21年-05月-23日)</t>
         </is>
       </c>
       <c r="H9" s="20" t="inlineStr">
@@ -30975,7 +30975,7 @@
           <t>G | 380呎 (1房)
 $1034万
 $27,210/呎
-(23年-05月)</t>
+(23年-05月-30日)</t>
         </is>
       </c>
       <c r="I9" s="20" t="inlineStr">
@@ -30983,7 +30983,7 @@
           <t>H | 379呎 (1房)
 $803万
 $21,196/呎
-(25年-06月)</t>
+(25年-06月-24日)</t>
         </is>
       </c>
       <c r="J9" s="20" t="inlineStr">
@@ -30991,7 +30991,7 @@
           <t>J | 418呎 (1房)
 $1013万
 $24,241/呎
-(26年-06月)</t>
+(26年-06月-23日)</t>
         </is>
       </c>
     </row>
@@ -31006,7 +31006,7 @@
           <t>A | 889呎 (3房)
 $3131万
 $35,222/呎
-(21年-06月)</t>
+(21年-06月-07日)</t>
         </is>
       </c>
       <c r="C10" s="20" t="inlineStr">
@@ -31014,7 +31014,7 @@
           <t>B | 550呎 (2房)
 $1919万
 $34,896/呎
-(26年-07月)</t>
+(26年-07月-06日)</t>
         </is>
       </c>
       <c r="D10" s="22" t="inlineStr">
@@ -31030,7 +31030,7 @@
           <t>D | 546呎 (2房)
 $1876万
 $34,351/呎
-(21年-06月)</t>
+(21年-06月-06日)</t>
         </is>
       </c>
       <c r="F10" s="20" t="inlineStr">
@@ -31038,7 +31038,7 @@
           <t>E | 695呎 (3房)
 $1519万
 $21,855/呎
-(25年-06月)</t>
+(25年-06月-24日)</t>
         </is>
       </c>
       <c r="G10" s="20" t="inlineStr">
@@ -31046,7 +31046,7 @@
           <t>F | 505呎 (2房)
 $1388万
 $27,492/呎
-(21年-05月)</t>
+(21年-05月-27日)</t>
         </is>
       </c>
       <c r="H10" s="20" t="inlineStr">
@@ -31054,7 +31054,7 @@
           <t>G | 380呎 (1房)
 $807万
 $21,239/呎
-(25年-06月)</t>
+(25年-06月-22日)</t>
         </is>
       </c>
       <c r="I10" s="20" t="inlineStr">
@@ -31062,7 +31062,7 @@
           <t>H | 379呎 (1房)
 $953万
 $25,149/呎
-(25年-05月)</t>
+(25年-05月-01日)</t>
         </is>
       </c>
       <c r="J10" s="20" t="inlineStr">
@@ -31070,7 +31070,7 @@
           <t>J | 418呎 (1房)
 $1010万
 $24,172/呎
-(26年-06月)</t>
+(26年-06月-23日)</t>
         </is>
       </c>
     </row>
@@ -31085,7 +31085,7 @@
           <t>A | 889呎 (3房)
 $3122万
 $35,122/呎
-(21年-07月)</t>
+(21年-07月-11日)</t>
         </is>
       </c>
       <c r="C11" s="22" t="inlineStr">
@@ -31109,7 +31109,7 @@
           <t>D | 546呎 (2房)
 $1870万
 $34,250/呎
-(21年-06月)</t>
+(21年-06月-15日)</t>
         </is>
       </c>
       <c r="F11" s="20" t="inlineStr">
@@ -31117,7 +31117,7 @@
           <t>E | 695呎 (3房)
 $1515万
 $21,792/呎
-(25年-06月)</t>
+(25年-06月-26日)</t>
         </is>
       </c>
       <c r="G11" s="20" t="inlineStr">
@@ -31125,7 +31125,7 @@
           <t>F | 505呎 (2房)
 $1370万
 $27,129/呎
-(21年-05月)</t>
+(21年-05月-24日)</t>
         </is>
       </c>
       <c r="H11" s="20" t="inlineStr">
@@ -31133,7 +31133,7 @@
           <t>G | 380呎 (1房)
 $1071万
 $28,189/呎
-(23年-04月)</t>
+(23年-04月-19日)</t>
         </is>
       </c>
       <c r="I11" s="20" t="inlineStr">
@@ -31141,7 +31141,7 @@
           <t>H | 379呎 (1房)
 $1020万
 $26,921/呎
-(21年-07月)</t>
+(21年-07月-20日)</t>
         </is>
       </c>
       <c r="J11" s="22" t="inlineStr">
@@ -31164,7 +31164,7 @@
           <t>A | 890呎 (3房)
 $2907万
 $32,663/呎
-(25年-09月)</t>
+(25年-09月-11日)</t>
         </is>
       </c>
       <c r="C12" s="23" t="inlineStr">
@@ -31180,7 +31180,7 @@
           <t>C | 550呎 (2房)
 $1860万
 $33,823/呎
-(21年-07月)</t>
+(21年-07月-05日)</t>
         </is>
       </c>
       <c r="E12" s="20" t="inlineStr">
@@ -31188,7 +31188,7 @@
           <t>D | 546呎 (2房)
 $1865万
 $34,151/呎
-(26年-04月)</t>
+(26年-04月-28日)</t>
         </is>
       </c>
       <c r="F12" s="20" t="inlineStr">
@@ -31196,7 +31196,7 @@
           <t>E | 695呎 (3房)
 $1466万
 $21,091/呎
-(25年-06月)</t>
+(25年-06月-12日)</t>
         </is>
       </c>
       <c r="G12" s="20" t="inlineStr">
@@ -31204,7 +31204,7 @@
           <t>F | 505呎 (2房)
 $1380万
 $27,336/呎
-(21年-05月)</t>
+(21年-05月-30日)</t>
         </is>
       </c>
       <c r="H12" s="20" t="inlineStr">
@@ -31212,7 +31212,7 @@
           <t>G | 380呎 (1房)
 $1025万
 $26,970/呎
-(21年-08月)</t>
+(21年-08月-04日)</t>
         </is>
       </c>
       <c r="I12" s="20" t="inlineStr">
@@ -31220,7 +31220,7 @@
           <t>H | 379呎 (1房)
 $1028万
 $27,123/呎
-(21年-07月)</t>
+(21年-07月-08日)</t>
         </is>
       </c>
       <c r="J12" s="20" t="inlineStr">
@@ -31228,7 +31228,7 @@
           <t>J | 418呎 (1房)
 $1004万
 $24,030/呎
-(26年-07月)</t>
+(26年-07月-01日)</t>
         </is>
       </c>
     </row>
@@ -31243,7 +31243,7 @@
           <t>A | 890呎 (3房)
 $2898万
 $32,564/呎
-(25年-12月)</t>
+(25年-12月-17日)</t>
         </is>
       </c>
       <c r="C13" s="23" t="inlineStr">
@@ -31267,7 +31267,7 @@
           <t>D | 546呎 (2房)
 $1859万
 $34,052/呎
-(21年-07月)</t>
+(21年-07月-29日)</t>
         </is>
       </c>
       <c r="F13" s="20" t="inlineStr">
@@ -31275,7 +31275,7 @@
           <t>E | 695呎 (3房)
 $1462万
 $21,030/呎
-(25年-06月)</t>
+(25年-06月-23日)</t>
         </is>
       </c>
       <c r="G13" s="20" t="inlineStr">
@@ -31283,7 +31283,7 @@
           <t>F | 505呎 (2房)
 $1355万
 $26,839/呎
-(21年-05月)</t>
+(21年-05月-30日)</t>
         </is>
       </c>
       <c r="H13" s="20" t="inlineStr">
@@ -31291,7 +31291,7 @@
           <t>G | 380呎 (1房)
 $1038万
 $27,327/呎
-(21年-05月)</t>
+(21年-05月-08日)</t>
         </is>
       </c>
       <c r="I13" s="20" t="inlineStr">
@@ -31299,7 +31299,7 @@
           <t>H | 379呎 (1房)
 $989万
 $26,101/呎
-(21年-07月)</t>
+(21年-07月-05日)</t>
         </is>
       </c>
       <c r="J13" s="20" t="inlineStr">
@@ -31307,7 +31307,7 @@
           <t>J | 418呎 (1房)
 $901万
 $21,559/呎
-(25年-12月)</t>
+(25年-12月-09日)</t>
         </is>
       </c>
     </row>
@@ -31322,7 +31322,7 @@
           <t>A | 890呎 (3房)
 $2916万
 $32,763/呎
-(24年-07月)</t>
+(24年-07月-23日)</t>
         </is>
       </c>
       <c r="C14" s="22" t="inlineStr">
@@ -31338,7 +31338,7 @@
           <t>C | 550呎 (2房)
 $1850万
 $33,628/呎
-(21年-06月)</t>
+(21年-06月-06日)</t>
         </is>
       </c>
       <c r="E14" s="20" t="inlineStr">
@@ -31346,7 +31346,7 @@
           <t>D | 546呎 (2房)
 $1854万
 $33,951/呎
-(26年-02月)</t>
+(26年-02月-26日)</t>
         </is>
       </c>
       <c r="F14" s="20" t="inlineStr">
@@ -31354,7 +31354,7 @@
           <t>E | 695呎 (3房)
 $1457万
 $20,968/呎
-(25年-06月)</t>
+(25年-06月-15日)</t>
         </is>
       </c>
       <c r="G14" s="20" t="inlineStr">
@@ -31362,7 +31362,7 @@
           <t>F | 505呎 (2房)
 $1366万
 $27,043/呎
-(21年-05月)</t>
+(21年-05月-30日)</t>
         </is>
       </c>
       <c r="H14" s="20" t="inlineStr">
@@ -31370,7 +31370,7 @@
           <t>G | 380呎 (1房)
 $994万
 $26,145/呎
-(21年-06月)</t>
+(21年-06月-09日)</t>
         </is>
       </c>
       <c r="I14" s="20" t="inlineStr">
@@ -31378,7 +31378,7 @@
           <t>H | 379呎 (1房)
 $997万
 $26,300/呎
-(21年-05月)</t>
+(21年-05月-26日)</t>
         </is>
       </c>
       <c r="J14" s="20" t="inlineStr">
@@ -31386,7 +31386,7 @@
           <t>J | 418呎 (1房)
 $899万
 $21,496/呎
-(25年-12月)</t>
+(25年-12月-09日)</t>
         </is>
       </c>
     </row>
@@ -31401,7 +31401,7 @@
           <t>A | 890呎 (3房)
 $2916万
 $32,763/呎
-(26年-04月)</t>
+(26年-04月-08日)</t>
         </is>
       </c>
       <c r="C15" s="20" t="inlineStr">
@@ -31409,7 +31409,7 @@
           <t>B | 550呎 (2房)
 $1892万
 $34,394/呎
-(26年-07月)</t>
+(26年-07月-06日)</t>
         </is>
       </c>
       <c r="D15" s="22" t="inlineStr">
@@ -31425,7 +31425,7 @@
           <t>D | 546呎 (2房)
 $1848万
 $33,852/呎
-(25年-10月)</t>
+(25年-10月-08日)</t>
         </is>
       </c>
       <c r="F15" s="20" t="inlineStr">
@@ -31433,7 +31433,7 @@
           <t>E | 695呎 (3房)
 $1453万
 $20,908/呎
-(25年-06月)</t>
+(25年-06月-16日)</t>
         </is>
       </c>
       <c r="G15" s="20" t="inlineStr">
@@ -31441,7 +31441,7 @@
           <t>F | 505呎 (2房)
 $1348万
 $26,685/呎
-(21年-05月)</t>
+(21年-05月-26日)</t>
         </is>
       </c>
       <c r="H15" s="20" t="inlineStr">
@@ -31449,7 +31449,7 @@
           <t>G | 380呎 (1房)
 $1001万
 $26,342/呎
-(21年-06月)</t>
+(21年-06月-09日)</t>
         </is>
       </c>
       <c r="I15" s="20" t="inlineStr">
@@ -31457,7 +31457,7 @@
           <t>H | 379呎 (1房)
 $984万
 $25,951/呎
-(21年-06月)</t>
+(21年-06月-17日)</t>
         </is>
       </c>
       <c r="J15" s="20" t="inlineStr">
@@ -31465,7 +31465,7 @@
           <t>J | 418呎 (1房)
 $896万
 $21,433/呎
-(25年-12月)</t>
+(25年-12月-07日)</t>
         </is>
       </c>
     </row>
@@ -31480,7 +31480,7 @@
           <t>A | 889呎 (3房)
 $3036万
 $34,145/呎
-(21年-05月)</t>
+(21年-05月-27日)</t>
         </is>
       </c>
       <c r="C16" s="22" t="inlineStr">
@@ -31504,7 +31504,7 @@
           <t>D | 546呎 (2房)
 $1843万
 $33,751/呎
-(26年-05月)</t>
+(26年-05月-31日)</t>
         </is>
       </c>
       <c r="F16" s="20" t="inlineStr">
@@ -31512,7 +31512,7 @@
           <t>E | 695呎 (3房)
 $1449万
 $20,848/呎
-(25年-06月)</t>
+(25年-06月-18日)</t>
         </is>
       </c>
       <c r="G16" s="20" t="inlineStr">
@@ -31520,7 +31520,7 @@
           <t>F | 505呎 (2房)
 $1372万
 $27,168/呎
-(21年-05月)</t>
+(21年-05月-08日)</t>
         </is>
       </c>
       <c r="H16" s="20" t="inlineStr">
@@ -31528,7 +31528,7 @@
           <t>G | 380呎 (1房)
 $998万
 $26,263/呎
-(21年-05月)</t>
+(21年-05月-31日)</t>
         </is>
       </c>
       <c r="I16" s="20" t="inlineStr">
@@ -31536,7 +31536,7 @@
           <t>H | 379呎 (1房)
 $1001万
 $26,420/呎
-(21年-06月)</t>
+(21年-06月-15日)</t>
         </is>
       </c>
       <c r="J16" s="20" t="inlineStr">
@@ -31544,7 +31544,7 @@
           <t>J | 418呎 (1房)
 $893万
 $21,370/呎
-(25年-12月)</t>
+(25年-12月-03日)</t>
         </is>
       </c>
     </row>
@@ -31559,7 +31559,7 @@
           <t>A | 890呎 (3房)
 $2996万
 $33,665/呎
-(21年-07月)</t>
+(21年-07月-11日)</t>
         </is>
       </c>
       <c r="C17" s="20" t="inlineStr">
@@ -31567,7 +31567,7 @@
           <t>B | 550呎 (2房)
 $1875万
 $34,094/呎
-(26年-07月)</t>
+(26年-07月-06日)</t>
         </is>
       </c>
       <c r="D17" s="22" t="inlineStr">
@@ -31583,7 +31583,7 @@
           <t>D | 546呎 (2房)
 $1832万
 $33,553/呎
-(26年-06月)</t>
+(26年-06月-17日)</t>
         </is>
       </c>
       <c r="F17" s="20" t="inlineStr">
@@ -31591,7 +31591,7 @@
           <t>E | 695呎 (3房)
 $1440万
 $20,725/呎
-(25年-06月)</t>
+(25年-06月-25日)</t>
         </is>
       </c>
       <c r="G17" s="20" t="inlineStr">
@@ -31599,7 +31599,7 @@
           <t>F | 505呎 (2房)
 $1336万
 $26,453/呎
-(21年-05月)</t>
+(21年-05月-31日)</t>
         </is>
       </c>
       <c r="H17" s="20" t="inlineStr">
@@ -31607,7 +31607,7 @@
           <t>G | 380呎 (1房)
 $992万
 $26,107/呎
-(21年-05月)</t>
+(21年-05月-30日)</t>
         </is>
       </c>
       <c r="I17" s="20" t="inlineStr">
@@ -31615,7 +31615,7 @@
           <t>H | 379呎 (1房)
 $985万
 $25,996/呎
-(21年-06月)</t>
+(21年-06月-06日)</t>
         </is>
       </c>
       <c r="J17" s="20" t="inlineStr">
@@ -31623,7 +31623,7 @@
           <t>J | 418呎 (1房)
 $888万
 $21,243/呎
-(25年-12月)</t>
+(25年-12月-09日)</t>
         </is>
       </c>
     </row>
@@ -31638,7 +31638,7 @@
           <t>A | 889呎 (3房)
 $2788万
 $31,363/呎
-(21年-05月)</t>
+(21年-05月-23日)</t>
         </is>
       </c>
       <c r="C18" s="23" t="inlineStr">
@@ -31654,7 +31654,7 @@
           <t>C | 550呎 (2房)
 $1823万
 $33,139/呎
-(21年-06月)</t>
+(21年-06月-09日)</t>
         </is>
       </c>
       <c r="E18" s="20" t="inlineStr">
@@ -31662,7 +31662,7 @@
           <t>D | 546呎 (2房)
 $1826万
 $33,452/呎
-(26年-04月)</t>
+(26年-04月-28日)</t>
         </is>
       </c>
       <c r="F18" s="20" t="inlineStr">
@@ -31670,7 +31670,7 @@
           <t>E | 695呎 (3房)
 $1415万
 $20,358/呎
-(25年-06月)</t>
+(25年-06月-12日)</t>
         </is>
       </c>
       <c r="G18" s="20" t="inlineStr">
@@ -31678,7 +31678,7 @@
           <t>F | 505呎 (2房)
 $1346万
 $26,654/呎
-(21年-05月)</t>
+(21年-05月-24日)</t>
         </is>
       </c>
       <c r="H18" s="20" t="inlineStr">
@@ -31686,7 +31686,7 @@
           <t>G | 380呎 (1房)
 $989万
 $26,028/呎
-(21年-05月)</t>
+(21年-05月-23日)</t>
         </is>
       </c>
       <c r="I18" s="20" t="inlineStr">
@@ -31694,7 +31694,7 @@
           <t>H | 379呎 (1房)
 $993万
 $26,190/呎
-(21年-06月)</t>
+(21年-06月-09日)</t>
         </is>
       </c>
       <c r="J18" s="20" t="inlineStr">
@@ -31702,7 +31702,7 @@
           <t>J | 418呎 (1房)
 $885万
 $21,180/呎
-(25年-11月)</t>
+(25年-11月-30日)</t>
         </is>
       </c>
     </row>
@@ -31717,7 +31717,7 @@
           <t>A | 889呎 (3房)
 $3010万
 $33,857/呎
-(21年-07月)</t>
+(21年-07月-25日)</t>
         </is>
       </c>
       <c r="C19" s="23" t="inlineStr">
@@ -31741,7 +31741,7 @@
           <t>D | 546呎 (2房)
 $1841万
 $33,723/呎
-(21年-05月)</t>
+(21年-05月-30日)</t>
         </is>
       </c>
       <c r="F19" s="20" t="inlineStr">
@@ -31749,7 +31749,7 @@
           <t>E | 695呎 (3房)
 $1710万
 $24,604/呎
-(24年-12月)</t>
+(24年-12月-30日)</t>
         </is>
       </c>
       <c r="G19" s="20" t="inlineStr">
@@ -31757,7 +31757,7 @@
           <t>F | 505呎 (2房)
 $1328万
 $26,299/呎
-(21年-05月)</t>
+(21年-05月-30日)</t>
         </is>
       </c>
       <c r="H19" s="20" t="inlineStr">
@@ -31765,7 +31765,7 @@
           <t>G | 380呎 (1房)
 $976万
 $25,680/呎
-(21年-05月)</t>
+(21年-05月-27日)</t>
         </is>
       </c>
       <c r="I19" s="20" t="inlineStr">
@@ -31773,7 +31773,7 @@
           <t>H | 379呎 (1房)
 $1000万
 $26,382/呎
-(21年-05月)</t>
+(21年-05月-26日)</t>
         </is>
       </c>
       <c r="J19" s="20" t="inlineStr">
@@ -31781,7 +31781,7 @@
           <t>J | 418呎 (1房)
 $883万
 $21,119/呎
-(25年-07月)</t>
+(25年-07月-16日)</t>
         </is>
       </c>
     </row>
@@ -31796,7 +31796,7 @@
           <t>A | 889呎 (3房)
 $2772万
 $31,178/呎
-(21年-05月)</t>
+(21年-05月-30日)</t>
         </is>
       </c>
       <c r="C20" s="23" t="inlineStr">
@@ -31820,7 +31820,7 @@
           <t>D | 546呎 (2房)
 $1836万
 $33,624/呎
-(21年-05月)</t>
+(21年-05月-30日)</t>
         </is>
       </c>
       <c r="F20" s="20" t="inlineStr">
@@ -31828,7 +31828,7 @@
           <t>E | 695呎 (3房)
 $1929万
 $27,756/呎
-(24年-01月)</t>
+(24年-01月-17日)</t>
         </is>
       </c>
       <c r="G20" s="20" t="inlineStr">
@@ -31836,7 +31836,7 @@
           <t>F | 505呎 (2房)
 $1352万
 $26,774/呎
-(21年-05月)</t>
+(21年-05月-30日)</t>
         </is>
       </c>
       <c r="H20" s="20" t="inlineStr">
@@ -31844,7 +31844,7 @@
           <t>G | 380呎 (1房)
 $973万
 $25,605/呎
-(21年-05月)</t>
+(21年-05月-27日)</t>
         </is>
       </c>
       <c r="I20" s="20" t="inlineStr">
@@ -31852,7 +31852,7 @@
           <t>H | 379呎 (1房)
 $997万
 $26,305/呎
-(21年-05月)</t>
+(21年-05月-30日)</t>
         </is>
       </c>
       <c r="J20" s="20" t="inlineStr">
@@ -31860,7 +31860,7 @@
           <t>J | 418呎 (1房)
 $880万
 $21,054/呎
-(25年-12月)</t>
+(25年-12月-09日)</t>
         </is>
       </c>
     </row>
@@ -31875,7 +31875,7 @@
           <t>A | 890呎 (3房)
 $2936万
 $32,985/呎
-(21年-10月)</t>
+(21年-10月-05日)</t>
         </is>
       </c>
       <c r="C21" s="23" t="inlineStr">
@@ -31899,7 +31899,7 @@
           <t>D | 546呎 (2房)
 $1839万
 $33,676/呎
-(26年-07月)</t>
+(26年-07月-07日)</t>
         </is>
       </c>
       <c r="F21" s="20" t="inlineStr">
@@ -31907,7 +31907,7 @@
           <t>E | 695呎 (3房)
 $1865万
 $26,836/呎
-(21年-05月)</t>
+(21年-05月-30日)</t>
         </is>
       </c>
       <c r="G21" s="20" t="inlineStr">
@@ -31915,7 +31915,7 @@
           <t>F | 505呎 (2房)
 $1320万
 $26,145/呎
-(21年-05月)</t>
+(21年-05月-27日)</t>
         </is>
       </c>
       <c r="H21" s="20" t="inlineStr">
@@ -31923,7 +31923,7 @@
           <t>G | 380呎 (1房)
 $970万
 $25,527/呎
-(21年-05月)</t>
+(21年-05月-23日)</t>
         </is>
       </c>
       <c r="I21" s="20" t="inlineStr">
@@ -31931,7 +31931,7 @@
           <t>H | 379呎 (1房)
 $974万
 $25,694/呎
-(21年-06月)</t>
+(21年-06月-10日)</t>
         </is>
       </c>
       <c r="J21" s="20" t="inlineStr">
@@ -31939,7 +31939,7 @@
           <t>J | 418呎 (1房)
 $877万
 $20,992/呎
-(25年-12月)</t>
+(25年-12月-04日)</t>
         </is>
       </c>
     </row>
@@ -31954,7 +31954,7 @@
           <t>A | 890呎 (3房)
 $2896万
 $32,544/呎
-(26年-02月)</t>
+(26年-02月-26日)</t>
         </is>
       </c>
       <c r="C22" s="23" t="inlineStr">
@@ -31970,7 +31970,7 @@
           <t>C | 550呎 (2房)
 $1801万
 $32,747/呎
-(26年-06月)</t>
+(26年-06月-14日)</t>
         </is>
       </c>
       <c r="E22" s="20" t="inlineStr">
@@ -31978,7 +31978,7 @@
           <t>D | 546呎 (2房)
 $1853万
 $33,932/呎
-(21年-05月)</t>
+(21年-05月-31日)</t>
         </is>
       </c>
       <c r="F22" s="20" t="inlineStr">
@@ -31986,7 +31986,7 @@
           <t>E | 696呎 (3房)
 $1879万
 $26,996/呎
-(21年-08月)</t>
+(21年-08月-04日)</t>
         </is>
       </c>
       <c r="G22" s="20" t="inlineStr">
@@ -31994,7 +31994,7 @@
           <t>F | 505呎 (2房)
 $1344万
 $26,616/呎
-(21年-05月)</t>
+(21年-05月-30日)</t>
         </is>
       </c>
       <c r="H22" s="20" t="inlineStr">
@@ -32002,7 +32002,7 @@
           <t>G | 380呎 (1房)
 $998万
 $26,254/呎
-(21年-05月)</t>
+(21年-05月-30日)</t>
         </is>
       </c>
       <c r="I22" s="20" t="inlineStr">
@@ -32010,7 +32010,7 @@
           <t>H | 379呎 (1房)
 $991万
 $26,152/呎
-(21年-05月)</t>
+(21年-05月-30日)</t>
         </is>
       </c>
       <c r="J22" s="20" t="inlineStr">
@@ -32018,7 +32018,7 @@
           <t>J | 418呎 (1房)
 $885万
 $21,168/呎
-(25年-08月)</t>
+(25年-08月-14日)</t>
         </is>
       </c>
     </row>
@@ -32033,7 +32033,7 @@
           <t>A | 890呎 (3房)
 $2888万
 $32,446/呎
-(26年-04月)</t>
+(26年-04月-19日)</t>
         </is>
       </c>
       <c r="C23" s="23" t="inlineStr">
@@ -32057,7 +32057,7 @@
           <t>D | 546呎 (2房)
 $1791万
 $32,805/呎
-(21年-05月)</t>
+(21年-05月-30日)</t>
         </is>
       </c>
       <c r="F23" s="20" t="inlineStr">
@@ -32065,7 +32065,7 @@
           <t>E | 695呎 (3房)
 $1893万
 $27,231/呎
-(21年-05月)</t>
+(21年-05月-26日)</t>
         </is>
       </c>
       <c r="G23" s="20" t="inlineStr">
@@ -32073,7 +32073,7 @@
           <t>F | 505呎 (2房)
 $1333万
 $26,395/呎
-(21年-05月)</t>
+(21年-05月-08日)</t>
         </is>
       </c>
       <c r="H23" s="20" t="inlineStr">
@@ -32081,7 +32081,7 @@
           <t>G | 380呎 (1房)
 $974万
 $25,639/呎
-(21年-05月)</t>
+(21年-05月-31日)</t>
         </is>
       </c>
       <c r="I23" s="20" t="inlineStr">
@@ -32089,7 +32089,7 @@
           <t>H | 379呎 (1房)
 $968万
 $25,542/呎
-(21年-05月)</t>
+(21年-05月-31日)</t>
         </is>
       </c>
       <c r="J23" s="20" t="inlineStr">
@@ -32097,7 +32097,7 @@
           <t>J | 418呎 (1房)
 $872万
 $20,866/呎
-(25年-07月)</t>
+(25年-07月-01日)</t>
         </is>
       </c>
     </row>
@@ -32112,7 +32112,7 @@
           <t>A | 889呎 (3房)
 $2795万
 $31,437/呎
-(21年-05月)</t>
+(21年-05月-31日)</t>
         </is>
       </c>
       <c r="C24" s="23" t="inlineStr">
@@ -32136,7 +32136,7 @@
           <t>D | 546呎 (2房)
 $1767万
 $32,364/呎
-(21年-05月)</t>
+(21年-05月-25日)</t>
         </is>
       </c>
       <c r="F24" s="20" t="inlineStr">
@@ -32144,7 +32144,7 @@
           <t>E | 696呎 (3房)
 $1906万
 $27,389/呎
-(21年-05月)</t>
+(21年-05月-08日)</t>
         </is>
       </c>
       <c r="G24" s="20" t="inlineStr">
@@ -32152,7 +32152,7 @@
           <t>F | 505呎 (2房)
 $1315万
 $26,043/呎
-(21年-06月)</t>
+(21年-06月-01日)</t>
         </is>
       </c>
       <c r="H24" s="20" t="inlineStr">
@@ -32160,7 +32160,7 @@
           <t>G | 380呎 (1房)
 $992万
 $26,094/呎
-(21年-06月)</t>
+(21年-06月-01日)</t>
         </is>
       </c>
       <c r="I24" s="20" t="inlineStr">
@@ -32168,7 +32168,7 @@
           <t>H | 379呎 (1房)
 $955万
 $25,201/呎
-(21年-06月)</t>
+(21年-06月-01日)</t>
         </is>
       </c>
       <c r="J24" s="20" t="inlineStr">
@@ -32176,7 +32176,7 @@
           <t>J | 418呎 (1房)
 $1111万
 $26,570/呎
-(23年-02月)</t>
+(23年-02月-28日)</t>
         </is>
       </c>
     </row>
@@ -32191,7 +32191,7 @@
           <t>A | 889呎 (3房)
 $2854万
 $32,098/呎
-(21年-05月)</t>
+(21年-05月-25日)</t>
         </is>
       </c>
       <c r="C25" s="23" t="inlineStr">
@@ -32215,7 +32215,7 @@
           <t>D | 546呎 (2房)
 $1786万
 $32,705/呎
-(21年-06月)</t>
+(21年-06月-01日)</t>
         </is>
       </c>
       <c r="F25" s="20" t="inlineStr">
@@ -32223,7 +32223,7 @@
           <t>E | 695呎 (3房)
 $1685万
 $24,242/呎
-(25年-04月)</t>
+(25年-04月-01日)</t>
         </is>
       </c>
       <c r="G25" s="20" t="inlineStr">
@@ -32231,7 +32231,7 @@
           <t>F | 505呎 (2房)
 $1329万
 $26,317/呎
-(21年-06月)</t>
+(21年-06月-01日)</t>
         </is>
       </c>
       <c r="H25" s="20" t="inlineStr">
@@ -32239,7 +32239,7 @@
           <t>G | 380呎 (1房)
 $971万
 $25,561/呎
-(21年-06月)</t>
+(21年-06月-01日)</t>
         </is>
       </c>
       <c r="I25" s="20" t="inlineStr">
@@ -32247,7 +32247,7 @@
           <t>H | 379呎 (1房)
 $985万
 $25,997/呎
-(21年-06月)</t>
+(21年-06月-01日)</t>
         </is>
       </c>
       <c r="J25" s="20" t="inlineStr">
@@ -32255,7 +32255,7 @@
           <t>J | 418呎 (1房)
 $869万
 $20,801/呎
-(25年-06月)</t>
+(25年-06月-24日)</t>
         </is>
       </c>
     </row>
@@ -32270,7 +32270,7 @@
           <t>A | 890呎 (3房)
 $2842万
 $31,933/呎
-(26年-04月)</t>
+(26年-04月-21日)</t>
         </is>
       </c>
       <c r="C26" s="23" t="inlineStr">
@@ -32294,7 +32294,7 @@
           <t>D | 546呎 (2房)
 $1762万
 $32,267/呎
-(21年-05月)</t>
+(21年-05月-25日)</t>
         </is>
       </c>
       <c r="F26" s="20" t="inlineStr">
@@ -32302,7 +32302,7 @@
           <t>E | 696呎 (3房)
 $1862万
 $26,754/呎
-(21年-06月)</t>
+(21年-06月-01日)</t>
         </is>
       </c>
       <c r="G26" s="20" t="inlineStr">
@@ -32310,7 +32310,7 @@
           <t>F | 505呎 (2房)
 $1325万
 $26,237/呎
-(21年-06月)</t>
+(21年-06月-01日)</t>
         </is>
       </c>
       <c r="H26" s="20" t="inlineStr">
@@ -32318,7 +32318,7 @@
           <t>G | 380呎 (1房)
 $989万
 $26,014/呎
-(21年-06月)</t>
+(21年-06月-01日)</t>
         </is>
       </c>
       <c r="I26" s="20" t="inlineStr">
@@ -32326,7 +32326,7 @@
           <t>H | 379呎 (1房)
 $962万
 $25,391/呎
-(21年-06月)</t>
+(21年-06月-01日)</t>
         </is>
       </c>
       <c r="J26" s="20" t="inlineStr">
@@ -32334,7 +32334,7 @@
           <t>J | 418呎 (1房)
 $867万
 $20,740/呎
-(25年-07月)</t>
+(25年-07月-14日)</t>
         </is>
       </c>
     </row>
@@ -32349,7 +32349,7 @@
           <t>A | 890呎 (3房)
 $2833万
 $31,837/呎
-(26年-05月)</t>
+(26年-05月-14日)</t>
         </is>
       </c>
       <c r="C27" s="23" t="inlineStr">
@@ -32373,7 +32373,7 @@
           <t>D | 546呎 (2房)
 $1775万
 $32,506/呎
-(21年-06月)</t>
+(21年-06月-01日)</t>
         </is>
       </c>
       <c r="F27" s="20" t="inlineStr">
@@ -32381,7 +32381,7 @@
           <t>E | 695呎 (3房)
 $1809万
 $26,030/呎
-(21年-06月)</t>
+(21年-06月-01日)</t>
         </is>
       </c>
       <c r="G27" s="20" t="inlineStr">
@@ -32389,7 +32389,7 @@
           <t>F | 505呎 (2房)
 $1275万
 $25,244/呎
-(21年-06月)</t>
+(21年-06月-01日)</t>
         </is>
       </c>
       <c r="H27" s="20" t="inlineStr">
@@ -32397,7 +32397,7 @@
           <t>G | 380呎 (1房)
 $975万
 $25,669/呎
-(21年-06月)</t>
+(21年-06月-01日)</t>
         </is>
       </c>
       <c r="I27" s="20" t="inlineStr">
@@ -32405,7 +32405,7 @@
           <t>H | 379呎 (1房)
 $959万
 $25,315/呎
-(21年-06月)</t>
+(21年-06月-01日)</t>
         </is>
       </c>
       <c r="J27" s="20" t="inlineStr">
@@ -32413,7 +32413,7 @@
           <t>J | 418呎 (1房)
 $899万
 $21,502/呎
-(25年-06月)</t>
+(25年-06月-22日)</t>
         </is>
       </c>
     </row>
@@ -32428,7 +32428,7 @@
           <t>A | 890呎 (3房)
 $2825万
 $31,741/呎
-(26年-06月)</t>
+(26年-06月-11日)</t>
         </is>
       </c>
       <c r="C28" s="23" t="inlineStr">
@@ -32452,7 +32452,7 @@
           <t>D | 546呎 (2房)
 $1788万
 $32,745/呎
-(21年-06月)</t>
+(21年-06月-01日)</t>
         </is>
       </c>
       <c r="F28" s="20" t="inlineStr">
@@ -32460,7 +32460,7 @@
           <t>E | 696呎 (3房)
 $1823万
 $26,188/呎
-(21年-06月)</t>
+(21年-06月-01日)</t>
         </is>
       </c>
       <c r="G28" s="20" t="inlineStr">
@@ -32468,7 +32468,7 @@
           <t>F | 505呎 (2房)
 $1284万
 $25,433/呎
-(21年-06月)</t>
+(21年-06月-01日)</t>
         </is>
       </c>
       <c r="H28" s="20" t="inlineStr">
@@ -32476,7 +32476,7 @@
           <t>G | 380呎 (1房)
 $962万
 $25,326/呎
-(21年-06月)</t>
+(21年-06月-01日)</t>
         </is>
       </c>
       <c r="I28" s="20" t="inlineStr">
@@ -32484,7 +32484,7 @@
           <t>H | 379呎 (1房)
 $966万
 $25,501/呎
-(21年-06月)</t>
+(21年-06月-01日)</t>
         </is>
       </c>
       <c r="J28" s="20" t="inlineStr">
@@ -32492,7 +32492,7 @@
           <t>J | 418呎 (1房)
 $871万
 $20,848/呎
-(25年-06月)</t>
+(25年-06月-23日)</t>
         </is>
       </c>
     </row>
@@ -32507,7 +32507,7 @@
           <t>A | 890呎 (3房)
 $2905万
 $32,636/呎
-(26年-07月)</t>
+(26年-07月-05日)</t>
         </is>
       </c>
       <c r="C29" s="23" t="inlineStr">
@@ -32539,7 +32539,7 @@
           <t>E | 695呎 (3房)
 $1684万
 $24,225/呎
-(24年-05月)</t>
+(24年-05月-07日)</t>
         </is>
       </c>
       <c r="G29" s="20" t="inlineStr">
@@ -32547,7 +32547,7 @@
           <t>F | 505呎 (2房)
 $1294万
 $25,619/呎
-(21年-06月)</t>
+(21年-06月-01日)</t>
         </is>
       </c>
       <c r="H29" s="20" t="inlineStr">
@@ -32555,7 +32555,7 @@
           <t>G | 380呎 (1房)
 $949万
 $24,985/呎
-(21年-06月)</t>
+(21年-06月-01日)</t>
         </is>
       </c>
       <c r="I29" s="20" t="inlineStr">
@@ -32563,7 +32563,7 @@
           <t>H | 379呎 (1房)
 $954万
 $25,163/呎
-(21年-06月)</t>
+(21年-06月-16日)</t>
         </is>
       </c>
       <c r="J29" s="20" t="inlineStr">
@@ -32571,7 +32571,7 @@
           <t>J | 418呎 (1房)
 $859万
 $20,552/呎
-(25年-07月)</t>
+(25年-07月-14日)</t>
         </is>
       </c>
     </row>
@@ -32610,7 +32610,7 @@
           <t>D | 546呎 (2房)
 $1693万
 $31,004/呎
-(21年-06月)</t>
+(21年-06月-01日)</t>
         </is>
       </c>
       <c r="F30" s="20" t="inlineStr">
@@ -32618,7 +32618,7 @@
           <t>E | 695呎 (3房)
 $1866万
 $26,854/呎
-(24年-01月)</t>
+(24年-01月-01日)</t>
         </is>
       </c>
       <c r="G30" s="20" t="inlineStr">
@@ -32626,7 +32626,7 @@
           <t>F | 505呎 (2房)
 $1260万
 $24,941/呎
-(21年-06月)</t>
+(21年-06月-01日)</t>
         </is>
       </c>
       <c r="H30" s="20" t="inlineStr">
@@ -32634,7 +32634,7 @@
           <t>G | 380呎 (1房)
 $944万
 $24,830/呎
-(21年-06月)</t>
+(21年-06月-01日)</t>
         </is>
       </c>
       <c r="I30" s="20" t="inlineStr">
@@ -32642,7 +32642,7 @@
           <t>H | 379呎 (1房)
 $968万
 $25,532/呎
-(21年-06月)</t>
+(21年-06月-01日)</t>
         </is>
       </c>
       <c r="J30" s="22" t="inlineStr">
@@ -32689,7 +32689,7 @@
           <t>D | 546呎 (2房)
 $1723万
 $31,559/呎
-(21年-06月)</t>
+(21年-06月-01日)</t>
         </is>
       </c>
       <c r="F31" s="20" t="inlineStr">
@@ -32697,7 +32697,7 @@
           <t>E | 695呎 (3房)
 $1644万
 $23,661/呎
-(24年-07月)</t>
+(24年-07月-14日)</t>
         </is>
       </c>
       <c r="G31" s="20" t="inlineStr">
@@ -32705,7 +32705,7 @@
           <t>F | 505呎 (2房)
 $1256万
 $24,866/呎
-(21年-06月)</t>
+(21年-06月-01日)</t>
         </is>
       </c>
       <c r="H31" s="20" t="inlineStr">
@@ -32713,7 +32713,7 @@
           <t>G | 380呎 (1房)
 $970万
 $25,534/呎
-(21年-05月)</t>
+(21年-05月-08日)</t>
         </is>
       </c>
       <c r="I31" s="20" t="inlineStr">
@@ -32721,7 +32721,7 @@
           <t>H | 379呎 (1房)
 $965万
 $25,454/呎
-(21年-06月)</t>
+(21年-06月-01日)</t>
         </is>
       </c>
       <c r="J31" s="20" t="inlineStr">
@@ -32729,7 +32729,7 @@
           <t>J | 417呎 (1房)
 $1077万
 $25,828/呎
-(21年-08月)</t>
+(21年-08月-05日)</t>
         </is>
       </c>
     </row>
@@ -32776,7 +32776,7 @@
           <t>E | 695呎 (3房)
 $1357万
 $19,521/呎
-(25年-06月)</t>
+(25年-06月-17日)</t>
         </is>
       </c>
       <c r="G32" s="20" t="inlineStr">
@@ -32784,7 +32784,7 @@
           <t>F | 505呎 (2房)
 $1295万
 $25,651/呎
-(21年-05月)</t>
+(21年-05月-08日)</t>
         </is>
       </c>
       <c r="H32" s="20" t="inlineStr">
@@ -32792,7 +32792,7 @@
           <t>G | 380呎 (1房)
 $950万
 $25,013/呎
-(21年-06月)</t>
+(21年-06月-15日)</t>
         </is>
       </c>
       <c r="I32" s="20" t="inlineStr">
@@ -32800,7 +32800,7 @@
           <t>H | 379呎 (1房)
 $965万
 $25,454/呎
-(21年-06月)</t>
+(21年-06月-01日)</t>
         </is>
       </c>
       <c r="J32" s="20" t="inlineStr">
@@ -32808,7 +32808,7 @@
           <t>J | 418呎 (1房)
 $1088万
 $26,034/呎
-(23年-04月)</t>
+(23年-04月-27日)</t>
         </is>
       </c>
     </row>
@@ -32855,7 +32855,7 @@
           <t>E | 695呎 (3房)
 $1639万
 $23,588/呎
-(24年-05月)</t>
+(24年-05月-05日)</t>
         </is>
       </c>
       <c r="G33" s="20" t="inlineStr">
@@ -32863,7 +32863,7 @@
           <t>F | 505呎 (2房)
 $1252万
 $24,788/呎
-(21年-06月)</t>
+(21年-06月-01日)</t>
         </is>
       </c>
       <c r="H33" s="20" t="inlineStr">
@@ -32871,7 +32871,7 @@
           <t>G | 380呎 (1房)
 $967万
 $25,454/呎
-(21年-06月)</t>
+(21年-06月-20日)</t>
         </is>
       </c>
       <c r="I33" s="20" t="inlineStr">
@@ -32879,7 +32879,7 @@
           <t>H | 379呎 (1房)
 $972万
 $25,635/呎
-(21年-06月)</t>
+(21年-06月-02日)</t>
         </is>
       </c>
       <c r="J33" s="20" t="inlineStr">
@@ -32887,7 +32887,7 @@
           <t>J | 418呎 (1房)
 $832万
 $19,899/呎
-(25年-07月)</t>
+(25年-07月-28日)</t>
         </is>
       </c>
     </row>
@@ -32934,7 +32934,7 @@
           <t>E | 695呎 (3房)
 $1849万
 $26,610/呎
-(24年-04月)</t>
+(24年-04月-11日)</t>
         </is>
       </c>
       <c r="G34" s="20" t="inlineStr">
@@ -32942,7 +32942,7 @@
           <t>F | 505呎 (2房)
 $1240万
 $24,563/呎
-(21年-06月)</t>
+(21年-06月-02日)</t>
         </is>
       </c>
       <c r="H34" s="20" t="inlineStr">
@@ -32950,7 +32950,7 @@
           <t>G | 380呎 (1房)
 $929万
 $24,442/呎
-(21年-06月)</t>
+(21年-06月-17日)</t>
         </is>
       </c>
       <c r="I34" s="20" t="inlineStr">
@@ -32958,7 +32958,7 @@
           <t>H | 379呎 (1房)
 $953万
 $25,151/呎
-(21年-05月)</t>
+(21年-05月-08日)</t>
         </is>
       </c>
       <c r="J34" s="20" t="inlineStr">
@@ -32966,7 +32966,7 @@
           <t>J | 418呎 (1房)
 $824万
 $19,711/呎
-(25年-08月)</t>
+(25年-08月-19日)</t>
         </is>
       </c>
     </row>
@@ -33013,7 +33013,7 @@
           <t>E | 695呎 (3房)
 $1364万
 $19,633/呎
-(25年-06月)</t>
+(25年-06月-16日)</t>
         </is>
       </c>
       <c r="G35" s="20" t="inlineStr">
@@ -33021,7 +33021,7 @@
           <t>F | 505呎 (2房)
 $1279万
 $25,328/呎
-(21年-06月)</t>
+(21年-06月-15日)</t>
         </is>
       </c>
       <c r="H35" s="20" t="inlineStr">
@@ -33029,7 +33029,7 @@
           <t>G | 380呎 (1房)
 $988万
 $25,996/呎
-(21年-07月)</t>
+(21年-07月-04日)</t>
         </is>
       </c>
       <c r="I35" s="20" t="inlineStr">
@@ -33037,7 +33037,7 @@
           <t>H | 379呎 (1房)
 $973万
 $25,665/呎
-(21年-08月)</t>
+(21年-08月-02日)</t>
         </is>
       </c>
       <c r="J35" s="20" t="inlineStr">
@@ -33045,7 +33045,7 @@
           <t>J | 418呎 (1房)
 $840万
 $20,089/呎
-(25年-06月)</t>
+(25年-06月-13日)</t>
         </is>
       </c>
     </row>
@@ -33092,7 +33092,7 @@
           <t>E | 695呎 (3房)
 $1387万
 $19,958/呎
-(25年-06月)</t>
+(25年-06月-11日)</t>
         </is>
       </c>
       <c r="G36" s="20" t="inlineStr">
@@ -33100,7 +33100,7 @@
           <t>F | 505呎 (2房)
 $1315万
 $26,047/呎
-(21年-06月)</t>
+(21年-06月-10日)</t>
         </is>
       </c>
       <c r="H36" s="20" t="inlineStr">
@@ -33108,7 +33108,7 @@
           <t>G | 380呎 (1房)
 $965万
 $25,384/呎
-(21年-07月)</t>
+(21年-07月-13日)</t>
         </is>
       </c>
       <c r="I36" s="20" t="inlineStr">
@@ -33116,7 +33116,7 @@
           <t>H | 379呎 (1房)
 $960万
 $25,322/呎
-(21年-08月)</t>
+(21年-08月-03日)</t>
         </is>
       </c>
       <c r="J36" s="20" t="inlineStr">
@@ -33124,7 +33124,7 @@
           <t>J | 418呎 (1房)
 $814万
 $19,468/呎
-(25年-08月)</t>
+(25年-08月-18日)</t>
         </is>
       </c>
     </row>
@@ -33171,7 +33171,7 @@
           <t>E | 695呎 (3房)
 $1371万
 $19,722/呎
-(25年-06月)</t>
+(25年-06月-11日)</t>
         </is>
       </c>
       <c r="G37" s="20" t="inlineStr">
@@ -33179,7 +33179,7 @@
           <t>F | 505呎 (2房)
 $1280万
 $25,355/呎
-(21年-06月)</t>
+(21年-06月-20日)</t>
         </is>
       </c>
       <c r="H37" s="20" t="inlineStr">
@@ -33187,7 +33187,7 @@
           <t>G | 380呎 (1房)
 $948万
 $24,957/呎
-(21年-07月)</t>
+(21年-07月-18日)</t>
         </is>
       </c>
       <c r="I37" s="20" t="inlineStr">
@@ -33195,7 +33195,7 @@
           <t>H | 379呎 (1房)
 $984万
 $25,951/呎
-(21年-08月)</t>
+(21年-08月-30日)</t>
         </is>
       </c>
       <c r="J37" s="20" t="inlineStr">
@@ -33203,7 +33203,7 @@
           <t>J | 418呎 (1房)
 $809万
 $19,344/呎
-(25年-08月)</t>
+(25年-08月-10日)</t>
         </is>
       </c>
     </row>
@@ -33222,7 +33222,7 @@
           <t>E | 705呎 (3房)
 $1357万
 $19,241/呎
-(25年-06月)</t>
+(25年-06月-16日)</t>
         </is>
       </c>
       <c r="G38" s="20" t="inlineStr">
@@ -33230,7 +33230,7 @@
           <t>F | 505呎 (2房)
 $1312万
 $25,985/呎
-(21年-07月)</t>
+(21年-07月-08日)</t>
         </is>
       </c>
       <c r="H38" s="20" t="inlineStr">
@@ -33238,7 +33238,7 @@
           <t>G | 380呎 (1房)
 $952万
 $25,058/呎
-(23年-12月)</t>
+(23年-12月-21日)</t>
         </is>
       </c>
       <c r="I38" s="20" t="inlineStr">
@@ -33246,7 +33246,7 @@
           <t>H | 379呎 (1房)
 $938万
 $24,747/呎
-(22年-09月)</t>
+(22年-09月-07日)</t>
         </is>
       </c>
       <c r="J38" s="20" t="inlineStr">
@@ -33254,7 +33254,7 @@
           <t>J | 418呎 (1房)
 $817万
 $19,552/呎
-(25年-07月)</t>
+(25年-07月-28日)</t>
         </is>
       </c>
     </row>
@@ -33416,7 +33416,7 @@
           <t>A | 320呎 (1房)
 $876万
 $27,366/呎
-(21年-06月)</t>
+(21年-06月-14日)</t>
         </is>
       </c>
       <c r="C5" s="20" t="inlineStr">
@@ -33424,7 +33424,7 @@
           <t>B | 296呎 (1房)
 $819万
 $27,653/呎
-(21年-05月)</t>
+(21年-05月-24日)</t>
         </is>
       </c>
       <c r="D5" s="20" t="inlineStr">
@@ -33432,7 +33432,7 @@
           <t>C | 321呎 (1房)
 $870万
 $27,098/呎
-(21年-06月)</t>
+(21年-06月-24日)</t>
         </is>
       </c>
       <c r="E5" s="20" t="inlineStr">
@@ -33440,7 +33440,7 @@
           <t>D | 331呎 (1房)
 $878万
 $26,537/呎
-(21年-06月)</t>
+(21年-06月-29日)</t>
         </is>
       </c>
       <c r="F5" s="20" t="inlineStr">
@@ -33448,7 +33448,7 @@
           <t>E | 301呎 (1房)
 $810万
 $26,915/呎
-(21年-06月)</t>
+(21年-06月-29日)</t>
         </is>
       </c>
       <c r="G5" s="20" t="inlineStr">
@@ -33456,7 +33456,7 @@
           <t>F | 301呎 (1房)
 $835万
 $27,749/呎
-(21年-07月)</t>
+(21年-07月-14日)</t>
         </is>
       </c>
       <c r="H5" s="20" t="inlineStr">
@@ -33464,7 +33464,7 @@
           <t>G | 208呎 (开放式)
 $595万
 $28,614/呎
-(21年-08月)</t>
+(21年-08月-03日)</t>
         </is>
       </c>
       <c r="I5" s="20" t="inlineStr">
@@ -33472,7 +33472,7 @@
           <t>H | 216呎 (开放式)
 $627万
 $29,040/呎
-(21年-09月)</t>
+(21年-09月-02日)</t>
         </is>
       </c>
     </row>
@@ -33487,7 +33487,7 @@
           <t>A | 320呎 (1房)
 $856万
 $26,757/呎
-(21年-06月)</t>
+(21年-06月-21日)</t>
         </is>
       </c>
       <c r="C6" s="20" t="inlineStr">
@@ -33495,7 +33495,7 @@
           <t>B | 296呎 (1房)
 $776万
 $26,228/呎
-(21年-06月)</t>
+(21年-06月-06日)</t>
         </is>
       </c>
       <c r="D6" s="20" t="inlineStr">
@@ -33503,7 +33503,7 @@
           <t>C | 321呎 (1房)
 $860万
 $26,780/呎
-(21年-05月)</t>
+(21年-05月-24日)</t>
         </is>
       </c>
       <c r="E6" s="20" t="inlineStr">
@@ -33511,7 +33511,7 @@
           <t>D | 330呎 (1房)
 $886万
 $26,851/呎
-(21年-07月)</t>
+(21年-07月-22日)</t>
         </is>
       </c>
       <c r="F6" s="20" t="inlineStr">
@@ -33519,7 +33519,7 @@
           <t>E | 301呎 (1房)
 $817万
 $27,147/呎
-(21年-06月)</t>
+(21年-06月-09日)</t>
         </is>
       </c>
       <c r="G6" s="20" t="inlineStr">
@@ -33527,7 +33527,7 @@
           <t>F | 302呎 (1房)
 $817万
 $27,047/呎
-(21年-07月)</t>
+(21年-07月-05日)</t>
         </is>
       </c>
       <c r="H6" s="20" t="inlineStr">
@@ -33535,7 +33535,7 @@
           <t>G | 208呎 (开放式)
 $607万
 $29,183/呎
-(21年-06月)</t>
+(21年-06月-09日)</t>
         </is>
       </c>
       <c r="I6" s="20" t="inlineStr">
@@ -33543,7 +33543,7 @@
           <t>H | 216呎 (开放式)
 $620万
 $28,702/呎
-(21年-08月)</t>
+(21年-08月-02日)</t>
         </is>
       </c>
     </row>
@@ -33558,7 +33558,7 @@
           <t>A | 320呎 (1房)
 $857万
 $26,793/呎
-(21年-06月)</t>
+(21年-06月-21日)</t>
         </is>
       </c>
       <c r="C7" s="20" t="inlineStr">
@@ -33566,7 +33566,7 @@
           <t>B | 296呎 (1房)
 $769万
 $25,993/呎
-(21年-06月)</t>
+(21年-06月-08日)</t>
         </is>
       </c>
       <c r="D7" s="20" t="inlineStr">
@@ -33574,7 +33574,7 @@
           <t>C | 321呎 (1房)
 $835万
 $25,998/呎
-(21年-05月)</t>
+(21年-05月-24日)</t>
         </is>
       </c>
       <c r="E7" s="20" t="inlineStr">
@@ -33582,7 +33582,7 @@
           <t>D | 330呎 (1房)
 $869万
 $26,336/呎
-(21年-07月)</t>
+(21年-07月-19日)</t>
         </is>
       </c>
       <c r="F7" s="20" t="inlineStr">
@@ -33590,7 +33590,7 @@
           <t>E | 302呎 (1房)
 $810万
 $26,814/呎
-(21年-06月)</t>
+(21年-06月-10日)</t>
         </is>
       </c>
       <c r="G7" s="20" t="inlineStr">
@@ -33598,7 +33598,7 @@
           <t>F | 302呎 (1房)
 $818万
 $27,083/呎
-(21年-07月)</t>
+(21年-07月-07日)</t>
         </is>
       </c>
       <c r="H7" s="20" t="inlineStr">
@@ -33606,7 +33606,7 @@
           <t>G | 208呎 (开放式)
 $600万
 $28,826/呎
-(21年-06月)</t>
+(21年-06月-10日)</t>
         </is>
       </c>
       <c r="I7" s="20" t="inlineStr">
@@ -33614,7 +33614,7 @@
           <t>H | 216呎 (开放式)
 $627万
 $29,041/呎
-(21年-06月)</t>
+(21年-06月-08日)</t>
         </is>
       </c>
     </row>
@@ -33629,7 +33629,7 @@
           <t>A | 320呎 (1房)
 $841万
 $26,270/呎
-(21年-06月)</t>
+(21年-06月-29日)</t>
         </is>
       </c>
       <c r="C8" s="20" t="inlineStr">
@@ -33637,7 +33637,7 @@
           <t>B | 296呎 (1房)
 $771万
 $26,033/呎
-(21年-06月)</t>
+(21年-06月-06日)</t>
         </is>
       </c>
       <c r="D8" s="20" t="inlineStr">
@@ -33645,7 +33645,7 @@
           <t>C | 321呎 (1房)
 $844万
 $26,301/呎
-(21年-06月)</t>
+(21年-06月-09日)</t>
         </is>
       </c>
       <c r="E8" s="20" t="inlineStr">
@@ -33653,7 +33653,7 @@
           <t>D | 331呎 (1房)
 $861万
 $26,018/呎
-(21年-07月)</t>
+(21年-07月-20日)</t>
         </is>
       </c>
       <c r="F8" s="20" t="inlineStr">
@@ -33661,7 +33661,7 @@
           <t>E | 301呎 (1房)
 $802万
 $26,655/呎
-(21年-06月)</t>
+(21年-06月-20日)</t>
         </is>
       </c>
       <c r="G8" s="20" t="inlineStr">
@@ -33669,7 +33669,7 @@
           <t>F | 301呎 (1房)
 $794万
 $26,373/呎
-(21年-07月)</t>
+(21年-07月-15日)</t>
         </is>
       </c>
       <c r="H8" s="20" t="inlineStr">
@@ -33677,7 +33677,7 @@
           <t>G | 208呎 (开放式)
 $578万
 $27,797/呎
-(21年-08月)</t>
+(21年-08月-05日)</t>
         </is>
       </c>
       <c r="I8" s="20" t="inlineStr">
@@ -33685,7 +33685,7 @@
           <t>H | 216呎 (开放式)
 $615万
 $28,489/呎
-(21年-08月)</t>
+(21年-08月-19日)</t>
         </is>
       </c>
     </row>
@@ -33700,7 +33700,7 @@
           <t>A | 299呎 (1房)
 $862万
 $28,823/呎
-(21年-06月)</t>
+(21年-06月-24日)</t>
         </is>
       </c>
       <c r="C9" s="20" t="inlineStr">
@@ -33708,7 +33708,7 @@
           <t>B | 272呎 (1房)
 $967万
 $35,561/呎
-(21年-05月)</t>
+(21年-05月-28日)</t>
         </is>
       </c>
       <c r="D9" s="20" t="inlineStr">
@@ -33716,7 +33716,7 @@
           <t>C | 299呎 (1房)
 $823万
 $27,535/呎
-(21年-06月)</t>
+(21年-06月-22日)</t>
         </is>
       </c>
       <c r="E9" s="20" t="inlineStr">
@@ -33724,7 +33724,7 @@
           <t>D | 330呎 (1房)
 $844万
 $25,587/呎
-(21年-07月)</t>
+(21年-07月-09日)</t>
         </is>
       </c>
       <c r="F9" s="20" t="inlineStr">
@@ -33732,7 +33732,7 @@
           <t>E | 302呎 (1房)
 $779万
 $25,786/呎
-(21年-06月)</t>
+(21年-06月-24日)</t>
         </is>
       </c>
       <c r="G9" s="20" t="inlineStr">
@@ -33740,7 +33740,7 @@
           <t>F | 302呎 (1房)
 $803万
 $26,586/呎
-(21年-07月)</t>
+(21年-07月-15日)</t>
         </is>
       </c>
       <c r="H9" s="20" t="inlineStr">
@@ -33748,7 +33748,7 @@
           <t>G | 208呎 (开放式)
 $573万
 $27,554/呎
-(21年-09月)</t>
+(21年-09月-08日)</t>
         </is>
       </c>
       <c r="I9" s="20" t="inlineStr">
@@ -33756,7 +33756,7 @@
           <t>H | 216呎 (开放式)
 $597万
 $27,651/呎
-(21年-09月)</t>
+(21年-09月-01日)</t>
         </is>
       </c>
     </row>
@@ -33774,7 +33774,7 @@
           <t>D | 309呎 (1房)
 $995万
 $32,200/呎
-(21年-07月)</t>
+(21年-07月-15日)</t>
         </is>
       </c>
       <c r="F10" s="20" t="inlineStr">
@@ -33782,7 +33782,7 @@
           <t>E | 280呎 (1房)
 $920万
 $32,858/呎
-(21年-06月)</t>
+(21年-06月-07日)</t>
         </is>
       </c>
       <c r="G10" s="20" t="inlineStr">
@@ -33790,7 +33790,7 @@
           <t>F | 280呎 (1房)
 $910万
 $32,510/呎
-(21年-07月)</t>
+(21年-07月-04日)</t>
         </is>
       </c>
       <c r="H10" s="20" t="inlineStr">
@@ -33798,7 +33798,7 @@
           <t>G | 186呎 (开放式)
 $682万
 $36,655/呎
-(21年-06月)</t>
+(21年-06月-24日)</t>
         </is>
       </c>
       <c r="I10" s="20" t="inlineStr">
@@ -33806,7 +33806,7 @@
           <t>H | 195呎 (开放式)
 $567万
 $29,100/呎
-(26年-02月)</t>
+(26年-02月-26日)</t>
         </is>
       </c>
     </row>
@@ -33968,7 +33968,7 @@
           <t>A | 320呎 (1房)
 $899万
 $28,107/呎
-(21年-06月)</t>
+(21年-06月-15日)</t>
         </is>
       </c>
       <c r="C5" s="20" t="inlineStr">
@@ -33976,7 +33976,7 @@
           <t>B | 296呎 (1房)
 $815万
 $27,545/呎
-(21年-06月)</t>
+(21年-06月-09日)</t>
         </is>
       </c>
       <c r="D5" s="20" t="inlineStr">
@@ -33984,7 +33984,7 @@
           <t>C | 321呎 (1房)
 $873万
 $27,204/呎
-(21年-07月)</t>
+(21年-07月-19日)</t>
         </is>
       </c>
       <c r="E5" s="20" t="inlineStr">
@@ -33992,7 +33992,7 @@
           <t>D | 330呎 (1房)
 $701万
 $21,238/呎
-(25年-07月)</t>
+(25年-07月-08日)</t>
         </is>
       </c>
       <c r="F5" s="20" t="inlineStr">
@@ -34000,7 +34000,7 @@
           <t>E | 301呎 (1房)
 $825万
 $27,414/呎
-(21年-07月)</t>
+(21年-07月-18日)</t>
         </is>
       </c>
       <c r="G5" s="20" t="inlineStr">
@@ -34008,7 +34008,7 @@
           <t>F | 301呎 (1房)
 $834万
 $27,703/呎
-(21年-06月)</t>
+(21年-06月-22日)</t>
         </is>
       </c>
       <c r="H5" s="20" t="inlineStr">
@@ -34016,7 +34016,7 @@
           <t>G | 208呎 (开放式)
 $613万
 $29,473/呎
-(21年-06月)</t>
+(21年-06月-15日)</t>
         </is>
       </c>
       <c r="I5" s="20" t="inlineStr">
@@ -34024,7 +34024,7 @@
           <t>H | 216呎 (开放式)
 $645万
 $29,867/呎
-(21年-07月)</t>
+(21年-07月-05日)</t>
         </is>
       </c>
     </row>
@@ -34039,7 +34039,7 @@
           <t>A | 320呎 (1房)
 $879万
 $27,482/呎
-(21年-06月)</t>
+(21年-06月-09日)</t>
         </is>
       </c>
       <c r="C6" s="20" t="inlineStr">
@@ -34047,7 +34047,7 @@
           <t>B | 296呎 (1房)
 $806万
 $27,224/呎
-(21年-06月)</t>
+(21年-06月-09日)</t>
         </is>
       </c>
       <c r="D6" s="20" t="inlineStr">
@@ -34055,7 +34055,7 @@
           <t>C | 321呎 (1房)
 $890万
 $27,733/呎
-(21年-07月)</t>
+(21年-07月-19日)</t>
         </is>
       </c>
       <c r="E6" s="20" t="inlineStr">
@@ -34063,7 +34063,7 @@
           <t>D | 330呎 (1房)
 $692万
 $20,984/呎
-(25年-07月)</t>
+(25年-07月-03日)</t>
         </is>
       </c>
       <c r="F6" s="20" t="inlineStr">
@@ -34071,7 +34071,7 @@
           <t>E | 302呎 (1房)
 $824万
 $27,283/呎
-(21年-07月)</t>
+(21年-07月-07日)</t>
         </is>
       </c>
       <c r="G6" s="20" t="inlineStr">
@@ -34079,7 +34079,7 @@
           <t>F | 301呎 (1房)
 $841万
 $27,945/呎
-(21年-06月)</t>
+(21年-06月-17日)</t>
         </is>
       </c>
       <c r="H6" s="20" t="inlineStr">
@@ -34087,7 +34087,7 @@
           <t>G | 208呎 (开放式)
 $593万
 $28,518/呎
-(21年-06月)</t>
+(21年-06月-15日)</t>
         </is>
       </c>
       <c r="I6" s="20" t="inlineStr">
@@ -34095,7 +34095,7 @@
           <t>H | 216呎 (开放式)
 $644万
 $29,824/呎
-(21年-06月)</t>
+(21年-06月-09日)</t>
         </is>
       </c>
     </row>
@@ -34110,7 +34110,7 @@
           <t>A | 320呎 (1房)
 $872万
 $27,235/呎
-(21年-06月)</t>
+(21年-06月-17日)</t>
         </is>
       </c>
       <c r="C7" s="20" t="inlineStr">
@@ -34118,7 +34118,7 @@
           <t>B | 296呎 (1房)
 $799万
 $26,984/呎
-(21年-05月)</t>
+(21年-05月-24日)</t>
         </is>
       </c>
       <c r="D7" s="20" t="inlineStr">
@@ -34126,7 +34126,7 @@
           <t>C | 321呎 (1房)
 $882万
 $27,489/呎
-(21年-07月)</t>
+(21年-07月-06日)</t>
         </is>
       </c>
       <c r="E7" s="20" t="inlineStr">
@@ -34134,7 +34134,7 @@
           <t>D | 330呎 (1房)
 $698万
 $21,152/呎
-(25年-06月)</t>
+(25年-06月-08日)</t>
         </is>
       </c>
       <c r="F7" s="20" t="inlineStr">
@@ -34142,7 +34142,7 @@
           <t>E | 302呎 (1房)
 $808万
 $26,757/呎
-(21年-07月)</t>
+(21年-07月-06日)</t>
         </is>
       </c>
       <c r="G7" s="20" t="inlineStr">
@@ -34150,7 +34150,7 @@
           <t>F | 301呎 (1房)
 $817万
 $27,129/呎
-(21年-06月)</t>
+(21年-06月-21日)</t>
         </is>
       </c>
       <c r="H7" s="20" t="inlineStr">
@@ -34158,7 +34158,7 @@
           <t>G | 208呎 (开放式)
 $588万
 $28,258/呎
-(21年-06月)</t>
+(21年-06月-09日)</t>
         </is>
       </c>
       <c r="I7" s="20" t="inlineStr">
@@ -34166,7 +34166,7 @@
           <t>H | 216呎 (开放式)
 $632万
 $29,268/呎
-(21年-06月)</t>
+(21年-06月-16日)</t>
         </is>
       </c>
     </row>
@@ -34181,7 +34181,7 @@
           <t>A | 320呎 (1房)
 $891万
 $27,838/呎
-(21年-06月)</t>
+(21年-06月-17日)</t>
         </is>
       </c>
       <c r="C8" s="20" t="inlineStr">
@@ -34189,7 +34189,7 @@
           <t>B | 296呎 (1房)
 $808万
 $27,301/呎
-(21年-06月)</t>
+(21年-06月-16日)</t>
         </is>
       </c>
       <c r="D8" s="20" t="inlineStr">
@@ -34197,7 +34197,7 @@
           <t>C | 321呎 (1房)
 $848万
 $26,407/呎
-(21年-07月)</t>
+(21年-07月-06日)</t>
         </is>
       </c>
       <c r="E8" s="20" t="inlineStr">
@@ -34205,7 +34205,7 @@
           <t>D | 330呎 (1房)
 $680万
 $20,608/呎
-(25年-06月)</t>
+(25年-06月-29日)</t>
         </is>
       </c>
       <c r="F8" s="20" t="inlineStr">
@@ -34213,7 +34213,7 @@
           <t>E | 302呎 (1房)
 $826万
 $27,349/呎
-(21年-07月)</t>
+(21年-07月-14日)</t>
         </is>
       </c>
       <c r="G8" s="20" t="inlineStr">
@@ -34221,7 +34221,7 @@
           <t>F | 301呎 (1房)
 $809万
 $26,880/呎
-(21年-07月)</t>
+(21年-07月-22日)</t>
         </is>
       </c>
       <c r="H8" s="20" t="inlineStr">
@@ -34229,7 +34229,7 @@
           <t>G | 208呎 (开放式)
 $601万
 $28,886/呎
-(21年-06月)</t>
+(21年-06月-09日)</t>
         </is>
       </c>
       <c r="I8" s="20" t="inlineStr">
@@ -34237,7 +34237,7 @@
           <t>H | 216呎 (开放式)
 $627万
 $29,010/呎
-(21年-06月)</t>
+(21年-06月-09日)</t>
         </is>
       </c>
     </row>
@@ -34252,7 +34252,7 @@
           <t>A | 299呎 (1房)
 $876万
 $29,307/呎
-(21年-07月)</t>
+(21年-07月-04日)</t>
         </is>
       </c>
       <c r="C9" s="20" t="inlineStr">
@@ -34260,7 +34260,7 @@
           <t>B | 272呎 (1房)
 $789万
 $29,008/呎
-(21年-07月)</t>
+(21年-07月-04日)</t>
         </is>
       </c>
       <c r="D9" s="20" t="inlineStr">
@@ -34268,7 +34268,7 @@
           <t>C | 299呎 (1房)
 $853万
 $28,527/呎
-(21年-07月)</t>
+(21年-07月-20日)</t>
         </is>
       </c>
       <c r="E9" s="20" t="inlineStr">
@@ -34276,7 +34276,7 @@
           <t>D | 331呎 (1房)
 $870万
 $26,277/呎
-(21年-07月)</t>
+(21年-07月-28日)</t>
         </is>
       </c>
       <c r="F9" s="20" t="inlineStr">
@@ -34284,7 +34284,7 @@
           <t>E | 302呎 (1房)
 $818万
 $27,099/呎
-(21年-07月)</t>
+(21年-07月-18日)</t>
         </is>
       </c>
       <c r="G9" s="20" t="inlineStr">
@@ -34292,7 +34292,7 @@
           <t>F | 302呎 (1房)
 $793万
 $26,270/呎
-(21年-07月)</t>
+(21年-07月-15日)</t>
         </is>
       </c>
       <c r="H9" s="20" t="inlineStr">
@@ -34300,7 +34300,7 @@
           <t>G | 208呎 (开放式)
 $583万
 $28,034/呎
-(21年-06月)</t>
+(21年-06月-22日)</t>
         </is>
       </c>
       <c r="I9" s="20" t="inlineStr">
@@ -34308,7 +34308,7 @@
           <t>H | 216呎 (开放式)
 $608万
 $28,164/呎
-(21年-09月)</t>
+(21年-09月-07日)</t>
         </is>
       </c>
     </row>
@@ -34326,7 +34326,7 @@
           <t>D | 309呎 (1房)
 $1022万
 $33,087/呎
-(21年-08月)</t>
+(21年-08月-25日)</t>
         </is>
       </c>
       <c r="F10" s="20" t="inlineStr">
@@ -34334,7 +34334,7 @@
           <t>E | 280呎 (1房)
 $806万
 $28,800/呎
-(26年-04月)</t>
+(26年-04月-08日)</t>
         </is>
       </c>
       <c r="G10" s="20" t="inlineStr">
@@ -34342,7 +34342,7 @@
           <t>F | 280呎 (1房)
 $740万
 $26,421/呎
-(26年-01月)</t>
+(26年-01月-14日)</t>
         </is>
       </c>
       <c r="H10" s="20" t="inlineStr">
@@ -34350,7 +34350,7 @@
           <t>G | 186呎 (开放式)
 $513万
 $27,581/呎
-(25年-07月)</t>
+(25年-07月-20日)</t>
         </is>
       </c>
       <c r="I10" s="20" t="inlineStr">
@@ -34358,7 +34358,7 @@
           <t>H | 195呎 (开放式)
 $623万
 $31,935/呎
-(26年-07月)</t>
+(26年-07月-06日)</t>
         </is>
       </c>
     </row>
@@ -34520,7 +34520,7 @@
           <t>A | 320呎 (1房)
 $898万
 $28,074/呎
-(21年-06月)</t>
+(21年-06月-01日)</t>
         </is>
       </c>
       <c r="C5" s="20" t="inlineStr">
@@ -34528,7 +34528,7 @@
           <t>B | 296呎 (1房)
 $806万
 $27,229/呎
-(21年-06月)</t>
+(21年-06月-01日)</t>
         </is>
       </c>
       <c r="D5" s="20" t="inlineStr">
@@ -34536,7 +34536,7 @@
           <t>C | 321呎 (1房)
 $856万
 $26,679/呎
-(21年-06月)</t>
+(21年-06月-01日)</t>
         </is>
       </c>
       <c r="E5" s="20" t="inlineStr">
@@ -34544,7 +34544,7 @@
           <t>D | 331呎 (1房)
 $898万
 $27,129/呎
-(21年-07月)</t>
+(21年-07月-18日)</t>
         </is>
       </c>
       <c r="F5" s="20" t="inlineStr">
@@ -34552,7 +34552,7 @@
           <t>E | 302呎 (1房)
 $828万
 $27,411/呎
-(21年-06月)</t>
+(21年-06月-01日)</t>
         </is>
       </c>
       <c r="G5" s="20" t="inlineStr">
@@ -34560,7 +34560,7 @@
           <t>F | 302呎 (1房)
 $836万
 $27,690/呎
-(21年-06月)</t>
+(21年-06月-01日)</t>
         </is>
       </c>
       <c r="H5" s="20" t="inlineStr">
@@ -34568,7 +34568,7 @@
           <t>G | 208呎 (开放式)
 $614万
 $29,518/呎
-(21年-07月)</t>
+(21年-07月-28日)</t>
         </is>
       </c>
       <c r="I5" s="20" t="inlineStr">
@@ -34576,7 +34576,7 @@
           <t>H | 216呎 (开放式)
 $634万
 $29,342/呎
-(21年-06月)</t>
+(21年-06月-19日)</t>
         </is>
       </c>
     </row>
@@ -34591,7 +34591,7 @@
           <t>A | 320呎 (1房)
 $870万
 $27,174/呎
-(21年-06月)</t>
+(21年-06月-01日)</t>
         </is>
       </c>
       <c r="C6" s="20" t="inlineStr">
@@ -34599,7 +34599,7 @@
           <t>B | 296呎 (1房)
 $788万
 $26,636/呎
-(21年-06月)</t>
+(21年-06月-01日)</t>
         </is>
       </c>
       <c r="D6" s="20" t="inlineStr">
@@ -34607,7 +34607,7 @@
           <t>C | 321呎 (1房)
 $846万
 $26,365/呎
-(21年-06月)</t>
+(21年-06月-01日)</t>
         </is>
       </c>
       <c r="E6" s="20" t="inlineStr">
@@ -34615,7 +34615,7 @@
           <t>D | 330呎 (1房)
 $878万
 $26,613/呎
-(21年-07月)</t>
+(21年-07月-02日)</t>
         </is>
       </c>
       <c r="F6" s="20" t="inlineStr">
@@ -34623,7 +34623,7 @@
           <t>E | 301呎 (1房)
 $810万
 $26,896/呎
-(21年-06月)</t>
+(21年-06月-01日)</t>
         </is>
       </c>
       <c r="G6" s="20" t="inlineStr">
@@ -34631,7 +34631,7 @@
           <t>F | 301呎 (1房)
 $801万
 $26,618/呎
-(21年-06月)</t>
+(21年-06月-01日)</t>
         </is>
       </c>
       <c r="H6" s="20" t="inlineStr">
@@ -34639,7 +34639,7 @@
           <t>G | 208呎 (开放式)
 $588万
 $28,290/呎
-(21年-07月)</t>
+(21年-07月-12日)</t>
         </is>
       </c>
       <c r="I6" s="20" t="inlineStr">
@@ -34647,7 +34647,7 @@
           <t>H | 216呎 (开放式)
 $633万
 $29,300/呎
-(21年-07月)</t>
+(21年-07月-22日)</t>
         </is>
       </c>
     </row>
@@ -34662,7 +34662,7 @@
           <t>A | 320呎 (1房)
 $880万
 $27,489/呎
-(21年-05月)</t>
+(21年-05月-19日)</t>
         </is>
       </c>
       <c r="C7" s="20" t="inlineStr">
@@ -34670,7 +34670,7 @@
           <t>B | 296呎 (1房)
 $806万
 $27,225/呎
-(21年-05月)</t>
+(21年-05月-24日)</t>
         </is>
       </c>
       <c r="D7" s="20" t="inlineStr">
@@ -34678,7 +34678,7 @@
           <t>C | 321呎 (1房)
 $856万
 $26,674/呎
-(21年-05月)</t>
+(21年-05月-23日)</t>
         </is>
       </c>
       <c r="E7" s="20" t="inlineStr">
@@ -34686,7 +34686,7 @@
           <t>D | 330呎 (1房)
 $879万
 $26,644/呎
-(21年-07月)</t>
+(21年-07月-19日)</t>
         </is>
       </c>
       <c r="F7" s="20" t="inlineStr">
@@ -34694,7 +34694,7 @@
           <t>E | 302呎 (1房)
 $794万
 $26,292/呎
-(21年-05月)</t>
+(21年-05月-30日)</t>
         </is>
       </c>
       <c r="G7" s="20" t="inlineStr">
@@ -34702,7 +34702,7 @@
           <t>F | 302呎 (1房)
 $811万
 $26,839/呎
-(21年-05月)</t>
+(21年-05月-30日)</t>
         </is>
       </c>
       <c r="H7" s="20" t="inlineStr">
@@ -34710,7 +34710,7 @@
           <t>G | 208呎 (开放式)
 $608万
 $29,224/呎
-(21年-07月)</t>
+(21年-07月-18日)</t>
         </is>
       </c>
       <c r="I7" s="20" t="inlineStr">
@@ -34718,7 +34718,7 @@
           <t>H | 216呎 (开放式)
 $608万
 $28,152/呎
-(21年-07月)</t>
+(21年-07月-20日)</t>
         </is>
       </c>
     </row>
@@ -34733,7 +34733,7 @@
           <t>A | 320呎 (1房)
 $863万
 $26,960/呎
-(21年-05月)</t>
+(21年-05月-30日)</t>
         </is>
       </c>
       <c r="C8" s="20" t="inlineStr">
@@ -34741,7 +34741,7 @@
           <t>B | 296呎 (1房)
 $766万
 $25,891/呎
-(21年-05月)</t>
+(21年-05月-26日)</t>
         </is>
       </c>
       <c r="D8" s="20" t="inlineStr">
@@ -34749,7 +34749,7 @@
           <t>C | 321呎 (1房)
 $840万
 $26,163/呎
-(21年-05月)</t>
+(21年-05月-24日)</t>
         </is>
       </c>
       <c r="E8" s="20" t="inlineStr">
@@ -34757,7 +34757,7 @@
           <t>D | 331呎 (1房)
 $844万
 $25,512/呎
-(21年-07月)</t>
+(21年-07月-18日)</t>
         </is>
       </c>
       <c r="F8" s="20" t="inlineStr">
@@ -34765,7 +34765,7 @@
           <t>E | 302呎 (1房)
 $795万
 $26,322/呎
-(21年-07月)</t>
+(21年-07月-08日)</t>
         </is>
       </c>
       <c r="G8" s="20" t="inlineStr">
@@ -34773,7 +34773,7 @@
           <t>F | 302呎 (1房)
 $787万
 $26,050/呎
-(21年-07月)</t>
+(21年-07月-05日)</t>
         </is>
       </c>
       <c r="H8" s="20" t="inlineStr">
@@ -34781,7 +34781,7 @@
           <t>G | 208呎 (开放式)
 $596万
 $28,674/呎
-(21年-07月)</t>
+(21年-07月-18日)</t>
         </is>
       </c>
       <c r="I8" s="20" t="inlineStr">
@@ -34789,7 +34789,7 @@
           <t>H | 216呎 (开放式)
 $609万
 $28,195/呎
-(21年-07月)</t>
+(21年-07月-15日)</t>
         </is>
       </c>
     </row>
@@ -34804,7 +34804,7 @@
           <t>A | 299呎 (1房)
 $840万
 $28,084/呎
-(21年-05月)</t>
+(21年-05月-31日)</t>
         </is>
       </c>
       <c r="C9" s="20" t="inlineStr">
@@ -34812,7 +34812,7 @@
           <t>B | 274呎 (1房)
 $790万
 $28,842/呎
-(21年-05月)</t>
+(21年-05月-30日)</t>
         </is>
       </c>
       <c r="D9" s="20" t="inlineStr">
@@ -34820,7 +34820,7 @@
           <t>C | 299呎 (1房)
 $836万
 $27,961/呎
-(21年-05月)</t>
+(21年-05月-31日)</t>
         </is>
       </c>
       <c r="E9" s="20" t="inlineStr">
@@ -34828,7 +34828,7 @@
           <t>D | 330呎 (1房)
 $655万
 $19,852/呎
-(25年-06月)</t>
+(25年-06月-26日)</t>
         </is>
       </c>
       <c r="F9" s="20" t="inlineStr">
@@ -34836,7 +34836,7 @@
           <t>E | 301呎 (1房)
 $771万
 $25,625/呎
-(21年-07月)</t>
+(21年-07月-15日)</t>
         </is>
       </c>
       <c r="G9" s="20" t="inlineStr">
@@ -34844,7 +34844,7 @@
           <t>F | 302呎 (1房)
 $796万
 $26,346/呎
-(21年-05月)</t>
+(21年-05月-30日)</t>
         </is>
       </c>
       <c r="H9" s="20" t="inlineStr">
@@ -34852,7 +34852,7 @@
           <t>G | 208呎 (开放式)
 $573万
 $27,554/呎
-(21年-08月)</t>
+(21年-08月-04日)</t>
         </is>
       </c>
       <c r="I9" s="20" t="inlineStr">
@@ -34860,7 +34860,7 @@
           <t>H | 216呎 (开放式)
 $597万
 $27,651/呎
-(21年-08月)</t>
+(21年-08月-11日)</t>
         </is>
       </c>
     </row>
@@ -34878,7 +34878,7 @@
           <t>D | 309呎 (1房)
 $980万
 $31,722/呎
-(23年-05月)</t>
+(23年-05月-09日)</t>
         </is>
       </c>
       <c r="F10" s="20" t="inlineStr">
@@ -34886,7 +34886,7 @@
           <t>E | 280呎 (1房)
 $806万
 $28,800/呎
-(26年-03月)</t>
+(26年-03月-31日)</t>
         </is>
       </c>
       <c r="G10" s="20" t="inlineStr">
@@ -34894,7 +34894,7 @@
           <t>F | 280呎 (1房)
 $806万
 $28,800/呎
-(26年-04月)</t>
+(26年-04月-12日)</t>
         </is>
       </c>
       <c r="H10" s="20" t="inlineStr">
@@ -34902,7 +34902,7 @@
           <t>G | 186呎 (开放式)
 $683万
 $36,718/呎
-(21年-07月)</t>
+(21年-07月-18日)</t>
         </is>
       </c>
       <c r="I10" s="20" t="inlineStr">
@@ -34910,7 +34910,7 @@
           <t>H | 194呎 (开放式)
 $708万
 $36,472/呎
-(21年-08月)</t>
+(21年-08月-10日)</t>
         </is>
       </c>
     </row>
@@ -35072,7 +35072,7 @@
           <t>A | 320呎 (1房)
 $868万
 $27,114/呎
-(21年-05月)</t>
+(21年-05月-26日)</t>
         </is>
       </c>
       <c r="C5" s="20" t="inlineStr">
@@ -35080,7 +35080,7 @@
           <t>B | 296呎 (1房)
 $823万
 $27,788/呎
-(21年-05月)</t>
+(21年-05月-26日)</t>
         </is>
       </c>
       <c r="D5" s="20" t="inlineStr">
@@ -35088,7 +35088,7 @@
           <t>C | 321呎 (1房)
 $871万
 $27,122/呎
-(21年-05月)</t>
+(21年-05月-27日)</t>
         </is>
       </c>
       <c r="E5" s="20" t="inlineStr">
@@ -35096,7 +35096,7 @@
           <t>D | 331呎 (1房)
 $853万
 $25,773/呎
-(21年-05月)</t>
+(21年-05月-27日)</t>
         </is>
       </c>
       <c r="F5" s="20" t="inlineStr">
@@ -35104,7 +35104,7 @@
           <t>E | 301呎 (1房)
 $786万
 $26,127/呎
-(21年-05月)</t>
+(21年-05月-26日)</t>
         </is>
       </c>
       <c r="G5" s="20" t="inlineStr">
@@ -35112,7 +35112,7 @@
           <t>F | 299呎 (1房)
 $778万
 $26,025/呎
-(21年-05月)</t>
+(21年-05月-08日)</t>
         </is>
       </c>
       <c r="H5" s="20" t="inlineStr">
@@ -35120,7 +35120,7 @@
           <t>G | 207呎 (开放式)
 $605万
 $29,211/呎
-(21年-07月)</t>
+(21年-07月-26日)</t>
         </is>
       </c>
       <c r="I5" s="20" t="inlineStr">
@@ -35128,7 +35128,7 @@
           <t>H | 321呎 (1房)
 $883万
 $27,510/呎
-(21年-05月)</t>
+(21年-05月-26日)</t>
         </is>
       </c>
     </row>
@@ -35143,7 +35143,7 @@
           <t>A | 320呎 (1房)
 $857万
 $26,790/呎
-(21年-05月)</t>
+(21年-05月-08日)</t>
         </is>
       </c>
       <c r="C6" s="20" t="inlineStr">
@@ -35151,7 +35151,7 @@
           <t>B | 296呎 (1房)
 $821万
 $27,740/呎
-(21年-05月)</t>
+(21年-05月-26日)</t>
         </is>
       </c>
       <c r="D6" s="20" t="inlineStr">
@@ -35159,7 +35159,7 @@
           <t>C | 321呎 (1房)
 $852万
 $26,534/呎
-(21年-05月)</t>
+(21年-05月-30日)</t>
         </is>
       </c>
       <c r="E6" s="20" t="inlineStr">
@@ -35167,7 +35167,7 @@
           <t>D | 330呎 (1房)
 $870万
 $26,350/呎
-(21年-05月)</t>
+(21年-05月-26日)</t>
         </is>
       </c>
       <c r="F6" s="20" t="inlineStr">
@@ -35175,7 +35175,7 @@
           <t>E | 301呎 (1房)
 $793万
 $26,357/呎
-(21年-05月)</t>
+(21年-05月-27日)</t>
         </is>
       </c>
       <c r="G6" s="20" t="inlineStr">
@@ -35183,7 +35183,7 @@
           <t>F | 299呎 (1房)
 $777万
 $25,994/呎
-(21年-05月)</t>
+(21年-05月-27日)</t>
         </is>
       </c>
       <c r="H6" s="20" t="inlineStr">
@@ -35191,7 +35191,7 @@
           <t>G | 207呎 (开放式)
 $597万
 $28,862/呎
-(21年-07月)</t>
+(21年-07月-20日)</t>
         </is>
       </c>
       <c r="I6" s="20" t="inlineStr">
@@ -35199,7 +35199,7 @@
           <t>H | 321呎 (1房)
 $855万
 $26,629/呎
-(21年-05月)</t>
+(21年-05月-30日)</t>
         </is>
       </c>
     </row>
@@ -35214,7 +35214,7 @@
           <t>A | 320呎 (1房)
 $841万
 $26,273/呎
-(21年-05月)</t>
+(21年-05月-08日)</t>
         </is>
       </c>
       <c r="C7" s="20" t="inlineStr">
@@ -35222,7 +35222,7 @@
           <t>B | 296呎 (1房)
 $781万
 $26,382/呎
-(21年-05月)</t>
+(21年-05月-23日)</t>
         </is>
       </c>
       <c r="D7" s="20" t="inlineStr">
@@ -35230,7 +35230,7 @@
           <t>C | 321呎 (1房)
 $853万
 $26,570/呎
-(21年-05月)</t>
+(21年-05月-23日)</t>
         </is>
       </c>
       <c r="E7" s="20" t="inlineStr">
@@ -35238,7 +35238,7 @@
           <t>D | 331呎 (1房)
 $835万
 $25,234/呎
-(21年-05月)</t>
+(21年-05月-08日)</t>
         </is>
       </c>
       <c r="F7" s="20" t="inlineStr">
@@ -35246,7 +35246,7 @@
           <t>E | 301呎 (1房)
 $770万
 $25,580/呎
-(21年-05月)</t>
+(21年-05月-08日)</t>
         </is>
       </c>
       <c r="G7" s="20" t="inlineStr">
@@ -35254,7 +35254,7 @@
           <t>F | 299呎 (1房)
 $794万
 $26,571/呎
-(21年-05月)</t>
+(21年-05月-24日)</t>
         </is>
       </c>
       <c r="H7" s="20" t="inlineStr">
@@ -35262,7 +35262,7 @@
           <t>G | 207呎 (开放式)
 $598万
 $28,906/呎
-(21年-07月)</t>
+(21年-07月-22日)</t>
         </is>
       </c>
       <c r="I7" s="20" t="inlineStr">
@@ -35270,7 +35270,7 @@
           <t>H | 321呎 (1房)
 $873万
 $27,211/呎
-(21年-05月)</t>
+(21年-05月-24日)</t>
         </is>
       </c>
     </row>
@@ -35285,7 +35285,7 @@
           <t>A | 320呎 (1房)
 $841万
 $26,294/呎
-(21年-07月)</t>
+(21年-07月-11日)</t>
         </is>
       </c>
       <c r="C8" s="20" t="inlineStr">
@@ -35293,7 +35293,7 @@
           <t>B | 296呎 (1房)
 $798万
 $26,967/呎
-(21年-05月)</t>
+(21年-05月-23日)</t>
         </is>
       </c>
       <c r="D8" s="20" t="inlineStr">
@@ -35301,7 +35301,7 @@
           <t>C | 321呎 (1房)
 $819万
 $25,529/呎
-(21年-05月)</t>
+(21年-05月-25日)</t>
         </is>
       </c>
       <c r="E8" s="20" t="inlineStr">
@@ -35309,7 +35309,7 @@
           <t>D | 330呎 (1房)
 $836万
 $25,344/呎
-(21年-05月)</t>
+(21年-05月-24日)</t>
         </is>
       </c>
       <c r="F8" s="20" t="inlineStr">
@@ -35317,7 +35317,7 @@
           <t>E | 302呎 (1房)
 $787万
 $26,061/呎
-(21年-05月)</t>
+(21年-05月-23日)</t>
         </is>
       </c>
       <c r="G8" s="20" t="inlineStr">
@@ -35325,7 +35325,7 @@
           <t>F | 299呎 (1房)
 $763万
 $25,534/呎
-(21年-05月)</t>
+(21年-05月-08日)</t>
         </is>
       </c>
       <c r="H8" s="20" t="inlineStr">
@@ -35333,7 +35333,7 @@
           <t>G | 207呎 (开放式)
 $605万
 $29,239/呎
-(21年-07月)</t>
+(21年-07月-09日)</t>
         </is>
       </c>
       <c r="I8" s="20" t="inlineStr">
@@ -35341,7 +35341,7 @@
           <t>H | 321呎 (1房)
 $857万
 $26,692/呎
-(21年-05月)</t>
+(21年-05月-08日)</t>
         </is>
       </c>
     </row>
@@ -35356,7 +35356,7 @@
           <t>A | 298呎 (1房)
 $838万
 $28,108/呎
-(21年-07月)</t>
+(21年-07月-18日)</t>
         </is>
       </c>
       <c r="C9" s="20" t="inlineStr">
@@ -35364,7 +35364,7 @@
           <t>B | 272呎 (1房)
 $795万
 $29,231/呎
-(21年-06月)</t>
+(21年-06月-02日)</t>
         </is>
       </c>
       <c r="D9" s="20" t="inlineStr">
@@ -35372,7 +35372,7 @@
           <t>C | 299呎 (1房)
 $824万
 $27,563/呎
-(21年-07月)</t>
+(21年-07月-28日)</t>
         </is>
       </c>
       <c r="E9" s="20" t="inlineStr">
@@ -35380,7 +35380,7 @@
           <t>D | 330呎 (1房)
 $828万
 $25,094/呎
-(21年-07月)</t>
+(21年-07月-18日)</t>
         </is>
       </c>
       <c r="F9" s="20" t="inlineStr">
@@ -35388,7 +35388,7 @@
           <t>E | 301呎 (1房)
 $764万
 $25,378/呎
-(21年-06月)</t>
+(21年-06月-02日)</t>
         </is>
       </c>
       <c r="G9" s="20" t="inlineStr">
@@ -35396,7 +35396,7 @@
           <t>F | 299呎 (1房)
 $780万
 $26,101/呎
-(21年-05月)</t>
+(21年-05月-08日)</t>
         </is>
       </c>
       <c r="H9" s="20" t="inlineStr">
@@ -35404,7 +35404,7 @@
           <t>G | 207呎 (开放式)
 $587万
 $28,378/呎
-(21年-09月)</t>
+(21年-09月-05日)</t>
         </is>
       </c>
       <c r="I9" s="20" t="inlineStr">
@@ -35412,7 +35412,7 @@
           <t>H | 321呎 (1房)
 $857万
 $26,710/呎
-(21年-07月)</t>
+(21年-07月-19日)</t>
         </is>
       </c>
     </row>
@@ -35430,7 +35430,7 @@
           <t>D | 309呎 (1房)
 $908万
 $29,385/呎
-(26年-06月)</t>
+(26年-06月-11日)</t>
         </is>
       </c>
       <c r="F10" s="20" t="inlineStr">
@@ -35438,7 +35438,7 @@
           <t>E | 280呎 (1房)
 $848万
 $30,286/呎
-(26年-06月)</t>
+(26年-06月-04日)</t>
         </is>
       </c>
       <c r="G10" s="20" t="inlineStr">
@@ -35446,7 +35446,7 @@
           <t>F | 277呎 (1房)
 $803万
 $29,000/呎
-(26年-06月)</t>
+(26年-06月-02日)</t>
         </is>
       </c>
       <c r="H10" s="22" t="inlineStr">
@@ -35462,7 +35462,7 @@
           <t>H | 300呎 (1房)
 $918万
 $30,600/呎
-(26年-05月)</t>
+(26年-05月-20日)</t>
         </is>
       </c>
     </row>
